--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071C4F0C-E02A-4DDA-B14E-214444D172DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A9CEFA-9DC7-4329-815F-3410DAE60C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2640" windowWidth="21600" windowHeight="12960" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="162">
   <si>
     <t>image_url</t>
   </si>
@@ -221,9 +221,6 @@
     <t>motorised</t>
   </si>
   <si>
-    <t>70 кг</t>
-  </si>
-  <si>
     <t>500x500</t>
   </si>
   <si>
@@ -748,15 +745,92 @@
   <si>
     <t>de</t>
   </si>
+  <si>
+    <t>www.shop.onkron.ru/images/product_images/popup_images/46_1.png</t>
+  </si>
+  <si>
+    <t>PT1-B</t>
+  </si>
+  <si>
+    <t>Для телевизоров диагональю 26"-55"
+Максимальная нагрузка: 30 кг
+VESA: 75x75, 100x100, 100x200, 200x100, 200x200, 200x300, 200x400, 300x100, 300x200, 300x300, 300x400, 400x200, 400x300, 400x400 мм
+Регулировка высоты: 594 мм, 634 мм, 674 мм
+Габариты основания: 430х240 мм
+Материалы: холоднокатаная сталь, закалённое стекло</t>
+  </si>
+  <si>
+    <t>www.shop.onkron.ru/images/product_images/popup_images/406_1.jpg</t>
+  </si>
+  <si>
+    <t>PT2-B</t>
+  </si>
+  <si>
+    <t>500x400</t>
+  </si>
+  <si>
+    <t>Для ТВ диагональю 32"-65"
+Максимальная вес ТВ: 35 кг
+VESA: 100x100, 100x200, 200x100, 200x200, 200x300, 200x400, 300x100, 300x200, 300x300, 300x400, 400x200, 400x300, 400x400 мм
+Угол поворота: 360&amp;deg;
+Высота столба: 625 мм
+Мягкие защитные проставки
+Габариты основания: 500х400x10 мм
+Материалы: холоднокатаная сталь, закалённое стекло</t>
+  </si>
+  <si>
+    <t>www.shop.onkron.ru/images/product_images/popup_images/407_1.jpg</t>
+  </si>
+  <si>
+    <t>PT3-B</t>
+  </si>
+  <si>
+    <t>Для ТВ диагональю 32"-75"
+Максимальный вес ТВ: 40 кг
+VESA: 100x100, 100x200, 200x100, 200x200, 200x300, 200x400, 300x100, 300x200, 300x300, 300x400, 400x200, 400x300, 400x400 мм
+Угол поворота: -54&amp;deg; ~ +54&amp;deg;
+Высота столба: 625 мм
+Мягкие защитные проставки
+Габариты основания: 550х400x10 мм
+Материалы: холоднокатаная сталь, закалённое стекло</t>
+  </si>
+  <si>
+    <t>www.shop.onkron.ru/images/product_images/popup_images/530_2.jpg</t>
+  </si>
+  <si>
+    <t>PT4-B</t>
+  </si>
+  <si>
+    <t>Для телевизоров диагональю 26"-55"
+Максимальная нагрузка: 35 кг
+VESA: 75x75, 100x100, 100x200, 200x100, 200x200, 200x300, 200x400, 300x100, 300x200, 300x300, 300x400, 400x200, 400x300, 400x400 мм
+Регулировка высоты: 315 - 435 мм
+Габариты основания: 400х260 мм
+Угол поворота: -35"~ +35"
+Материалы: закалённое стекло, сталь</t>
+  </si>
+  <si>
+    <t>30 kg</t>
+  </si>
+  <si>
+    <t>70 kg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -810,8 +884,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M37" totalsRowShown="0">
-  <autoFilter ref="A1:M37" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M41" totalsRowShown="0">
+  <autoFilter ref="A1:M41" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M41">
+    <sortCondition ref="J1:J41"/>
+  </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -1128,10 +1205,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
     <col min="6" max="6" width="26.140625" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" customWidth="1"/>
     <col min="8" max="8" width="26.7109375" customWidth="1"/>
@@ -1147,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1185,463 +1264,469 @@
     </row>
     <row r="2" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="F2">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="H2">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>58</v>
+      </c>
+      <c r="L2">
+        <v>130</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="F3">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="H3">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="K3" t="s">
-        <v>18</v>
+        <v>58</v>
+      </c>
+      <c r="L3">
+        <v>145</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>23</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="F4">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="H4">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="K4" t="s">
-        <v>18</v>
+        <v>58</v>
+      </c>
+      <c r="L4">
+        <v>150</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>27</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="F5">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="H5">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="K5" t="s">
-        <v>18</v>
+        <v>58</v>
+      </c>
+      <c r="L5">
+        <v>130</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="F6">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="H6">
-        <v>41</v>
+        <v>136.4</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="K6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F7">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="H7">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="F8">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="H8">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>58</v>
+      </c>
+      <c r="L8">
+        <v>125</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H9">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="J9" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
       </c>
-      <c r="L9">
-        <v>70</v>
-      </c>
       <c r="M9" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="H10">
-        <v>105.9</v>
+        <v>35</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="J10" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10">
-        <v>105.9</v>
+        <v>18</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="H11">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="J11" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="K11" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="L11">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="F12">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H12">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>53</v>
+        <v>18</v>
+      </c>
+      <c r="L12">
+        <v>40</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="H13">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I13" t="s">
         <v>16</v>
       </c>
       <c r="J13" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>40</v>
+        <v>18</v>
+      </c>
+      <c r="L13">
+        <v>45</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="F14">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="H14">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I14" t="s">
         <v>16</v>
@@ -1652,37 +1737,34 @@
       <c r="K14" t="s">
         <v>18</v>
       </c>
-      <c r="L14">
-        <v>40</v>
-      </c>
       <c r="M14" s="1" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="H15">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="J15" t="s">
         <v>18</v>
@@ -1690,98 +1772,92 @@
       <c r="K15" t="s">
         <v>18</v>
       </c>
-      <c r="L15">
-        <v>45</v>
-      </c>
       <c r="M15" s="1" t="s">
-        <v>76</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="F16">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="H16">
-        <v>40.5</v>
+        <v>35</v>
       </c>
       <c r="I16" t="s">
         <v>16</v>
       </c>
       <c r="J16" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="F17">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H17">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I17" t="s">
         <v>16</v>
       </c>
       <c r="J17" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="K17" t="s">
-        <v>40</v>
-      </c>
-      <c r="L17">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="B18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="F18">
         <v>65</v>
@@ -1790,109 +1866,109 @@
         <v>22</v>
       </c>
       <c r="H18">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I18" t="s">
         <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>39</v>
+        <v>152</v>
       </c>
       <c r="K18" t="s">
-        <v>40</v>
-      </c>
-      <c r="L18">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="F19">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H19">
         <v>70</v>
       </c>
       <c r="I19" t="s">
+        <v>161</v>
+      </c>
+      <c r="J19" t="s">
         <v>45</v>
       </c>
-      <c r="J19" t="s">
-        <v>89</v>
-      </c>
       <c r="K19" t="s">
-        <v>59</v>
+        <v>18</v>
+      </c>
+      <c r="L19">
+        <v>70</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="F20">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H20">
-        <v>55.5</v>
+        <v>41</v>
       </c>
       <c r="I20" t="s">
         <v>16</v>
       </c>
       <c r="J20" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K20" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="L20">
-        <v>55.5</v>
+        <v>41</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="B21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="F21">
         <v>75</v>
@@ -1901,48 +1977,45 @@
         <v>15</v>
       </c>
       <c r="H21">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I21" t="s">
         <v>16</v>
       </c>
       <c r="J21" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K21" t="s">
-        <v>40</v>
-      </c>
-      <c r="L21">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="F22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H22">
-        <v>60.5</v>
+        <v>40</v>
       </c>
       <c r="I22" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="J22" t="s">
         <v>39</v>
@@ -1950,37 +2023,34 @@
       <c r="K22" t="s">
         <v>40</v>
       </c>
-      <c r="L22">
-        <v>60.5</v>
-      </c>
       <c r="M22" s="1" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F23">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H23">
-        <v>60.5</v>
+        <v>50</v>
       </c>
       <c r="I23" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="J23" t="s">
         <v>39</v>
@@ -1989,33 +2059,33 @@
         <v>40</v>
       </c>
       <c r="L23">
-        <v>60.5</v>
+        <v>50</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F24">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H24">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I24" t="s">
         <v>16</v>
@@ -2027,504 +2097,651 @@
         <v>40</v>
       </c>
       <c r="L24">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F25">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25">
         <v>50</v>
       </c>
-      <c r="H25">
-        <v>90</v>
-      </c>
       <c r="I25" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="J25" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="K25" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L25">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F26">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G26" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H26">
-        <v>105.9</v>
+        <v>55.5</v>
       </c>
       <c r="I26" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="J26" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K26" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L26">
-        <v>105.9</v>
+        <v>55.5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F27">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H27">
-        <v>105.9</v>
+        <v>60</v>
       </c>
       <c r="I27" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="J27" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K27" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L27">
-        <v>105.9</v>
+        <v>60</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="E28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F28">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H28">
-        <v>105.9</v>
+        <v>60.5</v>
       </c>
       <c r="I28" t="s">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="J28" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K28" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L28">
-        <v>105.9</v>
+        <v>60.5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F29">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G29" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H29">
-        <v>105.9</v>
+        <v>60.5</v>
       </c>
       <c r="I29" t="s">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="J29" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K29" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L29">
-        <v>105.9</v>
+        <v>60.5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E30" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F30">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G30" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>32.5</v>
       </c>
       <c r="I30" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="J30" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="K30" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>32.5</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>123</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="E31" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F31">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="G31" t="s">
+        <v>67</v>
+      </c>
+      <c r="H31">
         <v>50</v>
       </c>
-      <c r="H31">
-        <v>130</v>
-      </c>
       <c r="I31" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="J31" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="K31" t="s">
-        <v>59</v>
-      </c>
-      <c r="L31">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F32">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="H32">
-        <v>150</v>
+        <v>65.5</v>
       </c>
       <c r="I32" t="s">
-        <v>57</v>
+        <v>161</v>
       </c>
       <c r="J32" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="K32" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="L32">
-        <v>150</v>
+        <v>55.5</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="E33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F33">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="H33">
-        <v>125</v>
+        <v>105.9</v>
       </c>
       <c r="I33" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="J33" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="K33" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="L33">
-        <v>125</v>
+        <v>105.9</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="B34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E34" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F34">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G34" t="s">
         <v>22</v>
       </c>
       <c r="H34">
-        <v>32.5</v>
+        <v>105.9</v>
       </c>
       <c r="I34" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J34" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K34" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="L34">
-        <v>32.5</v>
+        <v>105.9</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="B35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C35" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F35">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G35" t="s">
+        <v>49</v>
+      </c>
+      <c r="H35">
+        <v>105.9</v>
+      </c>
+      <c r="I35" t="s">
         <v>50</v>
       </c>
-      <c r="H35">
-        <v>65.5</v>
-      </c>
-      <c r="I35" t="s">
-        <v>45</v>
-      </c>
       <c r="J35" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="K35" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="L35">
-        <v>55.5</v>
+        <v>105.9</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C36" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E36" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F36">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="G36" t="s">
+        <v>49</v>
+      </c>
+      <c r="H36">
+        <v>105.9</v>
+      </c>
+      <c r="I36" t="s">
         <v>50</v>
       </c>
-      <c r="H36">
-        <v>136.4</v>
-      </c>
-      <c r="I36" t="s">
-        <v>57</v>
-      </c>
       <c r="J36" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="K36" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="L36">
+        <v>105.9</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="E37" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="F37">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="G37" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37">
+        <v>105.9</v>
+      </c>
+      <c r="I37" t="s">
+        <v>50</v>
+      </c>
+      <c r="J37" t="s">
+        <v>51</v>
+      </c>
+      <c r="K37" t="s">
+        <v>52</v>
+      </c>
+      <c r="L37">
+        <v>105.9</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" t="s">
+        <v>146</v>
+      </c>
+      <c r="C38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38">
+        <v>120</v>
+      </c>
+      <c r="G38" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38">
+        <v>125</v>
+      </c>
+      <c r="I38" t="s">
+        <v>56</v>
+      </c>
+      <c r="J38" t="s">
+        <v>51</v>
+      </c>
+      <c r="K38" t="s">
+        <v>52</v>
+      </c>
+      <c r="M38" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H37">
-        <v>145</v>
-      </c>
-      <c r="I37" t="s">
-        <v>57</v>
-      </c>
-      <c r="J37" t="s">
-        <v>58</v>
-      </c>
-      <c r="K37" t="s">
-        <v>59</v>
-      </c>
-      <c r="L37">
-        <v>145</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>145</v>
+    </row>
+    <row r="39" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" t="s">
+        <v>105</v>
+      </c>
+      <c r="E39" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39">
+        <v>90</v>
+      </c>
+      <c r="G39" t="s">
+        <v>49</v>
+      </c>
+      <c r="H39">
+        <v>90</v>
+      </c>
+      <c r="I39" t="s">
+        <v>50</v>
+      </c>
+      <c r="J39" t="s">
+        <v>106</v>
+      </c>
+      <c r="K39" t="s">
+        <v>52</v>
+      </c>
+      <c r="L39">
+        <v>90</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40">
+        <v>90</v>
+      </c>
+      <c r="G40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40">
+        <v>100</v>
+      </c>
+      <c r="I40" t="s">
+        <v>50</v>
+      </c>
+      <c r="J40" t="s">
+        <v>106</v>
+      </c>
+      <c r="K40" t="s">
+        <v>52</v>
+      </c>
+      <c r="L40">
+        <v>100</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" t="s">
+        <v>77</v>
+      </c>
+      <c r="E41" t="s">
+        <v>78</v>
+      </c>
+      <c r="F41">
+        <v>70</v>
+      </c>
+      <c r="G41" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41">
+        <v>40.5</v>
+      </c>
+      <c r="I41" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" t="s">
+        <v>79</v>
+      </c>
+      <c r="K41" t="s">
+        <v>52</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A9CEFA-9DC7-4329-815F-3410DAE60C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73F21E9-2D29-4F4D-987F-E90B218604A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -315,9 +315,6 @@
 VESA: 100*100, 200x200, 200x300, 200x400, 300x100, 300x200, 300x300, 300x400, 400x200, 400x300, 400x400, 500x200, 500x400, 600x200, 600x300, 600x400, 700x400, 700x500, 800x200, 800x400, 800x500, 900*400, 900*600, 900*800</t>
   </si>
   <si>
-    <t>#N/A</t>
-  </si>
-  <si>
     <t>FSPRO2L22-S</t>
   </si>
   <si>
@@ -814,6 +811,9 @@
   </si>
   <si>
     <t>70 kg</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/348_0.png</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1264,16 +1264,16 @@
     </row>
     <row r="2" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" t="s">
         <v>122</v>
       </c>
-      <c r="B2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C2" t="s">
-        <v>123</v>
-      </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -1297,21 +1297,21 @@
         <v>130</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" t="s">
         <v>142</v>
       </c>
-      <c r="B3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C3" t="s">
-        <v>143</v>
-      </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F3">
         <v>110</v>
@@ -1335,21 +1335,21 @@
         <v>145</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" t="s">
         <v>125</v>
       </c>
-      <c r="B4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" t="s">
-        <v>126</v>
-      </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F4">
         <v>120</v>
@@ -1373,7 +1373,7 @@
         <v>150</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1381,7 +1381,7 @@
         <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
@@ -1416,16 +1416,16 @@
     </row>
     <row r="6" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" t="s">
         <v>139</v>
       </c>
-      <c r="B6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" t="s">
-        <v>140</v>
-      </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -1446,21 +1446,21 @@
         <v>58</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" t="s">
         <v>86</v>
       </c>
-      <c r="B7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C7" t="s">
-        <v>87</v>
-      </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F7">
         <v>83</v>
@@ -1472,30 +1472,30 @@
         <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K7" t="s">
         <v>58</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" t="s">
         <v>128</v>
       </c>
-      <c r="B8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" t="s">
-        <v>129</v>
-      </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8">
         <v>110</v>
@@ -1510,7 +1510,7 @@
         <v>56</v>
       </c>
       <c r="J8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K8" t="s">
         <v>58</v>
@@ -1519,7 +1519,7 @@
         <v>125</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1527,7 +1527,7 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
@@ -1562,7 +1562,7 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
         <v>29</v>
@@ -1597,7 +1597,7 @@
         <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -1632,22 +1632,22 @@
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" t="s">
         <v>69</v>
       </c>
-      <c r="B12" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>70</v>
-      </c>
-      <c r="E12" t="s">
-        <v>71</v>
       </c>
       <c r="F12">
         <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H12">
         <v>40</v>
@@ -1665,21 +1665,21 @@
         <v>40</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" t="s">
         <v>73</v>
       </c>
-      <c r="B13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C13" t="s">
-        <v>74</v>
-      </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F13">
         <v>60</v>
@@ -1703,7 +1703,7 @@
         <v>45</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1711,7 +1711,7 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
@@ -1743,13 +1743,13 @@
     </row>
     <row r="15" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" t="s">
         <v>147</v>
-      </c>
-      <c r="B15" t="s">
-        <v>146</v>
-      </c>
-      <c r="C15" t="s">
-        <v>148</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -1758,13 +1758,13 @@
         <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H15">
         <v>30</v>
       </c>
       <c r="I15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J15" t="s">
         <v>18</v>
@@ -1773,18 +1773,18 @@
         <v>18</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" t="s">
         <v>157</v>
-      </c>
-      <c r="B16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C16" t="s">
-        <v>158</v>
       </c>
       <c r="E16" t="s">
         <v>14</v>
@@ -1793,7 +1793,7 @@
         <v>55</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H16">
         <v>35</v>
@@ -1808,7 +1808,7 @@
         <v>18</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1816,7 +1816,7 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -1848,13 +1848,13 @@
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" t="s">
         <v>150</v>
-      </c>
-      <c r="B18" t="s">
-        <v>146</v>
-      </c>
-      <c r="C18" t="s">
-        <v>151</v>
       </c>
       <c r="E18" t="s">
         <v>14</v>
@@ -1872,13 +1872,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K18" t="s">
         <v>18</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1886,7 +1886,7 @@
         <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C19" t="s">
         <v>43</v>
@@ -1904,7 +1904,7 @@
         <v>70</v>
       </c>
       <c r="I19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J19" t="s">
         <v>45</v>
@@ -1924,7 +1924,7 @@
         <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
@@ -1959,13 +1959,13 @@
     </row>
     <row r="21" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" t="s">
         <v>154</v>
-      </c>
-      <c r="B21" t="s">
-        <v>146</v>
-      </c>
-      <c r="C21" t="s">
-        <v>155</v>
       </c>
       <c r="E21" t="s">
         <v>14</v>
@@ -1989,7 +1989,7 @@
         <v>18</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1997,7 +1997,7 @@
         <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C22" t="s">
         <v>38</v>
@@ -2029,16 +2029,16 @@
     </row>
     <row r="23" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" t="s">
         <v>81</v>
       </c>
-      <c r="B23" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" t="s">
-        <v>82</v>
-      </c>
       <c r="E23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F23">
         <v>65</v>
@@ -2062,21 +2062,21 @@
         <v>50</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" t="s">
         <v>84</v>
       </c>
-      <c r="B24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
       <c r="E24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F24">
         <v>65</v>
@@ -2100,21 +2100,21 @@
         <v>50</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" t="s">
         <v>93</v>
       </c>
-      <c r="B25" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
       <c r="E25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F25">
         <v>75</v>
@@ -2138,21 +2138,21 @@
         <v>50</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" t="s">
         <v>90</v>
       </c>
-      <c r="B26" t="s">
-        <v>146</v>
-      </c>
-      <c r="C26" t="s">
-        <v>91</v>
-      </c>
       <c r="E26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F26">
         <v>70</v>
@@ -2176,21 +2176,21 @@
         <v>55.5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" t="s">
         <v>101</v>
       </c>
-      <c r="B27" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" t="s">
-        <v>102</v>
-      </c>
       <c r="E27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F27">
         <v>75</v>
@@ -2214,21 +2214,21 @@
         <v>60</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" t="s">
         <v>96</v>
       </c>
-      <c r="B28" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" t="s">
-        <v>97</v>
-      </c>
       <c r="E28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F28">
         <v>70</v>
@@ -2240,7 +2240,7 @@
         <v>60.5</v>
       </c>
       <c r="I28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J28" t="s">
         <v>39</v>
@@ -2252,21 +2252,21 @@
         <v>60.5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" t="s">
         <v>99</v>
       </c>
-      <c r="B29" t="s">
-        <v>146</v>
-      </c>
-      <c r="C29" t="s">
-        <v>100</v>
-      </c>
       <c r="E29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F29">
         <v>70</v>
@@ -2278,7 +2278,7 @@
         <v>60.5</v>
       </c>
       <c r="I29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J29" t="s">
         <v>39</v>
@@ -2290,21 +2290,21 @@
         <v>60.5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30" t="s">
         <v>132</v>
       </c>
-      <c r="B30" t="s">
-        <v>146</v>
-      </c>
-      <c r="C30" t="s">
-        <v>133</v>
-      </c>
       <c r="E30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F30">
         <v>60</v>
@@ -2328,27 +2328,27 @@
         <v>32.5</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C31" t="s">
         <v>64</v>
       </c>
-      <c r="B31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="E31" t="s">
         <v>65</v>
-      </c>
-      <c r="E31" t="s">
-        <v>66</v>
       </c>
       <c r="F31">
         <v>55</v>
       </c>
       <c r="G31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H31">
         <v>50</v>
@@ -2363,21 +2363,21 @@
         <v>40</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" t="s">
         <v>135</v>
       </c>
-      <c r="B32" t="s">
-        <v>146</v>
-      </c>
-      <c r="C32" t="s">
-        <v>136</v>
-      </c>
       <c r="E32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F32">
         <v>80</v>
@@ -2389,10 +2389,10 @@
         <v>65.5</v>
       </c>
       <c r="I32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K32" t="s">
         <v>39</v>
@@ -2401,21 +2401,21 @@
         <v>55.5</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" t="s">
         <v>113</v>
       </c>
-      <c r="B33" t="s">
-        <v>146</v>
-      </c>
-      <c r="C33" t="s">
-        <v>114</v>
-      </c>
       <c r="E33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F33">
         <v>65</v>
@@ -2439,21 +2439,21 @@
         <v>105.9</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" t="s">
         <v>116</v>
       </c>
-      <c r="B34" t="s">
-        <v>146</v>
-      </c>
-      <c r="C34" t="s">
-        <v>117</v>
-      </c>
       <c r="E34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F34">
         <v>65</v>
@@ -2477,21 +2477,21 @@
         <v>105.9</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35" t="s">
         <v>108</v>
       </c>
-      <c r="B35" t="s">
-        <v>146</v>
-      </c>
-      <c r="C35" t="s">
-        <v>109</v>
-      </c>
       <c r="E35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F35">
         <v>86</v>
@@ -2515,21 +2515,21 @@
         <v>105.9</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" t="s">
         <v>111</v>
       </c>
-      <c r="B36" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" t="s">
-        <v>112</v>
-      </c>
       <c r="E36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F36">
         <v>86</v>
@@ -2553,7 +2553,7 @@
         <v>105.9</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2561,7 +2561,7 @@
         <v>47</v>
       </c>
       <c r="B37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C37" t="s">
         <v>48</v>
@@ -2599,7 +2599,7 @@
         <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C38" t="s">
         <v>61</v>
@@ -2631,16 +2631,16 @@
     </row>
     <row r="39" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" t="s">
         <v>104</v>
       </c>
-      <c r="B39" t="s">
-        <v>146</v>
-      </c>
-      <c r="C39" t="s">
-        <v>105</v>
-      </c>
       <c r="E39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F39">
         <v>90</v>
@@ -2655,7 +2655,7 @@
         <v>50</v>
       </c>
       <c r="J39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K39" t="s">
         <v>52</v>
@@ -2664,21 +2664,21 @@
         <v>90</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" t="s">
         <v>119</v>
       </c>
-      <c r="B40" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" t="s">
-        <v>120</v>
-      </c>
       <c r="E40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F40">
         <v>90</v>
@@ -2693,7 +2693,7 @@
         <v>50</v>
       </c>
       <c r="J40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K40" t="s">
         <v>52</v>
@@ -2702,21 +2702,21 @@
         <v>100</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" t="s">
         <v>76</v>
       </c>
-      <c r="B41" t="s">
-        <v>146</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="E41" t="s">
         <v>77</v>
-      </c>
-      <c r="E41" t="s">
-        <v>78</v>
       </c>
       <c r="F41">
         <v>70</v>
@@ -2731,13 +2731,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K41" t="s">
         <v>52</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73F21E9-2D29-4F4D-987F-E90B218604A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AAC5E5-6F37-498C-A857-C296457872EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>описание</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/348_1.jpg</t>
-  </si>
-  <si>
     <t>FPRO2L20-B</t>
   </si>
   <si>
@@ -814,6 +811,9 @@
   </si>
   <si>
     <t>https://shop.onkron.ru/images/product_images/popup_images/348_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/161_0.png</t>
   </si>
 </sst>
 </file>
@@ -887,7 +887,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M41" totalsRowShown="0">
   <autoFilter ref="A1:M41" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M41">
-    <sortCondition ref="J1:J41"/>
+    <sortCondition ref="C1:C41"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
@@ -1209,7 +1209,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" customWidth="1"/>
     <col min="6" max="6" width="26.140625" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" customWidth="1"/>
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1264,1480 +1264,1480 @@
     </row>
     <row r="2" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2">
         <v>70</v>
       </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="I2" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L2">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F3">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="G3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H3">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="I3" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="K3" t="s">
-        <v>58</v>
-      </c>
-      <c r="L3">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H4">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="J4" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H5">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="K5" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>59</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>136.4</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="H7">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>88</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8">
+        <v>55</v>
+      </c>
+      <c r="G8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8">
+        <v>40</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8">
+        <v>40</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="F8">
-        <v>110</v>
-      </c>
-      <c r="G8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8">
-        <v>125</v>
-      </c>
-      <c r="I8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" t="s">
-        <v>129</v>
-      </c>
-      <c r="K8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8">
-        <v>125</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="F9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H9">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K9" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="L9">
+        <v>45</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F10">
         <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H10">
         <v>35</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11">
+        <v>65</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11">
+        <v>35</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="F11">
-        <v>60</v>
-      </c>
-      <c r="G11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11">
-        <v>41</v>
-      </c>
-      <c r="I11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" t="s">
-        <v>18</v>
-      </c>
-      <c r="L11">
-        <v>41</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="H12">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>18</v>
-      </c>
-      <c r="L12">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13">
         <v>70</v>
       </c>
-      <c r="F13">
-        <v>60</v>
-      </c>
       <c r="G13" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H13">
-        <v>45</v>
+        <v>40.5</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="K13" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="F14">
         <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H14">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="K14" t="s">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="L14">
+        <v>50</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="F15">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="H15">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="K15" t="s">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="L15">
+        <v>50</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>148</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C16" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="F16">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H16">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="K16" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>158</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="F17">
         <v>70</v>
       </c>
       <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17">
+        <v>55.5</v>
+      </c>
+      <c r="I17" t="s">
         <v>15</v>
       </c>
-      <c r="H17">
-        <v>45</v>
-      </c>
-      <c r="I17" t="s">
-        <v>16</v>
-      </c>
       <c r="J17" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="K17" t="s">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="L17">
+        <v>55.5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18">
+        <v>75</v>
+      </c>
+      <c r="G18" t="s">
         <v>14</v>
       </c>
-      <c r="F18">
-        <v>65</v>
-      </c>
-      <c r="G18" t="s">
-        <v>22</v>
-      </c>
       <c r="H18">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J18" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="K18" t="s">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="L18">
+        <v>50</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>152</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="F19">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H19">
-        <v>70</v>
+        <v>60.5</v>
       </c>
       <c r="I19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J19" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="K19" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L19">
-        <v>70</v>
+        <v>60.5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="F20">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H20">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="J20" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L20">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21">
+        <v>70</v>
+      </c>
+      <c r="G21" t="s">
         <v>14</v>
       </c>
-      <c r="F21">
-        <v>75</v>
-      </c>
-      <c r="G21" t="s">
-        <v>15</v>
-      </c>
       <c r="H21">
-        <v>40</v>
+        <v>60.5</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="J21" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K21" t="s">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="L21">
+        <v>60.5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>155</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22">
+        <v>75</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22">
+        <v>60</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" t="s">
         <v>38</v>
       </c>
-      <c r="E22" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22">
-        <v>65</v>
-      </c>
-      <c r="G22" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22">
-        <v>40</v>
-      </c>
-      <c r="I22" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>39</v>
       </c>
-      <c r="K22" t="s">
-        <v>40</v>
+      <c r="L22">
+        <v>60</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F23">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="H23">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J23" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="K23" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L23">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="B24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F24">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="G24" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="H24">
+        <v>105.9</v>
+      </c>
+      <c r="I24" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" t="s">
         <v>50</v>
       </c>
-      <c r="I24" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" t="s">
-        <v>39</v>
-      </c>
       <c r="K24" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L24">
-        <v>50</v>
+        <v>105.9</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="E25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F25">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H25">
+        <v>105.9</v>
+      </c>
+      <c r="I25" t="s">
+        <v>49</v>
+      </c>
+      <c r="J25" t="s">
         <v>50</v>
       </c>
-      <c r="I25" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" t="s">
-        <v>39</v>
-      </c>
       <c r="K25" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L25">
-        <v>50</v>
+        <v>105.9</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="B26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="E26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F26">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H26">
-        <v>55.5</v>
+        <v>105.9</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J26" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K26" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L26">
-        <v>55.5</v>
+        <v>105.9</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="F27">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H27">
-        <v>60</v>
+        <v>105.9</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J27" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K27" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L27">
-        <v>60</v>
+        <v>105.9</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F28">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H28">
-        <v>60.5</v>
+        <v>105.9</v>
       </c>
       <c r="I28" t="s">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="J28" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K28" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L28">
-        <v>60.5</v>
+        <v>105.9</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F29">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H29">
-        <v>60.5</v>
+        <v>100</v>
       </c>
       <c r="I29" t="s">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="J29" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="K29" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L29">
-        <v>60.5</v>
+        <v>100</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F30">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G30" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="H30">
-        <v>32.5</v>
+        <v>130</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="J30" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="K30" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="L30">
-        <v>32.5</v>
+        <v>130</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>161</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="G31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H31">
+        <v>130</v>
+      </c>
+      <c r="I31" t="s">
         <v>55</v>
       </c>
-      <c r="G31" t="s">
-        <v>66</v>
-      </c>
-      <c r="H31">
-        <v>50</v>
-      </c>
-      <c r="I31" t="s">
-        <v>16</v>
-      </c>
       <c r="J31" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="K31" t="s">
-        <v>40</v>
+        <v>57</v>
+      </c>
+      <c r="L31">
+        <v>130</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F32">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G32" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="H32">
-        <v>65.5</v>
+        <v>150</v>
       </c>
       <c r="I32" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="J32" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="K32" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="L32">
-        <v>55.5</v>
+        <v>150</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="B33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F33">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="G33" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="H33">
-        <v>105.9</v>
+        <v>125</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J33" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="K33" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L33">
-        <v>105.9</v>
+        <v>125</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="E34" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F34">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H34">
-        <v>105.9</v>
+        <v>32.5</v>
       </c>
       <c r="I34" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="J34" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="K34" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="L34">
-        <v>105.9</v>
+        <v>32.5</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="E35" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F35">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H35">
-        <v>105.9</v>
+        <v>65.5</v>
       </c>
       <c r="I35" t="s">
-        <v>50</v>
+        <v>159</v>
       </c>
       <c r="J35" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="K35" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="L35">
-        <v>105.9</v>
+        <v>55.5</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="B36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="E36" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F36">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="G36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H36">
-        <v>105.9</v>
+        <v>136.4</v>
       </c>
       <c r="I36" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J36" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K36" t="s">
-        <v>52</v>
-      </c>
-      <c r="L36">
-        <v>105.9</v>
+        <v>57</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F37">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="G37" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="H37">
-        <v>105.9</v>
+        <v>125</v>
       </c>
       <c r="I37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J37" t="s">
         <v>50</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>51</v>
       </c>
-      <c r="K37" t="s">
-        <v>52</v>
-      </c>
-      <c r="L37">
-        <v>105.9</v>
-      </c>
       <c r="M37" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="B38" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38">
+        <v>110</v>
+      </c>
+      <c r="G38" t="s">
+        <v>61</v>
+      </c>
+      <c r="H38">
         <v>145</v>
       </c>
-      <c r="C38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E38" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38">
-        <v>120</v>
-      </c>
-      <c r="G38" t="s">
-        <v>62</v>
-      </c>
-      <c r="H38">
-        <v>125</v>
-      </c>
       <c r="I38" t="s">
+        <v>55</v>
+      </c>
+      <c r="J38" t="s">
         <v>56</v>
       </c>
-      <c r="J38" t="s">
-        <v>51</v>
-      </c>
       <c r="K38" t="s">
-        <v>52</v>
+        <v>57</v>
+      </c>
+      <c r="L38">
+        <v>145</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>63</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="F39">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G39" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H39">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="I39" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="J39" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="L39">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="E40" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="F40">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G40" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H40">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="I40" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="J40" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="K40" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="L40">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C41" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="E41" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F41">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41">
+        <v>40</v>
+      </c>
+      <c r="I41" t="s">
         <v>15</v>
       </c>
-      <c r="H41">
-        <v>40.5</v>
-      </c>
-      <c r="I41" t="s">
-        <v>16</v>
-      </c>
       <c r="J41" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="K41" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AAC5E5-6F37-498C-A857-C296457872EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3D3BE4-9020-4CDB-AE1D-27DFD58E43E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -886,9 +886,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M41" totalsRowShown="0">
   <autoFilter ref="A1:M41" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M41">
-    <sortCondition ref="C1:C41"/>
-  </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -1210,7 +1207,7 @@
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="26.140625" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" customWidth="1"/>
     <col min="8" max="8" width="26.7109375" customWidth="1"/>
@@ -1282,7 +1279,7 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
@@ -1317,7 +1314,7 @@
         <v>65</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
@@ -1492,7 +1489,7 @@
         <v>65</v>
       </c>
       <c r="H8">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
@@ -1530,7 +1527,7 @@
         <v>21</v>
       </c>
       <c r="H9">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
@@ -1708,7 +1705,7 @@
         <v>21</v>
       </c>
       <c r="H14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
@@ -1746,7 +1743,7 @@
         <v>21</v>
       </c>
       <c r="H15">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
@@ -1784,7 +1781,7 @@
         <v>48</v>
       </c>
       <c r="H16">
-        <v>70</v>
+        <v>65.5</v>
       </c>
       <c r="I16" t="s">
         <v>159</v>
@@ -1794,6 +1791,9 @@
       </c>
       <c r="K16" t="s">
         <v>57</v>
+      </c>
+      <c r="L16">
+        <v>70</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>87</v>
@@ -1819,7 +1819,7 @@
         <v>14</v>
       </c>
       <c r="H17">
-        <v>55.5</v>
+        <v>45.5</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
@@ -1857,7 +1857,7 @@
         <v>14</v>
       </c>
       <c r="H18">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I18" t="s">
         <v>15</v>
@@ -1895,7 +1895,7 @@
         <v>14</v>
       </c>
       <c r="H19">
-        <v>60.5</v>
+        <v>45.5</v>
       </c>
       <c r="I19" t="s">
         <v>159</v>
@@ -1933,7 +1933,7 @@
         <v>14</v>
       </c>
       <c r="H20">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I20" t="s">
         <v>159</v>
@@ -1971,7 +1971,7 @@
         <v>14</v>
       </c>
       <c r="H21">
-        <v>60.5</v>
+        <v>45.5</v>
       </c>
       <c r="I21" t="s">
         <v>159</v>
@@ -2009,7 +2009,7 @@
         <v>14</v>
       </c>
       <c r="H22">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
@@ -2047,7 +2047,7 @@
         <v>48</v>
       </c>
       <c r="H23">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -2085,7 +2085,7 @@
         <v>48</v>
       </c>
       <c r="H24">
-        <v>105.9</v>
+        <v>90.9</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -2123,7 +2123,7 @@
         <v>21</v>
       </c>
       <c r="H25">
-        <v>105.9</v>
+        <v>90.9</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -2161,7 +2161,7 @@
         <v>21</v>
       </c>
       <c r="H26">
-        <v>105.9</v>
+        <v>90.9</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -2199,7 +2199,7 @@
         <v>48</v>
       </c>
       <c r="H27">
-        <v>105.9</v>
+        <v>90.9</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -2237,7 +2237,7 @@
         <v>48</v>
       </c>
       <c r="H28">
-        <v>105.9</v>
+        <v>90.9</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -2275,7 +2275,7 @@
         <v>48</v>
       </c>
       <c r="H29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -2313,10 +2313,10 @@
         <v>48</v>
       </c>
       <c r="H30">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I30" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J30" t="s">
         <v>56</v>
@@ -2351,10 +2351,10 @@
         <v>48</v>
       </c>
       <c r="H31">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I31" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J31" t="s">
         <v>56</v>
@@ -2389,10 +2389,10 @@
         <v>61</v>
       </c>
       <c r="H32">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I32" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J32" t="s">
         <v>56</v>
@@ -2427,10 +2427,10 @@
         <v>61</v>
       </c>
       <c r="H33">
-        <v>125</v>
+        <v>120.5</v>
       </c>
       <c r="I33" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J33" t="s">
         <v>128</v>
@@ -2465,7 +2465,7 @@
         <v>21</v>
       </c>
       <c r="H34">
-        <v>32.5</v>
+        <v>30.5</v>
       </c>
       <c r="I34" t="s">
         <v>15</v>
@@ -2503,7 +2503,7 @@
         <v>48</v>
       </c>
       <c r="H35">
-        <v>65.5</v>
+        <v>45.5</v>
       </c>
       <c r="I35" t="s">
         <v>159</v>
@@ -2576,16 +2576,19 @@
         <v>61</v>
       </c>
       <c r="H37">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I37" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J37" t="s">
         <v>50</v>
       </c>
       <c r="K37" t="s">
         <v>51</v>
+      </c>
+      <c r="L37">
+        <v>125</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>62</v>
@@ -2611,7 +2614,7 @@
         <v>61</v>
       </c>
       <c r="H38">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="I38" t="s">
         <v>55</v>
@@ -2725,7 +2728,7 @@
         <v>21</v>
       </c>
       <c r="H41">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I41" t="s">
         <v>15</v>
@@ -2735,6 +2738,9 @@
       </c>
       <c r="K41" t="s">
         <v>39</v>
+      </c>
+      <c r="L41">
+        <v>40</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>40</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3D3BE4-9020-4CDB-AE1D-27DFD58E43E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711A9930-B502-4A16-AA82-B88A394740AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -886,6 +886,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M41" totalsRowShown="0">
   <autoFilter ref="A1:M41" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M41">
+    <sortCondition ref="H1:H41"/>
+  </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -1261,60 +1264,60 @@
     </row>
     <row r="2" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
         <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="H2">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s">
         <v>17</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
@@ -1325,43 +1328,49 @@
       <c r="K3" t="s">
         <v>39</v>
       </c>
+      <c r="L3">
+        <v>40</v>
+      </c>
       <c r="M3" s="1" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
         <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="F4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H4">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="I4" t="s">
-        <v>158</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>39</v>
+      </c>
+      <c r="L4">
+        <v>32.5</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1401,51 +1410,51 @@
     </row>
     <row r="6" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
         <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
       </c>
       <c r="F6">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
         <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="F7">
         <v>55</v>
@@ -1465,28 +1474,31 @@
       <c r="K7" t="s">
         <v>17</v>
       </c>
+      <c r="L7">
+        <v>40</v>
+      </c>
       <c r="M7" s="1" t="s">
-        <v>157</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>144</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H8">
         <v>35</v>
@@ -1500,34 +1512,31 @@
       <c r="K8" t="s">
         <v>17</v>
       </c>
-      <c r="L8">
-        <v>40</v>
-      </c>
       <c r="M8" s="1" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
         <v>21</v>
       </c>
       <c r="H9">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
@@ -1538,25 +1547,22 @@
       <c r="K9" t="s">
         <v>17</v>
       </c>
-      <c r="L9">
-        <v>45</v>
-      </c>
       <c r="M9" s="1" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F10">
         <v>65</v>
@@ -1577,65 +1583,65 @@
         <v>17</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
         <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H11">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="K11" t="s">
         <v>17</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>26</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
         <v>144</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="F12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
         <v>21</v>
       </c>
       <c r="H12">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
@@ -1646,8 +1652,11 @@
       <c r="K12" t="s">
         <v>17</v>
       </c>
+      <c r="L12">
+        <v>45</v>
+      </c>
       <c r="M12" s="1" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1687,139 +1696,139 @@
     </row>
     <row r="14" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
         <v>144</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G14" t="s">
         <v>21</v>
       </c>
       <c r="H14">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="L14">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
         <v>144</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="F15">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
         <v>21</v>
       </c>
       <c r="H15">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K15" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="L15">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
         <v>144</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F16">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H16">
-        <v>65.5</v>
+        <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="K16" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L16">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
         <v>144</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
         <v>69</v>
       </c>
       <c r="F17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H17">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
@@ -1831,10 +1840,10 @@
         <v>39</v>
       </c>
       <c r="L17">
-        <v>55.5</v>
+        <v>50</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1877,13 +1886,13 @@
     </row>
     <row r="19" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
         <v>144</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
@@ -1898,7 +1907,7 @@
         <v>45.5</v>
       </c>
       <c r="I19" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="J19" t="s">
         <v>38</v>
@@ -1907,48 +1916,48 @@
         <v>39</v>
       </c>
       <c r="L19">
-        <v>60.5</v>
+        <v>55.5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
         <v>144</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F20">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s">
         <v>14</v>
       </c>
       <c r="H20">
-        <v>65</v>
+        <v>45.5</v>
       </c>
       <c r="I20" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="K20" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L20">
-        <v>70</v>
+        <v>60.5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1974,7 +1983,7 @@
         <v>45.5</v>
       </c>
       <c r="I21" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="J21" t="s">
         <v>38</v>
@@ -1991,560 +2000,557 @@
     </row>
     <row r="22" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="B22" t="s">
         <v>144</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F22">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H22">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
       </c>
       <c r="J22" t="s">
+        <v>135</v>
+      </c>
+      <c r="K22" t="s">
         <v>38</v>
       </c>
-      <c r="K22" t="s">
-        <v>39</v>
-      </c>
       <c r="L22">
-        <v>60</v>
+        <v>55.5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B23" t="s">
         <v>144</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
         <v>69</v>
       </c>
       <c r="F23">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H23">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="K23" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="L23">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
         <v>144</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="F24">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H24">
-        <v>90.9</v>
+        <v>65</v>
       </c>
       <c r="I24" t="s">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="J24" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K24" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="L24">
-        <v>105.9</v>
+        <v>70</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s">
         <v>144</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F25">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H25">
-        <v>90.9</v>
+        <v>65.5</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="J25" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="K25" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L25">
-        <v>105.9</v>
+        <v>70</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B26" t="s">
         <v>144</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
         <v>69</v>
       </c>
       <c r="F26">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H26">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
       </c>
       <c r="J26" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="K26" t="s">
         <v>51</v>
       </c>
       <c r="L26">
-        <v>105.9</v>
+        <v>90</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s">
         <v>144</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="F27">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G27" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H27">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
       </c>
       <c r="J27" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="K27" t="s">
-        <v>51</v>
-      </c>
-      <c r="L27">
-        <v>105.9</v>
+        <v>17</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B28" t="s">
         <v>144</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
         <v>69</v>
       </c>
       <c r="F28">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s">
         <v>48</v>
       </c>
       <c r="H28">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
       </c>
       <c r="J28" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="K28" t="s">
         <v>51</v>
       </c>
       <c r="L28">
-        <v>105.9</v>
+        <v>100</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
         <v>144</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E29" t="s">
         <v>69</v>
       </c>
       <c r="F29">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G29" t="s">
         <v>48</v>
       </c>
       <c r="H29">
-        <v>90</v>
+        <v>90.9</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
       </c>
       <c r="J29" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="K29" t="s">
         <v>51</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>105.9</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
         <v>144</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s">
         <v>69</v>
       </c>
       <c r="F30">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="G30" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H30">
-        <v>120</v>
+        <v>90.9</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
       </c>
       <c r="J30" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K30" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L30">
-        <v>130</v>
+        <v>105.9</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s">
         <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F31">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="G31" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H31">
-        <v>120</v>
+        <v>90.9</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
       </c>
       <c r="J31" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K31" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L31">
-        <v>130</v>
+        <v>105.9</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
         <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="F32">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H32">
-        <v>120</v>
+        <v>90.9</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
       </c>
       <c r="J32" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L32">
-        <v>150</v>
+        <v>105.9</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="B33" t="s">
         <v>144</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="E33" t="s">
         <v>69</v>
       </c>
       <c r="F33">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H33">
-        <v>120.5</v>
+        <v>90.9</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
       </c>
       <c r="J33" t="s">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="K33" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L33">
-        <v>125</v>
+        <v>105.9</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34">
+        <v>100</v>
+      </c>
+      <c r="G34" t="s">
+        <v>48</v>
+      </c>
+      <c r="H34">
+        <v>120</v>
+      </c>
+      <c r="I34" t="s">
+        <v>49</v>
+      </c>
+      <c r="J34" t="s">
+        <v>56</v>
+      </c>
+      <c r="K34" t="s">
+        <v>57</v>
+      </c>
+      <c r="L34">
         <v>130</v>
       </c>
-      <c r="B34" t="s">
-        <v>144</v>
-      </c>
-      <c r="C34" t="s">
-        <v>131</v>
-      </c>
-      <c r="E34" t="s">
-        <v>64</v>
-      </c>
-      <c r="F34">
-        <v>60</v>
-      </c>
-      <c r="G34" t="s">
-        <v>21</v>
-      </c>
-      <c r="H34">
-        <v>30.5</v>
-      </c>
-      <c r="I34" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" t="s">
-        <v>38</v>
-      </c>
-      <c r="K34" t="s">
-        <v>39</v>
-      </c>
-      <c r="L34">
-        <v>32.5</v>
-      </c>
       <c r="M34" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
         <v>144</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="E35" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="F35">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G35" t="s">
         <v>48</v>
       </c>
       <c r="H35">
-        <v>45.5</v>
+        <v>120</v>
       </c>
       <c r="I35" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
       <c r="J35" t="s">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="K35" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="L35">
-        <v>55.5</v>
+        <v>130</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s">
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E36" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F36">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G36" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H36">
-        <v>136.4</v>
+        <v>120</v>
       </c>
       <c r="I36" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J36" t="s">
         <v>56</v>
@@ -2552,8 +2558,11 @@
       <c r="K36" t="s">
         <v>57</v>
       </c>
+      <c r="L36">
+        <v>150</v>
+      </c>
       <c r="M36" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2596,13 +2605,13 @@
     </row>
     <row r="38" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B38" t="s">
         <v>144</v>
       </c>
       <c r="C38" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E38" t="s">
         <v>69</v>
@@ -2614,124 +2623,121 @@
         <v>61</v>
       </c>
       <c r="H38">
-        <v>130</v>
+        <v>120.5</v>
       </c>
       <c r="I38" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J38" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="K38" t="s">
         <v>57</v>
       </c>
       <c r="L38">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
         <v>144</v>
       </c>
       <c r="C39" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="E39" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="F39">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="G39" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="H39">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="I39" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="J39" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="K39" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="L39">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="B40" t="s">
         <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="F40">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H40">
-        <v>41</v>
+        <v>136.4</v>
       </c>
       <c r="I40" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="J40" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="K40" t="s">
-        <v>17</v>
-      </c>
-      <c r="L40">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="B41" t="s">
         <v>144</v>
       </c>
       <c r="C41" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="F41">
+        <v>55</v>
+      </c>
+      <c r="G41" t="s">
         <v>65</v>
       </c>
-      <c r="G41" t="s">
-        <v>21</v>
-      </c>
       <c r="H41">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="I41" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="J41" t="s">
         <v>38</v>
@@ -2739,11 +2745,8 @@
       <c r="K41" t="s">
         <v>39</v>
       </c>
-      <c r="L41">
-        <v>40</v>
-      </c>
       <c r="M41" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711A9930-B502-4A16-AA82-B88A394740AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4D231C-75DA-40BA-9737-D1E4367BDE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="489">
   <si>
     <t>image_url</t>
   </si>
@@ -102,9 +103,6 @@
 Материал: сталь</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/461_1.png</t>
-  </si>
-  <si>
     <t>TS1140-B</t>
   </si>
   <si>
@@ -117,9 +115,6 @@
 Регулировка высоты: 880 - 1100 мм
 Высота стойки: 1295 мм
 Размер основания: 618х256 мм</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/334_1.png</t>
   </si>
   <si>
     <t>TS1220-B</t>
@@ -141,13 +136,7 @@
 Материалы: массив бука, сталь</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/349_1.png</t>
-  </si>
-  <si>
     <t>TS1220-W</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/478_1.jpg</t>
   </si>
   <si>
     <t>TS5060-B</t>
@@ -159,9 +148,6 @@
 VESA: 100x100, 100x200, 200x100, 200x200, 200x300, 200x400, 300x100, 300x200, 300x300, 300x400, 400x200, 400x300, 400x400 мм
 Угол поворота: -54&amp;deg; ~ +54&amp;deg; (пластиковый ограничитель сзади предотвращает проворот)
 Высота столба: 1250 мм</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/437_1.png</t>
   </si>
   <si>
     <t>TS5065-B</t>
@@ -179,9 +165,6 @@
 Силиконовые защитные проставки
 Габариты основания: 550х400x10 мм
 Материалы: холоднокатаная сталь, закалённое стекло</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/413_1.jpg</t>
   </si>
   <si>
     <t>TS5550-B</t>
@@ -209,9 +192,6 @@
 Материалы: холоднокатаная сталь, закаленное стекло</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/672_1.jpg</t>
-  </si>
-  <si>
     <t>TS1552E-B</t>
   </si>
   <si>
@@ -231,9 +211,6 @@
 Дистанция пульта: 10 м
 Материал: холоднокатаная сталь
 Гарантия: ограниченная пожизненная</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/441_1.jpg</t>
   </si>
   <si>
     <t>TS1881E-B</t>
@@ -263,9 +240,6 @@
 Дальность действия пульта ДУ: 5 м
 Оснащена колёсиками с блокировкой движения
 Материалы: сталь, пластик</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/442_1.png</t>
   </si>
   <si>
     <t>TS1991E-B</t>
@@ -296,9 +270,6 @@
 Материалы: сталь, пластик</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/671_1.jpg</t>
-  </si>
-  <si>
     <t>TS2811E-B</t>
   </si>
   <si>
@@ -327,9 +298,6 @@
 Рычаги микрорегулировки позволяют настроить глубину каждого угла экрана
 Оснащена колёсиками с блокировкой движения
 Материалы: алюминий, сталь</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/503_2.jpg</t>
   </si>
   <si>
     <t>TS1131-B</t>
@@ -350,9 +318,6 @@
 Материал: сталь</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/502_1.png</t>
-  </si>
-  <si>
     <t>TS1137-B</t>
   </si>
   <si>
@@ -368,9 +333,6 @@
 Материал: сталь</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/412_13.jpg</t>
-  </si>
-  <si>
     <t>TS1350-B</t>
   </si>
   <si>
@@ -392,9 +354,6 @@
 Материалы: холоднокатаная сталь, пластик</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/243_1.png</t>
-  </si>
-  <si>
     <t>TS1351-B</t>
   </si>
   <si>
@@ -409,13 +368,7 @@
 Материалы: сталь, пластик</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/354_1.jpg</t>
-  </si>
-  <si>
     <t>TS1351-W</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/419_10.jpg</t>
   </si>
   <si>
     <t>TS1380-B</t>
@@ -437,9 +390,6 @@
 Материалы: холоднокатаная сталь, пластик</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/50_1.png</t>
-  </si>
-  <si>
     <t>TS1551-B</t>
   </si>
   <si>
@@ -454,9 +404,6 @@
 Материалы: сталь, пластик</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/476_1.png</t>
-  </si>
-  <si>
     <t>TS1551R-B</t>
   </si>
   <si>
@@ -469,9 +416,6 @@
 Регулировка полки по высоте
 Оснащена колёсиками с блокировкой движения
 Материал: основание, колонны, VESA-панель - сталь; полка - пластик</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/51_1.png</t>
   </si>
   <si>
     <t>TS1552-B</t>
@@ -489,13 +433,7 @@
 Материалы: сталь, пластик</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/143_1.png</t>
-  </si>
-  <si>
     <t>TS1552-W</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/481_1.png</t>
   </si>
   <si>
     <t>TS1571-B</t>
@@ -512,9 +450,6 @@
 Материал: сталь</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/482_1.png</t>
-  </si>
-  <si>
     <t>TS1871-B</t>
   </si>
   <si>
@@ -530,9 +465,6 @@
 Регулировка полки по высоте
 Оснащена колёсиками с блокировкой движения
 Материал: сталь</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/52_1.png</t>
   </si>
   <si>
     <t>TS1881-B</t>
@@ -550,13 +482,7 @@
 Материалы: сталь, пластик</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/144_1.png</t>
-  </si>
-  <si>
     <t>TS1881-W</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/355_1.jpg</t>
   </si>
   <si>
     <t>TS1881DV-B</t>
@@ -574,9 +500,6 @@
 Материалы: сталь, пластик</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/356_1.jpg</t>
-  </si>
-  <si>
     <t>TS1881DV-W</t>
   </si>
   <si>
@@ -590,9 +513,6 @@
 Регулировка высоты: 1350-1650 мм
 Оснащена колёсиками с блокировкой движения
 Материалы: сталь, пластик</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/445_1.jpg</t>
   </si>
   <si>
     <t>TS1891-B</t>
@@ -611,9 +531,6 @@
 Материалы: сталь, пластик</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/436_1.png</t>
-  </si>
-  <si>
     <t>TS1991-B</t>
   </si>
   <si>
@@ -630,9 +547,6 @@
 Материалы: сталь, пластик</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/470_1.png</t>
-  </si>
-  <si>
     <t>TS2080-B</t>
   </si>
   <si>
@@ -646,9 +560,6 @@
 Материал: сталь</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/618_1.jpg</t>
-  </si>
-  <si>
     <t>TS2081-B</t>
   </si>
   <si>
@@ -662,9 +573,6 @@
 Полка для AV
 Оснащена колёсами с блокировкой движения
 Материал: сталь</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/53_1.jpg</t>
   </si>
   <si>
     <t>TS2551-B</t>
@@ -681,9 +589,6 @@
 Материал: основание, VESA-панель, полка - сталь; колонна - алюминий</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/54_1.png</t>
-  </si>
-  <si>
     <t>TS2771-B</t>
   </si>
   <si>
@@ -701,9 +606,6 @@
 Материал: основание, VESA-панель, полка - сталь; колонны - алюминий</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/324_1.jpg</t>
-  </si>
-  <si>
     <t>TS2811-B</t>
   </si>
   <si>
@@ -715,9 +617,6 @@
 Оснащена колёсиками с блокировкой движения
 Раздвижное основание Расстояние между столбами регулируется в пределах 550-750 мм, ширина 670мм
 Материалы: алюминий, сталь</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/483_1.png</t>
   </si>
   <si>
     <t>TS2821-B</t>
@@ -740,9 +639,6 @@
     <t>de</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/46_1.png</t>
-  </si>
-  <si>
     <t>PT1-B</t>
   </si>
   <si>
@@ -752,9 +648,6 @@
 Регулировка высоты: 594 мм, 634 мм, 674 мм
 Габариты основания: 430х240 мм
 Материалы: холоднокатаная сталь, закалённое стекло</t>
-  </si>
-  <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/406_1.jpg</t>
   </si>
   <si>
     <t>PT2-B</t>
@@ -773,9 +666,6 @@
 Материалы: холоднокатаная сталь, закалённое стекло</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/407_1.jpg</t>
-  </si>
-  <si>
     <t>PT3-B</t>
   </si>
   <si>
@@ -789,9 +679,6 @@
 Материалы: холоднокатаная сталь, закалённое стекло</t>
   </si>
   <si>
-    <t>www.shop.onkron.ru/images/product_images/popup_images/530_2.jpg</t>
-  </si>
-  <si>
     <t>PT4-B</t>
   </si>
   <si>
@@ -814,6 +701,1101 @@
   </si>
   <si>
     <t>https://shop.onkron.ru/images/product_images/popup_images/161_0.png</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Image url</t>
+  </si>
+  <si>
+    <t>CPRO2L-3-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/162_0.png</t>
+  </si>
+  <si>
+    <t>CPRO2L-4-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/163_0.png</t>
+  </si>
+  <si>
+    <t>CR1S-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/166_0.png</t>
+  </si>
+  <si>
+    <t>D101E-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/153_0.png</t>
+  </si>
+  <si>
+    <t>D101FS-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/154_0.png</t>
+  </si>
+  <si>
+    <t>D121E-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/155_0.png</t>
+  </si>
+  <si>
+    <t>D208E-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/438_0.png</t>
+  </si>
+  <si>
+    <t>D208FS-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/167_0.png</t>
+  </si>
+  <si>
+    <t>D221E-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/158_0.png</t>
+  </si>
+  <si>
+    <t>D421E-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/322_0.png</t>
+  </si>
+  <si>
+    <t>FM1-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/11_0.png</t>
+  </si>
+  <si>
+    <t>FM2-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/15_0.png</t>
+  </si>
+  <si>
+    <t>FM5-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/24_0.png</t>
+  </si>
+  <si>
+    <t>FM6-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/25_0.png</t>
+  </si>
+  <si>
+    <t>FME-22B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/447_0.png</t>
+  </si>
+  <si>
+    <t>FME-44B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/449_0.png</t>
+  </si>
+  <si>
+    <t>FME-64B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/451_0.png</t>
+  </si>
+  <si>
+    <t>FPRO2L-20-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/348_0.png</t>
+  </si>
+  <si>
+    <t>G100-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/29_0.png</t>
+  </si>
+  <si>
+    <t>G100-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/357_0.png</t>
+  </si>
+  <si>
+    <t>G110-BG</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/538_0.png</t>
+  </si>
+  <si>
+    <t>G120-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/142_0.png</t>
+  </si>
+  <si>
+    <t>G130-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/504_0.png</t>
+  </si>
+  <si>
+    <t>G140-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/139_0.png</t>
+  </si>
+  <si>
+    <t>G150-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/141_0.png</t>
+  </si>
+  <si>
+    <t>G160-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/87_0.png</t>
+  </si>
+  <si>
+    <t>G160-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/308_0.png</t>
+  </si>
+  <si>
+    <t>G200-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/31_0.png</t>
+  </si>
+  <si>
+    <t>G200-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/358_0.png</t>
+  </si>
+  <si>
+    <t>G280-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/140_0.png</t>
+  </si>
+  <si>
+    <t>G45-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/501_0.png</t>
+  </si>
+  <si>
+    <t>G50-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/408_0.png</t>
+  </si>
+  <si>
+    <t>G70-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/138_0.png</t>
+  </si>
+  <si>
+    <t>G75-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/456_0.png</t>
+  </si>
+  <si>
+    <t>G80-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/27_0.png</t>
+  </si>
+  <si>
+    <t>G80-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/26_0.png</t>
+  </si>
+  <si>
+    <t>G90-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/405_0.png</t>
+  </si>
+  <si>
+    <t>K3A-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/239_0.png</t>
+  </si>
+  <si>
+    <t>K5A-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/34_0.png</t>
+  </si>
+  <si>
+    <t>M10-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/519_0.png</t>
+  </si>
+  <si>
+    <t>M10-BW</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/559_0.png</t>
+  </si>
+  <si>
+    <t>M1S-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/M1S_b_0.png</t>
+  </si>
+  <si>
+    <t>M2-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/35_0.png</t>
+  </si>
+  <si>
+    <t>M2S-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/36_0.png</t>
+  </si>
+  <si>
+    <t>M3S-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/18_0.png</t>
+  </si>
+  <si>
+    <t>M4-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/13_0.png</t>
+  </si>
+  <si>
+    <t>M4-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/37_0.png</t>
+  </si>
+  <si>
+    <t>M4R-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/464_0.png</t>
+  </si>
+  <si>
+    <t>M4S-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/19_0.png</t>
+  </si>
+  <si>
+    <t>M4SR-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/465_0.png</t>
+  </si>
+  <si>
+    <t>M5-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/39_0.png</t>
+  </si>
+  <si>
+    <t>M5-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/M5_w_0.png</t>
+  </si>
+  <si>
+    <t>M6L-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/41_0.png</t>
+  </si>
+  <si>
+    <t>M6L-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/40_0.png</t>
+  </si>
+  <si>
+    <t>M7L-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/42_0.png</t>
+  </si>
+  <si>
+    <t>M7L-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/360_0.png</t>
+  </si>
+  <si>
+    <t>M8L-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/440_0.png</t>
+  </si>
+  <si>
+    <t>MS75-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/500_0.png</t>
+  </si>
+  <si>
+    <t>MS80-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/499_0.png</t>
+  </si>
+  <si>
+    <t>N1L-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/12_0.png</t>
+  </si>
+  <si>
+    <t>N1L-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/364_0.png</t>
+  </si>
+  <si>
+    <t>N2L-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/45_0.png</t>
+  </si>
+  <si>
+    <t>N3L-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/164_0.png</t>
+  </si>
+  <si>
+    <t>N3LE-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/552_0.png</t>
+  </si>
+  <si>
+    <t>NN24-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/296_0.png</t>
+  </si>
+  <si>
+    <t>NN31-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/NN31_b_0.png</t>
+  </si>
+  <si>
+    <t>NP13-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/NP13_b_0.png</t>
+  </si>
+  <si>
+    <t>NP14-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/227_0.png</t>
+  </si>
+  <si>
+    <t>NP15-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/228_0.png</t>
+  </si>
+  <si>
+    <t>NP23-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/305_0.png</t>
+  </si>
+  <si>
+    <t>NP24-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/304_0.png</t>
+  </si>
+  <si>
+    <t>NP40-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/171_0.png</t>
+  </si>
+  <si>
+    <t>NP44-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/301_0.png</t>
+  </si>
+  <si>
+    <t>NP47-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/315_0.png</t>
+  </si>
+  <si>
+    <t>PRO7G-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/160_0.png</t>
+  </si>
+  <si>
+    <t>PRO7M-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/159_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/46_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/406_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/407_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/530_0.png</t>
+  </si>
+  <si>
+    <t>R1-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/458_0.png</t>
+  </si>
+  <si>
+    <t>R2-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/20_0.png</t>
+  </si>
+  <si>
+    <t>R3-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/21_0.png</t>
+  </si>
+  <si>
+    <t>R4-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/22_0.png</t>
+  </si>
+  <si>
+    <t>SM2-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/518_0.png</t>
+  </si>
+  <si>
+    <t>SM6-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/517_0.png</t>
+  </si>
+  <si>
+    <t>SM6-BW</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/561_0.png</t>
+  </si>
+  <si>
+    <t>SM6L-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/516_0.png</t>
+  </si>
+  <si>
+    <t>SN14-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/214_0.png</t>
+  </si>
+  <si>
+    <t>SN31-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/353_0.png</t>
+  </si>
+  <si>
+    <t>STE311-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/466_0.png</t>
+  </si>
+  <si>
+    <t>STE322-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/467_0.png</t>
+  </si>
+  <si>
+    <t>STE344-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/468_0.png</t>
+  </si>
+  <si>
+    <t>STE644-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/469_0.png</t>
+  </si>
+  <si>
+    <t>TM4-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/47_0.png</t>
+  </si>
+  <si>
+    <t>TM5-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/48_0.png</t>
+  </si>
+  <si>
+    <t>TM5-BW</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/611_0.png</t>
+  </si>
+  <si>
+    <t>TM5-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/363_0.png</t>
+  </si>
+  <si>
+    <t>TM6-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/49_0.png</t>
+  </si>
+  <si>
+    <t>TME-22B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/448_0.png</t>
+  </si>
+  <si>
+    <t>TME-44B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/450_0.png</t>
+  </si>
+  <si>
+    <t>TME-64B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/452_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/503_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/502_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/461_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/334_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/349_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/412_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/243_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/354_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/419_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/50_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/476_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/51_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/143_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/672_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/481_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/482_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/52_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/144_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/355_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/356_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/441_0.jpg</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/445_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/436_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/442_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/470_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/618_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/53_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/54_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/324_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/671_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/483_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/478_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/437_0.png</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/413_0.png</t>
+  </si>
+  <si>
+    <t>UF12-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/479_0.png</t>
+  </si>
+  <si>
+    <t>UF4-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/UF4_b_0.png</t>
+  </si>
+  <si>
+    <t>UT12-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/popup_images/443_0.png</t>
+  </si>
+  <si>
+    <t>UT4-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/80_0.png</t>
+  </si>
+  <si>
+    <t>D208FS-B-OLD</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/644_0.png</t>
+  </si>
+  <si>
+    <t>D221E-B-VP</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/645_0.png</t>
+  </si>
+  <si>
+    <t>D101E-B-VP</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/643_0.png</t>
+  </si>
+  <si>
+    <t>G160-B-OLD</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/641_0.png</t>
+  </si>
+  <si>
+    <t>G160-BW</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/676_0.png</t>
+  </si>
+  <si>
+    <t>G160-W-OLD</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/642_0.png</t>
+  </si>
+  <si>
+    <t>G220-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/715_0.png</t>
+  </si>
+  <si>
+    <t>G110-BW</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/657_0.png</t>
+  </si>
+  <si>
+    <t>G45-B V3</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/703_0.png</t>
+  </si>
+  <si>
+    <t>G45-B-OLD</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/668_0.png</t>
+  </si>
+  <si>
+    <t>G50-BW</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/656_0.png</t>
+  </si>
+  <si>
+    <t>G80-BW</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/679_0.png</t>
+  </si>
+  <si>
+    <t>G95-G</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/694_0.png</t>
+  </si>
+  <si>
+    <t>MW400-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/473_0.png</t>
+  </si>
+  <si>
+    <t>MW400-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/472_0.png</t>
+  </si>
+  <si>
+    <t>NWS-SC24</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/496_0.png</t>
+  </si>
+  <si>
+    <t>CM1-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/CM-1_B_0.png</t>
+  </si>
+  <si>
+    <t>CM1-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/CM-1_W_0.png</t>
+  </si>
+  <si>
+    <t>CM3-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/249_0.png</t>
+  </si>
+  <si>
+    <t>CM3-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/250_0.png</t>
+  </si>
+  <si>
+    <t>3390W1G005A</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/294_0.png</t>
+  </si>
+  <si>
+    <t>DE74-00027A</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/77_0.png</t>
+  </si>
+  <si>
+    <t>DE74-20102</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/78_0.png</t>
+  </si>
+  <si>
+    <t>ER245BD</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/295_0.png</t>
+  </si>
+  <si>
+    <t>KOR-610S</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/74_0.png</t>
+  </si>
+  <si>
+    <t>KOR-810S</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/DAE285_0.png</t>
+  </si>
+  <si>
+    <t>ADV1881-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/352_0.png</t>
+  </si>
+  <si>
+    <t>AMT1800-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/431_0.png</t>
+  </si>
+  <si>
+    <t>APP-1881-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/347_0.jpg</t>
+  </si>
+  <si>
+    <t>APS1881-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/418_0.png</t>
+  </si>
+  <si>
+    <t>APT-1551-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/350_0.png</t>
+  </si>
+  <si>
+    <t>APT-1881-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/351_0.png</t>
+  </si>
+  <si>
+    <t>ATL-1551-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/327_0.jpg</t>
+  </si>
+  <si>
+    <t>ATL-1881-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/292_0.png</t>
+  </si>
+  <si>
+    <t>AWL-75-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/332_0.png</t>
+  </si>
+  <si>
+    <t>AWL-75-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/333_0.png</t>
+  </si>
+  <si>
+    <t>A2G-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/290_0.png</t>
+  </si>
+  <si>
+    <t>A2N-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/471_0.jpg</t>
+  </si>
+  <si>
+    <t>A35-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/439_0.png</t>
+  </si>
+  <si>
+    <t>A3N-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/86_0.jpg</t>
+  </si>
+  <si>
+    <t>AAV-1-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/220_0.png</t>
+  </si>
+  <si>
+    <t>APM13T-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/434_0.png</t>
+  </si>
+  <si>
+    <t>ML-RC01</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/535_0.jpg</t>
+  </si>
+  <si>
+    <t>H1-G</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/556_0.jpg</t>
+  </si>
+  <si>
+    <t>H11-G</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/555_0.jpg</t>
+  </si>
+  <si>
+    <t>CDF222E-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/493_0.png</t>
+  </si>
+  <si>
+    <t>CDF222E-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/492_0.png</t>
+  </si>
+  <si>
+    <t>LMG30-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/455_0.png</t>
+  </si>
+  <si>
+    <t>LMG8-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/616_0.png</t>
+  </si>
+  <si>
+    <t>WDF221E-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/486_0.png</t>
+  </si>
+  <si>
+    <t>WDF221E-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/487_0.png</t>
+  </si>
+  <si>
+    <t>WDT221E-B</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/489_0.png</t>
+  </si>
+  <si>
+    <t>WDT221E-W</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/488_0.png</t>
+  </si>
+  <si>
+    <t>BPF32X1</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/446_0.png</t>
+  </si>
+  <si>
+    <t>CP1-2</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/511_0.png</t>
+  </si>
+  <si>
+    <t>CP3-4</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/505_0.png</t>
+  </si>
+  <si>
+    <t>CPH1-2Х3-4</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/512_0.png</t>
+  </si>
+  <si>
+    <t>CPH1-2Х3-8</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/513_0.png</t>
+  </si>
+  <si>
+    <t>FRT1-2</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/509_0.png</t>
+  </si>
+  <si>
+    <t>FSHS12Х1-2</t>
+  </si>
+  <si>
+    <t>GJSM1-2X3-4</t>
+  </si>
+  <si>
+    <t>https://shop.onkron.ru/images/product_images/thumbnail_images/508_0.png</t>
   </si>
 </sst>
 </file>
@@ -903,6 +1885,17 @@
     <tableColumn id="10" xr3:uid="{844FF9E0-D79C-4C59-B169-CB34BA723E23}" name="VESA category"/>
     <tableColumn id="11" xr3:uid="{9F8B31B3-F312-425E-89BF-123F5E4B613A}" name="максимальная суммарная нагрузка (с полками) кг"/>
     <tableColumn id="12" xr3:uid="{0F283AEA-EC94-4998-A426-87373DA19291}" name="описание" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{302B746E-BF0C-4161-ADAA-2CBEC0315F2D}" name="Таблица2" displayName="Таблица2" ref="A1:B204" totalsRowShown="0">
+  <autoFilter ref="A1:B204" xr:uid="{302B746E-BF0C-4161-ADAA-2CBEC0315F2D}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{8F01485B-76C2-443F-A37A-0C0236333F67}" name="SKU"/>
+    <tableColumn id="2" xr3:uid="{86E2293B-CA96-4AEA-B8AC-69E65ADA7FF6}" name="Image url"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1226,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1264,13 +2257,13 @@
     </row>
     <row r="2" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>278</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -1279,13 +2272,13 @@
         <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H2">
         <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -1294,27 +2287,27 @@
         <v>17</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>65</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3">
         <v>30</v>
@@ -1323,36 +2316,36 @@
         <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L3">
         <v>40</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>352</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F4">
         <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4">
         <v>30.5</v>
@@ -1361,27 +2354,27 @@
         <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L4">
         <v>32.5</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>279</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -1390,7 +2383,7 @@
         <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5">
         <v>35</v>
@@ -1399,24 +2392,24 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>281</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -1425,7 +2418,7 @@
         <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H6">
         <v>35</v>
@@ -1440,27 +2433,27 @@
         <v>17</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F7">
         <v>55</v>
       </c>
       <c r="G7" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H7">
         <v>35</v>
@@ -1478,18 +2471,18 @@
         <v>40</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>328</v>
+      </c>
+      <c r="B8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" t="s">
         <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
@@ -1498,7 +2491,7 @@
         <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8">
         <v>35</v>
@@ -1513,27 +2506,27 @@
         <v>17</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>329</v>
+      </c>
+      <c r="B9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
       </c>
       <c r="F9">
         <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9">
         <v>35</v>
@@ -1548,27 +2541,27 @@
         <v>17</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>330</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10">
         <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10">
         <v>35</v>
@@ -1583,18 +2576,18 @@
         <v>17</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>280</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1612,33 +2605,33 @@
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K11" t="s">
         <v>17</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>327</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F12">
         <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12">
         <v>40</v>
@@ -1656,21 +2649,21 @@
         <v>45</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>331</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F13">
         <v>70</v>
@@ -1685,33 +2678,33 @@
         <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="K13" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>357</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F14">
         <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H14">
         <v>41</v>
@@ -1729,27 +2722,27 @@
         <v>41</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>358</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F15">
         <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H15">
         <v>41</v>
@@ -1758,7 +2751,7 @@
         <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K15" t="s">
         <v>17</v>
@@ -1767,27 +2760,27 @@
         <v>41</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>332</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F16">
         <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16">
         <v>45</v>
@@ -1796,36 +2789,36 @@
         <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K16" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L16">
         <v>50</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="B17" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F17">
         <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H17">
         <v>45</v>
@@ -1834,30 +2827,30 @@
         <v>15</v>
       </c>
       <c r="J17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K17" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L17">
         <v>50</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>336</v>
       </c>
       <c r="B18" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F18">
         <v>75</v>
@@ -1872,30 +2865,30 @@
         <v>15</v>
       </c>
       <c r="J18" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L18">
         <v>50</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>335</v>
       </c>
       <c r="B19" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F19">
         <v>70</v>
@@ -1910,30 +2903,30 @@
         <v>15</v>
       </c>
       <c r="J19" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K19" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L19">
         <v>55.5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>337</v>
       </c>
       <c r="B20" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F20">
         <v>70</v>
@@ -1948,30 +2941,30 @@
         <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K20" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L20">
         <v>60.5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>338</v>
       </c>
       <c r="B21" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F21">
         <v>70</v>
@@ -1986,36 +2979,36 @@
         <v>15</v>
       </c>
       <c r="J21" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K21" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L21">
         <v>60.5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>353</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F22">
         <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H22">
         <v>45.5</v>
@@ -2024,30 +3017,30 @@
         <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="K22" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L22">
         <v>55.5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>340</v>
       </c>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F23">
         <v>75</v>
@@ -2062,30 +3055,30 @@
         <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L23">
         <v>60</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>339</v>
       </c>
       <c r="B24" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F24">
         <v>75</v>
@@ -2097,10 +3090,10 @@
         <v>65</v>
       </c>
       <c r="I24" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="J24" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K24" t="s">
         <v>17</v>
@@ -2109,91 +3102,91 @@
         <v>70</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>334</v>
       </c>
       <c r="B25" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="E25" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F25">
         <v>83</v>
       </c>
       <c r="G25" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H25">
         <v>65.5</v>
       </c>
       <c r="I25" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="J25" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K25" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L25">
         <v>70</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>341</v>
       </c>
       <c r="B26" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F26">
         <v>90</v>
       </c>
       <c r="G26" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H26">
         <v>75</v>
       </c>
       <c r="I26" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J26" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L26">
         <v>90</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -2211,7 +3204,7 @@
         <v>90</v>
       </c>
       <c r="I27" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J27" t="s">
         <v>16</v>
@@ -2225,528 +3218,528 @@
     </row>
     <row r="28" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>117</v>
+        <v>347</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F28">
         <v>90</v>
       </c>
       <c r="G28" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H28">
         <v>90</v>
       </c>
       <c r="I28" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J28" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>342</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="E29" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F29">
         <v>86</v>
       </c>
       <c r="G29" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H29">
         <v>90.9</v>
       </c>
       <c r="I29" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J29" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K29" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L29">
         <v>105.9</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>111</v>
+        <v>344</v>
       </c>
       <c r="B30" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F30">
         <v>65</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H30">
         <v>90.9</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J30" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K30" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L30">
         <v>105.9</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>345</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F31">
         <v>65</v>
       </c>
       <c r="G31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31">
         <v>90.9</v>
       </c>
       <c r="I31" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J31" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K31" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L31">
         <v>105.9</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F32">
         <v>86</v>
       </c>
       <c r="G32" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H32">
         <v>90.9</v>
       </c>
       <c r="I32" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J32" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K32" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L32">
         <v>105.9</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>343</v>
       </c>
       <c r="B33" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F33">
         <v>86</v>
       </c>
       <c r="G33" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H33">
         <v>90.9</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J33" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K33" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L33">
         <v>105.9</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>348</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F34">
         <v>100</v>
       </c>
       <c r="G34" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H34">
         <v>120</v>
       </c>
       <c r="I34" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J34" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="K34" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L34">
         <v>130</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>349</v>
       </c>
       <c r="B35" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F35">
         <v>100</v>
       </c>
       <c r="G35" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H35">
         <v>120</v>
       </c>
       <c r="I35" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J35" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="K35" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L35">
         <v>130</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F36">
         <v>120</v>
       </c>
       <c r="G36" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H36">
         <v>120</v>
       </c>
       <c r="I36" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J36" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="K36" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L36">
         <v>150</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E37" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F37">
         <v>120</v>
       </c>
       <c r="G37" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H37">
         <v>120</v>
       </c>
       <c r="I37" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J37" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K37" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L37">
         <v>125</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="E38" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F38">
         <v>110</v>
       </c>
       <c r="G38" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H38">
         <v>120.5</v>
       </c>
       <c r="I38" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J38" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="K38" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L38">
         <v>125</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>140</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F39">
         <v>110</v>
       </c>
       <c r="G39" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H39">
         <v>130</v>
       </c>
       <c r="I39" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J39" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="K39" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L39">
         <v>145</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>142</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>354</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F40">
         <v>100</v>
       </c>
       <c r="G40" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H40">
         <v>136.4</v>
       </c>
       <c r="I40" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J40" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="K40" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="B41" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E41" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F41">
         <v>55</v>
       </c>
       <c r="G41" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H41">
         <v>200</v>
       </c>
       <c r="I41" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J41" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K41" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2757,4 +3750,1653 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{674DE9AA-07F6-46A4-9D3E-77E413B393F7}">
+  <dimension ref="A1:B204"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>166</v>
+      </c>
+      <c r="B24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>170</v>
+      </c>
+      <c r="B26" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>178</v>
+      </c>
+      <c r="B30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>188</v>
+      </c>
+      <c r="B35" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>192</v>
+      </c>
+      <c r="B37" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>196</v>
+      </c>
+      <c r="B39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>198</v>
+      </c>
+      <c r="B40" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>200</v>
+      </c>
+      <c r="B41" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>206</v>
+      </c>
+      <c r="B44" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>210</v>
+      </c>
+      <c r="B46" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>212</v>
+      </c>
+      <c r="B47" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>216</v>
+      </c>
+      <c r="B49" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>218</v>
+      </c>
+      <c r="B50" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>222</v>
+      </c>
+      <c r="B52" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>224</v>
+      </c>
+      <c r="B53" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>226</v>
+      </c>
+      <c r="B54" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B55" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>230</v>
+      </c>
+      <c r="B56" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>232</v>
+      </c>
+      <c r="B57" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>234</v>
+      </c>
+      <c r="B58" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>236</v>
+      </c>
+      <c r="B59" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>238</v>
+      </c>
+      <c r="B60" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>240</v>
+      </c>
+      <c r="B61" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>242</v>
+      </c>
+      <c r="B62" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>244</v>
+      </c>
+      <c r="B63" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>246</v>
+      </c>
+      <c r="B64" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>248</v>
+      </c>
+      <c r="B65" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>250</v>
+      </c>
+      <c r="B66" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>252</v>
+      </c>
+      <c r="B67" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>254</v>
+      </c>
+      <c r="B68" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>256</v>
+      </c>
+      <c r="B69" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>258</v>
+      </c>
+      <c r="B70" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>260</v>
+      </c>
+      <c r="B71" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>262</v>
+      </c>
+      <c r="B72" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>264</v>
+      </c>
+      <c r="B73" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>266</v>
+      </c>
+      <c r="B74" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>268</v>
+      </c>
+      <c r="B75" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>270</v>
+      </c>
+      <c r="B76" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>272</v>
+      </c>
+      <c r="B77" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>274</v>
+      </c>
+      <c r="B78" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>276</v>
+      </c>
+      <c r="B79" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>111</v>
+      </c>
+      <c r="B80" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>113</v>
+      </c>
+      <c r="B81" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>116</v>
+      </c>
+      <c r="B82" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>118</v>
+      </c>
+      <c r="B83" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>282</v>
+      </c>
+      <c r="B84" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>284</v>
+      </c>
+      <c r="B85" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>286</v>
+      </c>
+      <c r="B86" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>288</v>
+      </c>
+      <c r="B87" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>290</v>
+      </c>
+      <c r="B88" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>292</v>
+      </c>
+      <c r="B89" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>294</v>
+      </c>
+      <c r="B90" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>296</v>
+      </c>
+      <c r="B91" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>298</v>
+      </c>
+      <c r="B92" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>300</v>
+      </c>
+      <c r="B93" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>302</v>
+      </c>
+      <c r="B94" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>304</v>
+      </c>
+      <c r="B95" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>306</v>
+      </c>
+      <c r="B96" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>308</v>
+      </c>
+      <c r="B97" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>310</v>
+      </c>
+      <c r="B98" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>312</v>
+      </c>
+      <c r="B99" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>314</v>
+      </c>
+      <c r="B100" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>316</v>
+      </c>
+      <c r="B101" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>318</v>
+      </c>
+      <c r="B102" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>320</v>
+      </c>
+      <c r="B103" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>322</v>
+      </c>
+      <c r="B104" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>324</v>
+      </c>
+      <c r="B105" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>57</v>
+      </c>
+      <c r="B106" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>60</v>
+      </c>
+      <c r="B107" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>19</v>
+      </c>
+      <c r="B108" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>22</v>
+      </c>
+      <c r="B109" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>25</v>
+      </c>
+      <c r="B110" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>62</v>
+      </c>
+      <c r="B111" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>66</v>
+      </c>
+      <c r="B112" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>68</v>
+      </c>
+      <c r="B113" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>69</v>
+      </c>
+      <c r="B114" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>72</v>
+      </c>
+      <c r="B115" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>74</v>
+      </c>
+      <c r="B116" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>76</v>
+      </c>
+      <c r="B117" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>78</v>
+      </c>
+      <c r="B118" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>35</v>
+      </c>
+      <c r="B119" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>79</v>
+      </c>
+      <c r="B120" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>81</v>
+      </c>
+      <c r="B121" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>84</v>
+      </c>
+      <c r="B122" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>86</v>
+      </c>
+      <c r="B123" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>87</v>
+      </c>
+      <c r="B124" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>89</v>
+      </c>
+      <c r="B125" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>39</v>
+      </c>
+      <c r="B126" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>91</v>
+      </c>
+      <c r="B127" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>93</v>
+      </c>
+      <c r="B128" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>45</v>
+      </c>
+      <c r="B129" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>95</v>
+      </c>
+      <c r="B130" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>97</v>
+      </c>
+      <c r="B131" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>100</v>
+      </c>
+      <c r="B132" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>102</v>
+      </c>
+      <c r="B133" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>105</v>
+      </c>
+      <c r="B134" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>50</v>
+      </c>
+      <c r="B135" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>107</v>
+      </c>
+      <c r="B136" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>26</v>
+      </c>
+      <c r="B137" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>28</v>
+      </c>
+      <c r="B138" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>31</v>
+      </c>
+      <c r="B139" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>360</v>
+      </c>
+      <c r="B140" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>362</v>
+      </c>
+      <c r="B141" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>364</v>
+      </c>
+      <c r="B142" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>366</v>
+      </c>
+      <c r="B143" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>368</v>
+      </c>
+      <c r="B144" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>370</v>
+      </c>
+      <c r="B145" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>372</v>
+      </c>
+      <c r="B146" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>374</v>
+      </c>
+      <c r="B147" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>376</v>
+      </c>
+      <c r="B148" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>378</v>
+      </c>
+      <c r="B149" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>380</v>
+      </c>
+      <c r="B150" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>382</v>
+      </c>
+      <c r="B151" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>384</v>
+      </c>
+      <c r="B152" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>386</v>
+      </c>
+      <c r="B153" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>388</v>
+      </c>
+      <c r="B154" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>390</v>
+      </c>
+      <c r="B155" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>392</v>
+      </c>
+      <c r="B156" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>394</v>
+      </c>
+      <c r="B157" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>396</v>
+      </c>
+      <c r="B158" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>398</v>
+      </c>
+      <c r="B159" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>400</v>
+      </c>
+      <c r="B160" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>402</v>
+      </c>
+      <c r="B161" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>404</v>
+      </c>
+      <c r="B162" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>406</v>
+      </c>
+      <c r="B163" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>408</v>
+      </c>
+      <c r="B164" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>410</v>
+      </c>
+      <c r="B165" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>412</v>
+      </c>
+      <c r="B166" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>414</v>
+      </c>
+      <c r="B167" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>416</v>
+      </c>
+      <c r="B168" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>418</v>
+      </c>
+      <c r="B169" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>420</v>
+      </c>
+      <c r="B170" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>422</v>
+      </c>
+      <c r="B171" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>424</v>
+      </c>
+      <c r="B172" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>426</v>
+      </c>
+      <c r="B173" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>428</v>
+      </c>
+      <c r="B174" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>430</v>
+      </c>
+      <c r="B175" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>432</v>
+      </c>
+      <c r="B176" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>434</v>
+      </c>
+      <c r="B177" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>436</v>
+      </c>
+      <c r="B178" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>438</v>
+      </c>
+      <c r="B179" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>440</v>
+      </c>
+      <c r="B180" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>442</v>
+      </c>
+      <c r="B181" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>444</v>
+      </c>
+      <c r="B182" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>446</v>
+      </c>
+      <c r="B183" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>448</v>
+      </c>
+      <c r="B184" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>450</v>
+      </c>
+      <c r="B185" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>452</v>
+      </c>
+      <c r="B186" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>454</v>
+      </c>
+      <c r="B187" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>456</v>
+      </c>
+      <c r="B188" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>458</v>
+      </c>
+      <c r="B189" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>460</v>
+      </c>
+      <c r="B190" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>462</v>
+      </c>
+      <c r="B191" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>464</v>
+      </c>
+      <c r="B192" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>466</v>
+      </c>
+      <c r="B193" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>468</v>
+      </c>
+      <c r="B194" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>470</v>
+      </c>
+      <c r="B195" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>472</v>
+      </c>
+      <c r="B196" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>474</v>
+      </c>
+      <c r="B197" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>476</v>
+      </c>
+      <c r="B198" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>478</v>
+      </c>
+      <c r="B199" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>480</v>
+      </c>
+      <c r="B200" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>482</v>
+      </c>
+      <c r="B201" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>484</v>
+      </c>
+      <c r="B202" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>486</v>
+      </c>
+      <c r="B203" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>487</v>
+      </c>
+      <c r="B204" t="s">
+        <v>488</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4D231C-75DA-40BA-9737-D1E4367BDE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F65927-6BCD-4B8E-A1E5-0C3062A41522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="490">
   <si>
     <t>image_url</t>
   </si>
@@ -1796,6 +1796,9 @@
   </si>
   <si>
     <t>https://shop.onkron.ru/images/product_images/thumbnail_images/508_0.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRO </t>
   </si>
 </sst>
 </file>
@@ -1869,7 +1872,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M41" totalsRowShown="0">
   <autoFilter ref="A1:M41" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M41">
-    <sortCondition ref="H1:H41"/>
+    <sortCondition ref="C1:C41"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
@@ -2257,63 +2260,63 @@
     </row>
     <row r="2" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>278</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
         <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>489</v>
       </c>
       <c r="F2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
         <v>17</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>112</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>359</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s">
         <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>489</v>
       </c>
       <c r="F3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="H3">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -2321,49 +2324,43 @@
       <c r="K3" t="s">
         <v>33</v>
       </c>
-      <c r="L3">
-        <v>40</v>
-      </c>
       <c r="M3" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>352</v>
+        <v>278</v>
       </c>
       <c r="B4" t="s">
         <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="H4">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4">
-        <v>32.5</v>
+        <v>17</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2403,51 +2400,51 @@
     </row>
     <row r="6" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B6" t="s">
         <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
       </c>
       <c r="F6">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G6" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>281</v>
       </c>
       <c r="B7" t="s">
         <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>55</v>
@@ -2467,31 +2464,28 @@
       <c r="K7" t="s">
         <v>17</v>
       </c>
-      <c r="L7">
-        <v>40</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B8" t="s">
         <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F8">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="H8">
         <v>35</v>
@@ -2505,31 +2499,34 @@
       <c r="K8" t="s">
         <v>17</v>
       </c>
+      <c r="L8">
+        <v>40</v>
+      </c>
       <c r="M8" s="1" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B9" t="s">
         <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
         <v>20</v>
       </c>
       <c r="H9">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
@@ -2540,19 +2537,22 @@
       <c r="K9" t="s">
         <v>17</v>
       </c>
+      <c r="L9">
+        <v>45</v>
+      </c>
       <c r="M9" s="1" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B10" t="s">
         <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
@@ -2576,65 +2576,65 @@
         <v>17</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>329</v>
       </c>
       <c r="B11" t="s">
         <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H11">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K11" t="s">
         <v>17</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>117</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
         <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
@@ -2645,11 +2645,8 @@
       <c r="K12" t="s">
         <v>17</v>
       </c>
-      <c r="L12">
-        <v>45</v>
-      </c>
       <c r="M12" s="1" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2689,139 +2686,139 @@
     </row>
     <row r="14" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="B14" t="s">
         <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
         <v>20</v>
       </c>
       <c r="H14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K14" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="L14">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="B15" t="s">
         <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="L15">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B16" t="s">
         <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F16">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H16">
-        <v>45</v>
+        <v>65.5</v>
       </c>
       <c r="I16" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="J16" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L16">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B17" t="s">
         <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>58</v>
       </c>
       <c r="F17">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H17">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
@@ -2833,10 +2830,10 @@
         <v>33</v>
       </c>
       <c r="L17">
-        <v>50</v>
+        <v>55.5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2879,13 +2876,13 @@
     </row>
     <row r="19" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B19" t="s">
         <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
@@ -2909,48 +2906,48 @@
         <v>33</v>
       </c>
       <c r="L19">
-        <v>55.5</v>
+        <v>60.5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B20" t="s">
         <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F20">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
         <v>14</v>
       </c>
       <c r="H20">
-        <v>45.5</v>
+        <v>65</v>
       </c>
       <c r="I20" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="J20" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L20">
-        <v>60.5</v>
+        <v>70</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2993,557 +2990,560 @@
     </row>
     <row r="22" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="B22" t="s">
         <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F22">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H22">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="K22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L22">
-        <v>55.5</v>
+        <v>60</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B23" t="s">
         <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
         <v>58</v>
       </c>
       <c r="F23">
+        <v>90</v>
+      </c>
+      <c r="G23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23">
         <v>75</v>
       </c>
-      <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23">
-        <v>50</v>
-      </c>
       <c r="I23" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="J23" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L23">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B24" t="s">
         <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F24">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H24">
-        <v>65</v>
+        <v>90.9</v>
       </c>
       <c r="I24" t="s">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="J24" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K24" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L24">
-        <v>70</v>
+        <v>105.9</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B25" t="s">
         <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F25">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G25" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H25">
-        <v>65.5</v>
+        <v>90.9</v>
       </c>
       <c r="I25" t="s">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="J25" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="K25" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L25">
-        <v>70</v>
+        <v>105.9</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B26" t="s">
         <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
       </c>
       <c r="F26">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="G26" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H26">
-        <v>75</v>
+        <v>90.9</v>
       </c>
       <c r="I26" t="s">
         <v>41</v>
       </c>
       <c r="J26" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="K26" t="s">
         <v>43</v>
       </c>
       <c r="L26">
+        <v>105.9</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>161</v>
+        <v>346</v>
       </c>
       <c r="B27" t="s">
         <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F27">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H27">
-        <v>90</v>
+        <v>90.9</v>
       </c>
       <c r="I27" t="s">
         <v>41</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="K27" t="s">
-        <v>17</v>
+        <v>43</v>
+      </c>
+      <c r="L27">
+        <v>105.9</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B28" t="s">
         <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
         <v>58</v>
       </c>
       <c r="F28">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s">
         <v>40</v>
       </c>
       <c r="H28">
-        <v>90</v>
+        <v>90.9</v>
       </c>
       <c r="I28" t="s">
         <v>41</v>
       </c>
       <c r="J28" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="K28" t="s">
         <v>43</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>105.9</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B29" t="s">
         <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
         <v>58</v>
       </c>
       <c r="F29">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
         <v>40</v>
       </c>
       <c r="H29">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s">
         <v>41</v>
       </c>
       <c r="J29" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s">
         <v>43</v>
       </c>
       <c r="L29">
-        <v>105.9</v>
+        <v>100</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B30" t="s">
         <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s">
         <v>58</v>
       </c>
       <c r="F30">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="G30" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H30">
-        <v>90.9</v>
+        <v>120</v>
       </c>
       <c r="I30" t="s">
         <v>41</v>
       </c>
       <c r="J30" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K30" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L30">
-        <v>105.9</v>
+        <v>130</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B31" t="s">
         <v>110</v>
       </c>
       <c r="C31" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F31">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="G31" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H31">
-        <v>90.9</v>
+        <v>120</v>
       </c>
       <c r="I31" t="s">
         <v>41</v>
       </c>
       <c r="J31" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K31" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L31">
-        <v>105.9</v>
+        <v>130</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B32" t="s">
         <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F32">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="G32" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="H32">
-        <v>90.9</v>
+        <v>120</v>
       </c>
       <c r="I32" t="s">
         <v>41</v>
       </c>
       <c r="J32" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K32" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L32">
-        <v>105.9</v>
+        <v>150</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B33" t="s">
         <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E33" t="s">
         <v>58</v>
       </c>
       <c r="F33">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="G33" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="H33">
-        <v>90.9</v>
+        <v>120.5</v>
       </c>
       <c r="I33" t="s">
         <v>41</v>
       </c>
       <c r="J33" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="K33" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L33">
-        <v>105.9</v>
+        <v>125</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B34" t="s">
         <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F34">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G34" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H34">
-        <v>120</v>
+        <v>30.5</v>
       </c>
       <c r="I34" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="J34" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="K34" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="L34">
-        <v>130</v>
+        <v>32.5</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B35" t="s">
         <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F35">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s">
         <v>40</v>
       </c>
       <c r="H35">
-        <v>120</v>
+        <v>45.5</v>
       </c>
       <c r="I35" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="J35" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="K35" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="L35">
-        <v>130</v>
+        <v>55.5</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B36" t="s">
         <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E36" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G36" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H36">
-        <v>120</v>
+        <v>136.4</v>
       </c>
       <c r="I36" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J36" t="s">
         <v>47</v>
@@ -3551,11 +3551,8 @@
       <c r="K36" t="s">
         <v>48</v>
       </c>
-      <c r="L36">
-        <v>150</v>
-      </c>
       <c r="M36" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3598,13 +3595,13 @@
     </row>
     <row r="38" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s">
         <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E38" t="s">
         <v>58</v>
@@ -3616,121 +3613,124 @@
         <v>51</v>
       </c>
       <c r="H38">
-        <v>120.5</v>
+        <v>130</v>
       </c>
       <c r="I38" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J38" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="K38" t="s">
         <v>48</v>
       </c>
       <c r="L38">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s">
         <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E39" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F39">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="G39" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H39">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="I39" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="J39" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="L39">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s">
         <v>110</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="E40" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F40">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G40" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H40">
-        <v>136.4</v>
+        <v>41</v>
       </c>
       <c r="I40" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="J40" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="K40" t="s">
-        <v>48</v>
+        <v>17</v>
+      </c>
+      <c r="L40">
+        <v>41</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>123</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s">
         <v>110</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="E41" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F41">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G41" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H41">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="I41" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="J41" t="s">
         <v>32</v>
@@ -3738,8 +3738,11 @@
       <c r="K41" t="s">
         <v>33</v>
       </c>
+      <c r="L41">
+        <v>40</v>
+      </c>
       <c r="M41" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F65927-6BCD-4B8E-A1E5-0C3062A41522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B814A07A-897D-427B-A3BD-8414226C475B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="489">
   <si>
     <t>image_url</t>
   </si>
@@ -1796,9 +1796,6 @@
   </si>
   <si>
     <t>https://shop.onkron.ru/images/product_images/thumbnail_images/508_0.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRO </t>
   </si>
 </sst>
 </file>
@@ -2269,7 +2266,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>489</v>
+        <v>63</v>
       </c>
       <c r="F2">
         <v>70</v>
@@ -2304,7 +2301,7 @@
         <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>489</v>
+        <v>63</v>
       </c>
       <c r="F3">
         <v>55</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B814A07A-897D-427B-A3BD-8414226C475B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE9728C-8035-4AF9-9A82-2936308BD57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="490">
   <si>
     <t>image_url</t>
   </si>
@@ -336,9 +336,6 @@
     <t>TS1350-B</t>
   </si>
   <si>
-    <t>professional | touch panel</t>
-  </si>
-  <si>
     <t>860x600</t>
   </si>
   <si>
@@ -1796,6 +1793,12 @@
   </si>
   <si>
     <t>https://shop.onkron.ru/images/product_images/thumbnail_images/508_0.png</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>touch panel</t>
   </si>
 </sst>
 </file>
@@ -2203,7 +2206,7 @@
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" customWidth="1"/>
     <col min="6" max="6" width="26.140625" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" customWidth="1"/>
     <col min="8" max="8" width="26.7109375" customWidth="1"/>
@@ -2219,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -2257,16 +2260,16 @@
     </row>
     <row r="2" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>488</v>
       </c>
       <c r="F2">
         <v>70</v>
@@ -2292,16 +2295,16 @@
     </row>
     <row r="3" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
         <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>488</v>
       </c>
       <c r="F3">
         <v>55</v>
@@ -2327,13 +2330,13 @@
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
         <v>110</v>
-      </c>
-      <c r="C4" t="s">
-        <v>111</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
@@ -2348,7 +2351,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -2357,18 +2360,18 @@
         <v>17</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -2386,24 +2389,24 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -2427,18 +2430,18 @@
         <v>17</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -2462,15 +2465,15 @@
         <v>17</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
         <v>57</v>
@@ -2505,10 +2508,10 @@
     </row>
     <row r="9" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
         <v>60</v>
@@ -2543,10 +2546,10 @@
     </row>
     <row r="10" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -2578,10 +2581,10 @@
     </row>
     <row r="11" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
@@ -2613,10 +2616,10 @@
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
         <v>25</v>
@@ -2648,16 +2651,16 @@
     </row>
     <row r="13" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
         <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>489</v>
       </c>
       <c r="F13">
         <v>70</v>
@@ -2672,24 +2675,24 @@
         <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K13" t="s">
         <v>43</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>58</v>
@@ -2716,18 +2719,18 @@
         <v>50</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
         <v>58</v>
@@ -2754,21 +2757,21 @@
         <v>50</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>489</v>
       </c>
       <c r="F16">
         <v>83</v>
@@ -2780,10 +2783,10 @@
         <v>65.5</v>
       </c>
       <c r="I16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K16" t="s">
         <v>48</v>
@@ -2792,18 +2795,18 @@
         <v>70</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>58</v>
@@ -2830,18 +2833,18 @@
         <v>55.5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
         <v>58</v>
@@ -2868,18 +2871,18 @@
         <v>50</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
@@ -2906,15 +2909,15 @@
         <v>60.5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
         <v>35</v>
@@ -2932,7 +2935,7 @@
         <v>65</v>
       </c>
       <c r="I20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J20" t="s">
         <v>37</v>
@@ -2949,13 +2952,13 @@
     </row>
     <row r="21" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
         <v>58</v>
@@ -2982,18 +2985,18 @@
         <v>60.5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
         <v>58</v>
@@ -3020,18 +3023,18 @@
         <v>60</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>58</v>
@@ -3049,7 +3052,7 @@
         <v>41</v>
       </c>
       <c r="J23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K23" t="s">
         <v>43</v>
@@ -3058,18 +3061,18 @@
         <v>90</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
         <v>58</v>
@@ -3096,18 +3099,18 @@
         <v>105.9</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
         <v>58</v>
@@ -3134,18 +3137,18 @@
         <v>105.9</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
@@ -3172,15 +3175,15 @@
         <v>105.9</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
         <v>39</v>
@@ -3215,13 +3218,13 @@
     </row>
     <row r="28" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
         <v>58</v>
@@ -3248,18 +3251,18 @@
         <v>105.9</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E29" t="s">
         <v>58</v>
@@ -3277,7 +3280,7 @@
         <v>41</v>
       </c>
       <c r="J29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K29" t="s">
         <v>43</v>
@@ -3286,18 +3289,18 @@
         <v>100</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
         <v>58</v>
@@ -3324,15 +3327,15 @@
         <v>130</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
         <v>45</v>
@@ -3367,13 +3370,13 @@
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E32" t="s">
         <v>58</v>
@@ -3400,18 +3403,18 @@
         <v>150</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s">
         <v>58</v>
@@ -3429,7 +3432,7 @@
         <v>41</v>
       </c>
       <c r="J33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K33" t="s">
         <v>48</v>
@@ -3438,18 +3441,18 @@
         <v>125</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
         <v>54</v>
@@ -3476,18 +3479,18 @@
         <v>32.5</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E35" t="s">
         <v>54</v>
@@ -3505,7 +3508,7 @@
         <v>15</v>
       </c>
       <c r="J35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K35" t="s">
         <v>32</v>
@@ -3514,18 +3517,18 @@
         <v>55.5</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E36" t="s">
         <v>54</v>
@@ -3549,15 +3552,15 @@
         <v>48</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
         <v>50</v>
@@ -3592,13 +3595,13 @@
     </row>
     <row r="38" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E38" t="s">
         <v>58</v>
@@ -3625,15 +3628,15 @@
         <v>145</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
         <v>26</v>
@@ -3668,10 +3671,10 @@
     </row>
     <row r="40" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
@@ -3706,10 +3709,10 @@
     </row>
     <row r="41" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
         <v>31</v>
@@ -3762,154 +3765,154 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" t="s">
         <v>124</v>
-      </c>
-      <c r="B1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" t="s">
         <v>126</v>
-      </c>
-      <c r="B2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" t="s">
         <v>128</v>
-      </c>
-      <c r="B3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" t="s">
         <v>130</v>
-      </c>
-      <c r="B4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
         <v>132</v>
-      </c>
-      <c r="B5" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" t="s">
         <v>134</v>
-      </c>
-      <c r="B6" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" t="s">
         <v>136</v>
-      </c>
-      <c r="B7" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" t="s">
         <v>138</v>
-      </c>
-      <c r="B8" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9" t="s">
         <v>140</v>
-      </c>
-      <c r="B9" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" t="s">
         <v>142</v>
-      </c>
-      <c r="B10" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" t="s">
         <v>144</v>
-      </c>
-      <c r="B11" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" t="s">
         <v>146</v>
-      </c>
-      <c r="B12" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" t="s">
         <v>148</v>
-      </c>
-      <c r="B13" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" t="s">
         <v>150</v>
-      </c>
-      <c r="B14" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" t="s">
         <v>152</v>
-      </c>
-      <c r="B15" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" t="s">
         <v>154</v>
-      </c>
-      <c r="B16" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" t="s">
         <v>156</v>
-      </c>
-      <c r="B17" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" t="s">
         <v>158</v>
-      </c>
-      <c r="B18" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3917,7 +3920,7 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3925,679 +3928,679 @@
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" t="s">
         <v>162</v>
-      </c>
-      <c r="B22" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" t="s">
         <v>164</v>
-      </c>
-      <c r="B23" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" t="s">
         <v>166</v>
-      </c>
-      <c r="B24" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" t="s">
         <v>168</v>
-      </c>
-      <c r="B25" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" t="s">
         <v>170</v>
-      </c>
-      <c r="B26" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" t="s">
         <v>172</v>
-      </c>
-      <c r="B27" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B28" t="s">
         <v>174</v>
-      </c>
-      <c r="B28" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>175</v>
+      </c>
+      <c r="B29" t="s">
         <v>176</v>
-      </c>
-      <c r="B29" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>177</v>
+      </c>
+      <c r="B30" t="s">
         <v>178</v>
-      </c>
-      <c r="B30" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31" t="s">
         <v>180</v>
-      </c>
-      <c r="B31" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32" t="s">
         <v>182</v>
-      </c>
-      <c r="B32" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>183</v>
+      </c>
+      <c r="B33" t="s">
         <v>184</v>
-      </c>
-      <c r="B33" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" t="s">
         <v>186</v>
-      </c>
-      <c r="B34" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>187</v>
+      </c>
+      <c r="B35" t="s">
         <v>188</v>
-      </c>
-      <c r="B35" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>189</v>
+      </c>
+      <c r="B36" t="s">
         <v>190</v>
-      </c>
-      <c r="B36" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>191</v>
+      </c>
+      <c r="B37" t="s">
         <v>192</v>
-      </c>
-      <c r="B37" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>193</v>
+      </c>
+      <c r="B38" t="s">
         <v>194</v>
-      </c>
-      <c r="B38" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" t="s">
         <v>196</v>
-      </c>
-      <c r="B39" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>197</v>
+      </c>
+      <c r="B40" t="s">
         <v>198</v>
-      </c>
-      <c r="B40" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>199</v>
+      </c>
+      <c r="B41" t="s">
         <v>200</v>
-      </c>
-      <c r="B41" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>201</v>
+      </c>
+      <c r="B42" t="s">
         <v>202</v>
-      </c>
-      <c r="B42" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>203</v>
+      </c>
+      <c r="B43" t="s">
         <v>204</v>
-      </c>
-      <c r="B43" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>205</v>
+      </c>
+      <c r="B44" t="s">
         <v>206</v>
-      </c>
-      <c r="B44" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45" t="s">
         <v>208</v>
-      </c>
-      <c r="B45" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>209</v>
+      </c>
+      <c r="B46" t="s">
         <v>210</v>
-      </c>
-      <c r="B46" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>211</v>
+      </c>
+      <c r="B47" t="s">
         <v>212</v>
-      </c>
-      <c r="B47" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>213</v>
+      </c>
+      <c r="B48" t="s">
         <v>214</v>
-      </c>
-      <c r="B48" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>215</v>
+      </c>
+      <c r="B49" t="s">
         <v>216</v>
-      </c>
-      <c r="B49" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>217</v>
+      </c>
+      <c r="B50" t="s">
         <v>218</v>
-      </c>
-      <c r="B50" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>219</v>
+      </c>
+      <c r="B51" t="s">
         <v>220</v>
-      </c>
-      <c r="B51" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>221</v>
+      </c>
+      <c r="B52" t="s">
         <v>222</v>
-      </c>
-      <c r="B52" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>223</v>
+      </c>
+      <c r="B53" t="s">
         <v>224</v>
-      </c>
-      <c r="B53" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>225</v>
+      </c>
+      <c r="B54" t="s">
         <v>226</v>
-      </c>
-      <c r="B54" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>227</v>
+      </c>
+      <c r="B55" t="s">
         <v>228</v>
-      </c>
-      <c r="B55" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>229</v>
+      </c>
+      <c r="B56" t="s">
         <v>230</v>
-      </c>
-      <c r="B56" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>231</v>
+      </c>
+      <c r="B57" t="s">
         <v>232</v>
-      </c>
-      <c r="B57" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>233</v>
+      </c>
+      <c r="B58" t="s">
         <v>234</v>
-      </c>
-      <c r="B58" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>235</v>
+      </c>
+      <c r="B59" t="s">
         <v>236</v>
-      </c>
-      <c r="B59" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>237</v>
+      </c>
+      <c r="B60" t="s">
         <v>238</v>
-      </c>
-      <c r="B60" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>239</v>
+      </c>
+      <c r="B61" t="s">
         <v>240</v>
-      </c>
-      <c r="B61" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>241</v>
+      </c>
+      <c r="B62" t="s">
         <v>242</v>
-      </c>
-      <c r="B62" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>243</v>
+      </c>
+      <c r="B63" t="s">
         <v>244</v>
-      </c>
-      <c r="B63" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>245</v>
+      </c>
+      <c r="B64" t="s">
         <v>246</v>
-      </c>
-      <c r="B64" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>247</v>
+      </c>
+      <c r="B65" t="s">
         <v>248</v>
-      </c>
-      <c r="B65" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>249</v>
+      </c>
+      <c r="B66" t="s">
         <v>250</v>
-      </c>
-      <c r="B66" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>251</v>
+      </c>
+      <c r="B67" t="s">
         <v>252</v>
-      </c>
-      <c r="B67" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>253</v>
+      </c>
+      <c r="B68" t="s">
         <v>254</v>
-      </c>
-      <c r="B68" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>255</v>
+      </c>
+      <c r="B69" t="s">
         <v>256</v>
-      </c>
-      <c r="B69" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>257</v>
+      </c>
+      <c r="B70" t="s">
         <v>258</v>
-      </c>
-      <c r="B70" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>259</v>
+      </c>
+      <c r="B71" t="s">
         <v>260</v>
-      </c>
-      <c r="B71" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>261</v>
+      </c>
+      <c r="B72" t="s">
         <v>262</v>
-      </c>
-      <c r="B72" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>263</v>
+      </c>
+      <c r="B73" t="s">
         <v>264</v>
-      </c>
-      <c r="B73" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>265</v>
+      </c>
+      <c r="B74" t="s">
         <v>266</v>
-      </c>
-      <c r="B74" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>267</v>
+      </c>
+      <c r="B75" t="s">
         <v>268</v>
-      </c>
-      <c r="B75" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>269</v>
+      </c>
+      <c r="B76" t="s">
         <v>270</v>
-      </c>
-      <c r="B76" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>271</v>
+      </c>
+      <c r="B77" t="s">
         <v>272</v>
-      </c>
-      <c r="B77" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>273</v>
+      </c>
+      <c r="B78" t="s">
         <v>274</v>
-      </c>
-      <c r="B78" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>275</v>
+      </c>
+      <c r="B79" t="s">
         <v>276</v>
-      </c>
-      <c r="B79" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B80" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B82" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B83" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>281</v>
+      </c>
+      <c r="B84" t="s">
         <v>282</v>
-      </c>
-      <c r="B84" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>283</v>
+      </c>
+      <c r="B85" t="s">
         <v>284</v>
-      </c>
-      <c r="B85" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>285</v>
+      </c>
+      <c r="B86" t="s">
         <v>286</v>
-      </c>
-      <c r="B86" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>287</v>
+      </c>
+      <c r="B87" t="s">
         <v>288</v>
-      </c>
-      <c r="B87" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>289</v>
+      </c>
+      <c r="B88" t="s">
         <v>290</v>
-      </c>
-      <c r="B88" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>291</v>
+      </c>
+      <c r="B89" t="s">
         <v>292</v>
-      </c>
-      <c r="B89" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>293</v>
+      </c>
+      <c r="B90" t="s">
         <v>294</v>
-      </c>
-      <c r="B90" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>295</v>
+      </c>
+      <c r="B91" t="s">
         <v>296</v>
-      </c>
-      <c r="B91" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>297</v>
+      </c>
+      <c r="B92" t="s">
         <v>298</v>
-      </c>
-      <c r="B92" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>299</v>
+      </c>
+      <c r="B93" t="s">
         <v>300</v>
-      </c>
-      <c r="B93" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>301</v>
+      </c>
+      <c r="B94" t="s">
         <v>302</v>
-      </c>
-      <c r="B94" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>303</v>
+      </c>
+      <c r="B95" t="s">
         <v>304</v>
-      </c>
-      <c r="B95" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>305</v>
+      </c>
+      <c r="B96" t="s">
         <v>306</v>
-      </c>
-      <c r="B96" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>307</v>
+      </c>
+      <c r="B97" t="s">
         <v>308</v>
-      </c>
-      <c r="B97" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>309</v>
+      </c>
+      <c r="B98" t="s">
         <v>310</v>
-      </c>
-      <c r="B98" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>311</v>
+      </c>
+      <c r="B99" t="s">
         <v>312</v>
-      </c>
-      <c r="B99" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>313</v>
+      </c>
+      <c r="B100" t="s">
         <v>314</v>
-      </c>
-      <c r="B100" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>315</v>
+      </c>
+      <c r="B101" t="s">
         <v>316</v>
-      </c>
-      <c r="B101" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>317</v>
+      </c>
+      <c r="B102" t="s">
         <v>318</v>
-      </c>
-      <c r="B102" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>319</v>
+      </c>
+      <c r="B103" t="s">
         <v>320</v>
-      </c>
-      <c r="B103" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>321</v>
+      </c>
+      <c r="B104" t="s">
         <v>322</v>
-      </c>
-      <c r="B104" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>323</v>
+      </c>
+      <c r="B105" t="s">
         <v>324</v>
-      </c>
-      <c r="B105" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -4605,7 +4608,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -4613,7 +4616,7 @@
         <v>60</v>
       </c>
       <c r="B107" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -4621,7 +4624,7 @@
         <v>19</v>
       </c>
       <c r="B108" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -4629,7 +4632,7 @@
         <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -4637,7 +4640,7 @@
         <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -4645,63 +4648,63 @@
         <v>62</v>
       </c>
       <c r="B111" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B112" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B113" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B114" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B115" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B116" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B117" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B118" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -4709,55 +4712,55 @@
         <v>35</v>
       </c>
       <c r="B119" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B120" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B121" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B122" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B123" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B124" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B125" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -4765,23 +4768,23 @@
         <v>39</v>
       </c>
       <c r="B126" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B127" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B128" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -4789,47 +4792,47 @@
         <v>45</v>
       </c>
       <c r="B129" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B130" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B131" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B132" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B133" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B134" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -4837,15 +4840,15 @@
         <v>50</v>
       </c>
       <c r="B135" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B136" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -4853,7 +4856,7 @@
         <v>26</v>
       </c>
       <c r="B137" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -4861,7 +4864,7 @@
         <v>28</v>
       </c>
       <c r="B138" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -4869,527 +4872,527 @@
         <v>31</v>
       </c>
       <c r="B139" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>359</v>
+      </c>
+      <c r="B140" t="s">
         <v>360</v>
-      </c>
-      <c r="B140" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>361</v>
+      </c>
+      <c r="B141" t="s">
         <v>362</v>
-      </c>
-      <c r="B141" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>363</v>
+      </c>
+      <c r="B142" t="s">
         <v>364</v>
-      </c>
-      <c r="B142" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>365</v>
+      </c>
+      <c r="B143" t="s">
         <v>366</v>
-      </c>
-      <c r="B143" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>367</v>
+      </c>
+      <c r="B144" t="s">
         <v>368</v>
-      </c>
-      <c r="B144" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>369</v>
+      </c>
+      <c r="B145" t="s">
         <v>370</v>
-      </c>
-      <c r="B145" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>371</v>
+      </c>
+      <c r="B146" t="s">
         <v>372</v>
-      </c>
-      <c r="B146" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>373</v>
+      </c>
+      <c r="B147" t="s">
         <v>374</v>
-      </c>
-      <c r="B147" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>375</v>
+      </c>
+      <c r="B148" t="s">
         <v>376</v>
-      </c>
-      <c r="B148" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>377</v>
+      </c>
+      <c r="B149" t="s">
         <v>378</v>
-      </c>
-      <c r="B149" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>379</v>
+      </c>
+      <c r="B150" t="s">
         <v>380</v>
-      </c>
-      <c r="B150" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>381</v>
+      </c>
+      <c r="B151" t="s">
         <v>382</v>
-      </c>
-      <c r="B151" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>383</v>
+      </c>
+      <c r="B152" t="s">
         <v>384</v>
-      </c>
-      <c r="B152" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>385</v>
+      </c>
+      <c r="B153" t="s">
         <v>386</v>
-      </c>
-      <c r="B153" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>387</v>
+      </c>
+      <c r="B154" t="s">
         <v>388</v>
-      </c>
-      <c r="B154" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>389</v>
+      </c>
+      <c r="B155" t="s">
         <v>390</v>
-      </c>
-      <c r="B155" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>391</v>
+      </c>
+      <c r="B156" t="s">
         <v>392</v>
-      </c>
-      <c r="B156" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>393</v>
+      </c>
+      <c r="B157" t="s">
         <v>394</v>
-      </c>
-      <c r="B157" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>395</v>
+      </c>
+      <c r="B158" t="s">
         <v>396</v>
-      </c>
-      <c r="B158" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>397</v>
+      </c>
+      <c r="B159" t="s">
         <v>398</v>
-      </c>
-      <c r="B159" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>399</v>
+      </c>
+      <c r="B160" t="s">
         <v>400</v>
-      </c>
-      <c r="B160" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>401</v>
+      </c>
+      <c r="B161" t="s">
         <v>402</v>
-      </c>
-      <c r="B161" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>403</v>
+      </c>
+      <c r="B162" t="s">
         <v>404</v>
-      </c>
-      <c r="B162" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>405</v>
+      </c>
+      <c r="B163" t="s">
         <v>406</v>
-      </c>
-      <c r="B163" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>407</v>
+      </c>
+      <c r="B164" t="s">
         <v>408</v>
-      </c>
-      <c r="B164" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>409</v>
+      </c>
+      <c r="B165" t="s">
         <v>410</v>
-      </c>
-      <c r="B165" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>411</v>
+      </c>
+      <c r="B166" t="s">
         <v>412</v>
-      </c>
-      <c r="B166" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>413</v>
+      </c>
+      <c r="B167" t="s">
         <v>414</v>
-      </c>
-      <c r="B167" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>415</v>
+      </c>
+      <c r="B168" t="s">
         <v>416</v>
-      </c>
-      <c r="B168" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>417</v>
+      </c>
+      <c r="B169" t="s">
         <v>418</v>
-      </c>
-      <c r="B169" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>419</v>
+      </c>
+      <c r="B170" t="s">
         <v>420</v>
-      </c>
-      <c r="B170" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>421</v>
+      </c>
+      <c r="B171" t="s">
         <v>422</v>
-      </c>
-      <c r="B171" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>423</v>
+      </c>
+      <c r="B172" t="s">
         <v>424</v>
-      </c>
-      <c r="B172" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>425</v>
+      </c>
+      <c r="B173" t="s">
         <v>426</v>
-      </c>
-      <c r="B173" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>427</v>
+      </c>
+      <c r="B174" t="s">
         <v>428</v>
-      </c>
-      <c r="B174" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>429</v>
+      </c>
+      <c r="B175" t="s">
         <v>430</v>
-      </c>
-      <c r="B175" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>431</v>
+      </c>
+      <c r="B176" t="s">
         <v>432</v>
-      </c>
-      <c r="B176" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>433</v>
+      </c>
+      <c r="B177" t="s">
         <v>434</v>
-      </c>
-      <c r="B177" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>435</v>
+      </c>
+      <c r="B178" t="s">
         <v>436</v>
-      </c>
-      <c r="B178" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>437</v>
+      </c>
+      <c r="B179" t="s">
         <v>438</v>
-      </c>
-      <c r="B179" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>439</v>
+      </c>
+      <c r="B180" t="s">
         <v>440</v>
-      </c>
-      <c r="B180" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>441</v>
+      </c>
+      <c r="B181" t="s">
         <v>442</v>
-      </c>
-      <c r="B181" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>443</v>
+      </c>
+      <c r="B182" t="s">
         <v>444</v>
-      </c>
-      <c r="B182" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>445</v>
+      </c>
+      <c r="B183" t="s">
         <v>446</v>
-      </c>
-      <c r="B183" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>447</v>
+      </c>
+      <c r="B184" t="s">
         <v>448</v>
-      </c>
-      <c r="B184" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>449</v>
+      </c>
+      <c r="B185" t="s">
         <v>450</v>
-      </c>
-      <c r="B185" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>451</v>
+      </c>
+      <c r="B186" t="s">
         <v>452</v>
-      </c>
-      <c r="B186" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>453</v>
+      </c>
+      <c r="B187" t="s">
         <v>454</v>
-      </c>
-      <c r="B187" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>455</v>
+      </c>
+      <c r="B188" t="s">
         <v>456</v>
-      </c>
-      <c r="B188" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>457</v>
+      </c>
+      <c r="B189" t="s">
         <v>458</v>
-      </c>
-      <c r="B189" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>459</v>
+      </c>
+      <c r="B190" t="s">
         <v>460</v>
-      </c>
-      <c r="B190" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>461</v>
+      </c>
+      <c r="B191" t="s">
         <v>462</v>
-      </c>
-      <c r="B191" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>463</v>
+      </c>
+      <c r="B192" t="s">
         <v>464</v>
-      </c>
-      <c r="B192" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>465</v>
+      </c>
+      <c r="B193" t="s">
         <v>466</v>
-      </c>
-      <c r="B193" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>467</v>
+      </c>
+      <c r="B194" t="s">
         <v>468</v>
-      </c>
-      <c r="B194" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>469</v>
+      </c>
+      <c r="B195" t="s">
         <v>470</v>
-      </c>
-      <c r="B195" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>471</v>
+      </c>
+      <c r="B196" t="s">
         <v>472</v>
-      </c>
-      <c r="B196" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>473</v>
+      </c>
+      <c r="B197" t="s">
         <v>474</v>
-      </c>
-      <c r="B197" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>475</v>
+      </c>
+      <c r="B198" t="s">
         <v>476</v>
-      </c>
-      <c r="B198" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>477</v>
+      </c>
+      <c r="B199" t="s">
         <v>478</v>
-      </c>
-      <c r="B199" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>479</v>
+      </c>
+      <c r="B200" t="s">
         <v>480</v>
-      </c>
-      <c r="B200" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>481</v>
+      </c>
+      <c r="B201" t="s">
         <v>482</v>
-      </c>
-      <c r="B201" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>483</v>
+      </c>
+      <c r="B202" t="s">
         <v>484</v>
-      </c>
-      <c r="B202" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>486</v>
+      </c>
+      <c r="B204" t="s">
         <v>487</v>
-      </c>
-      <c r="B204" t="s">
-        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE9728C-8035-4AF9-9A82-2936308BD57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95825DE-1351-49BD-A376-9D580478F83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -1872,7 +1872,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M41" totalsRowShown="0">
   <autoFilter ref="A1:M41" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M41">
-    <sortCondition ref="C1:C41"/>
+    <sortCondition ref="H1:H41"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
@@ -2260,63 +2260,63 @@
     </row>
     <row r="2" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>277</v>
       </c>
       <c r="B2" t="s">
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>488</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="H2">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s">
         <v>17</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>358</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>488</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -2324,43 +2324,49 @@
       <c r="K3" t="s">
         <v>33</v>
       </c>
+      <c r="L3">
+        <v>40</v>
+      </c>
       <c r="M3" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>277</v>
+        <v>351</v>
       </c>
       <c r="B4" t="s">
         <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="F4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="I4" t="s">
         <v>119</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="L4">
+        <v>32.5</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2400,51 +2406,51 @@
     </row>
     <row r="6" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B6" t="s">
         <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
       </c>
       <c r="F6">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>280</v>
+        <v>325</v>
       </c>
       <c r="B7" t="s">
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F7">
         <v>55</v>
@@ -2464,28 +2470,31 @@
       <c r="K7" t="s">
         <v>17</v>
       </c>
+      <c r="L7">
+        <v>40</v>
+      </c>
       <c r="M7" s="1" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H8">
         <v>35</v>
@@ -2499,34 +2508,31 @@
       <c r="K8" t="s">
         <v>17</v>
       </c>
-      <c r="L8">
-        <v>40</v>
-      </c>
       <c r="M8" s="1" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
         <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
         <v>20</v>
       </c>
       <c r="H9">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
@@ -2537,22 +2543,19 @@
       <c r="K9" t="s">
         <v>17</v>
       </c>
-      <c r="L9">
-        <v>45</v>
-      </c>
       <c r="M9" s="1" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
         <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
@@ -2576,65 +2579,65 @@
         <v>17</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>328</v>
+        <v>279</v>
       </c>
       <c r="B11" t="s">
         <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H11">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K11" t="s">
         <v>17</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B12" t="s">
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
@@ -2645,8 +2648,11 @@
       <c r="K12" t="s">
         <v>17</v>
       </c>
+      <c r="L12">
+        <v>45</v>
+      </c>
       <c r="M12" s="1" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2686,139 +2692,139 @@
     </row>
     <row r="14" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G14" t="s">
         <v>20</v>
       </c>
       <c r="H14">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L14">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="B15" t="s">
         <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F15">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L15">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
-        <v>489</v>
+        <v>58</v>
       </c>
       <c r="F16">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H16">
-        <v>65.5</v>
+        <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="K16" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="L16">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B17" t="s">
         <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>58</v>
       </c>
       <c r="F17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H17">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
@@ -2830,10 +2836,10 @@
         <v>33</v>
       </c>
       <c r="L17">
-        <v>55.5</v>
+        <v>50</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2876,13 +2882,13 @@
     </row>
     <row r="19" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B19" t="s">
         <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
@@ -2906,48 +2912,48 @@
         <v>33</v>
       </c>
       <c r="L19">
-        <v>60.5</v>
+        <v>55.5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F20">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s">
         <v>14</v>
       </c>
       <c r="H20">
-        <v>65</v>
+        <v>45.5</v>
       </c>
       <c r="I20" t="s">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K20" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="L20">
-        <v>70</v>
+        <v>60.5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2990,560 +2996,557 @@
     </row>
     <row r="22" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="B22" t="s">
         <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F22">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H22">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
       </c>
       <c r="J22" t="s">
+        <v>102</v>
+      </c>
+      <c r="K22" t="s">
         <v>32</v>
       </c>
-      <c r="K22" t="s">
-        <v>33</v>
-      </c>
       <c r="L22">
-        <v>60</v>
+        <v>55.5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s">
         <v>58</v>
       </c>
       <c r="F23">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H23">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I23" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="K23" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="L23">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B24" t="s">
         <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F24">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H24">
-        <v>90.9</v>
+        <v>65</v>
       </c>
       <c r="I24" t="s">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="J24" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K24" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="L24">
-        <v>105.9</v>
+        <v>70</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>58</v>
+        <v>489</v>
       </c>
       <c r="F25">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H25">
-        <v>90.9</v>
+        <v>65.5</v>
       </c>
       <c r="I25" t="s">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="J25" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="K25" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L25">
-        <v>105.9</v>
+        <v>70</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
       </c>
       <c r="F26">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H26">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="I26" t="s">
         <v>41</v>
       </c>
       <c r="J26" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="K26" t="s">
         <v>43</v>
       </c>
       <c r="L26">
-        <v>105.9</v>
+        <v>90</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>345</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s">
         <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>488</v>
       </c>
       <c r="F27">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G27" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H27">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s">
         <v>41</v>
       </c>
       <c r="J27" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
-      </c>
-      <c r="L27">
-        <v>105.9</v>
+        <v>17</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B28" t="s">
         <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E28" t="s">
         <v>58</v>
       </c>
       <c r="F28">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s">
         <v>40</v>
       </c>
       <c r="H28">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s">
         <v>41</v>
       </c>
       <c r="J28" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="K28" t="s">
         <v>43</v>
       </c>
       <c r="L28">
-        <v>105.9</v>
+        <v>100</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B29" t="s">
         <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E29" t="s">
         <v>58</v>
       </c>
       <c r="F29">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G29" t="s">
         <v>40</v>
       </c>
       <c r="H29">
-        <v>90</v>
+        <v>90.9</v>
       </c>
       <c r="I29" t="s">
         <v>41</v>
       </c>
       <c r="J29" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="K29" t="s">
         <v>43</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>105.9</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B30" t="s">
         <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s">
         <v>58</v>
       </c>
       <c r="F30">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="G30" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H30">
-        <v>120</v>
+        <v>90.9</v>
       </c>
       <c r="I30" t="s">
         <v>41</v>
       </c>
       <c r="J30" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K30" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L30">
-        <v>130</v>
+        <v>105.9</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F31">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="G31" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H31">
-        <v>120</v>
+        <v>90.9</v>
       </c>
       <c r="I31" t="s">
         <v>41</v>
       </c>
       <c r="J31" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K31" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L31">
-        <v>130</v>
+        <v>105.9</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B32" t="s">
         <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F32">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H32">
-        <v>120</v>
+        <v>90.9</v>
       </c>
       <c r="I32" t="s">
         <v>41</v>
       </c>
       <c r="J32" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K32" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L32">
-        <v>150</v>
+        <v>105.9</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s">
         <v>58</v>
       </c>
       <c r="F33">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H33">
-        <v>120.5</v>
+        <v>90.9</v>
       </c>
       <c r="I33" t="s">
         <v>41</v>
       </c>
       <c r="J33" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="K33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L33">
-        <v>125</v>
+        <v>105.9</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F34">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G34" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H34">
-        <v>30.5</v>
+        <v>120</v>
       </c>
       <c r="I34" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="J34" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L34">
-        <v>32.5</v>
+        <v>130</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F35">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G35" t="s">
         <v>40</v>
       </c>
       <c r="H35">
-        <v>45.5</v>
+        <v>120</v>
       </c>
       <c r="I35" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="J35" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="K35" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L35">
-        <v>55.5</v>
+        <v>130</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s">
         <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F36">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G36" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="H36">
-        <v>136.4</v>
+        <v>120</v>
       </c>
       <c r="I36" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J36" t="s">
         <v>47</v>
@@ -3551,8 +3554,11 @@
       <c r="K36" t="s">
         <v>48</v>
       </c>
+      <c r="L36">
+        <v>150</v>
+      </c>
       <c r="M36" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3595,13 +3601,13 @@
     </row>
     <row r="38" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s">
         <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E38" t="s">
         <v>58</v>
@@ -3613,124 +3619,121 @@
         <v>51</v>
       </c>
       <c r="H38">
-        <v>130</v>
+        <v>120.5</v>
       </c>
       <c r="I38" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J38" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="K38" t="s">
         <v>48</v>
       </c>
       <c r="L38">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F39">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="G39" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="H39">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="I39" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J39" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="K39" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="L39">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s">
         <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="E40" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F40">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H40">
-        <v>41</v>
+        <v>136.4</v>
       </c>
       <c r="I40" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J40" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="K40" t="s">
-        <v>17</v>
-      </c>
-      <c r="L40">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>358</v>
+        <v>122</v>
       </c>
       <c r="B41" t="s">
         <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="E41" t="s">
-        <v>23</v>
+        <v>488</v>
       </c>
       <c r="F41">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G41" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="H41">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="I41" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J41" t="s">
         <v>32</v>
@@ -3738,11 +3741,8 @@
       <c r="K41" t="s">
         <v>33</v>
       </c>
-      <c r="L41">
-        <v>40</v>
-      </c>
       <c r="M41" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95825DE-1351-49BD-A376-9D580478F83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5017C8C-D729-47BE-AE8C-FF107DC11CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="495">
   <si>
     <t>image_url</t>
   </si>
@@ -1800,12 +1800,27 @@
   <si>
     <t>touch panel</t>
   </si>
+  <si>
+    <t>TS1580-G</t>
+  </si>
+  <si>
+    <t>TS1580-C</t>
+  </si>
+  <si>
+    <t>600x600</t>
+  </si>
+  <si>
+    <t>images/TS1580_C</t>
+  </si>
+  <si>
+    <t>images/TS1580_G</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1820,6 +1835,11 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1842,10 +1862,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1869,8 +1892,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M41" totalsRowShown="0">
-  <autoFilter ref="A1:M41" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M43" totalsRowShown="0">
+  <autoFilter ref="A1:M43" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M41">
     <sortCondition ref="H1:H41"/>
   </sortState>
@@ -2201,8 +2224,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
@@ -2217,7 +2240,7 @@
     <col min="13" max="13" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2258,7 +2281,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="21.75" customHeight="1">
       <c r="A2" t="s">
         <v>277</v>
       </c>
@@ -2293,7 +2316,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="21.75" customHeight="1">
       <c r="A3" t="s">
         <v>358</v>
       </c>
@@ -2331,7 +2354,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="21.75" customHeight="1">
       <c r="A4" t="s">
         <v>351</v>
       </c>
@@ -2369,7 +2392,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="21.75" customHeight="1">
       <c r="A5" t="s">
         <v>278</v>
       </c>
@@ -2404,7 +2427,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="21.75" customHeight="1">
       <c r="A6" t="s">
         <v>280</v>
       </c>
@@ -2439,7 +2462,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="21.75" customHeight="1">
       <c r="A7" t="s">
         <v>325</v>
       </c>
@@ -2477,7 +2500,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="21.75" customHeight="1">
       <c r="A8" t="s">
         <v>327</v>
       </c>
@@ -2512,7 +2535,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="21.75" customHeight="1">
       <c r="A9" t="s">
         <v>328</v>
       </c>
@@ -2547,7 +2570,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="21.75" customHeight="1">
       <c r="A10" t="s">
         <v>329</v>
       </c>
@@ -2582,7 +2605,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="21.75" customHeight="1">
       <c r="A11" t="s">
         <v>279</v>
       </c>
@@ -2617,7 +2640,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="21.75" customHeight="1">
       <c r="A12" t="s">
         <v>326</v>
       </c>
@@ -2655,7 +2678,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="21.75" customHeight="1">
       <c r="A13" t="s">
         <v>330</v>
       </c>
@@ -2690,7 +2713,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="21.75" customHeight="1">
       <c r="A14" t="s">
         <v>356</v>
       </c>
@@ -2728,7 +2751,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="21.75" customHeight="1">
       <c r="A15" t="s">
         <v>357</v>
       </c>
@@ -2766,7 +2789,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="21.75" customHeight="1">
       <c r="A16" t="s">
         <v>331</v>
       </c>
@@ -2804,7 +2827,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="21.75" customHeight="1">
       <c r="A17" t="s">
         <v>332</v>
       </c>
@@ -2842,7 +2865,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="21.75" customHeight="1">
       <c r="A18" t="s">
         <v>335</v>
       </c>
@@ -2880,7 +2903,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="21.75" customHeight="1">
       <c r="A19" t="s">
         <v>334</v>
       </c>
@@ -2918,7 +2941,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="21.75" customHeight="1">
       <c r="A20" t="s">
         <v>336</v>
       </c>
@@ -2956,7 +2979,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="21.75" customHeight="1">
       <c r="A21" t="s">
         <v>337</v>
       </c>
@@ -2994,7 +3017,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="21.75" customHeight="1">
       <c r="A22" t="s">
         <v>352</v>
       </c>
@@ -3032,7 +3055,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="21.75" customHeight="1">
       <c r="A23" t="s">
         <v>339</v>
       </c>
@@ -3070,7 +3093,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="21.75" customHeight="1">
       <c r="A24" t="s">
         <v>338</v>
       </c>
@@ -3108,7 +3131,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="21.75" customHeight="1">
       <c r="A25" t="s">
         <v>333</v>
       </c>
@@ -3146,7 +3169,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="21.75" customHeight="1">
       <c r="A26" t="s">
         <v>340</v>
       </c>
@@ -3184,7 +3207,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="21.75" customHeight="1">
       <c r="A27" t="s">
         <v>160</v>
       </c>
@@ -3219,7 +3242,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="21.75" customHeight="1">
       <c r="A28" t="s">
         <v>346</v>
       </c>
@@ -3257,7 +3280,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="21.75" customHeight="1">
       <c r="A29" t="s">
         <v>341</v>
       </c>
@@ -3295,7 +3318,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="21.75" customHeight="1">
       <c r="A30" t="s">
         <v>343</v>
       </c>
@@ -3333,7 +3356,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="21.75" customHeight="1">
       <c r="A31" t="s">
         <v>344</v>
       </c>
@@ -3371,7 +3394,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="21.75" customHeight="1">
       <c r="A32" t="s">
         <v>345</v>
       </c>
@@ -3409,7 +3432,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="21.75" customHeight="1">
       <c r="A33" t="s">
         <v>342</v>
       </c>
@@ -3447,7 +3470,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="21.75" customHeight="1">
       <c r="A34" t="s">
         <v>347</v>
       </c>
@@ -3485,7 +3508,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="21.75" customHeight="1">
       <c r="A35" t="s">
         <v>348</v>
       </c>
@@ -3523,7 +3546,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="21.75" customHeight="1">
       <c r="A36" t="s">
         <v>349</v>
       </c>
@@ -3561,7 +3584,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="21.75" customHeight="1">
       <c r="A37" t="s">
         <v>354</v>
       </c>
@@ -3599,7 +3622,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="26.25" customHeight="1">
       <c r="A38" t="s">
         <v>350</v>
       </c>
@@ -3637,7 +3660,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="26.25" customHeight="1">
       <c r="A39" t="s">
         <v>355</v>
       </c>
@@ -3675,7 +3698,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="26.25" customHeight="1">
       <c r="A40" t="s">
         <v>353</v>
       </c>
@@ -3710,7 +3733,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="26.25" customHeight="1">
       <c r="A41" t="s">
         <v>122</v>
       </c>
@@ -3744,6 +3767,72 @@
       <c r="M41" s="1" t="s">
         <v>56</v>
       </c>
+    </row>
+    <row r="42" spans="1:13" ht="27.75" customHeight="1">
+      <c r="A42" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" t="s">
+        <v>490</v>
+      </c>
+      <c r="E42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42">
+        <v>75</v>
+      </c>
+      <c r="G42" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42">
+        <v>60</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" t="s">
+        <v>492</v>
+      </c>
+      <c r="K42" t="s">
+        <v>32</v>
+      </c>
+      <c r="M42" s="1"/>
+    </row>
+    <row r="43" spans="1:13" ht="32.25" customHeight="1">
+      <c r="A43" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" t="s">
+        <v>491</v>
+      </c>
+      <c r="E43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43">
+        <v>75</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43">
+        <v>60</v>
+      </c>
+      <c r="I43" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" t="s">
+        <v>492</v>
+      </c>
+      <c r="K43" t="s">
+        <v>32</v>
+      </c>
+      <c r="M43" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3758,12 +3847,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{674DE9AA-07F6-46A4-9D3E-77E413B393F7}">
   <dimension ref="A1:B204"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>123</v>
       </c>
@@ -3771,7 +3860,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -3779,7 +3868,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -3787,7 +3876,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>129</v>
       </c>
@@ -3795,7 +3884,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>131</v>
       </c>
@@ -3803,7 +3892,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>133</v>
       </c>
@@ -3811,7 +3900,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>135</v>
       </c>
@@ -3819,7 +3908,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>137</v>
       </c>
@@ -3827,7 +3916,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>139</v>
       </c>
@@ -3835,7 +3924,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>141</v>
       </c>
@@ -3843,7 +3932,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>143</v>
       </c>
@@ -3851,7 +3940,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>145</v>
       </c>
@@ -3859,7 +3948,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>147</v>
       </c>
@@ -3867,7 +3956,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>149</v>
       </c>
@@ -3875,7 +3964,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>151</v>
       </c>
@@ -3883,7 +3972,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>153</v>
       </c>
@@ -3891,7 +3980,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>155</v>
       </c>
@@ -3899,7 +3988,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>157</v>
       </c>
@@ -3907,7 +3996,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>159</v>
       </c>
@@ -3915,7 +4004,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -3923,7 +4012,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -3931,7 +4020,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>161</v>
       </c>
@@ -3939,7 +4028,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>163</v>
       </c>
@@ -3947,7 +4036,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>165</v>
       </c>
@@ -3955,7 +4044,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>167</v>
       </c>
@@ -3963,7 +4052,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>169</v>
       </c>
@@ -3971,7 +4060,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>171</v>
       </c>
@@ -3979,7 +4068,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>173</v>
       </c>
@@ -3987,7 +4076,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>175</v>
       </c>
@@ -3995,7 +4084,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>177</v>
       </c>
@@ -4003,7 +4092,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>179</v>
       </c>
@@ -4011,7 +4100,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>181</v>
       </c>
@@ -4019,7 +4108,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>183</v>
       </c>
@@ -4027,7 +4116,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>185</v>
       </c>
@@ -4035,7 +4124,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>187</v>
       </c>
@@ -4043,7 +4132,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>189</v>
       </c>
@@ -4051,7 +4140,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>191</v>
       </c>
@@ -4059,7 +4148,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>193</v>
       </c>
@@ -4067,7 +4156,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>195</v>
       </c>
@@ -4075,7 +4164,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>197</v>
       </c>
@@ -4083,7 +4172,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>199</v>
       </c>
@@ -4091,7 +4180,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>201</v>
       </c>
@@ -4099,7 +4188,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>203</v>
       </c>
@@ -4107,7 +4196,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>205</v>
       </c>
@@ -4115,7 +4204,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>207</v>
       </c>
@@ -4123,7 +4212,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>209</v>
       </c>
@@ -4131,7 +4220,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>211</v>
       </c>
@@ -4139,7 +4228,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>213</v>
       </c>
@@ -4147,7 +4236,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>215</v>
       </c>
@@ -4155,7 +4244,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>217</v>
       </c>
@@ -4163,7 +4252,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>219</v>
       </c>
@@ -4171,7 +4260,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>221</v>
       </c>
@@ -4179,7 +4268,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>223</v>
       </c>
@@ -4187,7 +4276,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>225</v>
       </c>
@@ -4195,7 +4284,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>227</v>
       </c>
@@ -4203,7 +4292,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>229</v>
       </c>
@@ -4211,7 +4300,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>231</v>
       </c>
@@ -4219,7 +4308,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>233</v>
       </c>
@@ -4227,7 +4316,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>235</v>
       </c>
@@ -4235,7 +4324,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>237</v>
       </c>
@@ -4243,7 +4332,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>239</v>
       </c>
@@ -4251,7 +4340,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>241</v>
       </c>
@@ -4259,7 +4348,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>243</v>
       </c>
@@ -4267,7 +4356,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>245</v>
       </c>
@@ -4275,7 +4364,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>247</v>
       </c>
@@ -4283,7 +4372,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>249</v>
       </c>
@@ -4291,7 +4380,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>251</v>
       </c>
@@ -4299,7 +4388,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>253</v>
       </c>
@@ -4307,7 +4396,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>255</v>
       </c>
@@ -4315,7 +4404,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>257</v>
       </c>
@@ -4323,7 +4412,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>259</v>
       </c>
@@ -4331,7 +4420,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>261</v>
       </c>
@@ -4339,7 +4428,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2">
       <c r="A73" t="s">
         <v>263</v>
       </c>
@@ -4347,7 +4436,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>265</v>
       </c>
@@ -4355,7 +4444,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>267</v>
       </c>
@@ -4363,7 +4452,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>269</v>
       </c>
@@ -4371,7 +4460,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>271</v>
       </c>
@@ -4379,7 +4468,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2">
       <c r="A78" t="s">
         <v>273</v>
       </c>
@@ -4387,7 +4476,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2">
       <c r="A79" t="s">
         <v>275</v>
       </c>
@@ -4395,7 +4484,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2">
       <c r="A80" t="s">
         <v>110</v>
       </c>
@@ -4403,7 +4492,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>112</v>
       </c>
@@ -4411,7 +4500,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>115</v>
       </c>
@@ -4419,7 +4508,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>117</v>
       </c>
@@ -4427,7 +4516,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>281</v>
       </c>
@@ -4435,7 +4524,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>283</v>
       </c>
@@ -4443,7 +4532,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2">
       <c r="A86" t="s">
         <v>285</v>
       </c>
@@ -4451,7 +4540,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2">
       <c r="A87" t="s">
         <v>287</v>
       </c>
@@ -4459,7 +4548,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2">
       <c r="A88" t="s">
         <v>289</v>
       </c>
@@ -4467,7 +4556,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2">
       <c r="A89" t="s">
         <v>291</v>
       </c>
@@ -4475,7 +4564,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2">
       <c r="A90" t="s">
         <v>293</v>
       </c>
@@ -4483,7 +4572,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2">
       <c r="A91" t="s">
         <v>295</v>
       </c>
@@ -4491,7 +4580,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2">
       <c r="A92" t="s">
         <v>297</v>
       </c>
@@ -4499,7 +4588,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2">
       <c r="A93" t="s">
         <v>299</v>
       </c>
@@ -4507,7 +4596,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2">
       <c r="A94" t="s">
         <v>301</v>
       </c>
@@ -4515,7 +4604,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2">
       <c r="A95" t="s">
         <v>303</v>
       </c>
@@ -4523,7 +4612,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2">
       <c r="A96" t="s">
         <v>305</v>
       </c>
@@ -4531,7 +4620,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2">
       <c r="A97" t="s">
         <v>307</v>
       </c>
@@ -4539,7 +4628,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2">
       <c r="A98" t="s">
         <v>309</v>
       </c>
@@ -4547,7 +4636,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2">
       <c r="A99" t="s">
         <v>311</v>
       </c>
@@ -4555,7 +4644,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2">
       <c r="A100" t="s">
         <v>313</v>
       </c>
@@ -4563,7 +4652,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2">
       <c r="A101" t="s">
         <v>315</v>
       </c>
@@ -4571,7 +4660,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2">
       <c r="A102" t="s">
         <v>317</v>
       </c>
@@ -4579,7 +4668,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2">
       <c r="A103" t="s">
         <v>319</v>
       </c>
@@ -4587,7 +4676,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2">
       <c r="A104" t="s">
         <v>321</v>
       </c>
@@ -4595,7 +4684,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2">
       <c r="A105" t="s">
         <v>323</v>
       </c>
@@ -4603,7 +4692,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2">
       <c r="A106" t="s">
         <v>57</v>
       </c>
@@ -4611,7 +4700,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2">
       <c r="A107" t="s">
         <v>60</v>
       </c>
@@ -4619,7 +4708,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2">
       <c r="A108" t="s">
         <v>19</v>
       </c>
@@ -4627,7 +4716,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2">
       <c r="A109" t="s">
         <v>22</v>
       </c>
@@ -4635,7 +4724,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2">
       <c r="A110" t="s">
         <v>25</v>
       </c>
@@ -4643,7 +4732,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2">
       <c r="A111" t="s">
         <v>62</v>
       </c>
@@ -4651,7 +4740,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2">
       <c r="A112" t="s">
         <v>65</v>
       </c>
@@ -4659,7 +4748,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2">
       <c r="A113" t="s">
         <v>67</v>
       </c>
@@ -4667,7 +4756,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2">
       <c r="A114" t="s">
         <v>68</v>
       </c>
@@ -4675,7 +4764,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2">
       <c r="A115" t="s">
         <v>71</v>
       </c>
@@ -4683,7 +4772,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2">
       <c r="A116" t="s">
         <v>73</v>
       </c>
@@ -4691,7 +4780,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2">
       <c r="A117" t="s">
         <v>75</v>
       </c>
@@ -4699,7 +4788,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2">
       <c r="A118" t="s">
         <v>77</v>
       </c>
@@ -4707,7 +4796,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2">
       <c r="A119" t="s">
         <v>35</v>
       </c>
@@ -4715,7 +4804,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2">
       <c r="A120" t="s">
         <v>78</v>
       </c>
@@ -4723,7 +4812,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2">
       <c r="A121" t="s">
         <v>80</v>
       </c>
@@ -4731,7 +4820,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2">
       <c r="A122" t="s">
         <v>83</v>
       </c>
@@ -4739,7 +4828,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2">
       <c r="A123" t="s">
         <v>85</v>
       </c>
@@ -4747,7 +4836,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2">
       <c r="A124" t="s">
         <v>86</v>
       </c>
@@ -4755,7 +4844,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2">
       <c r="A125" t="s">
         <v>88</v>
       </c>
@@ -4763,7 +4852,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2">
       <c r="A126" t="s">
         <v>39</v>
       </c>
@@ -4771,7 +4860,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2">
       <c r="A127" t="s">
         <v>90</v>
       </c>
@@ -4779,7 +4868,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2">
       <c r="A128" t="s">
         <v>92</v>
       </c>
@@ -4787,7 +4876,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2">
       <c r="A129" t="s">
         <v>45</v>
       </c>
@@ -4795,7 +4884,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2">
       <c r="A130" t="s">
         <v>94</v>
       </c>
@@ -4803,7 +4892,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2">
       <c r="A131" t="s">
         <v>96</v>
       </c>
@@ -4811,7 +4900,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2">
       <c r="A132" t="s">
         <v>99</v>
       </c>
@@ -4819,7 +4908,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2">
       <c r="A133" t="s">
         <v>101</v>
       </c>
@@ -4827,7 +4916,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2">
       <c r="A134" t="s">
         <v>104</v>
       </c>
@@ -4835,7 +4924,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2">
       <c r="A135" t="s">
         <v>50</v>
       </c>
@@ -4843,7 +4932,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2">
       <c r="A136" t="s">
         <v>106</v>
       </c>
@@ -4851,7 +4940,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2">
       <c r="A137" t="s">
         <v>26</v>
       </c>
@@ -4859,7 +4948,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2">
       <c r="A138" t="s">
         <v>28</v>
       </c>
@@ -4867,7 +4956,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2">
       <c r="A139" t="s">
         <v>31</v>
       </c>
@@ -4875,7 +4964,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2">
       <c r="A140" t="s">
         <v>359</v>
       </c>
@@ -4883,7 +4972,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2">
       <c r="A141" t="s">
         <v>361</v>
       </c>
@@ -4891,7 +4980,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2">
       <c r="A142" t="s">
         <v>363</v>
       </c>
@@ -4899,7 +4988,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2">
       <c r="A143" t="s">
         <v>365</v>
       </c>
@@ -4907,7 +4996,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2">
       <c r="A144" t="s">
         <v>367</v>
       </c>
@@ -4915,7 +5004,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2">
       <c r="A145" t="s">
         <v>369</v>
       </c>
@@ -4923,7 +5012,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2">
       <c r="A146" t="s">
         <v>371</v>
       </c>
@@ -4931,7 +5020,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2">
       <c r="A147" t="s">
         <v>373</v>
       </c>
@@ -4939,7 +5028,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2">
       <c r="A148" t="s">
         <v>375</v>
       </c>
@@ -4947,7 +5036,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2">
       <c r="A149" t="s">
         <v>377</v>
       </c>
@@ -4955,7 +5044,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2">
       <c r="A150" t="s">
         <v>379</v>
       </c>
@@ -4963,7 +5052,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2">
       <c r="A151" t="s">
         <v>381</v>
       </c>
@@ -4971,7 +5060,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2">
       <c r="A152" t="s">
         <v>383</v>
       </c>
@@ -4979,7 +5068,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2">
       <c r="A153" t="s">
         <v>385</v>
       </c>
@@ -4987,7 +5076,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2">
       <c r="A154" t="s">
         <v>387</v>
       </c>
@@ -4995,7 +5084,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2">
       <c r="A155" t="s">
         <v>389</v>
       </c>
@@ -5003,7 +5092,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2">
       <c r="A156" t="s">
         <v>391</v>
       </c>
@@ -5011,7 +5100,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2">
       <c r="A157" t="s">
         <v>393</v>
       </c>
@@ -5019,7 +5108,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2">
       <c r="A158" t="s">
         <v>395</v>
       </c>
@@ -5027,7 +5116,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2">
       <c r="A159" t="s">
         <v>397</v>
       </c>
@@ -5035,7 +5124,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2">
       <c r="A160" t="s">
         <v>399</v>
       </c>
@@ -5043,7 +5132,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2">
       <c r="A161" t="s">
         <v>401</v>
       </c>
@@ -5051,7 +5140,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2">
       <c r="A162" t="s">
         <v>403</v>
       </c>
@@ -5059,7 +5148,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2">
       <c r="A163" t="s">
         <v>405</v>
       </c>
@@ -5067,7 +5156,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2">
       <c r="A164" t="s">
         <v>407</v>
       </c>
@@ -5075,7 +5164,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2">
       <c r="A165" t="s">
         <v>409</v>
       </c>
@@ -5083,7 +5172,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2">
       <c r="A166" t="s">
         <v>411</v>
       </c>
@@ -5091,7 +5180,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2">
       <c r="A167" t="s">
         <v>413</v>
       </c>
@@ -5099,7 +5188,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2">
       <c r="A168" t="s">
         <v>415</v>
       </c>
@@ -5107,7 +5196,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2">
       <c r="A169" t="s">
         <v>417</v>
       </c>
@@ -5115,7 +5204,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2">
       <c r="A170" t="s">
         <v>419</v>
       </c>
@@ -5123,7 +5212,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2">
       <c r="A171" t="s">
         <v>421</v>
       </c>
@@ -5131,7 +5220,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2">
       <c r="A172" t="s">
         <v>423</v>
       </c>
@@ -5139,7 +5228,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2">
       <c r="A173" t="s">
         <v>425</v>
       </c>
@@ -5147,7 +5236,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2">
       <c r="A174" t="s">
         <v>427</v>
       </c>
@@ -5155,7 +5244,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2">
       <c r="A175" t="s">
         <v>429</v>
       </c>
@@ -5163,7 +5252,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2">
       <c r="A176" t="s">
         <v>431</v>
       </c>
@@ -5171,7 +5260,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2">
       <c r="A177" t="s">
         <v>433</v>
       </c>
@@ -5179,7 +5268,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2">
       <c r="A178" t="s">
         <v>435</v>
       </c>
@@ -5187,7 +5276,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2">
       <c r="A179" t="s">
         <v>437</v>
       </c>
@@ -5195,7 +5284,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2">
       <c r="A180" t="s">
         <v>439</v>
       </c>
@@ -5203,7 +5292,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2">
       <c r="A181" t="s">
         <v>441</v>
       </c>
@@ -5211,7 +5300,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2">
       <c r="A182" t="s">
         <v>443</v>
       </c>
@@ -5219,7 +5308,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2">
       <c r="A183" t="s">
         <v>445</v>
       </c>
@@ -5227,7 +5316,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2">
       <c r="A184" t="s">
         <v>447</v>
       </c>
@@ -5235,7 +5324,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2">
       <c r="A185" t="s">
         <v>449</v>
       </c>
@@ -5243,7 +5332,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2">
       <c r="A186" t="s">
         <v>451</v>
       </c>
@@ -5251,7 +5340,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2">
       <c r="A187" t="s">
         <v>453</v>
       </c>
@@ -5259,7 +5348,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2">
       <c r="A188" t="s">
         <v>455</v>
       </c>
@@ -5267,7 +5356,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2">
       <c r="A189" t="s">
         <v>457</v>
       </c>
@@ -5275,7 +5364,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2">
       <c r="A190" t="s">
         <v>459</v>
       </c>
@@ -5283,7 +5372,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2">
       <c r="A191" t="s">
         <v>461</v>
       </c>
@@ -5291,7 +5380,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2">
       <c r="A192" t="s">
         <v>463</v>
       </c>
@@ -5299,7 +5388,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2">
       <c r="A193" t="s">
         <v>465</v>
       </c>
@@ -5307,7 +5396,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2">
       <c r="A194" t="s">
         <v>467</v>
       </c>
@@ -5315,7 +5404,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2">
       <c r="A195" t="s">
         <v>469</v>
       </c>
@@ -5323,7 +5412,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2">
       <c r="A196" t="s">
         <v>471</v>
       </c>
@@ -5331,7 +5420,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2">
       <c r="A197" t="s">
         <v>473</v>
       </c>
@@ -5339,7 +5428,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2">
       <c r="A198" t="s">
         <v>475</v>
       </c>
@@ -5347,7 +5436,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2">
       <c r="A199" t="s">
         <v>477</v>
       </c>
@@ -5355,7 +5444,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2">
       <c r="A200" t="s">
         <v>479</v>
       </c>
@@ -5363,7 +5452,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2">
       <c r="A201" t="s">
         <v>481</v>
       </c>
@@ -5371,7 +5460,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2">
       <c r="A202" t="s">
         <v>483</v>
       </c>
@@ -5379,7 +5468,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2">
       <c r="A203" t="s">
         <v>485</v>
       </c>
@@ -5387,7 +5476,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2">
       <c r="A204" t="s">
         <v>486</v>
       </c>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5017C8C-D729-47BE-AE8C-FF107DC11CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B29C35E-680A-4746-B038-38E725C0C39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="1080" yWindow="1005" windowWidth="21600" windowHeight="14595" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="501">
   <si>
     <t>image_url</t>
   </si>
@@ -1815,12 +1815,30 @@
   <si>
     <t>images/TS1580_G</t>
   </si>
+  <si>
+    <t>PR-7640E-B</t>
+  </si>
+  <si>
+    <t>PR-7630E-B</t>
+  </si>
+  <si>
+    <t>PR-7620E-B</t>
+  </si>
+  <si>
+    <t>https://onkron.de/cdn/shop/files/FPRO2L-40_0_1_1.png?v=1775552264</t>
+  </si>
+  <si>
+    <t>https://onkron.de/cdn/shop/files/FPRO2L-30_0_1_1.png?v=1775221955</t>
+  </si>
+  <si>
+    <t>https://onkron.de/cdn/shop/files/FPRO2L-20_0_1.png?v=1775212604</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1841,6 +1859,15 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1859,10 +1886,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1870,8 +1898,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -1892,8 +1922,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M43" totalsRowShown="0">
-  <autoFilter ref="A1:M43" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M46" totalsRowShown="0">
+  <autoFilter ref="A1:M46" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M41">
     <sortCondition ref="H1:H41"/>
   </sortState>
@@ -2224,10 +2254,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="5" max="5" width="28.5703125" customWidth="1"/>
     <col min="6" max="6" width="26.140625" customWidth="1"/>
@@ -3834,12 +3865,115 @@
       </c>
       <c r="M43" s="1"/>
     </row>
+    <row r="44" spans="1:13" ht="30" customHeight="1">
+      <c r="A44" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>495</v>
+      </c>
+      <c r="E44" t="s">
+        <v>488</v>
+      </c>
+      <c r="F44">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
+        <v>40</v>
+      </c>
+      <c r="H44">
+        <v>100</v>
+      </c>
+      <c r="I44" t="s">
+        <v>120</v>
+      </c>
+      <c r="J44" t="s">
+        <v>47</v>
+      </c>
+      <c r="K44" t="s">
+        <v>48</v>
+      </c>
+      <c r="M44" s="1"/>
+    </row>
+    <row r="45" spans="1:13" ht="30" customHeight="1">
+      <c r="A45" t="s">
+        <v>499</v>
+      </c>
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>496</v>
+      </c>
+      <c r="E45" t="s">
+        <v>488</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
+        <v>40</v>
+      </c>
+      <c r="H45">
+        <v>100</v>
+      </c>
+      <c r="I45" t="s">
+        <v>120</v>
+      </c>
+      <c r="J45" t="s">
+        <v>47</v>
+      </c>
+      <c r="K45" t="s">
+        <v>48</v>
+      </c>
+      <c r="M45" s="1"/>
+    </row>
+    <row r="46" spans="1:13" ht="30" customHeight="1">
+      <c r="A46" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" t="s">
+        <v>497</v>
+      </c>
+      <c r="E46" t="s">
+        <v>488</v>
+      </c>
+      <c r="F46">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46">
+        <v>100</v>
+      </c>
+      <c r="I46" t="s">
+        <v>120</v>
+      </c>
+      <c r="J46" t="s">
+        <v>47</v>
+      </c>
+      <c r="K46" t="s">
+        <v>48</v>
+      </c>
+      <c r="M46" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A44" r:id="rId1" xr:uid="{940A5EEB-190A-497E-8F7E-3D7C079597B9}"/>
+    <hyperlink ref="A46" r:id="rId2" xr:uid="{2838C5F0-4488-45A4-974B-EFE844469EDF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B29C35E-680A-4746-B038-38E725C0C39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD947C5-5C05-462A-91AD-A7CD8C3D0FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1005" windowWidth="21600" windowHeight="14595" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -1825,13 +1825,13 @@
     <t>PR-7620E-B</t>
   </si>
   <si>
-    <t>https://onkron.de/cdn/shop/files/FPRO2L-40_0_1_1.png?v=1775552264</t>
-  </si>
-  <si>
-    <t>https://onkron.de/cdn/shop/files/FPRO2L-30_0_1_1.png?v=1775221955</t>
-  </si>
-  <si>
-    <t>https://onkron.de/cdn/shop/files/FPRO2L-20_0_1.png?v=1775212604</t>
+    <t>images/PR-7640E-B</t>
+  </si>
+  <si>
+    <t>images/PR-7630E-B</t>
+  </si>
+  <si>
+    <t>images/PR-7620E-B</t>
   </si>
 </sst>
 </file>
@@ -3899,7 +3899,7 @@
       <c r="M44" s="1"/>
     </row>
     <row r="45" spans="1:13" ht="30" customHeight="1">
-      <c r="A45" t="s">
+      <c r="A45" s="3" t="s">
         <v>499</v>
       </c>
       <c r="B45" t="s">
@@ -3966,14 +3966,10 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="A44" r:id="rId1" xr:uid="{940A5EEB-190A-497E-8F7E-3D7C079597B9}"/>
-    <hyperlink ref="A46" r:id="rId2" xr:uid="{2838C5F0-4488-45A4-974B-EFE844469EDF}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD947C5-5C05-462A-91AD-A7CD8C3D0FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E67A920-8BAB-4E48-B94C-42ABA1669C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1005" windowWidth="21600" windowHeight="14595" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -688,9 +688,6 @@
 Материалы: закалённое стекло, сталь</t>
   </si>
   <si>
-    <t>30 kg</t>
-  </si>
-  <si>
     <t>70 kg</t>
   </si>
   <si>
@@ -1832,6 +1829,9 @@
   </si>
   <si>
     <t>images/PR-7620E-B</t>
+  </si>
+  <si>
+    <t>35 kg</t>
   </si>
 </sst>
 </file>
@@ -2314,7 +2314,7 @@
     </row>
     <row r="2" spans="1:13" ht="21.75" customHeight="1">
       <c r="A2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B2" t="s">
         <v>109</v>
@@ -2335,7 +2335,7 @@
         <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>119</v>
+        <v>500</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="3" spans="1:13" ht="21.75" customHeight="1">
       <c r="A3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
@@ -2370,7 +2370,7 @@
         <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>119</v>
+        <v>500</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="4" spans="1:13" ht="21.75" customHeight="1">
       <c r="A4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B4" t="s">
         <v>109</v>
@@ -2408,7 +2408,7 @@
         <v>30.5</v>
       </c>
       <c r="I4" t="s">
-        <v>119</v>
+        <v>500</v>
       </c>
       <c r="J4" t="s">
         <v>32</v>
@@ -2425,7 +2425,7 @@
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1">
       <c r="A5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B5" t="s">
         <v>109</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="6" spans="1:13" ht="21.75" customHeight="1">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B6" t="s">
         <v>109</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="7" spans="1:13" ht="21.75" customHeight="1">
       <c r="A7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B7" t="s">
         <v>109</v>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="8" spans="1:13" ht="21.75" customHeight="1">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="9" spans="1:13" ht="21.75" customHeight="1">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B9" t="s">
         <v>109</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="10" spans="1:13" ht="21.75" customHeight="1">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B10" t="s">
         <v>109</v>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="11" spans="1:13" ht="21.75" customHeight="1">
       <c r="A11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B11" t="s">
         <v>109</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1">
       <c r="A12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B12" t="s">
         <v>109</v>
@@ -2711,7 +2711,7 @@
     </row>
     <row r="13" spans="1:13" ht="21.75" customHeight="1">
       <c r="A13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
@@ -2720,7 +2720,7 @@
         <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F13">
         <v>70</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="14" spans="1:13" ht="21.75" customHeight="1">
       <c r="A14" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="15" spans="1:13" ht="21.75" customHeight="1">
       <c r="A15" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B15" t="s">
         <v>109</v>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="16" spans="1:13" ht="21.75" customHeight="1">
       <c r="A16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="17" spans="1:13" ht="21.75" customHeight="1">
       <c r="A17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B17" t="s">
         <v>109</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1">
       <c r="A18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B18" t="s">
         <v>109</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="19" spans="1:13" ht="21.75" customHeight="1">
       <c r="A19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B19" t="s">
         <v>109</v>
@@ -2974,7 +2974,7 @@
     </row>
     <row r="20" spans="1:13" ht="21.75" customHeight="1">
       <c r="A20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="21" spans="1:13" ht="21.75" customHeight="1">
       <c r="A21" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B21" t="s">
         <v>109</v>
@@ -3050,7 +3050,7 @@
     </row>
     <row r="22" spans="1:13" ht="21.75" customHeight="1">
       <c r="A22" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B22" t="s">
         <v>109</v>
@@ -3088,7 +3088,7 @@
     </row>
     <row r="23" spans="1:13" ht="21.75" customHeight="1">
       <c r="A23" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1">
       <c r="A24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B24" t="s">
         <v>109</v>
@@ -3147,7 +3147,7 @@
         <v>65</v>
       </c>
       <c r="I24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J24" t="s">
         <v>37</v>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1">
       <c r="A25" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
@@ -3173,7 +3173,7 @@
         <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F25">
         <v>83</v>
@@ -3185,7 +3185,7 @@
         <v>65.5</v>
       </c>
       <c r="I25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J25" t="s">
         <v>69</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1">
       <c r="A26" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
@@ -3240,7 +3240,7 @@
     </row>
     <row r="27" spans="1:13" ht="21.75" customHeight="1">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s">
         <v>109</v>
@@ -3249,7 +3249,7 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F27">
         <v>70</v>
@@ -3275,7 +3275,7 @@
     </row>
     <row r="28" spans="1:13" ht="21.75" customHeight="1">
       <c r="A28" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B28" t="s">
         <v>109</v>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="29" spans="1:13" ht="21.75" customHeight="1">
       <c r="A29" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B29" t="s">
         <v>109</v>
@@ -3351,7 +3351,7 @@
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1">
       <c r="A30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B30" t="s">
         <v>109</v>
@@ -3389,7 +3389,7 @@
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1">
       <c r="A31" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1">
       <c r="A32" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s">
         <v>109</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1">
       <c r="A33" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1">
       <c r="A34" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="35" spans="1:13" ht="21.75" customHeight="1">
       <c r="A35" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="36" spans="1:13" ht="21.75" customHeight="1">
       <c r="A36" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s">
         <v>109</v>
@@ -3617,7 +3617,7 @@
     </row>
     <row r="37" spans="1:13" ht="21.75" customHeight="1">
       <c r="A37" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s">
         <v>109</v>
@@ -3655,7 +3655,7 @@
     </row>
     <row r="38" spans="1:13" ht="26.25" customHeight="1">
       <c r="A38" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B38" t="s">
         <v>109</v>
@@ -3693,7 +3693,7 @@
     </row>
     <row r="39" spans="1:13" ht="26.25" customHeight="1">
       <c r="A39" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
@@ -3731,7 +3731,7 @@
     </row>
     <row r="40" spans="1:13" ht="26.25" customHeight="1">
       <c r="A40" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B40" t="s">
         <v>109</v>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="41" spans="1:13" ht="26.25" customHeight="1">
       <c r="A41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B41" t="s">
         <v>109</v>
@@ -3775,7 +3775,7 @@
         <v>53</v>
       </c>
       <c r="E41" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F41">
         <v>55</v>
@@ -3801,13 +3801,13 @@
     </row>
     <row r="42" spans="1:13" ht="27.75" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B42" t="s">
         <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E42" t="s">
         <v>23</v>
@@ -3825,7 +3825,7 @@
         <v>15</v>
       </c>
       <c r="J42" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K42" t="s">
         <v>32</v>
@@ -3834,13 +3834,13 @@
     </row>
     <row r="43" spans="1:13" ht="32.25" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E43" t="s">
         <v>23</v>
@@ -3858,7 +3858,7 @@
         <v>15</v>
       </c>
       <c r="J43" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K43" t="s">
         <v>32</v>
@@ -3867,16 +3867,16 @@
     </row>
     <row r="44" spans="1:13" ht="30" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F44">
         <v>100</v>
@@ -3888,7 +3888,7 @@
         <v>100</v>
       </c>
       <c r="I44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J44" t="s">
         <v>47</v>
@@ -3900,16 +3900,16 @@
     </row>
     <row r="45" spans="1:13" ht="30" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E45" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F45">
         <v>100</v>
@@ -3921,7 +3921,7 @@
         <v>100</v>
       </c>
       <c r="I45" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J45" t="s">
         <v>47</v>
@@ -3933,16 +3933,16 @@
     </row>
     <row r="46" spans="1:13" ht="30" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E46" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F46">
         <v>100</v>
@@ -3954,7 +3954,7 @@
         <v>100</v>
       </c>
       <c r="I46" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J46" t="s">
         <v>47</v>
@@ -3984,154 +3984,154 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" t="s">
         <v>123</v>
-      </c>
-      <c r="B1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" t="s">
         <v>125</v>
-      </c>
-      <c r="B2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" t="s">
         <v>127</v>
-      </c>
-      <c r="B3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s">
         <v>129</v>
-      </c>
-      <c r="B4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" t="s">
         <v>131</v>
-      </c>
-      <c r="B5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" t="s">
         <v>133</v>
-      </c>
-      <c r="B6" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" t="s">
         <v>135</v>
-      </c>
-      <c r="B7" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" t="s">
         <v>137</v>
-      </c>
-      <c r="B8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" t="s">
         <v>139</v>
-      </c>
-      <c r="B9" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" t="s">
         <v>141</v>
-      </c>
-      <c r="B10" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" t="s">
         <v>143</v>
-      </c>
-      <c r="B11" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" t="s">
         <v>145</v>
-      </c>
-      <c r="B12" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" t="s">
         <v>147</v>
-      </c>
-      <c r="B13" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" t="s">
         <v>149</v>
-      </c>
-      <c r="B14" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" t="s">
         <v>151</v>
-      </c>
-      <c r="B15" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" t="s">
         <v>153</v>
-      </c>
-      <c r="B16" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" t="s">
         <v>155</v>
-      </c>
-      <c r="B17" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" t="s">
         <v>157</v>
-      </c>
-      <c r="B18" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4139,7 +4139,7 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4147,471 +4147,471 @@
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" t="s">
         <v>161</v>
-      </c>
-      <c r="B22" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" t="s">
         <v>163</v>
-      </c>
-      <c r="B23" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" t="s">
         <v>165</v>
-      </c>
-      <c r="B24" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" t="s">
         <v>167</v>
-      </c>
-      <c r="B25" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" t="s">
         <v>169</v>
-      </c>
-      <c r="B26" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" t="s">
         <v>171</v>
-      </c>
-      <c r="B27" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" t="s">
         <v>173</v>
-      </c>
-      <c r="B28" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" t="s">
         <v>175</v>
-      </c>
-      <c r="B29" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" t="s">
         <v>177</v>
-      </c>
-      <c r="B30" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" t="s">
         <v>179</v>
-      </c>
-      <c r="B31" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
+        <v>180</v>
+      </c>
+      <c r="B32" t="s">
         <v>181</v>
-      </c>
-      <c r="B32" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>182</v>
+      </c>
+      <c r="B33" t="s">
         <v>183</v>
-      </c>
-      <c r="B33" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" t="s">
         <v>185</v>
-      </c>
-      <c r="B34" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>186</v>
+      </c>
+      <c r="B35" t="s">
         <v>187</v>
-      </c>
-      <c r="B35" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" t="s">
         <v>189</v>
-      </c>
-      <c r="B36" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
+        <v>190</v>
+      </c>
+      <c r="B37" t="s">
         <v>191</v>
-      </c>
-      <c r="B37" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
+        <v>192</v>
+      </c>
+      <c r="B38" t="s">
         <v>193</v>
-      </c>
-      <c r="B38" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
+        <v>194</v>
+      </c>
+      <c r="B39" t="s">
         <v>195</v>
-      </c>
-      <c r="B39" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
+        <v>196</v>
+      </c>
+      <c r="B40" t="s">
         <v>197</v>
-      </c>
-      <c r="B40" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
+        <v>198</v>
+      </c>
+      <c r="B41" t="s">
         <v>199</v>
-      </c>
-      <c r="B41" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" t="s">
         <v>201</v>
-      </c>
-      <c r="B42" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
+        <v>202</v>
+      </c>
+      <c r="B43" t="s">
         <v>203</v>
-      </c>
-      <c r="B43" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
+        <v>204</v>
+      </c>
+      <c r="B44" t="s">
         <v>205</v>
-      </c>
-      <c r="B44" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
+        <v>206</v>
+      </c>
+      <c r="B45" t="s">
         <v>207</v>
-      </c>
-      <c r="B45" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
+        <v>208</v>
+      </c>
+      <c r="B46" t="s">
         <v>209</v>
-      </c>
-      <c r="B46" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
+        <v>210</v>
+      </c>
+      <c r="B47" t="s">
         <v>211</v>
-      </c>
-      <c r="B47" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
+        <v>212</v>
+      </c>
+      <c r="B48" t="s">
         <v>213</v>
-      </c>
-      <c r="B48" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
+        <v>214</v>
+      </c>
+      <c r="B49" t="s">
         <v>215</v>
-      </c>
-      <c r="B49" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
+        <v>216</v>
+      </c>
+      <c r="B50" t="s">
         <v>217</v>
-      </c>
-      <c r="B50" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
+        <v>218</v>
+      </c>
+      <c r="B51" t="s">
         <v>219</v>
-      </c>
-      <c r="B51" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
+        <v>220</v>
+      </c>
+      <c r="B52" t="s">
         <v>221</v>
-      </c>
-      <c r="B52" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
+        <v>222</v>
+      </c>
+      <c r="B53" t="s">
         <v>223</v>
-      </c>
-      <c r="B53" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
+        <v>224</v>
+      </c>
+      <c r="B54" t="s">
         <v>225</v>
-      </c>
-      <c r="B54" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
+        <v>226</v>
+      </c>
+      <c r="B55" t="s">
         <v>227</v>
-      </c>
-      <c r="B55" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
+        <v>228</v>
+      </c>
+      <c r="B56" t="s">
         <v>229</v>
-      </c>
-      <c r="B56" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
+        <v>230</v>
+      </c>
+      <c r="B57" t="s">
         <v>231</v>
-      </c>
-      <c r="B57" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
+        <v>232</v>
+      </c>
+      <c r="B58" t="s">
         <v>233</v>
-      </c>
-      <c r="B58" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
+        <v>234</v>
+      </c>
+      <c r="B59" t="s">
         <v>235</v>
-      </c>
-      <c r="B59" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
+        <v>236</v>
+      </c>
+      <c r="B60" t="s">
         <v>237</v>
-      </c>
-      <c r="B60" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
+        <v>238</v>
+      </c>
+      <c r="B61" t="s">
         <v>239</v>
-      </c>
-      <c r="B61" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
+        <v>240</v>
+      </c>
+      <c r="B62" t="s">
         <v>241</v>
-      </c>
-      <c r="B62" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
+        <v>242</v>
+      </c>
+      <c r="B63" t="s">
         <v>243</v>
-      </c>
-      <c r="B63" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
+        <v>244</v>
+      </c>
+      <c r="B64" t="s">
         <v>245</v>
-      </c>
-      <c r="B64" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
+        <v>246</v>
+      </c>
+      <c r="B65" t="s">
         <v>247</v>
-      </c>
-      <c r="B65" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
+        <v>248</v>
+      </c>
+      <c r="B66" t="s">
         <v>249</v>
-      </c>
-      <c r="B66" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
+        <v>250</v>
+      </c>
+      <c r="B67" t="s">
         <v>251</v>
-      </c>
-      <c r="B67" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
+        <v>252</v>
+      </c>
+      <c r="B68" t="s">
         <v>253</v>
-      </c>
-      <c r="B68" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
+        <v>254</v>
+      </c>
+      <c r="B69" t="s">
         <v>255</v>
-      </c>
-      <c r="B69" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
+        <v>256</v>
+      </c>
+      <c r="B70" t="s">
         <v>257</v>
-      </c>
-      <c r="B70" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
+        <v>258</v>
+      </c>
+      <c r="B71" t="s">
         <v>259</v>
-      </c>
-      <c r="B71" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
+        <v>260</v>
+      </c>
+      <c r="B72" t="s">
         <v>261</v>
-      </c>
-      <c r="B72" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
+        <v>262</v>
+      </c>
+      <c r="B73" t="s">
         <v>263</v>
-      </c>
-      <c r="B73" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
+        <v>264</v>
+      </c>
+      <c r="B74" t="s">
         <v>265</v>
-      </c>
-      <c r="B74" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
+        <v>266</v>
+      </c>
+      <c r="B75" t="s">
         <v>267</v>
-      </c>
-      <c r="B75" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
+        <v>268</v>
+      </c>
+      <c r="B76" t="s">
         <v>269</v>
-      </c>
-      <c r="B76" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
+        <v>270</v>
+      </c>
+      <c r="B77" t="s">
         <v>271</v>
-      </c>
-      <c r="B77" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
+        <v>272</v>
+      </c>
+      <c r="B78" t="s">
         <v>273</v>
-      </c>
-      <c r="B78" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
+        <v>274</v>
+      </c>
+      <c r="B79" t="s">
         <v>275</v>
-      </c>
-      <c r="B79" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -4619,7 +4619,7 @@
         <v>110</v>
       </c>
       <c r="B80" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -4627,7 +4627,7 @@
         <v>112</v>
       </c>
       <c r="B81" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -4635,7 +4635,7 @@
         <v>115</v>
       </c>
       <c r="B82" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -4643,183 +4643,183 @@
         <v>117</v>
       </c>
       <c r="B83" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
+        <v>280</v>
+      </c>
+      <c r="B84" t="s">
         <v>281</v>
-      </c>
-      <c r="B84" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
+        <v>282</v>
+      </c>
+      <c r="B85" t="s">
         <v>283</v>
-      </c>
-      <c r="B85" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
+        <v>284</v>
+      </c>
+      <c r="B86" t="s">
         <v>285</v>
-      </c>
-      <c r="B86" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
+        <v>286</v>
+      </c>
+      <c r="B87" t="s">
         <v>287</v>
-      </c>
-      <c r="B87" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
+        <v>288</v>
+      </c>
+      <c r="B88" t="s">
         <v>289</v>
-      </c>
-      <c r="B88" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
+        <v>290</v>
+      </c>
+      <c r="B89" t="s">
         <v>291</v>
-      </c>
-      <c r="B89" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
+        <v>292</v>
+      </c>
+      <c r="B90" t="s">
         <v>293</v>
-      </c>
-      <c r="B90" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
+        <v>294</v>
+      </c>
+      <c r="B91" t="s">
         <v>295</v>
-      </c>
-      <c r="B91" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
+        <v>296</v>
+      </c>
+      <c r="B92" t="s">
         <v>297</v>
-      </c>
-      <c r="B92" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
+        <v>298</v>
+      </c>
+      <c r="B93" t="s">
         <v>299</v>
-      </c>
-      <c r="B93" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
+        <v>300</v>
+      </c>
+      <c r="B94" t="s">
         <v>301</v>
-      </c>
-      <c r="B94" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
+        <v>302</v>
+      </c>
+      <c r="B95" t="s">
         <v>303</v>
-      </c>
-      <c r="B95" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
+        <v>304</v>
+      </c>
+      <c r="B96" t="s">
         <v>305</v>
-      </c>
-      <c r="B96" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
+        <v>306</v>
+      </c>
+      <c r="B97" t="s">
         <v>307</v>
-      </c>
-      <c r="B97" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
+        <v>308</v>
+      </c>
+      <c r="B98" t="s">
         <v>309</v>
-      </c>
-      <c r="B98" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
+        <v>310</v>
+      </c>
+      <c r="B99" t="s">
         <v>311</v>
-      </c>
-      <c r="B99" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
+        <v>312</v>
+      </c>
+      <c r="B100" t="s">
         <v>313</v>
-      </c>
-      <c r="B100" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
+        <v>314</v>
+      </c>
+      <c r="B101" t="s">
         <v>315</v>
-      </c>
-      <c r="B101" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
+        <v>316</v>
+      </c>
+      <c r="B102" t="s">
         <v>317</v>
-      </c>
-      <c r="B102" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
+        <v>318</v>
+      </c>
+      <c r="B103" t="s">
         <v>319</v>
-      </c>
-      <c r="B103" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
+        <v>320</v>
+      </c>
+      <c r="B104" t="s">
         <v>321</v>
-      </c>
-      <c r="B104" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
+        <v>322</v>
+      </c>
+      <c r="B105" t="s">
         <v>323</v>
-      </c>
-      <c r="B105" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -4827,7 +4827,7 @@
         <v>57</v>
       </c>
       <c r="B106" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -4835,7 +4835,7 @@
         <v>60</v>
       </c>
       <c r="B107" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -4843,7 +4843,7 @@
         <v>19</v>
       </c>
       <c r="B108" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -4851,7 +4851,7 @@
         <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -4859,7 +4859,7 @@
         <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -4867,7 +4867,7 @@
         <v>62</v>
       </c>
       <c r="B111" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -4875,7 +4875,7 @@
         <v>65</v>
       </c>
       <c r="B112" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -4883,7 +4883,7 @@
         <v>67</v>
       </c>
       <c r="B113" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -4891,7 +4891,7 @@
         <v>68</v>
       </c>
       <c r="B114" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -4899,7 +4899,7 @@
         <v>71</v>
       </c>
       <c r="B115" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -4907,7 +4907,7 @@
         <v>73</v>
       </c>
       <c r="B116" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -4915,7 +4915,7 @@
         <v>75</v>
       </c>
       <c r="B117" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -4923,7 +4923,7 @@
         <v>77</v>
       </c>
       <c r="B118" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -4931,7 +4931,7 @@
         <v>35</v>
       </c>
       <c r="B119" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -4939,7 +4939,7 @@
         <v>78</v>
       </c>
       <c r="B120" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -4947,7 +4947,7 @@
         <v>80</v>
       </c>
       <c r="B121" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -4955,7 +4955,7 @@
         <v>83</v>
       </c>
       <c r="B122" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4963,7 +4963,7 @@
         <v>85</v>
       </c>
       <c r="B123" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4971,7 +4971,7 @@
         <v>86</v>
       </c>
       <c r="B124" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4979,7 +4979,7 @@
         <v>88</v>
       </c>
       <c r="B125" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -4987,7 +4987,7 @@
         <v>39</v>
       </c>
       <c r="B126" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4995,7 +4995,7 @@
         <v>90</v>
       </c>
       <c r="B127" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -5003,7 +5003,7 @@
         <v>92</v>
       </c>
       <c r="B128" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -5011,7 +5011,7 @@
         <v>45</v>
       </c>
       <c r="B129" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -5019,7 +5019,7 @@
         <v>94</v>
       </c>
       <c r="B130" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -5027,7 +5027,7 @@
         <v>96</v>
       </c>
       <c r="B131" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -5035,7 +5035,7 @@
         <v>99</v>
       </c>
       <c r="B132" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -5043,7 +5043,7 @@
         <v>101</v>
       </c>
       <c r="B133" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -5051,7 +5051,7 @@
         <v>104</v>
       </c>
       <c r="B134" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -5059,7 +5059,7 @@
         <v>50</v>
       </c>
       <c r="B135" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -5067,7 +5067,7 @@
         <v>106</v>
       </c>
       <c r="B136" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -5075,7 +5075,7 @@
         <v>26</v>
       </c>
       <c r="B137" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -5083,7 +5083,7 @@
         <v>28</v>
       </c>
       <c r="B138" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -5091,527 +5091,527 @@
         <v>31</v>
       </c>
       <c r="B139" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
+        <v>358</v>
+      </c>
+      <c r="B140" t="s">
         <v>359</v>
-      </c>
-      <c r="B140" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
+        <v>360</v>
+      </c>
+      <c r="B141" t="s">
         <v>361</v>
-      </c>
-      <c r="B141" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
+        <v>362</v>
+      </c>
+      <c r="B142" t="s">
         <v>363</v>
-      </c>
-      <c r="B142" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
+        <v>364</v>
+      </c>
+      <c r="B143" t="s">
         <v>365</v>
-      </c>
-      <c r="B143" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
+        <v>366</v>
+      </c>
+      <c r="B144" t="s">
         <v>367</v>
-      </c>
-      <c r="B144" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
+        <v>368</v>
+      </c>
+      <c r="B145" t="s">
         <v>369</v>
-      </c>
-      <c r="B145" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
+        <v>370</v>
+      </c>
+      <c r="B146" t="s">
         <v>371</v>
-      </c>
-      <c r="B146" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
+        <v>372</v>
+      </c>
+      <c r="B147" t="s">
         <v>373</v>
-      </c>
-      <c r="B147" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
+        <v>374</v>
+      </c>
+      <c r="B148" t="s">
         <v>375</v>
-      </c>
-      <c r="B148" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
+        <v>376</v>
+      </c>
+      <c r="B149" t="s">
         <v>377</v>
-      </c>
-      <c r="B149" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
+        <v>378</v>
+      </c>
+      <c r="B150" t="s">
         <v>379</v>
-      </c>
-      <c r="B150" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
+        <v>380</v>
+      </c>
+      <c r="B151" t="s">
         <v>381</v>
-      </c>
-      <c r="B151" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
+        <v>382</v>
+      </c>
+      <c r="B152" t="s">
         <v>383</v>
-      </c>
-      <c r="B152" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
+        <v>384</v>
+      </c>
+      <c r="B153" t="s">
         <v>385</v>
-      </c>
-      <c r="B153" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>386</v>
+      </c>
+      <c r="B154" t="s">
         <v>387</v>
-      </c>
-      <c r="B154" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>388</v>
+      </c>
+      <c r="B155" t="s">
         <v>389</v>
-      </c>
-      <c r="B155" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>390</v>
+      </c>
+      <c r="B156" t="s">
         <v>391</v>
-      </c>
-      <c r="B156" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>392</v>
+      </c>
+      <c r="B157" t="s">
         <v>393</v>
-      </c>
-      <c r="B157" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>394</v>
+      </c>
+      <c r="B158" t="s">
         <v>395</v>
-      </c>
-      <c r="B158" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
+        <v>396</v>
+      </c>
+      <c r="B159" t="s">
         <v>397</v>
-      </c>
-      <c r="B159" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
+        <v>398</v>
+      </c>
+      <c r="B160" t="s">
         <v>399</v>
-      </c>
-      <c r="B160" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>400</v>
+      </c>
+      <c r="B161" t="s">
         <v>401</v>
-      </c>
-      <c r="B161" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>402</v>
+      </c>
+      <c r="B162" t="s">
         <v>403</v>
-      </c>
-      <c r="B162" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>404</v>
+      </c>
+      <c r="B163" t="s">
         <v>405</v>
-      </c>
-      <c r="B163" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>406</v>
+      </c>
+      <c r="B164" t="s">
         <v>407</v>
-      </c>
-      <c r="B164" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>408</v>
+      </c>
+      <c r="B165" t="s">
         <v>409</v>
-      </c>
-      <c r="B165" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
+        <v>410</v>
+      </c>
+      <c r="B166" t="s">
         <v>411</v>
-      </c>
-      <c r="B166" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
+        <v>412</v>
+      </c>
+      <c r="B167" t="s">
         <v>413</v>
-      </c>
-      <c r="B167" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>414</v>
+      </c>
+      <c r="B168" t="s">
         <v>415</v>
-      </c>
-      <c r="B168" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
+        <v>416</v>
+      </c>
+      <c r="B169" t="s">
         <v>417</v>
-      </c>
-      <c r="B169" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>418</v>
+      </c>
+      <c r="B170" t="s">
         <v>419</v>
-      </c>
-      <c r="B170" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
+        <v>420</v>
+      </c>
+      <c r="B171" t="s">
         <v>421</v>
-      </c>
-      <c r="B171" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
+        <v>422</v>
+      </c>
+      <c r="B172" t="s">
         <v>423</v>
-      </c>
-      <c r="B172" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
+        <v>424</v>
+      </c>
+      <c r="B173" t="s">
         <v>425</v>
-      </c>
-      <c r="B173" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
+        <v>426</v>
+      </c>
+      <c r="B174" t="s">
         <v>427</v>
-      </c>
-      <c r="B174" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
+        <v>428</v>
+      </c>
+      <c r="B175" t="s">
         <v>429</v>
-      </c>
-      <c r="B175" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
+        <v>430</v>
+      </c>
+      <c r="B176" t="s">
         <v>431</v>
-      </c>
-      <c r="B176" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
+        <v>432</v>
+      </c>
+      <c r="B177" t="s">
         <v>433</v>
-      </c>
-      <c r="B177" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
+        <v>434</v>
+      </c>
+      <c r="B178" t="s">
         <v>435</v>
-      </c>
-      <c r="B178" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
+        <v>436</v>
+      </c>
+      <c r="B179" t="s">
         <v>437</v>
-      </c>
-      <c r="B179" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
+        <v>438</v>
+      </c>
+      <c r="B180" t="s">
         <v>439</v>
-      </c>
-      <c r="B180" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
+        <v>440</v>
+      </c>
+      <c r="B181" t="s">
         <v>441</v>
-      </c>
-      <c r="B181" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
+        <v>442</v>
+      </c>
+      <c r="B182" t="s">
         <v>443</v>
-      </c>
-      <c r="B182" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
+        <v>444</v>
+      </c>
+      <c r="B183" t="s">
         <v>445</v>
-      </c>
-      <c r="B183" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
+        <v>446</v>
+      </c>
+      <c r="B184" t="s">
         <v>447</v>
-      </c>
-      <c r="B184" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
+        <v>448</v>
+      </c>
+      <c r="B185" t="s">
         <v>449</v>
-      </c>
-      <c r="B185" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
+        <v>450</v>
+      </c>
+      <c r="B186" t="s">
         <v>451</v>
-      </c>
-      <c r="B186" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
+        <v>452</v>
+      </c>
+      <c r="B187" t="s">
         <v>453</v>
-      </c>
-      <c r="B187" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
+        <v>454</v>
+      </c>
+      <c r="B188" t="s">
         <v>455</v>
-      </c>
-      <c r="B188" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
+        <v>456</v>
+      </c>
+      <c r="B189" t="s">
         <v>457</v>
-      </c>
-      <c r="B189" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
+        <v>458</v>
+      </c>
+      <c r="B190" t="s">
         <v>459</v>
-      </c>
-      <c r="B190" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
+        <v>460</v>
+      </c>
+      <c r="B191" t="s">
         <v>461</v>
-      </c>
-      <c r="B191" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
+        <v>462</v>
+      </c>
+      <c r="B192" t="s">
         <v>463</v>
-      </c>
-      <c r="B192" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
+        <v>464</v>
+      </c>
+      <c r="B193" t="s">
         <v>465</v>
-      </c>
-      <c r="B193" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
+        <v>466</v>
+      </c>
+      <c r="B194" t="s">
         <v>467</v>
-      </c>
-      <c r="B194" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
+        <v>468</v>
+      </c>
+      <c r="B195" t="s">
         <v>469</v>
-      </c>
-      <c r="B195" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
+        <v>470</v>
+      </c>
+      <c r="B196" t="s">
         <v>471</v>
-      </c>
-      <c r="B196" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
+        <v>472</v>
+      </c>
+      <c r="B197" t="s">
         <v>473</v>
-      </c>
-      <c r="B197" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
+        <v>474</v>
+      </c>
+      <c r="B198" t="s">
         <v>475</v>
-      </c>
-      <c r="B198" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
+        <v>476</v>
+      </c>
+      <c r="B199" t="s">
         <v>477</v>
-      </c>
-      <c r="B199" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
+        <v>478</v>
+      </c>
+      <c r="B200" t="s">
         <v>479</v>
-      </c>
-      <c r="B200" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
+        <v>480</v>
+      </c>
+      <c r="B201" t="s">
         <v>481</v>
-      </c>
-      <c r="B201" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
+        <v>482</v>
+      </c>
+      <c r="B202" t="s">
         <v>483</v>
-      </c>
-      <c r="B202" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
+        <v>485</v>
+      </c>
+      <c r="B204" t="s">
         <v>486</v>
-      </c>
-      <c r="B204" t="s">
-        <v>487</v>
       </c>
     </row>
   </sheetData>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E67A920-8BAB-4E48-B94C-42ABA1669C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B409462B-C139-495C-A213-750AA58B7004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1005" windowWidth="21600" windowHeight="14595" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="-90" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="511">
   <si>
     <t>image_url</t>
   </si>
@@ -1832,6 +1832,36 @@
   </si>
   <si>
     <t>35 kg</t>
+  </si>
+  <si>
+    <t>TS1881-G</t>
+  </si>
+  <si>
+    <t>TS1881-C</t>
+  </si>
+  <si>
+    <t>TS1571-G</t>
+  </si>
+  <si>
+    <t>TS1571-C</t>
+  </si>
+  <si>
+    <t>images/TS1571-G</t>
+  </si>
+  <si>
+    <t>images/TS1571-C</t>
+  </si>
+  <si>
+    <t>images/TS1881-G</t>
+  </si>
+  <si>
+    <t>images/TS1881-C</t>
+  </si>
+  <si>
+    <t>TS2551-C</t>
+  </si>
+  <si>
+    <t>images/TS2551-C</t>
   </si>
 </sst>
 </file>
@@ -1922,10 +1952,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M46" totalsRowShown="0">
-  <autoFilter ref="A1:M46" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M41">
-    <sortCondition ref="H1:H41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M51" totalsRowShown="0">
+  <autoFilter ref="A1:M51" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M46">
+    <sortCondition ref="H1:H46"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
@@ -2254,7 +2284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -2425,57 +2455,55 @@
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1">
       <c r="A5" t="s">
-        <v>277</v>
+        <v>510</v>
       </c>
       <c r="B5" t="s">
         <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>509</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="F5">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H5">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="21.75" customHeight="1">
       <c r="A6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B6" t="s">
         <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
       </c>
       <c r="F6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H6">
         <v>35</v>
@@ -2484,27 +2512,27 @@
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="21.75" customHeight="1">
       <c r="A7" t="s">
-        <v>324</v>
+        <v>279</v>
       </c>
       <c r="B7" t="s">
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>55</v>
@@ -2524,31 +2552,28 @@
       <c r="K7" t="s">
         <v>17</v>
       </c>
-      <c r="L7">
-        <v>40</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="21.75" customHeight="1">
       <c r="A8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F8">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="H8">
         <v>35</v>
@@ -2562,19 +2587,22 @@
       <c r="K8" t="s">
         <v>17</v>
       </c>
+      <c r="L8">
+        <v>40</v>
+      </c>
       <c r="M8" s="1" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="21.75" customHeight="1">
       <c r="A9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B9" t="s">
         <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
@@ -2598,18 +2626,18 @@
         <v>17</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="21.75" customHeight="1">
       <c r="A10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B10" t="s">
         <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
@@ -2638,57 +2666,57 @@
     </row>
     <row r="11" spans="1:13" ht="21.75" customHeight="1">
       <c r="A11" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="B11" t="s">
         <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H11">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K11" t="s">
         <v>17</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1">
       <c r="A12" t="s">
-        <v>325</v>
+        <v>278</v>
       </c>
       <c r="B12" t="s">
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H12">
         <v>40</v>
@@ -2697,100 +2725,97 @@
         <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K12" t="s">
         <v>17</v>
       </c>
-      <c r="L12">
-        <v>45</v>
-      </c>
       <c r="M12" s="1" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="21.75" customHeight="1">
       <c r="A13" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>488</v>
+        <v>58</v>
       </c>
       <c r="F13">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H13">
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>43</v>
+        <v>17</v>
+      </c>
+      <c r="L13">
+        <v>45</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="21.75" customHeight="1">
       <c r="A14" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>488</v>
       </c>
       <c r="F14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H14">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="K14" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.75" customHeight="1">
       <c r="A15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B15" t="s">
         <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -2808,7 +2833,7 @@
         <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K15" t="s">
         <v>17</v>
@@ -2817,56 +2842,56 @@
         <v>41</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="21.75" customHeight="1">
       <c r="A16" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G16" t="s">
         <v>20</v>
       </c>
       <c r="H16">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I16" t="s">
         <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L16">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="21.75" customHeight="1">
       <c r="A17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B17" t="s">
         <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
         <v>58</v>
@@ -2898,22 +2923,22 @@
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1">
       <c r="A18" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B18" t="s">
         <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
         <v>58</v>
       </c>
       <c r="F18">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H18">
         <v>45</v>
@@ -2931,30 +2956,30 @@
         <v>50</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="21.75" customHeight="1">
       <c r="A19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B19" t="s">
         <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
       </c>
       <c r="F19">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
       </c>
       <c r="H19">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="I19" t="s">
         <v>15</v>
@@ -2966,21 +2991,21 @@
         <v>33</v>
       </c>
       <c r="L19">
-        <v>55.5</v>
+        <v>50</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="21.75" customHeight="1">
       <c r="A20" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
         <v>58</v>
@@ -3004,21 +3029,21 @@
         <v>33</v>
       </c>
       <c r="L20">
-        <v>60.5</v>
+        <v>55.5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="21.75" customHeight="1">
       <c r="A21" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B21" t="s">
         <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
         <v>58</v>
@@ -3050,22 +3075,22 @@
     </row>
     <row r="22" spans="1:13" ht="21.75" customHeight="1">
       <c r="A22" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="B22" t="s">
         <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F22">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H22">
         <v>45.5</v>
@@ -3074,68 +3099,68 @@
         <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="K22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L22">
-        <v>55.5</v>
+        <v>60.5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="21.75" customHeight="1">
       <c r="A23" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F23">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H23">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="I23" t="s">
         <v>15</v>
       </c>
       <c r="J23" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" t="s">
         <v>32</v>
       </c>
-      <c r="K23" t="s">
-        <v>33</v>
-      </c>
       <c r="L23">
-        <v>60</v>
+        <v>55.5</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1">
       <c r="A24" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B24" t="s">
         <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F24">
         <v>75</v>
@@ -3144,299 +3169,299 @@
         <v>14</v>
       </c>
       <c r="H24">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="I24" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="J24" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K24" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="L24">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1">
       <c r="A25" t="s">
-        <v>332</v>
+        <v>505</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>503</v>
       </c>
       <c r="E25" t="s">
-        <v>488</v>
+        <v>58</v>
       </c>
       <c r="F25">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H25">
-        <v>65.5</v>
+        <v>50</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="J25" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="K25" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="L25">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1">
       <c r="A26" t="s">
-        <v>339</v>
+        <v>506</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>504</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
       </c>
       <c r="F26">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H26">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I26" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="J26" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="K26" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="L26">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="21.75" customHeight="1">
       <c r="A27" t="s">
-        <v>159</v>
+        <v>337</v>
       </c>
       <c r="B27" t="s">
         <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>487</v>
+        <v>36</v>
       </c>
       <c r="F27">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
       </c>
       <c r="H27">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I27" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="K27" t="s">
         <v>17</v>
       </c>
+      <c r="L27">
+        <v>70</v>
+      </c>
       <c r="M27" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="21.75" customHeight="1">
       <c r="A28" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="B28" t="s">
         <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>58</v>
+        <v>488</v>
       </c>
       <c r="F28">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G28" t="s">
         <v>40</v>
       </c>
       <c r="H28">
-        <v>90</v>
+        <v>65.5</v>
       </c>
       <c r="I28" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="J28" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="K28" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="21.75" customHeight="1">
       <c r="A29" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B29" t="s">
         <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
         <v>58</v>
       </c>
       <c r="F29">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
         <v>40</v>
       </c>
       <c r="H29">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="I29" t="s">
         <v>41</v>
       </c>
       <c r="J29" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="K29" t="s">
         <v>43</v>
       </c>
       <c r="L29">
-        <v>105.9</v>
+        <v>90</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1">
       <c r="A30" t="s">
-        <v>342</v>
+        <v>159</v>
       </c>
       <c r="B30" t="s">
         <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>58</v>
+        <v>487</v>
       </c>
       <c r="F30">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G30" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H30">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="I30" t="s">
         <v>41</v>
       </c>
       <c r="J30" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="K30" t="s">
-        <v>43</v>
-      </c>
-      <c r="L30">
-        <v>105.9</v>
+        <v>17</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1">
       <c r="A31" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E31" t="s">
         <v>58</v>
       </c>
       <c r="F31">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H31">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="I31" t="s">
         <v>41</v>
       </c>
       <c r="J31" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s">
         <v>43</v>
       </c>
       <c r="L31">
-        <v>105.9</v>
+        <v>100</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1">
       <c r="A32" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s">
         <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F32">
         <v>86</v>
@@ -3460,18 +3485,18 @@
         <v>105.9</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1">
       <c r="A33" t="s">
-        <v>341</v>
+        <v>507</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>501</v>
       </c>
       <c r="E33" t="s">
         <v>58</v>
@@ -3503,139 +3528,139 @@
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1">
       <c r="A34" t="s">
-        <v>346</v>
+        <v>508</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>502</v>
       </c>
       <c r="E34" t="s">
         <v>58</v>
       </c>
       <c r="F34">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="G34" t="s">
         <v>40</v>
       </c>
       <c r="H34">
-        <v>120</v>
+        <v>90.9</v>
       </c>
       <c r="I34" t="s">
         <v>41</v>
       </c>
       <c r="J34" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K34" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L34">
-        <v>130</v>
+        <v>105.9</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="21.75" customHeight="1">
       <c r="A35" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F35">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="G35" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H35">
-        <v>120</v>
+        <v>90.9</v>
       </c>
       <c r="I35" t="s">
         <v>41</v>
       </c>
       <c r="J35" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L35">
-        <v>130</v>
+        <v>105.9</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="21.75" customHeight="1">
       <c r="A36" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s">
         <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E36" t="s">
         <v>58</v>
       </c>
       <c r="F36">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="G36" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H36">
-        <v>120</v>
+        <v>90.9</v>
       </c>
       <c r="I36" t="s">
         <v>41</v>
       </c>
       <c r="J36" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K36" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L36">
-        <v>150</v>
+        <v>105.9</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="21.75" customHeight="1">
       <c r="A37" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s">
         <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E37" t="s">
         <v>36</v>
       </c>
       <c r="F37">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="G37" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H37">
-        <v>120</v>
+        <v>90.9</v>
       </c>
       <c r="I37" t="s">
         <v>41</v>
@@ -3647,74 +3672,74 @@
         <v>43</v>
       </c>
       <c r="L37">
-        <v>125</v>
+        <v>105.9</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="26.25" customHeight="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="21.75" customHeight="1">
       <c r="A38" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s">
         <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E38" t="s">
         <v>58</v>
       </c>
       <c r="F38">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H38">
-        <v>120.5</v>
+        <v>90.9</v>
       </c>
       <c r="I38" t="s">
         <v>41</v>
       </c>
       <c r="J38" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="K38" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L38">
-        <v>125</v>
+        <v>105.9</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="26.25" customHeight="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="E39" t="s">
         <v>58</v>
       </c>
       <c r="F39">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G39" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H39">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I39" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J39" t="s">
         <v>47</v>
@@ -3723,24 +3748,24 @@
         <v>48</v>
       </c>
       <c r="L39">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="26.25" customHeight="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="21.75" customHeight="1">
       <c r="A40" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s">
         <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="E40" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F40">
         <v>100</v>
@@ -3749,10 +3774,10 @@
         <v>40</v>
       </c>
       <c r="H40">
-        <v>136.4</v>
+        <v>120</v>
       </c>
       <c r="I40" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J40" t="s">
         <v>47</v>
@@ -3760,135 +3785,151 @@
       <c r="K40" t="s">
         <v>48</v>
       </c>
+      <c r="L40">
+        <v>130</v>
+      </c>
       <c r="M40" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="26.25" customHeight="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="21.75" customHeight="1">
       <c r="A41" t="s">
-        <v>121</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s">
         <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="E41" t="s">
-        <v>487</v>
+        <v>58</v>
       </c>
       <c r="F41">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="G41" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H41">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="I41" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J41" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K41" t="s">
-        <v>33</v>
+        <v>48</v>
+      </c>
+      <c r="L41">
+        <v>150</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A42" s="2" t="s">
-        <v>493</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A42" t="s">
+        <v>353</v>
       </c>
       <c r="B42" t="s">
         <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>489</v>
+        <v>50</v>
       </c>
       <c r="E42" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F42">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="G42" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="H42">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I42" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="J42" t="s">
-        <v>491</v>
+        <v>42</v>
       </c>
       <c r="K42" t="s">
-        <v>32</v>
-      </c>
-      <c r="M42" s="1"/>
-    </row>
-    <row r="43" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A43" s="2" t="s">
-        <v>492</v>
+        <v>43</v>
+      </c>
+      <c r="L42">
+        <v>125</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A43" t="s">
+        <v>349</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>490</v>
+        <v>96</v>
       </c>
       <c r="E43" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F43">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G43" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="H43">
-        <v>60</v>
+        <v>120.5</v>
       </c>
       <c r="I43" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="J43" t="s">
-        <v>491</v>
+        <v>97</v>
       </c>
       <c r="K43" t="s">
-        <v>32</v>
-      </c>
-      <c r="M43" s="1"/>
-    </row>
-    <row r="44" spans="1:13" ht="30" customHeight="1">
-      <c r="A44" s="3" t="s">
-        <v>497</v>
+        <v>48</v>
+      </c>
+      <c r="L43">
+        <v>125</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A44" t="s">
+        <v>354</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>494</v>
+        <v>106</v>
       </c>
       <c r="E44" t="s">
-        <v>487</v>
+        <v>58</v>
       </c>
       <c r="F44">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G44" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="H44">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="I44" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="J44" t="s">
         <v>47</v>
@@ -3896,20 +3937,25 @@
       <c r="K44" t="s">
         <v>48</v>
       </c>
-      <c r="M44" s="1"/>
-    </row>
-    <row r="45" spans="1:13" ht="30" customHeight="1">
-      <c r="A45" s="3" t="s">
-        <v>498</v>
+      <c r="L44">
+        <v>145</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A45" t="s">
+        <v>352</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>495</v>
+        <v>104</v>
       </c>
       <c r="E45" t="s">
-        <v>487</v>
+        <v>54</v>
       </c>
       <c r="F45">
         <v>100</v>
@@ -3918,10 +3964,10 @@
         <v>40</v>
       </c>
       <c r="H45">
-        <v>100</v>
+        <v>136.4</v>
       </c>
       <c r="I45" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="J45" t="s">
         <v>47</v>
@@ -3929,40 +3975,209 @@
       <c r="K45" t="s">
         <v>48</v>
       </c>
-      <c r="M45" s="1"/>
-    </row>
-    <row r="46" spans="1:13" ht="30" customHeight="1">
-      <c r="A46" s="3" t="s">
-        <v>499</v>
+      <c r="M45" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A46" t="s">
+        <v>121</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>496</v>
+        <v>53</v>
       </c>
       <c r="E46" t="s">
         <v>487</v>
       </c>
       <c r="F46">
+        <v>55</v>
+      </c>
+      <c r="G46" t="s">
+        <v>55</v>
+      </c>
+      <c r="H46">
+        <v>200</v>
+      </c>
+      <c r="I46" t="s">
+        <v>46</v>
+      </c>
+      <c r="J46" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" t="s">
+        <v>33</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="27.75" customHeight="1">
+      <c r="A47" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>489</v>
+      </c>
+      <c r="E47" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47">
+        <v>75</v>
+      </c>
+      <c r="G47" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47">
+        <v>60</v>
+      </c>
+      <c r="I47" t="s">
+        <v>15</v>
+      </c>
+      <c r="J47" t="s">
+        <v>491</v>
+      </c>
+      <c r="K47" t="s">
+        <v>32</v>
+      </c>
+      <c r="M47" s="1"/>
+    </row>
+    <row r="48" spans="1:13" ht="32.25" customHeight="1">
+      <c r="A48" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
+        <v>490</v>
+      </c>
+      <c r="E48" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48">
+        <v>75</v>
+      </c>
+      <c r="G48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48">
+        <v>60</v>
+      </c>
+      <c r="I48" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" t="s">
+        <v>491</v>
+      </c>
+      <c r="K48" t="s">
+        <v>32</v>
+      </c>
+      <c r="M48" s="1"/>
+    </row>
+    <row r="49" spans="1:13" ht="30" customHeight="1">
+      <c r="A49" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" t="s">
+        <v>494</v>
+      </c>
+      <c r="E49" t="s">
+        <v>487</v>
+      </c>
+      <c r="F49">
         <v>100</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G49" t="s">
         <v>40</v>
       </c>
-      <c r="H46">
+      <c r="H49">
         <v>100</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I49" t="s">
         <v>119</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J49" t="s">
         <v>47</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K49" t="s">
         <v>48</v>
       </c>
-      <c r="M46" s="1"/>
+      <c r="M49" s="1"/>
+    </row>
+    <row r="50" spans="1:13" ht="30" customHeight="1">
+      <c r="A50" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
+        <v>495</v>
+      </c>
+      <c r="E50" t="s">
+        <v>487</v>
+      </c>
+      <c r="F50">
+        <v>100</v>
+      </c>
+      <c r="G50" t="s">
+        <v>40</v>
+      </c>
+      <c r="H50">
+        <v>100</v>
+      </c>
+      <c r="I50" t="s">
+        <v>119</v>
+      </c>
+      <c r="J50" t="s">
+        <v>47</v>
+      </c>
+      <c r="K50" t="s">
+        <v>48</v>
+      </c>
+      <c r="M50" s="1"/>
+    </row>
+    <row r="51" spans="1:13" ht="30" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" t="s">
+        <v>496</v>
+      </c>
+      <c r="E51" t="s">
+        <v>487</v>
+      </c>
+      <c r="F51">
+        <v>100</v>
+      </c>
+      <c r="G51" t="s">
+        <v>40</v>
+      </c>
+      <c r="H51">
+        <v>100</v>
+      </c>
+      <c r="I51" t="s">
+        <v>119</v>
+      </c>
+      <c r="J51" t="s">
+        <v>47</v>
+      </c>
+      <c r="K51" t="s">
+        <v>48</v>
+      </c>
+      <c r="M51" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B409462B-C139-495C-A213-750AA58B7004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502F6703-4ED0-4E6F-B120-69E6DCCCA0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1846,22 +1846,22 @@
     <t>TS1571-C</t>
   </si>
   <si>
-    <t>images/TS1571-G</t>
-  </si>
-  <si>
-    <t>images/TS1571-C</t>
-  </si>
-  <si>
-    <t>images/TS1881-G</t>
-  </si>
-  <si>
-    <t>images/TS1881-C</t>
-  </si>
-  <si>
     <t>TS2551-C</t>
   </si>
   <si>
     <t>images/TS2551-C</t>
+  </si>
+  <si>
+    <t>images/1571-G</t>
+  </si>
+  <si>
+    <t>images/1571-C</t>
+  </si>
+  <si>
+    <t>images/1881-G</t>
+  </si>
+  <si>
+    <t>images/1881-C</t>
   </si>
 </sst>
 </file>
@@ -2455,13 +2455,13 @@
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1">
       <c r="A5" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B5" t="s">
         <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E5" t="s">
         <v>54</v>
@@ -3189,7 +3189,7 @@
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1">
       <c r="A25" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1">
       <c r="A26" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1">
       <c r="A33" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1">
       <c r="A34" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502F6703-4ED0-4E6F-B120-69E6DCCCA0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781FAED2-67BB-4F22-834F-5F10B954CEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="-90" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1834,12 +1834,6 @@
     <t>35 kg</t>
   </si>
   <si>
-    <t>TS1881-G</t>
-  </si>
-  <si>
-    <t>TS1881-C</t>
-  </si>
-  <si>
     <t>TS1571-G</t>
   </si>
   <si>
@@ -1858,10 +1852,16 @@
     <t>images/1571-C</t>
   </si>
   <si>
-    <t>images/1881-G</t>
-  </si>
-  <si>
-    <t>images/1881-C</t>
+    <t>images/1871-G</t>
+  </si>
+  <si>
+    <t>images/1871-C</t>
+  </si>
+  <si>
+    <t>TS1871-G</t>
+  </si>
+  <si>
+    <t>TS1871-C</t>
   </si>
 </sst>
 </file>
@@ -2455,13 +2455,13 @@
     </row>
     <row r="5" spans="1:13" ht="21.75" customHeight="1">
       <c r="A5" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B5" t="s">
         <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E5" t="s">
         <v>54</v>
@@ -3189,13 +3189,13 @@
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1">
       <c r="A25" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E25" t="s">
         <v>58</v>
@@ -3227,13 +3227,13 @@
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1">
       <c r="A26" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
@@ -3379,48 +3379,51 @@
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1">
       <c r="A30" t="s">
-        <v>159</v>
+        <v>507</v>
       </c>
       <c r="B30" t="s">
         <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>509</v>
       </c>
       <c r="E30" t="s">
-        <v>487</v>
+        <v>58</v>
       </c>
       <c r="F30">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H30">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I30" t="s">
         <v>41</v>
       </c>
       <c r="J30" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="K30" t="s">
-        <v>17</v>
+        <v>43</v>
+      </c>
+      <c r="L30">
+        <v>90</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1">
       <c r="A31" t="s">
-        <v>345</v>
+        <v>508</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>510</v>
       </c>
       <c r="E31" t="s">
         <v>58</v>
@@ -3432,7 +3435,7 @@
         <v>40</v>
       </c>
       <c r="H31">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I31" t="s">
         <v>41</v>
@@ -3444,97 +3447,94 @@
         <v>43</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1">
       <c r="A32" t="s">
-        <v>340</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
         <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>487</v>
       </c>
       <c r="F32">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G32" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H32">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="I32" t="s">
         <v>41</v>
       </c>
       <c r="J32" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="K32" t="s">
-        <v>43</v>
-      </c>
-      <c r="L32">
-        <v>105.9</v>
+        <v>17</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1">
       <c r="A33" t="s">
-        <v>509</v>
+        <v>345</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>501</v>
+        <v>90</v>
       </c>
       <c r="E33" t="s">
         <v>58</v>
       </c>
       <c r="F33">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s">
         <v>40</v>
       </c>
       <c r="H33">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s">
         <v>41</v>
       </c>
       <c r="J33" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="K33" t="s">
         <v>43</v>
       </c>
       <c r="L33">
-        <v>105.9</v>
+        <v>100</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1">
       <c r="A34" t="s">
-        <v>510</v>
+        <v>340</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>502</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
         <v>58</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781FAED2-67BB-4F22-834F-5F10B954CEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA6A545-CB4C-4681-B4F9-34F3F901B4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="img" sheetId="2" r:id="rId2"/>
+    <sheet name="old" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="514">
   <si>
     <t>image_url</t>
   </si>
@@ -1862,6 +1863,15 @@
   </si>
   <si>
     <t>TS1871-C</t>
+  </si>
+  <si>
+    <t>dual screen</t>
+  </si>
+  <si>
+    <t>DS-5201</t>
+  </si>
+  <si>
+    <t>images/DS-5201</t>
   </si>
 </sst>
 </file>
@@ -1934,7 +1944,10 @@
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1952,10 +1965,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M51" totalsRowShown="0">
-  <autoFilter ref="A1:M51" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M46">
-    <sortCondition ref="H1:H46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M48" totalsRowShown="0">
+  <autoFilter ref="A1:M48" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M47">
+    <sortCondition ref="C1:C47"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
@@ -1970,7 +1983,7 @@
     <tableColumn id="9" xr3:uid="{FA17DC80-D978-4A1C-8033-2A8B8A61EABD}" name="максимальная VESA"/>
     <tableColumn id="10" xr3:uid="{844FF9E0-D79C-4C59-B169-CB34BA723E23}" name="VESA category"/>
     <tableColumn id="11" xr3:uid="{9F8B31B3-F312-425E-89BF-123F5E4B613A}" name="максимальная суммарная нагрузка (с полками) кг"/>
-    <tableColumn id="12" xr3:uid="{0F283AEA-EC94-4998-A426-87373DA19291}" name="описание" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{0F283AEA-EC94-4998-A426-87373DA19291}" name="описание" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1982,6 +1995,31 @@
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{8F01485B-76C2-443F-A37A-0C0236333F67}" name="SKU"/>
     <tableColumn id="2" xr3:uid="{86E2293B-CA96-4AEA-B8AC-69E65ADA7FF6}" name="Image url"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D96137D9-2B71-48AC-A7E9-D96437E261BC}" name="Таблица14" displayName="Таблица14" ref="A1:M51" totalsRowShown="0">
+  <autoFilter ref="A1:M51" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M51">
+    <sortCondition ref="C1:C51"/>
+  </sortState>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{54AD82BD-2B08-4F9A-842A-ED8A5A8DD480}" name="image_url"/>
+    <tableColumn id="13" xr3:uid="{A6A0D78A-537E-4CAB-AB90-A0692E1FF8BA}" name="Domain"/>
+    <tableColumn id="2" xr3:uid="{0945D5AB-0111-4C70-BF77-4318D20A8171}" name="sku"/>
+    <tableColumn id="3" xr3:uid="{C2A66CCC-EB14-4AAD-9D49-93EED63C4E55}" name="image"/>
+    <tableColumn id="4" xr3:uid="{3AC7768C-7C67-4C59-B88D-5B6B336375F6}" name="Type"/>
+    <tableColumn id="5" xr3:uid="{64B6A584-1CCA-4D2D-834E-DA59BCDA26E0}" name="максимальная диагональ"/>
+    <tableColumn id="6" xr3:uid="{D5AB3E49-2322-4282-AFAB-08B474DBF266}" name="Diagonal category"/>
+    <tableColumn id="7" xr3:uid="{D0C09914-A5A6-4D23-9B7E-48F6376F53F3}" name="максимальная нагрузка кг"/>
+    <tableColumn id="8" xr3:uid="{6CEF3EAC-4BB9-4B5B-B9BD-0A78D6A913CE}" name="Load capacity category kg"/>
+    <tableColumn id="9" xr3:uid="{D3E2FA1B-F732-4C56-B22B-8D7D0173021F}" name="максимальная VESA"/>
+    <tableColumn id="10" xr3:uid="{B1101660-298E-4F38-8984-6368AB15A151}" name="VESA category"/>
+    <tableColumn id="11" xr3:uid="{F88613B8-CF27-4717-8453-AF8BCA026DCD}" name="максимальная суммарная нагрузка (с полками) кг"/>
+    <tableColumn id="12" xr3:uid="{7731229F-69CD-4BCC-A6A6-A67A0A12F756}" name="описание" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2284,7 +2322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -2344,63 +2382,63 @@
     </row>
     <row r="2" spans="1:13" ht="21.75" customHeight="1">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>487</v>
       </c>
       <c r="F2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>500</v>
+        <v>41</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
         <v>17</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="21.75" customHeight="1">
       <c r="A3" t="s">
-        <v>357</v>
+        <v>121</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>487</v>
       </c>
       <c r="F3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="H3">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="I3" t="s">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -2408,128 +2446,118 @@
       <c r="K3" t="s">
         <v>33</v>
       </c>
-      <c r="L3">
+      <c r="M3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>496</v>
+      </c>
+      <c r="E4" t="s">
+        <v>487</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4">
-        <v>60</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
       <c r="H4">
-        <v>30.5</v>
+        <v>100</v>
       </c>
       <c r="I4" t="s">
-        <v>500</v>
+        <v>119</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4">
-        <v>32.5</v>
-      </c>
-      <c r="M4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E5" t="s">
+        <v>487</v>
+      </c>
+      <c r="F5">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A5" t="s">
-        <v>504</v>
-      </c>
-      <c r="B5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" t="s">
-        <v>503</v>
-      </c>
-      <c r="E5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5">
-        <v>75</v>
-      </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>494</v>
+      </c>
+      <c r="E6" t="s">
+        <v>487</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6" t="s">
         <v>40</v>
       </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A6" t="s">
-        <v>277</v>
-      </c>
-      <c r="B6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>65</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
       <c r="H6">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="J6" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" ht="21.75" customHeight="1">
       <c r="A7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B7" t="s">
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -2541,10 +2569,10 @@
         <v>55</v>
       </c>
       <c r="H7">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -2553,27 +2581,27 @@
         <v>17</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="21.75" customHeight="1">
       <c r="A8" t="s">
-        <v>324</v>
+        <v>277</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H8">
         <v>35</v>
@@ -2582,71 +2610,68 @@
         <v>15</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
       </c>
-      <c r="L8">
-        <v>40</v>
-      </c>
       <c r="M8" s="1" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="21.75" customHeight="1">
       <c r="A9" t="s">
-        <v>326</v>
+        <v>278</v>
       </c>
       <c r="B9" t="s">
         <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H9">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="21.75" customHeight="1">
       <c r="A10" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
       <c r="B10" t="s">
         <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="H10">
         <v>35</v>
@@ -2661,27 +2686,27 @@
         <v>17</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="21.75" customHeight="1">
       <c r="A11" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B11" t="s">
         <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F11">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="H11">
         <v>35</v>
@@ -2695,28 +2720,31 @@
       <c r="K11" t="s">
         <v>17</v>
       </c>
+      <c r="L11">
+        <v>40</v>
+      </c>
       <c r="M11" s="1" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="21.75" customHeight="1">
       <c r="A12" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="B12" t="s">
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F12">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H12">
         <v>40</v>
@@ -2725,36 +2753,39 @@
         <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
         <v>17</v>
       </c>
+      <c r="L12">
+        <v>45</v>
+      </c>
       <c r="M12" s="1" t="s">
-        <v>116</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="21.75" customHeight="1">
       <c r="A13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
         <v>20</v>
       </c>
       <c r="H13">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
@@ -2765,133 +2796,127 @@
       <c r="K13" t="s">
         <v>17</v>
       </c>
-      <c r="L13">
-        <v>45</v>
-      </c>
       <c r="M13" s="1" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="21.75" customHeight="1">
       <c r="A14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>488</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H14">
-        <v>40.5</v>
+        <v>35</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="K14" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="21.75" customHeight="1">
       <c r="A15" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="B15" t="s">
         <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>488</v>
       </c>
       <c r="F15">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G15" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H15">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="21.75" customHeight="1">
       <c r="A16" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
         <v>20</v>
       </c>
       <c r="H16">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I16" t="s">
         <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K16" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="L16">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="21.75" customHeight="1">
       <c r="A17" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B17" t="s">
         <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>58</v>
@@ -2923,63 +2948,63 @@
     </row>
     <row r="18" spans="1:13" ht="21.75" customHeight="1">
       <c r="A18" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B18" t="s">
         <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>488</v>
       </c>
       <c r="F18">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H18">
-        <v>45</v>
+        <v>65.5</v>
       </c>
       <c r="I18" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="J18" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L18">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="21.75" customHeight="1">
       <c r="A19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B19" t="s">
         <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
       </c>
       <c r="F19">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
       </c>
       <c r="H19">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="I19" t="s">
         <v>15</v>
@@ -2991,33 +3016,33 @@
         <v>33</v>
       </c>
       <c r="L19">
-        <v>50</v>
+        <v>55.5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="21.75" customHeight="1">
       <c r="A20" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
         <v>58</v>
       </c>
       <c r="F20">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
         <v>14</v>
       </c>
       <c r="H20">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="I20" t="s">
         <v>15</v>
@@ -3029,71 +3054,71 @@
         <v>33</v>
       </c>
       <c r="L20">
-        <v>55.5</v>
+        <v>50</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="21.75" customHeight="1">
       <c r="A21" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B21" t="s">
         <v>109</v>
       </c>
       <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21">
         <v>75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21">
-        <v>70</v>
       </c>
       <c r="G21" t="s">
         <v>14</v>
       </c>
       <c r="H21">
-        <v>45.5</v>
+        <v>65</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="J21" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L21">
-        <v>60.5</v>
+        <v>70</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="21.75" customHeight="1">
       <c r="A22" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B22" t="s">
         <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
         <v>58</v>
       </c>
       <c r="F22">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
       </c>
       <c r="H22">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
@@ -3105,59 +3130,59 @@
         <v>33</v>
       </c>
       <c r="L22">
-        <v>60.5</v>
+        <v>60</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="21.75" customHeight="1">
       <c r="A23" t="s">
-        <v>351</v>
+        <v>506</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>502</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F23">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H23">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="I23" t="s">
         <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="K23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L23">
-        <v>55.5</v>
+        <v>60</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1">
       <c r="A24" t="s">
-        <v>338</v>
+        <v>505</v>
       </c>
       <c r="B24" t="s">
         <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>501</v>
       </c>
       <c r="E24" t="s">
         <v>58</v>
@@ -3188,17 +3213,17 @@
       </c>
     </row>
     <row r="25" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A25" t="s">
-        <v>505</v>
+      <c r="A25" s="2" t="s">
+        <v>492</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="E25" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F25">
         <v>75</v>
@@ -3207,36 +3232,31 @@
         <v>14</v>
       </c>
       <c r="H25">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
       </c>
       <c r="J25" t="s">
+        <v>491</v>
+      </c>
+      <c r="K25" t="s">
         <v>32</v>
       </c>
-      <c r="K25" t="s">
-        <v>33</v>
-      </c>
-      <c r="L25">
-        <v>60</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A26" t="s">
-        <v>506</v>
+      <c r="A26" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F26">
         <v>75</v>
@@ -3245,109 +3265,104 @@
         <v>14</v>
       </c>
       <c r="H26">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
       </c>
       <c r="J26" t="s">
+        <v>491</v>
+      </c>
+      <c r="K26" t="s">
         <v>32</v>
       </c>
-      <c r="K26" t="s">
-        <v>33</v>
-      </c>
-      <c r="L26">
-        <v>60</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="M26" s="1"/>
     </row>
     <row r="27" spans="1:13" ht="21.75" customHeight="1">
       <c r="A27" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B27" t="s">
         <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F27">
+        <v>90</v>
+      </c>
+      <c r="G27" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27">
         <v>75</v>
       </c>
-      <c r="G27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27">
-        <v>65</v>
-      </c>
       <c r="I27" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="J27" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="K27" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L27">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="21.75" customHeight="1">
       <c r="A28" t="s">
-        <v>332</v>
+        <v>508</v>
       </c>
       <c r="B28" t="s">
         <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>510</v>
       </c>
       <c r="E28" t="s">
-        <v>488</v>
+        <v>58</v>
       </c>
       <c r="F28">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s">
         <v>40</v>
       </c>
       <c r="H28">
-        <v>65.5</v>
+        <v>75</v>
       </c>
       <c r="I28" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="J28" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="K28" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L28">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="21.75" customHeight="1">
       <c r="A29" t="s">
-        <v>339</v>
+        <v>507</v>
       </c>
       <c r="B29" t="s">
         <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>509</v>
       </c>
       <c r="E29" t="s">
         <v>58</v>
@@ -3379,162 +3394,165 @@
     </row>
     <row r="30" spans="1:13" ht="21.75" customHeight="1">
       <c r="A30" t="s">
-        <v>507</v>
+        <v>340</v>
       </c>
       <c r="B30" t="s">
         <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>509</v>
+        <v>83</v>
       </c>
       <c r="E30" t="s">
         <v>58</v>
       </c>
       <c r="F30">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G30" t="s">
         <v>40</v>
       </c>
       <c r="H30">
-        <v>75</v>
+        <v>90.9</v>
       </c>
       <c r="I30" t="s">
         <v>41</v>
       </c>
       <c r="J30" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="K30" t="s">
         <v>43</v>
       </c>
       <c r="L30">
-        <v>90</v>
+        <v>105.9</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="21.75" customHeight="1">
       <c r="A31" t="s">
-        <v>508</v>
+        <v>342</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>510</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s">
         <v>58</v>
       </c>
       <c r="F31">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="G31" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H31">
-        <v>75</v>
+        <v>90.9</v>
       </c>
       <c r="I31" t="s">
         <v>41</v>
       </c>
       <c r="J31" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="K31" t="s">
         <v>43</v>
       </c>
       <c r="L31">
-        <v>90</v>
+        <v>105.9</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="21.75" customHeight="1">
       <c r="A32" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
       <c r="B32" t="s">
         <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>487</v>
+        <v>58</v>
       </c>
       <c r="F32">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G32" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H32">
-        <v>90</v>
+        <v>90.9</v>
       </c>
       <c r="I32" t="s">
         <v>41</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="K32" t="s">
-        <v>17</v>
+        <v>43</v>
+      </c>
+      <c r="L32">
+        <v>105.9</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="21.75" customHeight="1">
       <c r="A33" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F33">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s">
         <v>40</v>
       </c>
       <c r="H33">
-        <v>90</v>
+        <v>90.9</v>
       </c>
       <c r="I33" t="s">
         <v>41</v>
       </c>
       <c r="J33" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="K33" t="s">
         <v>43</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>105.9</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="21.75" customHeight="1">
       <c r="A34" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E34" t="s">
         <v>58</v>
@@ -3566,347 +3584,342 @@
     </row>
     <row r="35" spans="1:13" ht="21.75" customHeight="1">
       <c r="A35" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E35" t="s">
         <v>58</v>
       </c>
       <c r="F35">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H35">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s">
         <v>41</v>
       </c>
       <c r="J35" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="K35" t="s">
         <v>43</v>
       </c>
       <c r="L35">
-        <v>105.9</v>
+        <v>100</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="21.75" customHeight="1">
       <c r="A36" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B36" t="s">
         <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E36" t="s">
         <v>58</v>
       </c>
       <c r="F36">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="G36" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H36">
-        <v>90.9</v>
+        <v>120</v>
       </c>
       <c r="I36" t="s">
         <v>41</v>
       </c>
       <c r="J36" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K36" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L36">
-        <v>105.9</v>
+        <v>130</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="21.75" customHeight="1">
       <c r="A37" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s">
         <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E37" t="s">
         <v>36</v>
       </c>
       <c r="F37">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="G37" t="s">
         <v>40</v>
       </c>
       <c r="H37">
-        <v>90.9</v>
+        <v>120</v>
       </c>
       <c r="I37" t="s">
         <v>41</v>
       </c>
       <c r="J37" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K37" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L37">
-        <v>105.9</v>
+        <v>130</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="21.75" customHeight="1">
       <c r="A38" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s">
         <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E38" t="s">
         <v>58</v>
       </c>
       <c r="F38">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="G38" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="H38">
-        <v>90.9</v>
+        <v>120</v>
       </c>
       <c r="I38" t="s">
         <v>41</v>
       </c>
       <c r="J38" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K38" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L38">
-        <v>105.9</v>
+        <v>150</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E39" t="s">
         <v>58</v>
       </c>
       <c r="F39">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G39" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="H39">
-        <v>120</v>
+        <v>120.5</v>
       </c>
       <c r="I39" t="s">
         <v>41</v>
       </c>
       <c r="J39" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="K39" t="s">
         <v>48</v>
       </c>
       <c r="L39">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="21.75" customHeight="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="26.25" customHeight="1">
       <c r="A40" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s">
         <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="E40" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40">
+        <v>60</v>
+      </c>
+      <c r="G40" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40">
+        <v>30.5</v>
+      </c>
+      <c r="I40" t="s">
+        <v>500</v>
+      </c>
+      <c r="J40" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" t="s">
+        <v>33</v>
+      </c>
+      <c r="L40">
+        <v>32.5</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A41" t="s">
+        <v>504</v>
+      </c>
+      <c r="B41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" t="s">
+        <v>503</v>
+      </c>
+      <c r="E41" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41">
+        <v>75</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41">
+        <v>40</v>
+      </c>
+      <c r="I41" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" t="s">
+        <v>33</v>
+      </c>
+      <c r="M41" s="1"/>
+    </row>
+    <row r="42" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A42" t="s">
+        <v>351</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" t="s">
+        <v>101</v>
+      </c>
+      <c r="E42" t="s">
+        <v>54</v>
+      </c>
+      <c r="F42">
+        <v>80</v>
+      </c>
+      <c r="G42" t="s">
+        <v>40</v>
+      </c>
+      <c r="H42">
+        <v>45.5</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" t="s">
+        <v>102</v>
+      </c>
+      <c r="K42" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42">
+        <v>55.5</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="27.75" customHeight="1">
+      <c r="A43" t="s">
+        <v>353</v>
+      </c>
+      <c r="B43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" t="s">
         <v>36</v>
       </c>
-      <c r="F40">
-        <v>100</v>
-      </c>
-      <c r="G40" t="s">
-        <v>40</v>
-      </c>
-      <c r="H40">
+      <c r="F43">
         <v>120</v>
-      </c>
-      <c r="I40" t="s">
-        <v>41</v>
-      </c>
-      <c r="J40" t="s">
-        <v>47</v>
-      </c>
-      <c r="K40" t="s">
-        <v>48</v>
-      </c>
-      <c r="L40">
-        <v>130</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A41" t="s">
-        <v>348</v>
-      </c>
-      <c r="B41" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41" t="s">
-        <v>94</v>
-      </c>
-      <c r="E41" t="s">
-        <v>58</v>
-      </c>
-      <c r="F41">
-        <v>120</v>
-      </c>
-      <c r="G41" t="s">
-        <v>51</v>
-      </c>
-      <c r="H41">
-        <v>120</v>
-      </c>
-      <c r="I41" t="s">
-        <v>41</v>
-      </c>
-      <c r="J41" t="s">
-        <v>47</v>
-      </c>
-      <c r="K41" t="s">
-        <v>48</v>
-      </c>
-      <c r="L41">
-        <v>150</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A42" t="s">
-        <v>353</v>
-      </c>
-      <c r="B42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42">
-        <v>120</v>
-      </c>
-      <c r="G42" t="s">
-        <v>51</v>
-      </c>
-      <c r="H42">
-        <v>120</v>
-      </c>
-      <c r="I42" t="s">
-        <v>41</v>
-      </c>
-      <c r="J42" t="s">
-        <v>42</v>
-      </c>
-      <c r="K42" t="s">
-        <v>43</v>
-      </c>
-      <c r="L42">
-        <v>125</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A43" t="s">
-        <v>349</v>
-      </c>
-      <c r="B43" t="s">
-        <v>109</v>
-      </c>
-      <c r="C43" t="s">
-        <v>96</v>
-      </c>
-      <c r="E43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F43">
-        <v>110</v>
       </c>
       <c r="G43" t="s">
         <v>51</v>
       </c>
       <c r="H43">
-        <v>120.5</v>
+        <v>120</v>
       </c>
       <c r="I43" t="s">
         <v>41</v>
       </c>
       <c r="J43" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="K43" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L43">
         <v>125</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="26.25" customHeight="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="32.25" customHeight="1">
       <c r="A44" t="s">
         <v>354</v>
       </c>
@@ -3944,240 +3957,152 @@
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="26.25" customHeight="1">
+    <row r="45" spans="1:13" ht="30" customHeight="1">
       <c r="A45" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="E45" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F45">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G45" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H45">
-        <v>136.4</v>
+        <v>41</v>
       </c>
       <c r="I45" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="J45" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="K45" t="s">
-        <v>48</v>
+        <v>17</v>
+      </c>
+      <c r="L45">
+        <v>41</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="26.25" customHeight="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="30" customHeight="1">
       <c r="A46" t="s">
-        <v>121</v>
+        <v>356</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="E46" t="s">
-        <v>487</v>
+        <v>23</v>
       </c>
       <c r="F46">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G46" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H46">
-        <v>200</v>
+        <v>41</v>
       </c>
       <c r="I46" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="J46" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K46" t="s">
-        <v>33</v>
+        <v>17</v>
+      </c>
+      <c r="L46">
+        <v>41</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A47" s="2" t="s">
-        <v>493</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="30" customHeight="1">
+      <c r="A47" t="s">
+        <v>357</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>489</v>
+        <v>31</v>
       </c>
       <c r="E47" t="s">
         <v>23</v>
       </c>
       <c r="F47">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G47" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H47">
+        <v>30</v>
+      </c>
+      <c r="I47" t="s">
+        <v>500</v>
+      </c>
+      <c r="J47" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47">
+        <v>40</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="30" customHeight="1">
+      <c r="A48" t="s">
+        <v>513</v>
+      </c>
+      <c r="C48" t="s">
+        <v>512</v>
+      </c>
+      <c r="E48" t="s">
+        <v>511</v>
+      </c>
+      <c r="F48">
         <v>60</v>
       </c>
-      <c r="I47" t="s">
-        <v>15</v>
-      </c>
-      <c r="J47" t="s">
-        <v>491</v>
-      </c>
-      <c r="K47" t="s">
-        <v>32</v>
-      </c>
-      <c r="M47" s="1"/>
-    </row>
-    <row r="48" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A48" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" t="s">
-        <v>490</v>
-      </c>
-      <c r="E48" t="s">
-        <v>23</v>
-      </c>
-      <c r="F48">
-        <v>75</v>
-      </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H48">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I48" t="s">
         <v>15</v>
       </c>
       <c r="J48" t="s">
-        <v>491</v>
+        <v>32</v>
       </c>
       <c r="K48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="1:13" ht="30" customHeight="1">
-      <c r="A49" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="B49" t="s">
-        <v>109</v>
-      </c>
-      <c r="C49" t="s">
-        <v>494</v>
-      </c>
-      <c r="E49" t="s">
-        <v>487</v>
-      </c>
-      <c r="F49">
-        <v>100</v>
-      </c>
-      <c r="G49" t="s">
-        <v>40</v>
-      </c>
-      <c r="H49">
-        <v>100</v>
-      </c>
-      <c r="I49" t="s">
-        <v>119</v>
-      </c>
-      <c r="J49" t="s">
-        <v>47</v>
-      </c>
-      <c r="K49" t="s">
-        <v>48</v>
-      </c>
+    <row r="49" spans="13:13" ht="38.25" customHeight="1">
       <c r="M49" s="1"/>
-    </row>
-    <row r="50" spans="1:13" ht="30" customHeight="1">
-      <c r="A50" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="B50" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50" t="s">
-        <v>495</v>
-      </c>
-      <c r="E50" t="s">
-        <v>487</v>
-      </c>
-      <c r="F50">
-        <v>100</v>
-      </c>
-      <c r="G50" t="s">
-        <v>40</v>
-      </c>
-      <c r="H50">
-        <v>100</v>
-      </c>
-      <c r="I50" t="s">
-        <v>119</v>
-      </c>
-      <c r="J50" t="s">
-        <v>47</v>
-      </c>
-      <c r="K50" t="s">
-        <v>48</v>
-      </c>
-      <c r="M50" s="1"/>
-    </row>
-    <row r="51" spans="1:13" ht="30" customHeight="1">
-      <c r="A51" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="B51" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" t="s">
-        <v>496</v>
-      </c>
-      <c r="E51" t="s">
-        <v>487</v>
-      </c>
-      <c r="F51">
-        <v>100</v>
-      </c>
-      <c r="G51" t="s">
-        <v>40</v>
-      </c>
-      <c r="H51">
-        <v>100</v>
-      </c>
-      <c r="I51" t="s">
-        <v>119</v>
-      </c>
-      <c r="J51" t="s">
-        <v>47</v>
-      </c>
-      <c r="K51" t="s">
-        <v>48</v>
-      </c>
-      <c r="M51" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5836,4 +5761,1910 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B127DB4E-B67F-4CF6-BB95-F5F4AF64274C}">
+  <dimension ref="A1:M51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" customWidth="1"/>
+    <col min="6" max="6" width="26.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.28515625" customWidth="1"/>
+    <col min="10" max="10" width="21.28515625" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" customWidth="1"/>
+    <col min="12" max="12" width="48.28515625" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F2">
+        <v>70</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2">
+        <v>90</v>
+      </c>
+      <c r="I2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>487</v>
+      </c>
+      <c r="F3">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3">
+        <v>200</v>
+      </c>
+      <c r="I3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>496</v>
+      </c>
+      <c r="E4" t="s">
+        <v>487</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E5" t="s">
+        <v>487</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>494</v>
+      </c>
+      <c r="E6" t="s">
+        <v>487</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>55</v>
+      </c>
+      <c r="G7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7">
+        <v>30</v>
+      </c>
+      <c r="I7" t="s">
+        <v>500</v>
+      </c>
+      <c r="J7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>65</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9">
+        <v>40</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A10" t="s">
+        <v>279</v>
+      </c>
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>55</v>
+      </c>
+      <c r="G10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A11" t="s">
+        <v>324</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11">
+        <v>55</v>
+      </c>
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11">
+        <v>35</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11">
+        <v>40</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <v>40</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12">
+        <v>45</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A13" t="s">
+        <v>326</v>
+      </c>
+      <c r="B13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13">
+        <v>65</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>35</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A14" t="s">
+        <v>327</v>
+      </c>
+      <c r="B14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14">
+        <v>65</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14">
+        <v>35</v>
+      </c>
+      <c r="I14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A15" t="s">
+        <v>328</v>
+      </c>
+      <c r="B15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15">
+        <v>65</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15">
+        <v>35</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A16" t="s">
+        <v>329</v>
+      </c>
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>488</v>
+      </c>
+      <c r="F16">
+        <v>70</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16">
+        <v>40.5</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>63</v>
+      </c>
+      <c r="K16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A17" t="s">
+        <v>330</v>
+      </c>
+      <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17">
+        <v>65</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17">
+        <v>45</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17">
+        <v>50</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A18" t="s">
+        <v>331</v>
+      </c>
+      <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18">
+        <v>65</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18">
+        <v>45</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" t="s">
+        <v>33</v>
+      </c>
+      <c r="L18">
+        <v>50</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A19" t="s">
+        <v>332</v>
+      </c>
+      <c r="B19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
+        <v>488</v>
+      </c>
+      <c r="F19">
+        <v>83</v>
+      </c>
+      <c r="G19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19">
+        <v>65.5</v>
+      </c>
+      <c r="I19" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19">
+        <v>70</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A20" t="s">
+        <v>333</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20">
+        <v>70</v>
+      </c>
+      <c r="G20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20">
+        <v>45.5</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L20">
+        <v>55.5</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A21" t="s">
+        <v>334</v>
+      </c>
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21">
+        <v>75</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21">
+        <v>45</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21">
+        <v>50</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A22" t="s">
+        <v>335</v>
+      </c>
+      <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22">
+        <v>70</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22">
+        <v>45.5</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22">
+        <v>60.5</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A23" t="s">
+        <v>337</v>
+      </c>
+      <c r="B23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23">
+        <v>75</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23">
+        <v>65</v>
+      </c>
+      <c r="I23" t="s">
+        <v>119</v>
+      </c>
+      <c r="J23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K23" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23">
+        <v>70</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A24" t="s">
+        <v>336</v>
+      </c>
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24">
+        <v>70</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24">
+        <v>45.5</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24">
+        <v>60.5</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A25" t="s">
+        <v>338</v>
+      </c>
+      <c r="B25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25">
+        <v>75</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25">
+        <v>50</v>
+      </c>
+      <c r="I25" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25">
+        <v>60</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A26" t="s">
+        <v>506</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" t="s">
+        <v>502</v>
+      </c>
+      <c r="E26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26">
+        <v>75</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26">
+        <v>50</v>
+      </c>
+      <c r="I26" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26">
+        <v>60</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A27" t="s">
+        <v>505</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>501</v>
+      </c>
+      <c r="E27" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27">
+        <v>75</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27">
+        <v>50</v>
+      </c>
+      <c r="I27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" t="s">
+        <v>33</v>
+      </c>
+      <c r="L27">
+        <v>60</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A28" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s">
+        <v>490</v>
+      </c>
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28">
+        <v>75</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28">
+        <v>60</v>
+      </c>
+      <c r="I28" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" t="s">
+        <v>491</v>
+      </c>
+      <c r="K28" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" s="1"/>
+    </row>
+    <row r="29" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>489</v>
+      </c>
+      <c r="E29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29">
+        <v>75</v>
+      </c>
+      <c r="G29" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29">
+        <v>60</v>
+      </c>
+      <c r="I29" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" t="s">
+        <v>491</v>
+      </c>
+      <c r="K29" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" s="1"/>
+    </row>
+    <row r="30" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A30" t="s">
+        <v>339</v>
+      </c>
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30">
+        <v>90</v>
+      </c>
+      <c r="G30" t="s">
+        <v>40</v>
+      </c>
+      <c r="H30">
+        <v>75</v>
+      </c>
+      <c r="I30" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" t="s">
+        <v>81</v>
+      </c>
+      <c r="K30" t="s">
+        <v>43</v>
+      </c>
+      <c r="L30">
+        <v>90</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A31" t="s">
+        <v>508</v>
+      </c>
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" t="s">
+        <v>510</v>
+      </c>
+      <c r="E31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31">
+        <v>90</v>
+      </c>
+      <c r="G31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H31">
+        <v>75</v>
+      </c>
+      <c r="I31" t="s">
+        <v>41</v>
+      </c>
+      <c r="J31" t="s">
+        <v>81</v>
+      </c>
+      <c r="K31" t="s">
+        <v>43</v>
+      </c>
+      <c r="L31">
+        <v>90</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A32" t="s">
+        <v>507</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" t="s">
+        <v>509</v>
+      </c>
+      <c r="E32" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32">
+        <v>90</v>
+      </c>
+      <c r="G32" t="s">
+        <v>40</v>
+      </c>
+      <c r="H32">
+        <v>75</v>
+      </c>
+      <c r="I32" t="s">
+        <v>41</v>
+      </c>
+      <c r="J32" t="s">
+        <v>81</v>
+      </c>
+      <c r="K32" t="s">
+        <v>43</v>
+      </c>
+      <c r="L32">
+        <v>90</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A33" t="s">
+        <v>340</v>
+      </c>
+      <c r="B33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33">
+        <v>86</v>
+      </c>
+      <c r="G33" t="s">
+        <v>40</v>
+      </c>
+      <c r="H33">
+        <v>90.9</v>
+      </c>
+      <c r="I33" t="s">
+        <v>41</v>
+      </c>
+      <c r="J33" t="s">
+        <v>42</v>
+      </c>
+      <c r="K33" t="s">
+        <v>43</v>
+      </c>
+      <c r="L33">
+        <v>105.9</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A34" t="s">
+        <v>342</v>
+      </c>
+      <c r="B34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" t="s">
+        <v>58</v>
+      </c>
+      <c r="F34">
+        <v>65</v>
+      </c>
+      <c r="G34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34">
+        <v>90.9</v>
+      </c>
+      <c r="I34" t="s">
+        <v>41</v>
+      </c>
+      <c r="J34" t="s">
+        <v>42</v>
+      </c>
+      <c r="K34" t="s">
+        <v>43</v>
+      </c>
+      <c r="L34">
+        <v>105.9</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A35" t="s">
+        <v>343</v>
+      </c>
+      <c r="B35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" t="s">
+        <v>58</v>
+      </c>
+      <c r="F35">
+        <v>65</v>
+      </c>
+      <c r="G35" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35">
+        <v>90.9</v>
+      </c>
+      <c r="I35" t="s">
+        <v>41</v>
+      </c>
+      <c r="J35" t="s">
+        <v>42</v>
+      </c>
+      <c r="K35" t="s">
+        <v>43</v>
+      </c>
+      <c r="L35">
+        <v>105.9</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A36" t="s">
+        <v>344</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36">
+        <v>86</v>
+      </c>
+      <c r="G36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H36">
+        <v>90.9</v>
+      </c>
+      <c r="I36" t="s">
+        <v>41</v>
+      </c>
+      <c r="J36" t="s">
+        <v>42</v>
+      </c>
+      <c r="K36" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36">
+        <v>105.9</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A37" t="s">
+        <v>341</v>
+      </c>
+      <c r="B37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37">
+        <v>86</v>
+      </c>
+      <c r="G37" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37">
+        <v>90.9</v>
+      </c>
+      <c r="I37" t="s">
+        <v>41</v>
+      </c>
+      <c r="J37" t="s">
+        <v>42</v>
+      </c>
+      <c r="K37" t="s">
+        <v>43</v>
+      </c>
+      <c r="L37">
+        <v>105.9</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A38" t="s">
+        <v>345</v>
+      </c>
+      <c r="B38" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38">
+        <v>90</v>
+      </c>
+      <c r="G38" t="s">
+        <v>40</v>
+      </c>
+      <c r="H38">
+        <v>90</v>
+      </c>
+      <c r="I38" t="s">
+        <v>41</v>
+      </c>
+      <c r="J38" t="s">
+        <v>81</v>
+      </c>
+      <c r="K38" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38">
+        <v>100</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A39" t="s">
+        <v>346</v>
+      </c>
+      <c r="B39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
+        <v>40</v>
+      </c>
+      <c r="H39">
+        <v>120</v>
+      </c>
+      <c r="I39" t="s">
+        <v>41</v>
+      </c>
+      <c r="J39" t="s">
+        <v>47</v>
+      </c>
+      <c r="K39" t="s">
+        <v>48</v>
+      </c>
+      <c r="L39">
+        <v>130</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A40" t="s">
+        <v>347</v>
+      </c>
+      <c r="B40" t="s">
+        <v>109</v>
+      </c>
+      <c r="C40" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40">
+        <v>120</v>
+      </c>
+      <c r="I40" t="s">
+        <v>41</v>
+      </c>
+      <c r="J40" t="s">
+        <v>47</v>
+      </c>
+      <c r="K40" t="s">
+        <v>48</v>
+      </c>
+      <c r="L40">
+        <v>130</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A41" t="s">
+        <v>348</v>
+      </c>
+      <c r="B41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41">
+        <v>120</v>
+      </c>
+      <c r="G41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H41">
+        <v>120</v>
+      </c>
+      <c r="I41" t="s">
+        <v>41</v>
+      </c>
+      <c r="J41" t="s">
+        <v>47</v>
+      </c>
+      <c r="K41" t="s">
+        <v>48</v>
+      </c>
+      <c r="L41">
+        <v>150</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="21.75" customHeight="1">
+      <c r="A42" t="s">
+        <v>349</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" t="s">
+        <v>96</v>
+      </c>
+      <c r="E42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42">
+        <v>110</v>
+      </c>
+      <c r="G42" t="s">
+        <v>51</v>
+      </c>
+      <c r="H42">
+        <v>120.5</v>
+      </c>
+      <c r="I42" t="s">
+        <v>41</v>
+      </c>
+      <c r="J42" t="s">
+        <v>97</v>
+      </c>
+      <c r="K42" t="s">
+        <v>48</v>
+      </c>
+      <c r="L42">
+        <v>125</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A43" t="s">
+        <v>350</v>
+      </c>
+      <c r="B43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" t="s">
+        <v>99</v>
+      </c>
+      <c r="E43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43">
+        <v>60</v>
+      </c>
+      <c r="G43" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43">
+        <v>30.5</v>
+      </c>
+      <c r="I43" t="s">
+        <v>500</v>
+      </c>
+      <c r="J43" t="s">
+        <v>32</v>
+      </c>
+      <c r="K43" t="s">
+        <v>33</v>
+      </c>
+      <c r="L43">
+        <v>32.5</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A44" t="s">
+        <v>504</v>
+      </c>
+      <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>503</v>
+      </c>
+      <c r="E44" t="s">
+        <v>54</v>
+      </c>
+      <c r="F44">
+        <v>75</v>
+      </c>
+      <c r="G44" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44">
+        <v>40</v>
+      </c>
+      <c r="I44" t="s">
+        <v>15</v>
+      </c>
+      <c r="J44" t="s">
+        <v>32</v>
+      </c>
+      <c r="K44" t="s">
+        <v>33</v>
+      </c>
+      <c r="M44" s="1"/>
+    </row>
+    <row r="45" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A45" t="s">
+        <v>351</v>
+      </c>
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>101</v>
+      </c>
+      <c r="E45" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s">
+        <v>40</v>
+      </c>
+      <c r="H45">
+        <v>45.5</v>
+      </c>
+      <c r="I45" t="s">
+        <v>15</v>
+      </c>
+      <c r="J45" t="s">
+        <v>102</v>
+      </c>
+      <c r="K45" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45">
+        <v>55.5</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A46" t="s">
+        <v>352</v>
+      </c>
+      <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" t="s">
+        <v>104</v>
+      </c>
+      <c r="E46" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46">
+        <v>100</v>
+      </c>
+      <c r="G46" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46">
+        <v>136.4</v>
+      </c>
+      <c r="I46" t="s">
+        <v>46</v>
+      </c>
+      <c r="J46" t="s">
+        <v>47</v>
+      </c>
+      <c r="K46" t="s">
+        <v>48</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="27.75" customHeight="1">
+      <c r="A47" t="s">
+        <v>353</v>
+      </c>
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47">
+        <v>120</v>
+      </c>
+      <c r="G47" t="s">
+        <v>51</v>
+      </c>
+      <c r="H47">
+        <v>120</v>
+      </c>
+      <c r="I47" t="s">
+        <v>41</v>
+      </c>
+      <c r="J47" t="s">
+        <v>42</v>
+      </c>
+      <c r="K47" t="s">
+        <v>43</v>
+      </c>
+      <c r="L47">
+        <v>125</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="32.25" customHeight="1">
+      <c r="A48" t="s">
+        <v>354</v>
+      </c>
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
+        <v>106</v>
+      </c>
+      <c r="E48" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48">
+        <v>110</v>
+      </c>
+      <c r="G48" t="s">
+        <v>51</v>
+      </c>
+      <c r="H48">
+        <v>130</v>
+      </c>
+      <c r="I48" t="s">
+        <v>46</v>
+      </c>
+      <c r="J48" t="s">
+        <v>47</v>
+      </c>
+      <c r="K48" t="s">
+        <v>48</v>
+      </c>
+      <c r="L48">
+        <v>145</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="30" customHeight="1">
+      <c r="A49" t="s">
+        <v>355</v>
+      </c>
+      <c r="B49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49">
+        <v>60</v>
+      </c>
+      <c r="G49" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49">
+        <v>41</v>
+      </c>
+      <c r="I49" t="s">
+        <v>15</v>
+      </c>
+      <c r="J49" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49">
+        <v>41</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="30" customHeight="1">
+      <c r="A50" t="s">
+        <v>356</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50">
+        <v>60</v>
+      </c>
+      <c r="G50" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50">
+        <v>41</v>
+      </c>
+      <c r="I50" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50">
+        <v>41</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="30" customHeight="1">
+      <c r="A51" t="s">
+        <v>357</v>
+      </c>
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51">
+        <v>65</v>
+      </c>
+      <c r="G51" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51">
+        <v>30</v>
+      </c>
+      <c r="I51" t="s">
+        <v>500</v>
+      </c>
+      <c r="J51" t="s">
+        <v>32</v>
+      </c>
+      <c r="K51" t="s">
+        <v>33</v>
+      </c>
+      <c r="L51">
+        <v>40</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA6A545-CB4C-4681-B4F9-34F3F901B4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24076283-C91A-4BE8-AC72-E12CA25D21CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="513">
   <si>
     <t>image_url</t>
   </si>
@@ -1863,9 +1863,6 @@
   </si>
   <si>
     <t>TS1871-C</t>
-  </si>
-  <si>
-    <t>dual screen</t>
   </si>
   <si>
     <t>DS-5201</t>
@@ -4073,13 +4070,13 @@
     </row>
     <row r="48" spans="1:13" ht="30" customHeight="1">
       <c r="A48" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C48" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E48" t="s">
-        <v>511</v>
+        <v>23</v>
       </c>
       <c r="F48">
         <v>60</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24076283-C91A-4BE8-AC72-E12CA25D21CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E23AFC3-9EFC-4B6B-BBA4-C5708665371E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1875,7 +1875,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1905,6 +1905,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1927,7 +1935,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1936,6 +1944,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -2737,8 +2746,8 @@
       <c r="E12" t="s">
         <v>58</v>
       </c>
-      <c r="F12">
-        <v>60</v>
+      <c r="F12" s="4">
+        <v>55</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
@@ -4079,7 +4088,7 @@
         <v>23</v>
       </c>
       <c r="F48">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G48" t="s">
         <v>20</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E23AFC3-9EFC-4B6B-BBA4-C5708665371E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88187150-537C-4DF5-B5F2-1D9B6416187A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="523">
   <si>
     <t>image_url</t>
   </si>
@@ -1869,6 +1869,36 @@
   </si>
   <si>
     <t>images/DS-5201</t>
+  </si>
+  <si>
+    <t>TS1590-B</t>
+  </si>
+  <si>
+    <t>TS1590-C</t>
+  </si>
+  <si>
+    <t>TS1590-G</t>
+  </si>
+  <si>
+    <t>TS1171-B</t>
+  </si>
+  <si>
+    <t>TS1552E-W</t>
+  </si>
+  <si>
+    <t>TS1991-W</t>
+  </si>
+  <si>
+    <t>serie</t>
+  </si>
+  <si>
+    <t>ONKRON PRO</t>
+  </si>
+  <si>
+    <t>dual screen</t>
+  </si>
+  <si>
+    <t>ONKRON</t>
   </si>
 </sst>
 </file>
@@ -1971,16 +2001,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:M48" totalsRowShown="0">
-  <autoFilter ref="A1:M48" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M47">
-    <sortCondition ref="C1:C47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N54" totalsRowShown="0">
+  <autoFilter ref="A1:N54" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N54">
+    <sortCondition ref="K1:K54"/>
   </sortState>
-  <tableColumns count="13">
+  <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
     <tableColumn id="2" xr3:uid="{EE3BD87B-A978-4430-88EF-5ABEE2EBC957}" name="sku"/>
     <tableColumn id="3" xr3:uid="{45FEC725-33B8-48CC-8758-CE575B0AAA81}" name="image"/>
+    <tableColumn id="14" xr3:uid="{53260C34-4DBE-4B14-9660-30544E4018B2}" name="serie"/>
     <tableColumn id="4" xr3:uid="{30C9C4DD-76FC-4021-AE83-F166AD3AD064}" name="Type"/>
     <tableColumn id="5" xr3:uid="{686DA4FF-756D-4B19-B58B-3C46042A55D2}" name="максимальная диагональ"/>
     <tableColumn id="6" xr3:uid="{00DD0BFB-8E12-4891-B707-8A693B9956BE}" name="Diagonal category"/>
@@ -2328,24 +2359,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" customWidth="1"/>
-    <col min="6" max="6" width="26.140625" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" customWidth="1"/>
-    <col min="8" max="8" width="26.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.28515625" customWidth="1"/>
-    <col min="10" max="10" width="21.28515625" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" customWidth="1"/>
-    <col min="12" max="12" width="48.28515625" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" customWidth="1"/>
+    <col min="7" max="7" width="26.140625" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
+    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="10" max="10" width="25.28515625" customWidth="1"/>
+    <col min="11" max="11" width="21.28515625" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" customWidth="1"/>
+    <col min="13" max="13" width="48.28515625" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2359,1756 +2391,2125 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>519</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A2" t="s">
-        <v>159</v>
+    <row r="2" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>499</v>
       </c>
       <c r="B2" t="s">
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>496</v>
       </c>
       <c r="E2" t="s">
-        <v>487</v>
-      </c>
-      <c r="F2">
+        <v>520</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A3" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
+        <v>495</v>
+      </c>
+      <c r="E3" t="s">
+        <v>520</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+      <c r="H3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>494</v>
+      </c>
+      <c r="E4" t="s">
+        <v>520</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4" t="s">
+        <v>119</v>
+      </c>
+      <c r="K4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>522</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5">
+        <v>120</v>
+      </c>
+      <c r="J5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5">
+        <v>130</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" t="s">
+        <v>522</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6">
+        <v>120</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6">
+        <v>130</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" t="s">
+        <v>522</v>
+      </c>
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>120</v>
+      </c>
+      <c r="H7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7">
+        <v>120</v>
+      </c>
+      <c r="J7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7">
+        <v>150</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A8" t="s">
+        <v>354</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" t="s">
+        <v>522</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8">
+        <v>110</v>
+      </c>
+      <c r="H8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8">
+        <v>130</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8">
+        <v>145</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A9" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1991-W</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" t="s">
+        <v>518</v>
+      </c>
+      <c r="E9" t="s">
+        <v>522</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <v>120</v>
+      </c>
+      <c r="J9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A10" t="s">
+        <v>332</v>
+      </c>
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
+        <v>522</v>
+      </c>
+      <c r="F10" t="s">
+        <v>488</v>
+      </c>
+      <c r="G10">
+        <v>83</v>
+      </c>
+      <c r="H10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10">
+        <v>65.5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>119</v>
+      </c>
+      <c r="K10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10">
         <v>70</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2">
-        <v>90</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="N10" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" t="s">
+        <v>522</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>110</v>
+      </c>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11">
+        <v>120.5</v>
+      </c>
+      <c r="J11" t="s">
         <v>41</v>
       </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" t="s">
-        <v>487</v>
-      </c>
-      <c r="F3">
+      <c r="K11" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11">
+        <v>125</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" t="s">
+        <v>522</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
         <v>55</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H12" t="s">
         <v>55</v>
       </c>
-      <c r="H3">
-        <v>200</v>
-      </c>
-      <c r="I3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="B4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" t="s">
-        <v>496</v>
-      </c>
-      <c r="E4" t="s">
-        <v>487</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
-      <c r="I4" t="s">
-        <v>119</v>
-      </c>
-      <c r="J4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="B5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" t="s">
-        <v>495</v>
-      </c>
-      <c r="E5" t="s">
-        <v>487</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5">
-        <v>100</v>
-      </c>
-      <c r="I5" t="s">
-        <v>119</v>
-      </c>
-      <c r="J5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" t="s">
-        <v>48</v>
-      </c>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="B6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" t="s">
-        <v>494</v>
-      </c>
-      <c r="E6" t="s">
-        <v>487</v>
-      </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6">
-        <v>100</v>
-      </c>
-      <c r="I6" t="s">
-        <v>119</v>
-      </c>
-      <c r="J6" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A7" t="s">
-        <v>276</v>
-      </c>
-      <c r="B7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7">
-        <v>55</v>
-      </c>
-      <c r="G7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7">
+      <c r="I12">
         <v>30</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J12" t="s">
         <v>500</v>
-      </c>
-      <c r="J7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A8" t="s">
-        <v>277</v>
-      </c>
-      <c r="B8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8">
-        <v>65</v>
-      </c>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8">
-        <v>35</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>113</v>
-      </c>
-      <c r="K8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A9" t="s">
-        <v>278</v>
-      </c>
-      <c r="B9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9">
-        <v>40</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A10" t="s">
-        <v>279</v>
-      </c>
-      <c r="B10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10">
-        <v>55</v>
-      </c>
-      <c r="G10" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10">
-        <v>35</v>
-      </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" t="s">
-        <v>17</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A11" t="s">
-        <v>324</v>
-      </c>
-      <c r="B11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11">
-        <v>55</v>
-      </c>
-      <c r="G11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11">
-        <v>35</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11">
-        <v>40</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A12" t="s">
-        <v>325</v>
-      </c>
-      <c r="B12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="4">
-        <v>55</v>
-      </c>
-      <c r="G12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12">
-        <v>40</v>
-      </c>
-      <c r="I12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" t="s">
-        <v>17</v>
       </c>
       <c r="K12" t="s">
         <v>17</v>
       </c>
-      <c r="L12">
-        <v>45</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="21.75" customHeight="1">
+      <c r="L12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="21.75" customHeight="1">
       <c r="A13" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13">
-        <v>65</v>
-      </c>
-      <c r="G13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13">
+        <v>522</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>55</v>
+      </c>
+      <c r="H13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13">
         <v>35</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>15</v>
-      </c>
-      <c r="J13" t="s">
-        <v>17</v>
       </c>
       <c r="K13" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="21.75" customHeight="1">
+      <c r="L13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="21.75" customHeight="1">
       <c r="A14" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14">
-        <v>65</v>
-      </c>
-      <c r="G14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14">
+        <v>522</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14">
+        <v>55</v>
+      </c>
+      <c r="H14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14">
         <v>35</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>15</v>
-      </c>
-      <c r="J14" t="s">
-        <v>17</v>
       </c>
       <c r="K14" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14">
+        <v>40</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A15" t="s">
+        <v>325</v>
+      </c>
+      <c r="B15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" t="s">
+        <v>522</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="4">
+        <v>55</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15">
+        <v>40</v>
+      </c>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M15">
+        <v>45</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A16" t="s">
+        <v>327</v>
+      </c>
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>522</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16">
+        <v>65</v>
+      </c>
+      <c r="H16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16">
+        <v>35</v>
+      </c>
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A15" t="s">
-        <v>329</v>
-      </c>
-      <c r="B15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" t="s">
-        <v>488</v>
-      </c>
-      <c r="F15">
+    <row r="17" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A17" t="s">
+        <v>328</v>
+      </c>
+      <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>522</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17">
+        <v>65</v>
+      </c>
+      <c r="H17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17">
+        <v>35</v>
+      </c>
+      <c r="J17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A18" t="s">
+        <v>355</v>
+      </c>
+      <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>522</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18">
+        <v>60</v>
+      </c>
+      <c r="H18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18">
+        <v>41</v>
+      </c>
+      <c r="J18" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18">
+        <v>41</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A19" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1171-B</v>
+      </c>
+      <c r="B19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" t="s">
+        <v>516</v>
+      </c>
+      <c r="E19" t="s">
+        <v>522</v>
+      </c>
+      <c r="F19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19">
+        <v>60</v>
+      </c>
+      <c r="H19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19">
+        <v>40</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19">
+        <v>45</v>
+      </c>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>520</v>
+      </c>
+      <c r="F20" t="s">
+        <v>521</v>
+      </c>
+      <c r="G20">
         <v>70</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H20" t="s">
         <v>14</v>
       </c>
-      <c r="H15">
-        <v>40.5</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="I20">
+        <v>90</v>
+      </c>
+      <c r="J20" t="s">
+        <v>41</v>
+      </c>
+      <c r="K20" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A21" t="s">
+        <v>277</v>
+      </c>
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" t="s">
+        <v>522</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21">
+        <v>65</v>
+      </c>
+      <c r="H21" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21">
+        <v>35</v>
+      </c>
+      <c r="J21" t="s">
         <v>15</v>
       </c>
-      <c r="J15" t="s">
-        <v>63</v>
-      </c>
-      <c r="K15" t="s">
-        <v>43</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A16" t="s">
-        <v>330</v>
-      </c>
-      <c r="B16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="K21" t="s">
+        <v>113</v>
+      </c>
+      <c r="L21" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A22" t="s">
+        <v>337</v>
+      </c>
+      <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" t="s">
+        <v>522</v>
+      </c>
+      <c r="F22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22">
+        <v>75</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22">
         <v>65</v>
       </c>
-      <c r="E16" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16">
-        <v>65</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="J22" t="s">
+        <v>119</v>
+      </c>
+      <c r="K22" t="s">
+        <v>37</v>
+      </c>
+      <c r="L22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22">
+        <v>70</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A23" t="s">
+        <v>278</v>
+      </c>
+      <c r="B23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" t="s">
+        <v>522</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23">
+        <v>40</v>
+      </c>
+      <c r="J23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A24" t="s">
+        <v>356</v>
+      </c>
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>522</v>
+      </c>
+      <c r="F24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
         <v>20</v>
       </c>
-      <c r="H16">
-        <v>45</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="I24">
+        <v>41</v>
+      </c>
+      <c r="J24" t="s">
         <v>15</v>
       </c>
-      <c r="J16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16">
-        <v>50</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A17" t="s">
-        <v>331</v>
-      </c>
-      <c r="B17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17">
-        <v>65</v>
-      </c>
-      <c r="G17" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17">
-        <v>45</v>
-      </c>
-      <c r="I17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17" t="s">
-        <v>33</v>
-      </c>
-      <c r="L17">
-        <v>50</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A18" t="s">
-        <v>332</v>
-      </c>
-      <c r="B18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="s">
-        <v>488</v>
-      </c>
-      <c r="F18">
-        <v>83</v>
-      </c>
-      <c r="G18" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18">
-        <v>65.5</v>
-      </c>
-      <c r="I18" t="s">
-        <v>119</v>
-      </c>
-      <c r="J18" t="s">
-        <v>69</v>
-      </c>
-      <c r="K18" t="s">
-        <v>48</v>
-      </c>
-      <c r="L18">
-        <v>70</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A19" t="s">
-        <v>333</v>
-      </c>
-      <c r="B19" t="s">
-        <v>109</v>
-      </c>
-      <c r="C19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19">
-        <v>70</v>
-      </c>
-      <c r="G19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19">
-        <v>45.5</v>
-      </c>
-      <c r="I19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" t="s">
-        <v>33</v>
-      </c>
-      <c r="L19">
-        <v>55.5</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A20" t="s">
-        <v>334</v>
-      </c>
-      <c r="B20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20">
-        <v>75</v>
-      </c>
-      <c r="G20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20">
-        <v>45</v>
-      </c>
-      <c r="I20" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" t="s">
-        <v>32</v>
-      </c>
-      <c r="K20" t="s">
-        <v>33</v>
-      </c>
-      <c r="L20">
-        <v>50</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A21" t="s">
-        <v>337</v>
-      </c>
-      <c r="B21" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21">
-        <v>75</v>
-      </c>
-      <c r="G21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21">
-        <v>65</v>
-      </c>
-      <c r="I21" t="s">
-        <v>119</v>
-      </c>
-      <c r="J21" t="s">
-        <v>37</v>
-      </c>
-      <c r="K21" t="s">
+      <c r="K24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L24" t="s">
         <v>17</v>
       </c>
-      <c r="L21">
-        <v>70</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A22" t="s">
-        <v>338</v>
-      </c>
-      <c r="B22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22">
-        <v>75</v>
-      </c>
-      <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22">
-        <v>50</v>
-      </c>
-      <c r="I22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" t="s">
-        <v>32</v>
-      </c>
-      <c r="K22" t="s">
-        <v>33</v>
-      </c>
-      <c r="L22">
-        <v>60</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A23" t="s">
-        <v>506</v>
-      </c>
-      <c r="B23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" t="s">
-        <v>502</v>
-      </c>
-      <c r="E23" t="s">
-        <v>58</v>
-      </c>
-      <c r="F23">
-        <v>75</v>
-      </c>
-      <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23">
-        <v>50</v>
-      </c>
-      <c r="I23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23" t="s">
-        <v>33</v>
-      </c>
-      <c r="L23">
-        <v>60</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A24" t="s">
-        <v>505</v>
-      </c>
-      <c r="B24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" t="s">
-        <v>501</v>
-      </c>
-      <c r="E24" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24">
-        <v>75</v>
-      </c>
-      <c r="G24" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24">
-        <v>50</v>
-      </c>
-      <c r="I24" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24" t="s">
-        <v>33</v>
-      </c>
-      <c r="L24">
-        <v>60</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>492</v>
+      <c r="M24">
+        <v>41</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A25" t="s">
+        <v>121</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>490</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25">
-        <v>75</v>
-      </c>
-      <c r="G25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25">
-        <v>60</v>
-      </c>
-      <c r="I25" t="s">
-        <v>15</v>
+        <v>520</v>
+      </c>
+      <c r="F25" t="s">
+        <v>521</v>
+      </c>
+      <c r="G25">
+        <v>55</v>
+      </c>
+      <c r="H25" t="s">
+        <v>55</v>
+      </c>
+      <c r="I25">
+        <v>200</v>
       </c>
       <c r="J25" t="s">
-        <v>491</v>
+        <v>46</v>
       </c>
       <c r="K25" t="s">
         <v>32</v>
       </c>
-      <c r="M25" s="1"/>
-    </row>
-    <row r="26" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>493</v>
+      <c r="L25" t="s">
+        <v>33</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A26" t="s">
+        <v>330</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>489</v>
+        <v>65</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26">
-        <v>75</v>
-      </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26">
-        <v>60</v>
-      </c>
-      <c r="I26" t="s">
+        <v>522</v>
+      </c>
+      <c r="F26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26">
+        <v>65</v>
+      </c>
+      <c r="H26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26">
+        <v>45</v>
+      </c>
+      <c r="J26" t="s">
         <v>15</v>
-      </c>
-      <c r="J26" t="s">
-        <v>491</v>
       </c>
       <c r="K26" t="s">
         <v>32</v>
       </c>
-      <c r="M26" s="1"/>
-    </row>
-    <row r="27" spans="1:13" ht="21.75" customHeight="1">
+      <c r="L26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M26">
+        <v>50</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="21.75" customHeight="1">
       <c r="A27" t="s">
+        <v>331</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" t="s">
+        <v>522</v>
+      </c>
+      <c r="F27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27">
+        <v>65</v>
+      </c>
+      <c r="H27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27">
+        <v>45</v>
+      </c>
+      <c r="J27" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" t="s">
+        <v>33</v>
+      </c>
+      <c r="M27">
+        <v>50</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A28" t="s">
+        <v>333</v>
+      </c>
+      <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" t="s">
+        <v>522</v>
+      </c>
+      <c r="F28" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28">
+        <v>70</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28">
+        <v>45.5</v>
+      </c>
+      <c r="J28" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" t="s">
+        <v>33</v>
+      </c>
+      <c r="M28">
+        <v>55.5</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A29" t="s">
+        <v>334</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" t="s">
+        <v>522</v>
+      </c>
+      <c r="F29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29">
+        <v>45</v>
+      </c>
+      <c r="J29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" t="s">
+        <v>33</v>
+      </c>
+      <c r="M29">
+        <v>50</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A30" t="s">
+        <v>338</v>
+      </c>
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" t="s">
+        <v>522</v>
+      </c>
+      <c r="F30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30">
+        <v>50</v>
+      </c>
+      <c r="J30" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" t="s">
+        <v>33</v>
+      </c>
+      <c r="M30">
+        <v>60</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A31" t="s">
+        <v>506</v>
+      </c>
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" t="s">
+        <v>502</v>
+      </c>
+      <c r="E31" t="s">
+        <v>522</v>
+      </c>
+      <c r="F31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31">
+        <v>75</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31">
+        <v>50</v>
+      </c>
+      <c r="J31" t="s">
+        <v>15</v>
+      </c>
+      <c r="K31" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" t="s">
+        <v>33</v>
+      </c>
+      <c r="M31">
+        <v>60</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A32" t="s">
+        <v>505</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" t="s">
+        <v>501</v>
+      </c>
+      <c r="E32" t="s">
+        <v>522</v>
+      </c>
+      <c r="F32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32">
+        <v>50</v>
+      </c>
+      <c r="J32" t="s">
+        <v>15</v>
+      </c>
+      <c r="K32" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" t="s">
+        <v>33</v>
+      </c>
+      <c r="M32">
+        <v>60</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A33" t="s">
+        <v>350</v>
+      </c>
+      <c r="B33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" t="s">
+        <v>522</v>
+      </c>
+      <c r="F33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33">
+        <v>60</v>
+      </c>
+      <c r="H33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33">
+        <v>30.5</v>
+      </c>
+      <c r="J33" t="s">
+        <v>500</v>
+      </c>
+      <c r="K33" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" t="s">
+        <v>33</v>
+      </c>
+      <c r="M33">
+        <v>32.5</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A34" t="s">
+        <v>504</v>
+      </c>
+      <c r="B34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" t="s">
+        <v>503</v>
+      </c>
+      <c r="E34" t="s">
+        <v>522</v>
+      </c>
+      <c r="F34" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34">
+        <v>75</v>
+      </c>
+      <c r="H34" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34">
+        <v>40</v>
+      </c>
+      <c r="J34" t="s">
+        <v>15</v>
+      </c>
+      <c r="K34" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" t="s">
+        <v>33</v>
+      </c>
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A35" t="s">
+        <v>357</v>
+      </c>
+      <c r="B35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" t="s">
+        <v>522</v>
+      </c>
+      <c r="F35" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35">
+        <v>65</v>
+      </c>
+      <c r="H35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35">
+        <v>30</v>
+      </c>
+      <c r="J35" t="s">
+        <v>500</v>
+      </c>
+      <c r="K35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" t="s">
+        <v>33</v>
+      </c>
+      <c r="M35">
+        <v>40</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A36" t="s">
+        <v>512</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>511</v>
+      </c>
+      <c r="E36" t="s">
+        <v>522</v>
+      </c>
+      <c r="F36" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36">
+        <v>65</v>
+      </c>
+      <c r="H36" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36">
+        <v>40</v>
+      </c>
+      <c r="J36" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" t="s">
+        <v>33</v>
+      </c>
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A37" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1552E-W</v>
+      </c>
+      <c r="B37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" t="s">
+        <v>517</v>
+      </c>
+      <c r="E37" t="s">
+        <v>522</v>
+      </c>
+      <c r="F37" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37">
+        <v>67</v>
+      </c>
+      <c r="J37" t="s">
+        <v>119</v>
+      </c>
+      <c r="K37" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" t="s">
+        <v>33</v>
+      </c>
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A38" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B38" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" t="s">
+        <v>490</v>
+      </c>
+      <c r="E38" t="s">
+        <v>522</v>
+      </c>
+      <c r="F38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38">
+        <v>75</v>
+      </c>
+      <c r="H38" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38">
+        <v>60</v>
+      </c>
+      <c r="J38" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38" t="s">
+        <v>491</v>
+      </c>
+      <c r="L38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A39" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" t="s">
+        <v>489</v>
+      </c>
+      <c r="E39" t="s">
+        <v>522</v>
+      </c>
+      <c r="F39" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39">
+        <v>75</v>
+      </c>
+      <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39">
+        <v>60</v>
+      </c>
+      <c r="J39" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" t="s">
+        <v>491</v>
+      </c>
+      <c r="L39" t="s">
+        <v>32</v>
+      </c>
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:14" ht="26.25" customHeight="1">
+      <c r="A40" t="s">
+        <v>351</v>
+      </c>
+      <c r="B40" t="s">
+        <v>109</v>
+      </c>
+      <c r="C40" t="s">
+        <v>101</v>
+      </c>
+      <c r="E40" t="s">
+        <v>522</v>
+      </c>
+      <c r="F40" t="s">
+        <v>54</v>
+      </c>
+      <c r="G40">
+        <v>80</v>
+      </c>
+      <c r="H40" t="s">
+        <v>40</v>
+      </c>
+      <c r="I40">
+        <v>45.5</v>
+      </c>
+      <c r="J40" t="s">
+        <v>15</v>
+      </c>
+      <c r="K40" t="s">
+        <v>102</v>
+      </c>
+      <c r="L40" t="s">
+        <v>32</v>
+      </c>
+      <c r="M40">
+        <v>55.5</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="26.25" customHeight="1">
+      <c r="A41" t="s">
+        <v>340</v>
+      </c>
+      <c r="B41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" t="s">
+        <v>522</v>
+      </c>
+      <c r="F41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G41">
+        <v>86</v>
+      </c>
+      <c r="H41" t="s">
+        <v>40</v>
+      </c>
+      <c r="I41">
+        <v>90.9</v>
+      </c>
+      <c r="J41" t="s">
+        <v>41</v>
+      </c>
+      <c r="K41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L41" t="s">
+        <v>43</v>
+      </c>
+      <c r="M41">
+        <v>105.9</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="26.25" customHeight="1">
+      <c r="A42" t="s">
+        <v>342</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" t="s">
+        <v>86</v>
+      </c>
+      <c r="E42" t="s">
+        <v>522</v>
+      </c>
+      <c r="F42" t="s">
+        <v>521</v>
+      </c>
+      <c r="G42">
+        <v>65</v>
+      </c>
+      <c r="H42" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42">
+        <v>90.9</v>
+      </c>
+      <c r="J42" t="s">
+        <v>41</v>
+      </c>
+      <c r="K42" t="s">
+        <v>42</v>
+      </c>
+      <c r="L42" t="s">
+        <v>43</v>
+      </c>
+      <c r="M42">
+        <v>105.9</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A43" t="s">
+        <v>343</v>
+      </c>
+      <c r="B43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+      <c r="E43" t="s">
+        <v>522</v>
+      </c>
+      <c r="F43" t="s">
+        <v>521</v>
+      </c>
+      <c r="G43">
+        <v>65</v>
+      </c>
+      <c r="H43" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43">
+        <v>90.9</v>
+      </c>
+      <c r="J43" t="s">
+        <v>41</v>
+      </c>
+      <c r="K43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L43" t="s">
+        <v>43</v>
+      </c>
+      <c r="M43">
+        <v>105.9</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A44" t="s">
+        <v>344</v>
+      </c>
+      <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" t="s">
+        <v>522</v>
+      </c>
+      <c r="F44" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44">
+        <v>86</v>
+      </c>
+      <c r="H44" t="s">
+        <v>40</v>
+      </c>
+      <c r="I44">
+        <v>90.9</v>
+      </c>
+      <c r="J44" t="s">
+        <v>41</v>
+      </c>
+      <c r="K44" t="s">
+        <v>42</v>
+      </c>
+      <c r="L44" t="s">
+        <v>43</v>
+      </c>
+      <c r="M44">
+        <v>105.9</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="30" customHeight="1">
+      <c r="A45" t="s">
+        <v>341</v>
+      </c>
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>85</v>
+      </c>
+      <c r="E45" t="s">
+        <v>522</v>
+      </c>
+      <c r="F45" t="s">
+        <v>58</v>
+      </c>
+      <c r="G45">
+        <v>86</v>
+      </c>
+      <c r="H45" t="s">
+        <v>40</v>
+      </c>
+      <c r="I45">
+        <v>90.9</v>
+      </c>
+      <c r="J45" t="s">
+        <v>41</v>
+      </c>
+      <c r="K45" t="s">
+        <v>42</v>
+      </c>
+      <c r="L45" t="s">
+        <v>43</v>
+      </c>
+      <c r="M45">
+        <v>105.9</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="30" customHeight="1">
+      <c r="A46" t="s">
+        <v>353</v>
+      </c>
+      <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46" t="s">
+        <v>522</v>
+      </c>
+      <c r="F46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46">
+        <v>120</v>
+      </c>
+      <c r="H46" t="s">
+        <v>51</v>
+      </c>
+      <c r="I46">
+        <v>120</v>
+      </c>
+      <c r="J46" t="s">
+        <v>41</v>
+      </c>
+      <c r="K46" t="s">
+        <v>42</v>
+      </c>
+      <c r="L46" t="s">
+        <v>43</v>
+      </c>
+      <c r="M46">
+        <v>125</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="30" customHeight="1">
+      <c r="A47" t="s">
         <v>339</v>
       </c>
-      <c r="B27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
         <v>80</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E47" t="s">
+        <v>522</v>
+      </c>
+      <c r="F47" t="s">
         <v>58</v>
       </c>
-      <c r="F27">
+      <c r="G47">
         <v>90</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H47" t="s">
         <v>40</v>
       </c>
-      <c r="H27">
+      <c r="I47">
         <v>75</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J47" t="s">
         <v>41</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K47" t="s">
         <v>81</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L47" t="s">
         <v>43</v>
       </c>
-      <c r="L27">
+      <c r="M47">
         <v>90</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="N47" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A28" t="s">
+    <row r="48" spans="1:14" ht="30" customHeight="1">
+      <c r="A48" t="s">
         <v>508</v>
       </c>
-      <c r="B28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
         <v>510</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E48" t="s">
+        <v>522</v>
+      </c>
+      <c r="F48" t="s">
         <v>58</v>
       </c>
-      <c r="F28">
+      <c r="G48">
         <v>90</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H48" t="s">
         <v>40</v>
       </c>
-      <c r="H28">
+      <c r="I48">
         <v>75</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J48" t="s">
         <v>41</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K48" t="s">
         <v>81</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L48" t="s">
         <v>43</v>
       </c>
-      <c r="L28">
+      <c r="M48">
         <v>90</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="N48" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A29" t="s">
+    <row r="49" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A49" t="s">
         <v>507</v>
       </c>
-      <c r="B29" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" t="s">
         <v>509</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E49" t="s">
+        <v>522</v>
+      </c>
+      <c r="F49" t="s">
         <v>58</v>
       </c>
-      <c r="F29">
+      <c r="G49">
         <v>90</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H49" t="s">
         <v>40</v>
       </c>
-      <c r="H29">
+      <c r="I49">
         <v>75</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J49" t="s">
         <v>41</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K49" t="s">
         <v>81</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L49" t="s">
         <v>43</v>
       </c>
-      <c r="L29">
+      <c r="M49">
         <v>90</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="N49" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A30" t="s">
-        <v>340</v>
-      </c>
-      <c r="B30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-      <c r="E30" t="s">
+    <row r="50" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A50" t="s">
+        <v>345</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" t="s">
+        <v>522</v>
+      </c>
+      <c r="F50" t="s">
         <v>58</v>
       </c>
-      <c r="F30">
-        <v>86</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="G50">
+        <v>90</v>
+      </c>
+      <c r="H50" t="s">
         <v>40</v>
       </c>
-      <c r="H30">
-        <v>90.9</v>
-      </c>
-      <c r="I30" t="s">
+      <c r="I50">
+        <v>90</v>
+      </c>
+      <c r="J50" t="s">
         <v>41</v>
       </c>
-      <c r="J30" t="s">
-        <v>42</v>
-      </c>
-      <c r="K30" t="s">
+      <c r="K50" t="s">
+        <v>81</v>
+      </c>
+      <c r="L50" t="s">
         <v>43</v>
       </c>
-      <c r="L30">
-        <v>105.9</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A31" t="s">
-        <v>342</v>
-      </c>
-      <c r="B31" t="s">
-        <v>109</v>
-      </c>
-      <c r="C31" t="s">
-        <v>86</v>
-      </c>
-      <c r="E31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F31">
-        <v>65</v>
-      </c>
-      <c r="G31" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31">
-        <v>90.9</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="M50">
+        <v>100</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A51" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-B</v>
+      </c>
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" t="s">
+        <v>513</v>
+      </c>
+      <c r="E51" t="s">
+        <v>522</v>
+      </c>
+      <c r="F51" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51">
+        <v>90</v>
+      </c>
+      <c r="H51" t="s">
+        <v>40</v>
+      </c>
+      <c r="I51">
+        <v>100</v>
+      </c>
+      <c r="J51" t="s">
         <v>41</v>
       </c>
-      <c r="J31" t="s">
-        <v>42</v>
-      </c>
-      <c r="K31" t="s">
+      <c r="K51" t="s">
+        <v>81</v>
+      </c>
+      <c r="L51" t="s">
         <v>43</v>
       </c>
-      <c r="L31">
-        <v>105.9</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A32" t="s">
-        <v>343</v>
-      </c>
-      <c r="B32" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" t="s">
-        <v>58</v>
-      </c>
-      <c r="F32">
-        <v>65</v>
-      </c>
-      <c r="G32" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32">
-        <v>90.9</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A52" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-C</v>
+      </c>
+      <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" t="s">
+        <v>514</v>
+      </c>
+      <c r="E52" t="s">
+        <v>522</v>
+      </c>
+      <c r="F52" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52">
+        <v>90</v>
+      </c>
+      <c r="H52" t="s">
+        <v>40</v>
+      </c>
+      <c r="I52">
+        <v>100</v>
+      </c>
+      <c r="J52" t="s">
         <v>41</v>
       </c>
-      <c r="J32" t="s">
-        <v>42</v>
-      </c>
-      <c r="K32" t="s">
+      <c r="K52" t="s">
+        <v>81</v>
+      </c>
+      <c r="L52" t="s">
         <v>43</v>
       </c>
-      <c r="L32">
-        <v>105.9</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A33" t="s">
-        <v>344</v>
-      </c>
-      <c r="B33" t="s">
-        <v>109</v>
-      </c>
-      <c r="C33" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F33">
-        <v>86</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A53" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-G</v>
+      </c>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>515</v>
+      </c>
+      <c r="E53" t="s">
+        <v>522</v>
+      </c>
+      <c r="F53" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53">
+        <v>90</v>
+      </c>
+      <c r="H53" t="s">
         <v>40</v>
       </c>
-      <c r="H33">
-        <v>90.9</v>
-      </c>
-      <c r="I33" t="s">
+      <c r="I53">
+        <v>100</v>
+      </c>
+      <c r="J53" t="s">
         <v>41</v>
       </c>
-      <c r="J33" t="s">
-        <v>42</v>
-      </c>
-      <c r="K33" t="s">
+      <c r="K53" t="s">
+        <v>81</v>
+      </c>
+      <c r="L53" t="s">
         <v>43</v>
       </c>
-      <c r="L33">
-        <v>105.9</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A34" t="s">
-        <v>341</v>
-      </c>
-      <c r="B34" t="s">
-        <v>109</v>
-      </c>
-      <c r="C34" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" t="s">
-        <v>58</v>
-      </c>
-      <c r="F34">
-        <v>86</v>
-      </c>
-      <c r="G34" t="s">
-        <v>40</v>
-      </c>
-      <c r="H34">
-        <v>90.9</v>
-      </c>
-      <c r="I34" t="s">
-        <v>41</v>
-      </c>
-      <c r="J34" t="s">
-        <v>42</v>
-      </c>
-      <c r="K34" t="s">
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" ht="37.5" customHeight="1">
+      <c r="A54" t="s">
+        <v>329</v>
+      </c>
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" t="s">
+        <v>522</v>
+      </c>
+      <c r="F54" t="s">
+        <v>488</v>
+      </c>
+      <c r="G54">
+        <v>70</v>
+      </c>
+      <c r="H54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54">
+        <v>40.5</v>
+      </c>
+      <c r="J54" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54" t="s">
+        <v>63</v>
+      </c>
+      <c r="L54" t="s">
         <v>43</v>
       </c>
-      <c r="L34">
-        <v>105.9</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A35" t="s">
-        <v>345</v>
-      </c>
-      <c r="B35" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" t="s">
-        <v>90</v>
-      </c>
-      <c r="E35" t="s">
-        <v>58</v>
-      </c>
-      <c r="F35">
-        <v>90</v>
-      </c>
-      <c r="G35" t="s">
-        <v>40</v>
-      </c>
-      <c r="H35">
-        <v>90</v>
-      </c>
-      <c r="I35" t="s">
-        <v>41</v>
-      </c>
-      <c r="J35" t="s">
-        <v>81</v>
-      </c>
-      <c r="K35" t="s">
-        <v>43</v>
-      </c>
-      <c r="L35">
-        <v>100</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A36" t="s">
-        <v>346</v>
-      </c>
-      <c r="B36" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36" t="s">
-        <v>92</v>
-      </c>
-      <c r="E36" t="s">
-        <v>58</v>
-      </c>
-      <c r="F36">
-        <v>100</v>
-      </c>
-      <c r="G36" t="s">
-        <v>40</v>
-      </c>
-      <c r="H36">
-        <v>120</v>
-      </c>
-      <c r="I36" t="s">
-        <v>41</v>
-      </c>
-      <c r="J36" t="s">
-        <v>47</v>
-      </c>
-      <c r="K36" t="s">
-        <v>48</v>
-      </c>
-      <c r="L36">
-        <v>130</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A37" t="s">
-        <v>347</v>
-      </c>
-      <c r="B37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" t="s">
-        <v>36</v>
-      </c>
-      <c r="F37">
-        <v>100</v>
-      </c>
-      <c r="G37" t="s">
-        <v>40</v>
-      </c>
-      <c r="H37">
-        <v>120</v>
-      </c>
-      <c r="I37" t="s">
-        <v>41</v>
-      </c>
-      <c r="J37" t="s">
-        <v>47</v>
-      </c>
-      <c r="K37" t="s">
-        <v>48</v>
-      </c>
-      <c r="L37">
-        <v>130</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A38" t="s">
-        <v>348</v>
-      </c>
-      <c r="B38" t="s">
-        <v>109</v>
-      </c>
-      <c r="C38" t="s">
-        <v>94</v>
-      </c>
-      <c r="E38" t="s">
-        <v>58</v>
-      </c>
-      <c r="F38">
-        <v>120</v>
-      </c>
-      <c r="G38" t="s">
-        <v>51</v>
-      </c>
-      <c r="H38">
-        <v>120</v>
-      </c>
-      <c r="I38" t="s">
-        <v>41</v>
-      </c>
-      <c r="J38" t="s">
-        <v>47</v>
-      </c>
-      <c r="K38" t="s">
-        <v>48</v>
-      </c>
-      <c r="L38">
-        <v>150</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="21.75" customHeight="1">
-      <c r="A39" t="s">
-        <v>349</v>
-      </c>
-      <c r="B39" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" t="s">
-        <v>96</v>
-      </c>
-      <c r="E39" t="s">
-        <v>58</v>
-      </c>
-      <c r="F39">
-        <v>110</v>
-      </c>
-      <c r="G39" t="s">
-        <v>51</v>
-      </c>
-      <c r="H39">
-        <v>120.5</v>
-      </c>
-      <c r="I39" t="s">
-        <v>41</v>
-      </c>
-      <c r="J39" t="s">
-        <v>97</v>
-      </c>
-      <c r="K39" t="s">
-        <v>48</v>
-      </c>
-      <c r="L39">
-        <v>125</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A40" t="s">
-        <v>350</v>
-      </c>
-      <c r="B40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40" t="s">
-        <v>99</v>
-      </c>
-      <c r="E40" t="s">
-        <v>54</v>
-      </c>
-      <c r="F40">
-        <v>60</v>
-      </c>
-      <c r="G40" t="s">
-        <v>20</v>
-      </c>
-      <c r="H40">
-        <v>30.5</v>
-      </c>
-      <c r="I40" t="s">
-        <v>500</v>
-      </c>
-      <c r="J40" t="s">
-        <v>32</v>
-      </c>
-      <c r="K40" t="s">
-        <v>33</v>
-      </c>
-      <c r="L40">
-        <v>32.5</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A41" t="s">
-        <v>504</v>
-      </c>
-      <c r="B41" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41" t="s">
-        <v>503</v>
-      </c>
-      <c r="E41" t="s">
-        <v>54</v>
-      </c>
-      <c r="F41">
-        <v>75</v>
-      </c>
-      <c r="G41" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41">
-        <v>40</v>
-      </c>
-      <c r="I41" t="s">
-        <v>15</v>
-      </c>
-      <c r="J41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K41" t="s">
-        <v>33</v>
-      </c>
-      <c r="M41" s="1"/>
-    </row>
-    <row r="42" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A42" t="s">
-        <v>351</v>
-      </c>
-      <c r="B42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42" t="s">
-        <v>101</v>
-      </c>
-      <c r="E42" t="s">
-        <v>54</v>
-      </c>
-      <c r="F42">
-        <v>80</v>
-      </c>
-      <c r="G42" t="s">
-        <v>40</v>
-      </c>
-      <c r="H42">
-        <v>45.5</v>
-      </c>
-      <c r="I42" t="s">
-        <v>15</v>
-      </c>
-      <c r="J42" t="s">
-        <v>102</v>
-      </c>
-      <c r="K42" t="s">
-        <v>32</v>
-      </c>
-      <c r="L42">
-        <v>55.5</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A43" t="s">
-        <v>353</v>
-      </c>
-      <c r="B43" t="s">
-        <v>109</v>
-      </c>
-      <c r="C43" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43" t="s">
-        <v>36</v>
-      </c>
-      <c r="F43">
-        <v>120</v>
-      </c>
-      <c r="G43" t="s">
-        <v>51</v>
-      </c>
-      <c r="H43">
-        <v>120</v>
-      </c>
-      <c r="I43" t="s">
-        <v>41</v>
-      </c>
-      <c r="J43" t="s">
-        <v>42</v>
-      </c>
-      <c r="K43" t="s">
-        <v>43</v>
-      </c>
-      <c r="L43">
-        <v>125</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A44" t="s">
-        <v>354</v>
-      </c>
-      <c r="B44" t="s">
-        <v>109</v>
-      </c>
-      <c r="C44" t="s">
-        <v>106</v>
-      </c>
-      <c r="E44" t="s">
-        <v>58</v>
-      </c>
-      <c r="F44">
-        <v>110</v>
-      </c>
-      <c r="G44" t="s">
-        <v>51</v>
-      </c>
-      <c r="H44">
-        <v>130</v>
-      </c>
-      <c r="I44" t="s">
-        <v>46</v>
-      </c>
-      <c r="J44" t="s">
-        <v>47</v>
-      </c>
-      <c r="K44" t="s">
-        <v>48</v>
-      </c>
-      <c r="L44">
-        <v>145</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="30" customHeight="1">
-      <c r="A45" t="s">
-        <v>355</v>
-      </c>
-      <c r="B45" t="s">
-        <v>109</v>
-      </c>
-      <c r="C45" t="s">
-        <v>26</v>
-      </c>
-      <c r="E45" t="s">
-        <v>23</v>
-      </c>
-      <c r="F45">
-        <v>60</v>
-      </c>
-      <c r="G45" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45">
-        <v>41</v>
-      </c>
-      <c r="I45" t="s">
-        <v>15</v>
-      </c>
-      <c r="J45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K45" t="s">
-        <v>17</v>
-      </c>
-      <c r="L45">
-        <v>41</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="30" customHeight="1">
-      <c r="A46" t="s">
-        <v>356</v>
-      </c>
-      <c r="B46" t="s">
-        <v>109</v>
-      </c>
-      <c r="C46" t="s">
-        <v>28</v>
-      </c>
-      <c r="E46" t="s">
-        <v>23</v>
-      </c>
-      <c r="F46">
-        <v>60</v>
-      </c>
-      <c r="G46" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46">
-        <v>41</v>
-      </c>
-      <c r="I46" t="s">
-        <v>15</v>
-      </c>
-      <c r="J46" t="s">
-        <v>29</v>
-      </c>
-      <c r="K46" t="s">
-        <v>17</v>
-      </c>
-      <c r="L46">
-        <v>41</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="30" customHeight="1">
-      <c r="A47" t="s">
-        <v>357</v>
-      </c>
-      <c r="B47" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" t="s">
-        <v>31</v>
-      </c>
-      <c r="E47" t="s">
-        <v>23</v>
-      </c>
-      <c r="F47">
-        <v>65</v>
-      </c>
-      <c r="G47" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47">
-        <v>30</v>
-      </c>
-      <c r="I47" t="s">
-        <v>500</v>
-      </c>
-      <c r="J47" t="s">
-        <v>32</v>
-      </c>
-      <c r="K47" t="s">
-        <v>33</v>
-      </c>
-      <c r="L47">
-        <v>40</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="30" customHeight="1">
-      <c r="A48" t="s">
-        <v>512</v>
-      </c>
-      <c r="C48" t="s">
-        <v>511</v>
-      </c>
-      <c r="E48" t="s">
-        <v>23</v>
-      </c>
-      <c r="F48">
-        <v>65</v>
-      </c>
-      <c r="G48" t="s">
-        <v>20</v>
-      </c>
-      <c r="H48">
-        <v>40</v>
-      </c>
-      <c r="I48" t="s">
-        <v>15</v>
-      </c>
-      <c r="J48" t="s">
-        <v>32</v>
-      </c>
-      <c r="K48" t="s">
-        <v>33</v>
-      </c>
-      <c r="M48" s="1"/>
-    </row>
-    <row r="49" spans="13:13" ht="38.25" customHeight="1">
-      <c r="M49" s="1"/>
+      <c r="N54" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88187150-537C-4DF5-B5F2-1D9B6416187A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CCE0DE-E8A9-4EB1-A04F-C933472E8D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="527">
   <si>
     <t>image_url</t>
   </si>
@@ -1899,6 +1899,18 @@
   </si>
   <si>
     <t>ONKRON</t>
+  </si>
+  <si>
+    <t>TS1580-B</t>
+  </si>
+  <si>
+    <t>TS2811DS-B</t>
+  </si>
+  <si>
+    <t>TS2811DSE-B</t>
+  </si>
+  <si>
+    <t>images/TS2811DS-B</t>
   </si>
 </sst>
 </file>
@@ -2001,10 +2013,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N54" totalsRowShown="0">
-  <autoFilter ref="A1:N54" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N54">
-    <sortCondition ref="K1:K54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N57" totalsRowShown="0">
+  <autoFilter ref="A1:N57" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N55">
+    <sortCondition ref="C1:C55"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
@@ -2359,7 +2371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -2422,128 +2434,132 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>499</v>
+      <c r="A2" t="s">
+        <v>512</v>
       </c>
       <c r="B2" t="s">
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="E2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2">
         <v>40</v>
       </c>
-      <c r="I2">
-        <v>100</v>
-      </c>
       <c r="J2" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>498</v>
+      <c r="A3" t="s">
+        <v>159</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>495</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
         <v>520</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>521</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="I3">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J3" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N3" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>497</v>
+      <c r="A4" t="s">
+        <v>121</v>
       </c>
       <c r="B4" t="s">
         <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>494</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>520</v>
       </c>
       <c r="F4" t="s">
+        <v>521</v>
+      </c>
+      <c r="G4">
+        <v>55</v>
+      </c>
+      <c r="H4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4">
+        <v>200</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>496</v>
+      </c>
+      <c r="E5" t="s">
+        <v>520</v>
+      </c>
+      <c r="F5" t="s">
         <v>36</v>
-      </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4">
-        <v>100</v>
-      </c>
-      <c r="J4" t="s">
-        <v>119</v>
-      </c>
-      <c r="K4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L4" t="s">
-        <v>48</v>
-      </c>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A5" t="s">
-        <v>346</v>
-      </c>
-      <c r="B5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" t="s">
-        <v>522</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -2552,10 +2568,10 @@
         <v>40</v>
       </c>
       <c r="I5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="K5" t="s">
         <v>47</v>
@@ -2563,25 +2579,20 @@
       <c r="L5" t="s">
         <v>48</v>
       </c>
-      <c r="M5">
-        <v>130</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>93</v>
-      </c>
+      <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A6" t="s">
-        <v>347</v>
+      <c r="A6" s="3" t="s">
+        <v>498</v>
       </c>
       <c r="B6" t="s">
         <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>495</v>
       </c>
       <c r="E6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F6" t="s">
         <v>36</v>
@@ -2593,10 +2604,10 @@
         <v>40</v>
       </c>
       <c r="I6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="K6" t="s">
         <v>47</v>
@@ -2604,40 +2615,35 @@
       <c r="L6" t="s">
         <v>48</v>
       </c>
-      <c r="M6">
-        <v>130</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A7" t="s">
-        <v>348</v>
+      <c r="A7" s="3" t="s">
+        <v>497</v>
       </c>
       <c r="B7" t="s">
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>494</v>
       </c>
       <c r="E7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J7" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="K7" t="s">
         <v>47</v>
@@ -2645,1486 +2651,1483 @@
       <c r="L7" t="s">
         <v>48</v>
       </c>
-      <c r="M7">
-        <v>150</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="21.75" customHeight="1">
       <c r="A8" t="s">
-        <v>354</v>
+        <v>276</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
         <v>522</v>
       </c>
       <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>55</v>
+      </c>
+      <c r="H8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8">
+        <v>30</v>
+      </c>
+      <c r="J8" t="s">
+        <v>500</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" t="s">
+        <v>522</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>65</v>
+      </c>
+      <c r="H9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9">
+        <v>35</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" t="s">
+        <v>113</v>
+      </c>
+      <c r="L9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" t="s">
+        <v>522</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10">
+        <v>40</v>
+      </c>
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A11" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" t="s">
+        <v>522</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11">
+        <v>35</v>
+      </c>
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A12" t="s">
+        <v>324</v>
+      </c>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" t="s">
+        <v>522</v>
+      </c>
+      <c r="F12" t="s">
         <v>58</v>
       </c>
-      <c r="G8">
-        <v>110</v>
-      </c>
-      <c r="H8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8">
+      <c r="G12">
+        <v>55</v>
+      </c>
+      <c r="H12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12">
+        <v>35</v>
+      </c>
+      <c r="J12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12">
+        <v>40</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A13" t="s">
+        <v>325</v>
+      </c>
+      <c r="B13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>522</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="4">
+        <v>55</v>
+      </c>
+      <c r="H13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13">
+        <v>40</v>
+      </c>
+      <c r="J13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" t="s">
+        <v>17</v>
+      </c>
+      <c r="M13">
+        <v>45</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A14" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1171-B</v>
+      </c>
+      <c r="B14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" t="s">
+        <v>516</v>
+      </c>
+      <c r="E14" t="s">
+        <v>522</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14">
+        <v>60</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14">
+        <v>40</v>
+      </c>
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14">
+        <v>45</v>
+      </c>
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A15" t="s">
+        <v>327</v>
+      </c>
+      <c r="B15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
+        <v>522</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15">
+        <v>65</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15">
+        <v>35</v>
+      </c>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A16" t="s">
+        <v>328</v>
+      </c>
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>522</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16">
+        <v>65</v>
+      </c>
+      <c r="H16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16">
+        <v>35</v>
+      </c>
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A17" t="s">
+        <v>329</v>
+      </c>
+      <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" t="s">
+        <v>522</v>
+      </c>
+      <c r="F17" t="s">
+        <v>488</v>
+      </c>
+      <c r="G17">
+        <v>70</v>
+      </c>
+      <c r="H17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17">
+        <v>40.5</v>
+      </c>
+      <c r="J17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" t="s">
+        <v>63</v>
+      </c>
+      <c r="L17" t="s">
+        <v>43</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A18" t="s">
+        <v>330</v>
+      </c>
+      <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" t="s">
+        <v>522</v>
+      </c>
+      <c r="F18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18">
+        <v>65</v>
+      </c>
+      <c r="H18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18">
+        <v>45</v>
+      </c>
+      <c r="J18" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18">
+        <v>50</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A19" t="s">
+        <v>331</v>
+      </c>
+      <c r="B19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s">
+        <v>522</v>
+      </c>
+      <c r="F19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19">
+        <v>65</v>
+      </c>
+      <c r="H19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19">
+        <v>45</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" t="s">
+        <v>33</v>
+      </c>
+      <c r="M19">
+        <v>50</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A20" t="s">
+        <v>332</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" t="s">
+        <v>522</v>
+      </c>
+      <c r="F20" t="s">
+        <v>488</v>
+      </c>
+      <c r="G20">
+        <v>83</v>
+      </c>
+      <c r="H20" t="s">
+        <v>40</v>
+      </c>
+      <c r="I20">
+        <v>65.5</v>
+      </c>
+      <c r="J20" t="s">
+        <v>119</v>
+      </c>
+      <c r="K20" t="s">
+        <v>69</v>
+      </c>
+      <c r="L20" t="s">
+        <v>48</v>
+      </c>
+      <c r="M20">
+        <v>70</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A21" t="s">
+        <v>333</v>
+      </c>
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" t="s">
+        <v>522</v>
+      </c>
+      <c r="F21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21">
+        <v>70</v>
+      </c>
+      <c r="H21" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21">
+        <v>45.5</v>
+      </c>
+      <c r="J21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M21">
+        <v>55.5</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A22" t="s">
+        <v>334</v>
+      </c>
+      <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" t="s">
+        <v>522</v>
+      </c>
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22">
+        <v>75</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22">
+        <v>45</v>
+      </c>
+      <c r="J22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" t="s">
+        <v>33</v>
+      </c>
+      <c r="M22">
+        <v>50</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A23" t="s">
+        <v>337</v>
+      </c>
+      <c r="B23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" t="s">
+        <v>522</v>
+      </c>
+      <c r="F23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23">
+        <v>65</v>
+      </c>
+      <c r="J23" t="s">
+        <v>119</v>
+      </c>
+      <c r="K23" t="s">
+        <v>37</v>
+      </c>
+      <c r="L23" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23">
+        <v>70</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A24" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1552E-W</v>
+      </c>
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>517</v>
+      </c>
+      <c r="E24" t="s">
+        <v>522</v>
+      </c>
+      <c r="F24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24">
+        <v>67</v>
+      </c>
+      <c r="J24" t="s">
+        <v>119</v>
+      </c>
+      <c r="K24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" t="s">
+        <v>33</v>
+      </c>
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A25" t="s">
+        <v>338</v>
+      </c>
+      <c r="B25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" t="s">
+        <v>522</v>
+      </c>
+      <c r="F25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25">
+        <v>75</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25">
+        <v>50</v>
+      </c>
+      <c r="J25" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M25">
+        <v>60</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A26" t="s">
+        <v>506</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" t="s">
+        <v>502</v>
+      </c>
+      <c r="E26" t="s">
+        <v>522</v>
+      </c>
+      <c r="F26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26">
+        <v>75</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26">
+        <v>50</v>
+      </c>
+      <c r="J26" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M26">
+        <v>60</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A27" t="s">
+        <v>505</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>501</v>
+      </c>
+      <c r="E27" t="s">
+        <v>522</v>
+      </c>
+      <c r="F27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27">
+        <v>75</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27">
+        <v>50</v>
+      </c>
+      <c r="J27" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" t="s">
+        <v>33</v>
+      </c>
+      <c r="M27">
+        <v>60</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A28" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s">
+        <v>490</v>
+      </c>
+      <c r="E28" t="s">
+        <v>522</v>
+      </c>
+      <c r="F28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28">
+        <v>75</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28">
+        <v>60</v>
+      </c>
+      <c r="J28" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" t="s">
+        <v>491</v>
+      </c>
+      <c r="L28" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A29" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1580-B</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>523</v>
+      </c>
+      <c r="E29" t="s">
+        <v>522</v>
+      </c>
+      <c r="F29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29">
+        <v>60</v>
+      </c>
+      <c r="J29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" t="s">
+        <v>491</v>
+      </c>
+      <c r="L29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A30" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" t="s">
+        <v>489</v>
+      </c>
+      <c r="E30" t="s">
+        <v>522</v>
+      </c>
+      <c r="F30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30">
+        <v>60</v>
+      </c>
+      <c r="J30" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" t="s">
+        <v>491</v>
+      </c>
+      <c r="L30" t="s">
+        <v>32</v>
+      </c>
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A31" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-B</v>
+      </c>
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" t="s">
+        <v>513</v>
+      </c>
+      <c r="E31" t="s">
+        <v>522</v>
+      </c>
+      <c r="F31" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31">
+        <v>90</v>
+      </c>
+      <c r="H31" t="s">
+        <v>40</v>
+      </c>
+      <c r="I31">
+        <v>100</v>
+      </c>
+      <c r="J31" t="s">
+        <v>41</v>
+      </c>
+      <c r="K31" t="s">
+        <v>81</v>
+      </c>
+      <c r="L31" t="s">
+        <v>43</v>
+      </c>
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A32" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-C</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" t="s">
+        <v>514</v>
+      </c>
+      <c r="E32" t="s">
+        <v>522</v>
+      </c>
+      <c r="F32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32">
+        <v>90</v>
+      </c>
+      <c r="H32" t="s">
+        <v>40</v>
+      </c>
+      <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32" t="s">
+        <v>41</v>
+      </c>
+      <c r="K32" t="s">
+        <v>81</v>
+      </c>
+      <c r="L32" t="s">
+        <v>43</v>
+      </c>
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A33" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-G</v>
+      </c>
+      <c r="B33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" t="s">
+        <v>515</v>
+      </c>
+      <c r="E33" t="s">
+        <v>522</v>
+      </c>
+      <c r="F33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33">
+        <v>90</v>
+      </c>
+      <c r="H33" t="s">
+        <v>40</v>
+      </c>
+      <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33" t="s">
+        <v>41</v>
+      </c>
+      <c r="K33" t="s">
+        <v>81</v>
+      </c>
+      <c r="L33" t="s">
+        <v>43</v>
+      </c>
+      <c r="N33" s="1"/>
+    </row>
+    <row r="34" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A34" t="s">
+        <v>339</v>
+      </c>
+      <c r="B34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" t="s">
+        <v>522</v>
+      </c>
+      <c r="F34" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34">
+        <v>90</v>
+      </c>
+      <c r="H34" t="s">
+        <v>40</v>
+      </c>
+      <c r="I34">
+        <v>75</v>
+      </c>
+      <c r="J34" t="s">
+        <v>41</v>
+      </c>
+      <c r="K34" t="s">
+        <v>81</v>
+      </c>
+      <c r="L34" t="s">
+        <v>43</v>
+      </c>
+      <c r="M34">
+        <v>90</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A35" t="s">
+        <v>508</v>
+      </c>
+      <c r="B35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" t="s">
+        <v>510</v>
+      </c>
+      <c r="E35" t="s">
+        <v>522</v>
+      </c>
+      <c r="F35" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35">
+        <v>90</v>
+      </c>
+      <c r="H35" t="s">
+        <v>40</v>
+      </c>
+      <c r="I35">
+        <v>75</v>
+      </c>
+      <c r="J35" t="s">
+        <v>41</v>
+      </c>
+      <c r="K35" t="s">
+        <v>81</v>
+      </c>
+      <c r="L35" t="s">
+        <v>43</v>
+      </c>
+      <c r="M35">
+        <v>90</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A36" t="s">
+        <v>507</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>509</v>
+      </c>
+      <c r="E36" t="s">
+        <v>522</v>
+      </c>
+      <c r="F36" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36">
+        <v>90</v>
+      </c>
+      <c r="H36" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36">
+        <v>75</v>
+      </c>
+      <c r="J36" t="s">
+        <v>41</v>
+      </c>
+      <c r="K36" t="s">
+        <v>81</v>
+      </c>
+      <c r="L36" t="s">
+        <v>43</v>
+      </c>
+      <c r="M36">
+        <v>90</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A37" t="s">
+        <v>340</v>
+      </c>
+      <c r="B37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" t="s">
+        <v>522</v>
+      </c>
+      <c r="F37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37">
+        <v>86</v>
+      </c>
+      <c r="H37" t="s">
+        <v>40</v>
+      </c>
+      <c r="I37">
+        <v>90.9</v>
+      </c>
+      <c r="J37" t="s">
+        <v>41</v>
+      </c>
+      <c r="K37" t="s">
+        <v>42</v>
+      </c>
+      <c r="L37" t="s">
+        <v>43</v>
+      </c>
+      <c r="M37">
+        <v>105.9</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A38" t="s">
+        <v>342</v>
+      </c>
+      <c r="B38" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" t="s">
+        <v>522</v>
+      </c>
+      <c r="F38" t="s">
+        <v>521</v>
+      </c>
+      <c r="G38">
+        <v>65</v>
+      </c>
+      <c r="H38" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38">
+        <v>90.9</v>
+      </c>
+      <c r="J38" t="s">
+        <v>41</v>
+      </c>
+      <c r="K38" t="s">
+        <v>42</v>
+      </c>
+      <c r="L38" t="s">
+        <v>43</v>
+      </c>
+      <c r="M38">
+        <v>105.9</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A39" t="s">
+        <v>343</v>
+      </c>
+      <c r="B39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" t="s">
+        <v>522</v>
+      </c>
+      <c r="F39" t="s">
+        <v>521</v>
+      </c>
+      <c r="G39">
+        <v>65</v>
+      </c>
+      <c r="H39" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39">
+        <v>90.9</v>
+      </c>
+      <c r="J39" t="s">
+        <v>41</v>
+      </c>
+      <c r="K39" t="s">
+        <v>42</v>
+      </c>
+      <c r="L39" t="s">
+        <v>43</v>
+      </c>
+      <c r="M39">
+        <v>105.9</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A40" t="s">
+        <v>344</v>
+      </c>
+      <c r="B40" t="s">
+        <v>109</v>
+      </c>
+      <c r="C40" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" t="s">
+        <v>522</v>
+      </c>
+      <c r="F40" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40">
+        <v>86</v>
+      </c>
+      <c r="H40" t="s">
+        <v>40</v>
+      </c>
+      <c r="I40">
+        <v>90.9</v>
+      </c>
+      <c r="J40" t="s">
+        <v>41</v>
+      </c>
+      <c r="K40" t="s">
+        <v>42</v>
+      </c>
+      <c r="L40" t="s">
+        <v>43</v>
+      </c>
+      <c r="M40">
+        <v>105.9</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="26.25" customHeight="1">
+      <c r="A41" t="s">
+        <v>341</v>
+      </c>
+      <c r="B41" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" t="s">
+        <v>522</v>
+      </c>
+      <c r="F41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G41">
+        <v>86</v>
+      </c>
+      <c r="H41" t="s">
+        <v>40</v>
+      </c>
+      <c r="I41">
+        <v>90.9</v>
+      </c>
+      <c r="J41" t="s">
+        <v>41</v>
+      </c>
+      <c r="K41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L41" t="s">
+        <v>43</v>
+      </c>
+      <c r="M41">
+        <v>105.9</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="26.25" customHeight="1">
+      <c r="A42" t="s">
+        <v>345</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" t="s">
+        <v>522</v>
+      </c>
+      <c r="F42" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42">
+        <v>90</v>
+      </c>
+      <c r="H42" t="s">
+        <v>40</v>
+      </c>
+      <c r="I42">
+        <v>90</v>
+      </c>
+      <c r="J42" t="s">
+        <v>41</v>
+      </c>
+      <c r="K42" t="s">
+        <v>81</v>
+      </c>
+      <c r="L42" t="s">
+        <v>43</v>
+      </c>
+      <c r="M42">
+        <v>100</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="26.25" customHeight="1">
+      <c r="A43" t="s">
+        <v>346</v>
+      </c>
+      <c r="B43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" t="s">
+        <v>522</v>
+      </c>
+      <c r="F43" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43">
+        <v>100</v>
+      </c>
+      <c r="H43" t="s">
+        <v>40</v>
+      </c>
+      <c r="I43">
+        <v>120</v>
+      </c>
+      <c r="J43" t="s">
+        <v>41</v>
+      </c>
+      <c r="K43" t="s">
+        <v>47</v>
+      </c>
+      <c r="L43" t="s">
+        <v>48</v>
+      </c>
+      <c r="M43">
         <v>130</v>
       </c>
-      <c r="J8" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="N43" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A44" t="s">
+        <v>347</v>
+      </c>
+      <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>45</v>
+      </c>
+      <c r="E44" t="s">
+        <v>522</v>
+      </c>
+      <c r="F44" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44">
+        <v>100</v>
+      </c>
+      <c r="H44" t="s">
+        <v>40</v>
+      </c>
+      <c r="I44">
+        <v>120</v>
+      </c>
+      <c r="J44" t="s">
+        <v>41</v>
+      </c>
+      <c r="K44" t="s">
         <v>47</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L44" t="s">
         <v>48</v>
       </c>
-      <c r="M8">
-        <v>145</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A9" t="str">
+      <c r="M44">
+        <v>130</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A45" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1991-W</v>
       </c>
-      <c r="B9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
         <v>518</v>
-      </c>
-      <c r="E9" t="s">
-        <v>522</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
-      <c r="H9" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9">
-        <v>120</v>
-      </c>
-      <c r="J9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9" t="s">
-        <v>48</v>
-      </c>
-      <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A10" t="s">
-        <v>332</v>
-      </c>
-      <c r="B10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" t="s">
-        <v>522</v>
-      </c>
-      <c r="F10" t="s">
-        <v>488</v>
-      </c>
-      <c r="G10">
-        <v>83</v>
-      </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10">
-        <v>65.5</v>
-      </c>
-      <c r="J10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K10" t="s">
-        <v>69</v>
-      </c>
-      <c r="L10" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10">
-        <v>70</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A11" t="s">
-        <v>349</v>
-      </c>
-      <c r="B11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" t="s">
-        <v>522</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11">
-        <v>110</v>
-      </c>
-      <c r="H11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11">
-        <v>120.5</v>
-      </c>
-      <c r="J11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" t="s">
-        <v>97</v>
-      </c>
-      <c r="L11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11">
-        <v>125</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A12" t="s">
-        <v>276</v>
-      </c>
-      <c r="B12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" t="s">
-        <v>522</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12">
-        <v>55</v>
-      </c>
-      <c r="H12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I12">
-        <v>30</v>
-      </c>
-      <c r="J12" t="s">
-        <v>500</v>
-      </c>
-      <c r="K12" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" t="s">
-        <v>17</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A13" t="s">
-        <v>279</v>
-      </c>
-      <c r="B13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E13" t="s">
-        <v>522</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
-        <v>55</v>
-      </c>
-      <c r="H13" t="s">
-        <v>55</v>
-      </c>
-      <c r="I13">
-        <v>35</v>
-      </c>
-      <c r="J13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" t="s">
-        <v>17</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A14" t="s">
-        <v>324</v>
-      </c>
-      <c r="B14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" t="s">
-        <v>522</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14">
-        <v>55</v>
-      </c>
-      <c r="H14" t="s">
-        <v>55</v>
-      </c>
-      <c r="I14">
-        <v>35</v>
-      </c>
-      <c r="J14" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" t="s">
-        <v>17</v>
-      </c>
-      <c r="M14">
-        <v>40</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A15" t="s">
-        <v>325</v>
-      </c>
-      <c r="B15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" t="s">
-        <v>522</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="4">
-        <v>55</v>
-      </c>
-      <c r="H15" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15">
-        <v>40</v>
-      </c>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" t="s">
-        <v>17</v>
-      </c>
-      <c r="M15">
-        <v>45</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A16" t="s">
-        <v>327</v>
-      </c>
-      <c r="B16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>522</v>
-      </c>
-      <c r="F16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16">
-        <v>65</v>
-      </c>
-      <c r="H16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16">
-        <v>35</v>
-      </c>
-      <c r="J16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" t="s">
-        <v>17</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A17" t="s">
-        <v>328</v>
-      </c>
-      <c r="B17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>522</v>
-      </c>
-      <c r="F17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17">
-        <v>65</v>
-      </c>
-      <c r="H17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17">
-        <v>35</v>
-      </c>
-      <c r="J17" t="s">
-        <v>15</v>
-      </c>
-      <c r="K17" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" t="s">
-        <v>17</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A18" t="s">
-        <v>355</v>
-      </c>
-      <c r="B18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" t="s">
-        <v>522</v>
-      </c>
-      <c r="F18" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18">
-        <v>60</v>
-      </c>
-      <c r="H18" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18">
-        <v>41</v>
-      </c>
-      <c r="J18" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M18">
-        <v>41</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A19" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1171-B</v>
-      </c>
-      <c r="B19" t="s">
-        <v>109</v>
-      </c>
-      <c r="C19" t="s">
-        <v>516</v>
-      </c>
-      <c r="E19" t="s">
-        <v>522</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19">
-        <v>60</v>
-      </c>
-      <c r="H19" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19">
-        <v>40</v>
-      </c>
-      <c r="J19" t="s">
-        <v>15</v>
-      </c>
-      <c r="K19" t="s">
-        <v>17</v>
-      </c>
-      <c r="L19" t="s">
-        <v>17</v>
-      </c>
-      <c r="M19">
-        <v>45</v>
-      </c>
-      <c r="N19" s="1"/>
-    </row>
-    <row r="20" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A20" t="s">
-        <v>159</v>
-      </c>
-      <c r="B20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" t="s">
-        <v>520</v>
-      </c>
-      <c r="F20" t="s">
-        <v>521</v>
-      </c>
-      <c r="G20">
-        <v>70</v>
-      </c>
-      <c r="H20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20">
-        <v>90</v>
-      </c>
-      <c r="J20" t="s">
-        <v>41</v>
-      </c>
-      <c r="K20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" t="s">
-        <v>17</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A21" t="s">
-        <v>277</v>
-      </c>
-      <c r="B21" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" t="s">
-        <v>522</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
-        <v>65</v>
-      </c>
-      <c r="H21" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21">
-        <v>35</v>
-      </c>
-      <c r="J21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" t="s">
-        <v>113</v>
-      </c>
-      <c r="L21" t="s">
-        <v>17</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A22" t="s">
-        <v>337</v>
-      </c>
-      <c r="B22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" t="s">
-        <v>522</v>
-      </c>
-      <c r="F22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22">
-        <v>75</v>
-      </c>
-      <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22">
-        <v>65</v>
-      </c>
-      <c r="J22" t="s">
-        <v>119</v>
-      </c>
-      <c r="K22" t="s">
-        <v>37</v>
-      </c>
-      <c r="L22" t="s">
-        <v>17</v>
-      </c>
-      <c r="M22">
-        <v>70</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A23" t="s">
-        <v>278</v>
-      </c>
-      <c r="B23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" t="s">
-        <v>522</v>
-      </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23">
-        <v>75</v>
-      </c>
-      <c r="H23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23">
-        <v>40</v>
-      </c>
-      <c r="J23" t="s">
-        <v>15</v>
-      </c>
-      <c r="K23" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" t="s">
-        <v>17</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A24" t="s">
-        <v>356</v>
-      </c>
-      <c r="B24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" t="s">
-        <v>522</v>
-      </c>
-      <c r="F24" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24">
-        <v>60</v>
-      </c>
-      <c r="H24" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24">
-        <v>41</v>
-      </c>
-      <c r="J24" t="s">
-        <v>15</v>
-      </c>
-      <c r="K24" t="s">
-        <v>29</v>
-      </c>
-      <c r="L24" t="s">
-        <v>17</v>
-      </c>
-      <c r="M24">
-        <v>41</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" t="s">
-        <v>520</v>
-      </c>
-      <c r="F25" t="s">
-        <v>521</v>
-      </c>
-      <c r="G25">
-        <v>55</v>
-      </c>
-      <c r="H25" t="s">
-        <v>55</v>
-      </c>
-      <c r="I25">
-        <v>200</v>
-      </c>
-      <c r="J25" t="s">
-        <v>46</v>
-      </c>
-      <c r="K25" t="s">
-        <v>32</v>
-      </c>
-      <c r="L25" t="s">
-        <v>33</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A26" t="s">
-        <v>330</v>
-      </c>
-      <c r="B26" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" t="s">
-        <v>522</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26">
-        <v>65</v>
-      </c>
-      <c r="H26" t="s">
-        <v>20</v>
-      </c>
-      <c r="I26">
-        <v>45</v>
-      </c>
-      <c r="J26" t="s">
-        <v>15</v>
-      </c>
-      <c r="K26" t="s">
-        <v>32</v>
-      </c>
-      <c r="L26" t="s">
-        <v>33</v>
-      </c>
-      <c r="M26">
-        <v>50</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A27" t="s">
-        <v>331</v>
-      </c>
-      <c r="B27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" t="s">
-        <v>522</v>
-      </c>
-      <c r="F27" t="s">
-        <v>58</v>
-      </c>
-      <c r="G27">
-        <v>65</v>
-      </c>
-      <c r="H27" t="s">
-        <v>20</v>
-      </c>
-      <c r="I27">
-        <v>45</v>
-      </c>
-      <c r="J27" t="s">
-        <v>15</v>
-      </c>
-      <c r="K27" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" t="s">
-        <v>33</v>
-      </c>
-      <c r="M27">
-        <v>50</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A28" t="s">
-        <v>333</v>
-      </c>
-      <c r="B28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" t="s">
-        <v>522</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-      <c r="G28">
-        <v>70</v>
-      </c>
-      <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28">
-        <v>45.5</v>
-      </c>
-      <c r="J28" t="s">
-        <v>15</v>
-      </c>
-      <c r="K28" t="s">
-        <v>32</v>
-      </c>
-      <c r="L28" t="s">
-        <v>33</v>
-      </c>
-      <c r="M28">
-        <v>55.5</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A29" t="s">
-        <v>334</v>
-      </c>
-      <c r="B29" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" t="s">
-        <v>73</v>
-      </c>
-      <c r="E29" t="s">
-        <v>522</v>
-      </c>
-      <c r="F29" t="s">
-        <v>58</v>
-      </c>
-      <c r="G29">
-        <v>75</v>
-      </c>
-      <c r="H29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29">
-        <v>45</v>
-      </c>
-      <c r="J29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29" t="s">
-        <v>32</v>
-      </c>
-      <c r="L29" t="s">
-        <v>33</v>
-      </c>
-      <c r="M29">
-        <v>50</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A30" t="s">
-        <v>338</v>
-      </c>
-      <c r="B30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" t="s">
-        <v>522</v>
-      </c>
-      <c r="F30" t="s">
-        <v>58</v>
-      </c>
-      <c r="G30">
-        <v>75</v>
-      </c>
-      <c r="H30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30">
-        <v>50</v>
-      </c>
-      <c r="J30" t="s">
-        <v>15</v>
-      </c>
-      <c r="K30" t="s">
-        <v>32</v>
-      </c>
-      <c r="L30" t="s">
-        <v>33</v>
-      </c>
-      <c r="M30">
-        <v>60</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A31" t="s">
-        <v>506</v>
-      </c>
-      <c r="B31" t="s">
-        <v>109</v>
-      </c>
-      <c r="C31" t="s">
-        <v>502</v>
-      </c>
-      <c r="E31" t="s">
-        <v>522</v>
-      </c>
-      <c r="F31" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31">
-        <v>75</v>
-      </c>
-      <c r="H31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31">
-        <v>50</v>
-      </c>
-      <c r="J31" t="s">
-        <v>15</v>
-      </c>
-      <c r="K31" t="s">
-        <v>32</v>
-      </c>
-      <c r="L31" t="s">
-        <v>33</v>
-      </c>
-      <c r="M31">
-        <v>60</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A32" t="s">
-        <v>505</v>
-      </c>
-      <c r="B32" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" t="s">
-        <v>501</v>
-      </c>
-      <c r="E32" t="s">
-        <v>522</v>
-      </c>
-      <c r="F32" t="s">
-        <v>58</v>
-      </c>
-      <c r="G32">
-        <v>75</v>
-      </c>
-      <c r="H32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32">
-        <v>50</v>
-      </c>
-      <c r="J32" t="s">
-        <v>15</v>
-      </c>
-      <c r="K32" t="s">
-        <v>32</v>
-      </c>
-      <c r="L32" t="s">
-        <v>33</v>
-      </c>
-      <c r="M32">
-        <v>60</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A33" t="s">
-        <v>350</v>
-      </c>
-      <c r="B33" t="s">
-        <v>109</v>
-      </c>
-      <c r="C33" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" t="s">
-        <v>522</v>
-      </c>
-      <c r="F33" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33">
-        <v>60</v>
-      </c>
-      <c r="H33" t="s">
-        <v>20</v>
-      </c>
-      <c r="I33">
-        <v>30.5</v>
-      </c>
-      <c r="J33" t="s">
-        <v>500</v>
-      </c>
-      <c r="K33" t="s">
-        <v>32</v>
-      </c>
-      <c r="L33" t="s">
-        <v>33</v>
-      </c>
-      <c r="M33">
-        <v>32.5</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A34" t="s">
-        <v>504</v>
-      </c>
-      <c r="B34" t="s">
-        <v>109</v>
-      </c>
-      <c r="C34" t="s">
-        <v>503</v>
-      </c>
-      <c r="E34" t="s">
-        <v>522</v>
-      </c>
-      <c r="F34" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34">
-        <v>75</v>
-      </c>
-      <c r="H34" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34">
-        <v>40</v>
-      </c>
-      <c r="J34" t="s">
-        <v>15</v>
-      </c>
-      <c r="K34" t="s">
-        <v>32</v>
-      </c>
-      <c r="L34" t="s">
-        <v>33</v>
-      </c>
-      <c r="N34" s="1"/>
-    </row>
-    <row r="35" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A35" t="s">
-        <v>357</v>
-      </c>
-      <c r="B35" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" t="s">
-        <v>522</v>
-      </c>
-      <c r="F35" t="s">
-        <v>23</v>
-      </c>
-      <c r="G35">
-        <v>65</v>
-      </c>
-      <c r="H35" t="s">
-        <v>20</v>
-      </c>
-      <c r="I35">
-        <v>30</v>
-      </c>
-      <c r="J35" t="s">
-        <v>500</v>
-      </c>
-      <c r="K35" t="s">
-        <v>32</v>
-      </c>
-      <c r="L35" t="s">
-        <v>33</v>
-      </c>
-      <c r="M35">
-        <v>40</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A36" t="s">
-        <v>512</v>
-      </c>
-      <c r="B36" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36" t="s">
-        <v>511</v>
-      </c>
-      <c r="E36" t="s">
-        <v>522</v>
-      </c>
-      <c r="F36" t="s">
-        <v>23</v>
-      </c>
-      <c r="G36">
-        <v>65</v>
-      </c>
-      <c r="H36" t="s">
-        <v>20</v>
-      </c>
-      <c r="I36">
-        <v>40</v>
-      </c>
-      <c r="J36" t="s">
-        <v>15</v>
-      </c>
-      <c r="K36" t="s">
-        <v>32</v>
-      </c>
-      <c r="L36" t="s">
-        <v>33</v>
-      </c>
-      <c r="N36" s="1"/>
-    </row>
-    <row r="37" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A37" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1552E-W</v>
-      </c>
-      <c r="B37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C37" t="s">
-        <v>517</v>
-      </c>
-      <c r="E37" t="s">
-        <v>522</v>
-      </c>
-      <c r="F37" t="s">
-        <v>36</v>
-      </c>
-      <c r="G37">
-        <v>75</v>
-      </c>
-      <c r="H37" t="s">
-        <v>14</v>
-      </c>
-      <c r="I37">
-        <v>67</v>
-      </c>
-      <c r="J37" t="s">
-        <v>119</v>
-      </c>
-      <c r="K37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L37" t="s">
-        <v>33</v>
-      </c>
-      <c r="N37" s="1"/>
-    </row>
-    <row r="38" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A38" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B38" t="s">
-        <v>109</v>
-      </c>
-      <c r="C38" t="s">
-        <v>490</v>
-      </c>
-      <c r="E38" t="s">
-        <v>522</v>
-      </c>
-      <c r="F38" t="s">
-        <v>23</v>
-      </c>
-      <c r="G38">
-        <v>75</v>
-      </c>
-      <c r="H38" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38">
-        <v>60</v>
-      </c>
-      <c r="J38" t="s">
-        <v>15</v>
-      </c>
-      <c r="K38" t="s">
-        <v>491</v>
-      </c>
-      <c r="L38" t="s">
-        <v>32</v>
-      </c>
-      <c r="N38" s="1"/>
-    </row>
-    <row r="39" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A39" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B39" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" t="s">
-        <v>489</v>
-      </c>
-      <c r="E39" t="s">
-        <v>522</v>
-      </c>
-      <c r="F39" t="s">
-        <v>23</v>
-      </c>
-      <c r="G39">
-        <v>75</v>
-      </c>
-      <c r="H39" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39">
-        <v>60</v>
-      </c>
-      <c r="J39" t="s">
-        <v>15</v>
-      </c>
-      <c r="K39" t="s">
-        <v>491</v>
-      </c>
-      <c r="L39" t="s">
-        <v>32</v>
-      </c>
-      <c r="N39" s="1"/>
-    </row>
-    <row r="40" spans="1:14" ht="26.25" customHeight="1">
-      <c r="A40" t="s">
-        <v>351</v>
-      </c>
-      <c r="B40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40" t="s">
-        <v>101</v>
-      </c>
-      <c r="E40" t="s">
-        <v>522</v>
-      </c>
-      <c r="F40" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40">
-        <v>80</v>
-      </c>
-      <c r="H40" t="s">
-        <v>40</v>
-      </c>
-      <c r="I40">
-        <v>45.5</v>
-      </c>
-      <c r="J40" t="s">
-        <v>15</v>
-      </c>
-      <c r="K40" t="s">
-        <v>102</v>
-      </c>
-      <c r="L40" t="s">
-        <v>32</v>
-      </c>
-      <c r="M40">
-        <v>55.5</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="26.25" customHeight="1">
-      <c r="A41" t="s">
-        <v>340</v>
-      </c>
-      <c r="B41" t="s">
-        <v>109</v>
-      </c>
-      <c r="C41" t="s">
-        <v>83</v>
-      </c>
-      <c r="E41" t="s">
-        <v>522</v>
-      </c>
-      <c r="F41" t="s">
-        <v>58</v>
-      </c>
-      <c r="G41">
-        <v>86</v>
-      </c>
-      <c r="H41" t="s">
-        <v>40</v>
-      </c>
-      <c r="I41">
-        <v>90.9</v>
-      </c>
-      <c r="J41" t="s">
-        <v>41</v>
-      </c>
-      <c r="K41" t="s">
-        <v>42</v>
-      </c>
-      <c r="L41" t="s">
-        <v>43</v>
-      </c>
-      <c r="M41">
-        <v>105.9</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="26.25" customHeight="1">
-      <c r="A42" t="s">
-        <v>342</v>
-      </c>
-      <c r="B42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42" t="s">
-        <v>86</v>
-      </c>
-      <c r="E42" t="s">
-        <v>522</v>
-      </c>
-      <c r="F42" t="s">
-        <v>521</v>
-      </c>
-      <c r="G42">
-        <v>65</v>
-      </c>
-      <c r="H42" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42">
-        <v>90.9</v>
-      </c>
-      <c r="J42" t="s">
-        <v>41</v>
-      </c>
-      <c r="K42" t="s">
-        <v>42</v>
-      </c>
-      <c r="L42" t="s">
-        <v>43</v>
-      </c>
-      <c r="M42">
-        <v>105.9</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="27.75" customHeight="1">
-      <c r="A43" t="s">
-        <v>343</v>
-      </c>
-      <c r="B43" t="s">
-        <v>109</v>
-      </c>
-      <c r="C43" t="s">
-        <v>88</v>
-      </c>
-      <c r="E43" t="s">
-        <v>522</v>
-      </c>
-      <c r="F43" t="s">
-        <v>521</v>
-      </c>
-      <c r="G43">
-        <v>65</v>
-      </c>
-      <c r="H43" t="s">
-        <v>20</v>
-      </c>
-      <c r="I43">
-        <v>90.9</v>
-      </c>
-      <c r="J43" t="s">
-        <v>41</v>
-      </c>
-      <c r="K43" t="s">
-        <v>42</v>
-      </c>
-      <c r="L43" t="s">
-        <v>43</v>
-      </c>
-      <c r="M43">
-        <v>105.9</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A44" t="s">
-        <v>344</v>
-      </c>
-      <c r="B44" t="s">
-        <v>109</v>
-      </c>
-      <c r="C44" t="s">
-        <v>39</v>
-      </c>
-      <c r="E44" t="s">
-        <v>522</v>
-      </c>
-      <c r="F44" t="s">
-        <v>36</v>
-      </c>
-      <c r="G44">
-        <v>86</v>
-      </c>
-      <c r="H44" t="s">
-        <v>40</v>
-      </c>
-      <c r="I44">
-        <v>90.9</v>
-      </c>
-      <c r="J44" t="s">
-        <v>41</v>
-      </c>
-      <c r="K44" t="s">
-        <v>42</v>
-      </c>
-      <c r="L44" t="s">
-        <v>43</v>
-      </c>
-      <c r="M44">
-        <v>105.9</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="30" customHeight="1">
-      <c r="A45" t="s">
-        <v>341</v>
-      </c>
-      <c r="B45" t="s">
-        <v>109</v>
-      </c>
-      <c r="C45" t="s">
-        <v>85</v>
       </c>
       <c r="E45" t="s">
         <v>522</v>
@@ -4133,45 +4136,40 @@
         <v>58</v>
       </c>
       <c r="G45">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="H45" t="s">
         <v>40</v>
       </c>
       <c r="I45">
-        <v>90.9</v>
+        <v>120</v>
       </c>
       <c r="J45" t="s">
         <v>41</v>
       </c>
       <c r="K45" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L45" t="s">
-        <v>43</v>
-      </c>
-      <c r="M45">
-        <v>105.9</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>84</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="N45" s="1"/>
     </row>
     <row r="46" spans="1:14" ht="30" customHeight="1">
       <c r="A46" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="E46" t="s">
         <v>522</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G46">
         <v>120</v>
@@ -4186,27 +4184,27 @@
         <v>41</v>
       </c>
       <c r="K46" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L46" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M46">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="30" customHeight="1">
       <c r="A47" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E47" t="s">
         <v>522</v>
@@ -4215,237 +4213,239 @@
         <v>58</v>
       </c>
       <c r="G47">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="H47" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I47">
-        <v>75</v>
+        <v>120.5</v>
       </c>
       <c r="J47" t="s">
         <v>41</v>
       </c>
       <c r="K47" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="L47" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M47">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="30" customHeight="1">
       <c r="A48" t="s">
-        <v>508</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s">
         <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>510</v>
+        <v>99</v>
       </c>
       <c r="E48" t="s">
         <v>522</v>
       </c>
       <c r="F48" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G48">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H48" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I48">
-        <v>75</v>
+        <v>30.5</v>
       </c>
       <c r="J48" t="s">
-        <v>41</v>
+        <v>500</v>
       </c>
       <c r="K48" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="L48" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="M48">
-        <v>90</v>
+        <v>32.5</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="34.5" customHeight="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="30" customHeight="1">
       <c r="A49" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B49" t="s">
         <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="E49" t="s">
         <v>522</v>
       </c>
       <c r="F49" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G49">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H49" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49">
         <v>40</v>
       </c>
-      <c r="I49">
-        <v>75</v>
-      </c>
       <c r="J49" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="L49" t="s">
-        <v>43</v>
-      </c>
-      <c r="M49">
-        <v>90</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>82</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N49" s="1"/>
     </row>
     <row r="50" spans="1:14" ht="34.5" customHeight="1">
       <c r="A50" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E50" t="s">
         <v>522</v>
       </c>
       <c r="F50" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G50">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s">
         <v>40</v>
       </c>
       <c r="I50">
-        <v>90</v>
+        <v>45.5</v>
       </c>
       <c r="J50" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="L50" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="M50">
-        <v>100</v>
+        <v>55.5</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A51" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-B</v>
+      <c r="A51" t="s">
+        <v>353</v>
       </c>
       <c r="B51" t="s">
         <v>109</v>
       </c>
       <c r="C51" t="s">
-        <v>513</v>
+        <v>50</v>
       </c>
       <c r="E51" t="s">
         <v>522</v>
       </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G51">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H51" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I51">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J51" t="s">
         <v>41</v>
       </c>
       <c r="K51" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L51" t="s">
         <v>43</v>
       </c>
-      <c r="N51" s="1"/>
-    </row>
-    <row r="52" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A52" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-C</v>
+      <c r="M51">
+        <v>125</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A52" t="s">
+        <v>354</v>
       </c>
       <c r="B52" t="s">
         <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>514</v>
+        <v>106</v>
       </c>
       <c r="E52" t="s">
         <v>522</v>
       </c>
       <c r="F52" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G52">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="H52" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I52">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="J52" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K52" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L52" t="s">
-        <v>43</v>
-      </c>
-      <c r="N52" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="M52">
+        <v>145</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="53" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A53" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-G</v>
+      <c r="A53" t="s">
+        <v>355</v>
       </c>
       <c r="B53" t="s">
         <v>109</v>
       </c>
       <c r="C53" t="s">
-        <v>515</v>
+        <v>26</v>
       </c>
       <c r="E53" t="s">
         <v>522</v>
@@ -4454,62 +4454,184 @@
         <v>23</v>
       </c>
       <c r="G53">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H53" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I53">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="J53" t="s">
+        <v>15</v>
+      </c>
+      <c r="K53" t="s">
+        <v>17</v>
+      </c>
+      <c r="L53" t="s">
+        <v>17</v>
+      </c>
+      <c r="M53">
         <v>41</v>
       </c>
-      <c r="K53" t="s">
-        <v>81</v>
-      </c>
-      <c r="L53" t="s">
-        <v>43</v>
-      </c>
-      <c r="N53" s="1"/>
-    </row>
-    <row r="54" spans="1:14" ht="37.5" customHeight="1">
+      <c r="N53" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="33.75" customHeight="1">
       <c r="A54" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="B54" t="s">
         <v>109</v>
       </c>
       <c r="C54" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E54" t="s">
         <v>522</v>
       </c>
       <c r="F54" t="s">
-        <v>488</v>
+        <v>23</v>
       </c>
       <c r="G54">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H54" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I54">
-        <v>40.5</v>
+        <v>41</v>
       </c>
       <c r="J54" t="s">
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="L54" t="s">
-        <v>43</v>
+        <v>17</v>
+      </c>
+      <c r="M54">
+        <v>41</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="37.5" customHeight="1">
+      <c r="A55" t="s">
+        <v>357</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" t="s">
+        <v>522</v>
+      </c>
+      <c r="F55" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55">
+        <v>65</v>
+      </c>
+      <c r="H55" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55">
+        <v>30</v>
+      </c>
+      <c r="J55" t="s">
+        <v>500</v>
+      </c>
+      <c r="K55" t="s">
+        <v>32</v>
+      </c>
+      <c r="L55" t="s">
+        <v>33</v>
+      </c>
+      <c r="M55">
+        <v>40</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A56" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS2811DS-B</v>
+      </c>
+      <c r="B56" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" t="s">
+        <v>524</v>
+      </c>
+      <c r="E56" t="s">
+        <v>520</v>
+      </c>
+      <c r="F56" t="s">
+        <v>521</v>
+      </c>
+      <c r="G56">
+        <v>75</v>
+      </c>
+      <c r="H56" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56">
+        <v>130</v>
+      </c>
+      <c r="J56" t="s">
+        <v>46</v>
+      </c>
+      <c r="K56" t="s">
+        <v>47</v>
+      </c>
+      <c r="L56" t="s">
+        <v>48</v>
+      </c>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="1:14" ht="42" customHeight="1">
+      <c r="A57" t="s">
+        <v>526</v>
+      </c>
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s">
+        <v>525</v>
+      </c>
+      <c r="E57" t="s">
+        <v>520</v>
+      </c>
+      <c r="F57" t="s">
+        <v>36</v>
+      </c>
+      <c r="G57">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57">
+        <v>130</v>
+      </c>
+      <c r="J57" t="s">
+        <v>46</v>
+      </c>
+      <c r="K57" t="s">
+        <v>47</v>
+      </c>
+      <c r="L57" t="s">
+        <v>48</v>
+      </c>
+      <c r="N57" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CCE0DE-E8A9-4EB1-A04F-C933472E8D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0C8955-3278-4810-89DC-8F8C0D9ABE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="528">
   <si>
     <t>image_url</t>
   </si>
@@ -1911,6 +1911,9 @@
   </si>
   <si>
     <t>images/TS2811DS-B</t>
+  </si>
+  <si>
+    <t>17"-60"</t>
   </si>
 </sst>
 </file>
@@ -2015,9 +2018,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N57" totalsRowShown="0">
   <autoFilter ref="A1:N57" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N55">
-    <sortCondition ref="C1:C55"/>
-  </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -2527,7 +2527,7 @@
         <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>527</v>
       </c>
       <c r="I4">
         <v>200</v>
@@ -2673,7 +2673,7 @@
         <v>55</v>
       </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>527</v>
       </c>
       <c r="I8">
         <v>30</v>
@@ -2787,7 +2787,7 @@
         <v>55</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
+        <v>527</v>
       </c>
       <c r="I11">
         <v>35</v>
@@ -2825,7 +2825,7 @@
         <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>55</v>
+        <v>527</v>
       </c>
       <c r="I12">
         <v>35</v>
@@ -2866,7 +2866,7 @@
         <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>527</v>
       </c>
       <c r="I13">
         <v>40</v>
@@ -2908,7 +2908,7 @@
         <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>527</v>
       </c>
       <c r="I14">
         <v>40</v>
@@ -4257,7 +4257,7 @@
         <v>60</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>527</v>
       </c>
       <c r="I48">
         <v>30.5</v>
@@ -4457,7 +4457,7 @@
         <v>60</v>
       </c>
       <c r="H53" t="s">
-        <v>20</v>
+        <v>527</v>
       </c>
       <c r="I53">
         <v>41</v>
@@ -4498,7 +4498,7 @@
         <v>60</v>
       </c>
       <c r="H54" t="s">
-        <v>20</v>
+        <v>527</v>
       </c>
       <c r="I54">
         <v>41</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0C8955-3278-4810-89DC-8F8C0D9ABE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0196EF73-6CB1-437D-B480-2192F032D69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="530">
   <si>
     <t>image_url</t>
   </si>
@@ -1914,6 +1914,12 @@
   </si>
   <si>
     <t>17"-60"</t>
+  </si>
+  <si>
+    <t>TS2551-ST</t>
+  </si>
+  <si>
+    <t>images/TS2551-ST</t>
   </si>
 </sst>
 </file>
@@ -2016,8 +2022,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N57" totalsRowShown="0">
-  <autoFilter ref="A1:N57" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N58" totalsRowShown="0">
+  <autoFilter ref="A1:N58" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -2371,7 +2377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -4632,6 +4638,42 @@
         <v>48</v>
       </c>
       <c r="N57" s="1"/>
+    </row>
+    <row r="58" spans="1:14" ht="36.75" customHeight="1">
+      <c r="A58" t="s">
+        <v>529</v>
+      </c>
+      <c r="B58" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" t="s">
+        <v>528</v>
+      </c>
+      <c r="E58" t="s">
+        <v>522</v>
+      </c>
+      <c r="F58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58">
+        <v>75</v>
+      </c>
+      <c r="H58" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58">
+        <v>60</v>
+      </c>
+      <c r="J58" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58" t="s">
+        <v>32</v>
+      </c>
+      <c r="L58" t="s">
+        <v>32</v>
+      </c>
+      <c r="N58" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0196EF73-6CB1-437D-B480-2192F032D69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298BD2A4-3740-4CE4-9A63-14F6E38A08E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="532">
   <si>
     <t>image_url</t>
   </si>
@@ -1920,6 +1920,12 @@
   </si>
   <si>
     <t>images/TS2551-ST</t>
+  </si>
+  <si>
+    <t>TS2811E-WO</t>
+  </si>
+  <si>
+    <t>images/TS2811E-WO</t>
   </si>
 </sst>
 </file>
@@ -2022,8 +2028,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N58" totalsRowShown="0">
-  <autoFilter ref="A1:N58" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N59" totalsRowShown="0">
+  <autoFilter ref="A1:N59" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -2377,7 +2383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -4402,97 +4408,92 @@
         <v>52</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="34.5" customHeight="1">
+    <row r="52" spans="1:14" ht="32.25" customHeight="1">
       <c r="A52" t="s">
-        <v>354</v>
+        <v>531</v>
       </c>
       <c r="B52" t="s">
         <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>106</v>
+        <v>530</v>
       </c>
       <c r="E52" t="s">
         <v>522</v>
       </c>
       <c r="F52" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G52">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H52" t="s">
         <v>51</v>
       </c>
       <c r="I52">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J52" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K52" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L52" t="s">
-        <v>48</v>
-      </c>
-      <c r="M52">
-        <v>145</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="33.75" customHeight="1">
+        <v>43</v>
+      </c>
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" ht="34.5" customHeight="1">
       <c r="A53" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B53" t="s">
         <v>109</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="E53" t="s">
         <v>522</v>
       </c>
       <c r="F53" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G53">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="H53" t="s">
-        <v>527</v>
+        <v>51</v>
       </c>
       <c r="I53">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="J53" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="K53" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="L53" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="M53">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="33.75" customHeight="1">
       <c r="A54" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B54" t="s">
         <v>109</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E54" t="s">
         <v>522</v>
@@ -4513,7 +4514,7 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="L54" t="s">
         <v>17</v>
@@ -4522,18 +4523,18 @@
         <v>41</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="37.5" customHeight="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="33.75" customHeight="1">
       <c r="A55" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B55" t="s">
         <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E55" t="s">
         <v>522</v>
@@ -4542,82 +4543,87 @@
         <v>23</v>
       </c>
       <c r="G55">
+        <v>60</v>
+      </c>
+      <c r="H55" t="s">
+        <v>527</v>
+      </c>
+      <c r="I55">
+        <v>41</v>
+      </c>
+      <c r="J55" t="s">
+        <v>15</v>
+      </c>
+      <c r="K55" t="s">
+        <v>29</v>
+      </c>
+      <c r="L55" t="s">
+        <v>17</v>
+      </c>
+      <c r="M55">
+        <v>41</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="37.5" customHeight="1">
+      <c r="A56" t="s">
+        <v>357</v>
+      </c>
+      <c r="B56" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56" t="s">
+        <v>522</v>
+      </c>
+      <c r="F56" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56">
         <v>65</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H56" t="s">
         <v>20</v>
       </c>
-      <c r="I55">
+      <c r="I56">
         <v>30</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J56" t="s">
         <v>500</v>
       </c>
-      <c r="K55" t="s">
+      <c r="K56" t="s">
         <v>32</v>
       </c>
-      <c r="L55" t="s">
+      <c r="L56" t="s">
         <v>33</v>
       </c>
-      <c r="M55">
+      <c r="M56">
         <v>40</v>
       </c>
-      <c r="N55" s="1" t="s">
+      <c r="N56" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A56" t="str">
+    <row r="57" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A57" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS2811DS-B</v>
       </c>
-      <c r="B56" t="s">
-        <v>109</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s">
         <v>524</v>
-      </c>
-      <c r="E56" t="s">
-        <v>520</v>
-      </c>
-      <c r="F56" t="s">
-        <v>521</v>
-      </c>
-      <c r="G56">
-        <v>75</v>
-      </c>
-      <c r="H56" t="s">
-        <v>14</v>
-      </c>
-      <c r="I56">
-        <v>130</v>
-      </c>
-      <c r="J56" t="s">
-        <v>46</v>
-      </c>
-      <c r="K56" t="s">
-        <v>47</v>
-      </c>
-      <c r="L56" t="s">
-        <v>48</v>
-      </c>
-      <c r="N56" s="1"/>
-    </row>
-    <row r="57" spans="1:14" ht="42" customHeight="1">
-      <c r="A57" t="s">
-        <v>526</v>
-      </c>
-      <c r="B57" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57" t="s">
-        <v>525</v>
       </c>
       <c r="E57" t="s">
         <v>520</v>
       </c>
       <c r="F57" t="s">
-        <v>36</v>
+        <v>521</v>
       </c>
       <c r="G57">
         <v>75</v>
@@ -4639,21 +4645,21 @@
       </c>
       <c r="N57" s="1"/>
     </row>
-    <row r="58" spans="1:14" ht="36.75" customHeight="1">
+    <row r="58" spans="1:14" ht="42" customHeight="1">
       <c r="A58" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B58" t="s">
         <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E58" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F58" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G58">
         <v>75</v>
@@ -4662,18 +4668,54 @@
         <v>14</v>
       </c>
       <c r="I58">
+        <v>130</v>
+      </c>
+      <c r="J58" t="s">
+        <v>46</v>
+      </c>
+      <c r="K58" t="s">
+        <v>47</v>
+      </c>
+      <c r="L58" t="s">
+        <v>48</v>
+      </c>
+      <c r="N58" s="1"/>
+    </row>
+    <row r="59" spans="1:14" ht="36.75" customHeight="1">
+      <c r="A59" t="s">
+        <v>529</v>
+      </c>
+      <c r="B59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" t="s">
+        <v>528</v>
+      </c>
+      <c r="E59" t="s">
+        <v>522</v>
+      </c>
+      <c r="F59" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59">
+        <v>75</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59">
         <v>60</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J59" t="s">
         <v>15</v>
       </c>
-      <c r="K58" t="s">
+      <c r="K59" t="s">
         <v>32</v>
       </c>
-      <c r="L58" t="s">
+      <c r="L59" t="s">
         <v>32</v>
       </c>
-      <c r="N58" s="1"/>
+      <c r="N59" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298BD2A4-3740-4CE4-9A63-14F6E38A08E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FA3A49-87A4-415F-B701-9F5B035709E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="535">
   <si>
     <t>image_url</t>
   </si>
@@ -1926,6 +1926,15 @@
   </si>
   <si>
     <t>images/TS2811E-WO</t>
+  </si>
+  <si>
+    <t>DS-6575LC</t>
+  </si>
+  <si>
+    <t>images/DS-6575LC</t>
+  </si>
+  <si>
+    <t>600x800</t>
   </si>
 </sst>
 </file>
@@ -2028,8 +2037,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N59" totalsRowShown="0">
-  <autoFilter ref="A1:N59" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N60" totalsRowShown="0">
+  <autoFilter ref="A1:N60" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -2383,7 +2392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -4716,6 +4725,42 @@
         <v>32</v>
       </c>
       <c r="N59" s="1"/>
+    </row>
+    <row r="60" spans="1:14" ht="29.25" customHeight="1">
+      <c r="A60" t="s">
+        <v>533</v>
+      </c>
+      <c r="B60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" t="s">
+        <v>532</v>
+      </c>
+      <c r="E60" t="s">
+        <v>522</v>
+      </c>
+      <c r="F60" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60">
+        <v>75</v>
+      </c>
+      <c r="H60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60">
+        <v>65</v>
+      </c>
+      <c r="J60" t="s">
+        <v>119</v>
+      </c>
+      <c r="K60" t="s">
+        <v>534</v>
+      </c>
+      <c r="L60" t="s">
+        <v>32</v>
+      </c>
+      <c r="N60" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FA3A49-87A4-415F-B701-9F5B035709E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854CCD06-F2E8-462D-BC46-CCBF92688581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -3863,7 +3863,7 @@
         <v>86</v>
       </c>
       <c r="E38" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F38" t="s">
         <v>521</v>
@@ -3904,7 +3904,7 @@
         <v>88</v>
       </c>
       <c r="E39" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F39" t="s">
         <v>521</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854CCD06-F2E8-462D-BC46-CCBF92688581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410CA4D4-6902-49E8-9301-E286FA63E81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="540">
   <si>
     <t>image_url</t>
   </si>
@@ -1935,6 +1935,21 @@
   </si>
   <si>
     <t>600x800</t>
+  </si>
+  <si>
+    <t>TS1571-W</t>
+  </si>
+  <si>
+    <t>TS1991E-W</t>
+  </si>
+  <si>
+    <t>TS1871-W</t>
+  </si>
+  <si>
+    <t>images/1571-W</t>
+  </si>
+  <si>
+    <t>images/1871-W</t>
   </si>
 </sst>
 </file>
@@ -2037,8 +2052,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N60" totalsRowShown="0">
-  <autoFilter ref="A1:N60" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N63" totalsRowShown="0">
+  <autoFilter ref="A1:N63" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -2392,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -2920,7 +2935,7 @@
         <v>516</v>
       </c>
       <c r="E14" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F14" t="s">
         <v>58</v>
@@ -3388,13 +3403,10 @@
     </row>
     <row r="26" spans="1:14" ht="21.75" customHeight="1">
       <c r="A26" t="s">
-        <v>506</v>
-      </c>
-      <c r="B26" t="s">
-        <v>109</v>
+        <v>538</v>
       </c>
       <c r="C26" t="s">
-        <v>502</v>
+        <v>535</v>
       </c>
       <c r="E26" t="s">
         <v>522</v>
@@ -3423,19 +3435,17 @@
       <c r="M26">
         <v>60</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1">
       <c r="A27" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B27" t="s">
         <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E27" t="s">
         <v>522</v>
@@ -3469,20 +3479,20 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>492</v>
+      <c r="A28" t="s">
+        <v>505</v>
       </c>
       <c r="B28" t="s">
         <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E28" t="s">
         <v>522</v>
       </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G28">
         <v>75</v>
@@ -3491,65 +3501,70 @@
         <v>14</v>
       </c>
       <c r="I28">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
       </c>
       <c r="K28" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" t="s">
+        <v>33</v>
+      </c>
+      <c r="M28">
+        <v>60</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>490</v>
+      </c>
+      <c r="E29" t="s">
+        <v>522</v>
+      </c>
+      <c r="F29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29">
+        <v>60</v>
+      </c>
+      <c r="J29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" t="s">
         <v>491</v>
       </c>
-      <c r="L28" t="s">
+      <c r="L29" t="s">
         <v>32</v>
       </c>
-      <c r="N28" s="1"/>
-    </row>
-    <row r="29" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A29" t="str">
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A30" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1580-B</v>
       </c>
-      <c r="B29" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" t="s">
         <v>523</v>
-      </c>
-      <c r="E29" t="s">
-        <v>522</v>
-      </c>
-      <c r="F29" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29">
-        <v>75</v>
-      </c>
-      <c r="H29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29">
-        <v>60</v>
-      </c>
-      <c r="J29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29" t="s">
-        <v>491</v>
-      </c>
-      <c r="L29" t="s">
-        <v>32</v>
-      </c>
-      <c r="N29" s="1"/>
-    </row>
-    <row r="30" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" t="s">
-        <v>489</v>
       </c>
       <c r="E30" t="s">
         <v>522</v>
@@ -3578,15 +3593,14 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A31" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-B</v>
+      <c r="A31" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="E31" t="s">
         <v>522</v>
@@ -3595,35 +3609,35 @@
         <v>23</v>
       </c>
       <c r="G31">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J31" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>81</v>
+        <v>491</v>
       </c>
       <c r="L31" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" ht="21.75" customHeight="1">
       <c r="A32" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-C</v>
+        <v>images/TS1590-B</v>
       </c>
       <c r="B32" t="s">
         <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E32" t="s">
         <v>522</v>
@@ -3654,13 +3668,13 @@
     <row r="33" spans="1:14" ht="21.75" customHeight="1">
       <c r="A33" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-G</v>
+        <v>images/TS1590-C</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E33" t="s">
         <v>522</v>
@@ -3689,20 +3703,21 @@
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A34" t="s">
-        <v>339</v>
+      <c r="A34" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-G</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>515</v>
       </c>
       <c r="E34" t="s">
         <v>522</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G34">
         <v>90</v>
@@ -3711,7 +3726,7 @@
         <v>40</v>
       </c>
       <c r="I34">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J34" t="s">
         <v>41</v>
@@ -3722,22 +3737,17 @@
       <c r="L34" t="s">
         <v>43</v>
       </c>
-      <c r="M34">
-        <v>90</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="N34" s="1"/>
     </row>
     <row r="35" spans="1:14" ht="21.75" customHeight="1">
       <c r="A35" t="s">
-        <v>508</v>
+        <v>339</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>510</v>
+        <v>80</v>
       </c>
       <c r="E35" t="s">
         <v>522</v>
@@ -3772,13 +3782,13 @@
     </row>
     <row r="36" spans="1:14" ht="21.75" customHeight="1">
       <c r="A36" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="B36" t="s">
         <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="E36" t="s">
         <v>522</v>
@@ -3807,19 +3817,17 @@
       <c r="M36">
         <v>90</v>
       </c>
-      <c r="N36" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="N36" s="1"/>
     </row>
     <row r="37" spans="1:14" ht="21.75" customHeight="1">
       <c r="A37" t="s">
-        <v>340</v>
+        <v>508</v>
       </c>
       <c r="B37" t="s">
         <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>510</v>
       </c>
       <c r="E37" t="s">
         <v>522</v>
@@ -3828,92 +3836,92 @@
         <v>58</v>
       </c>
       <c r="G37">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s">
         <v>40</v>
       </c>
       <c r="I37">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="J37" t="s">
         <v>41</v>
       </c>
       <c r="K37" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L37" t="s">
         <v>43</v>
       </c>
       <c r="M37">
-        <v>105.9</v>
+        <v>90</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="21.75" customHeight="1">
       <c r="A38" t="s">
-        <v>342</v>
+        <v>507</v>
       </c>
       <c r="B38" t="s">
         <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>509</v>
       </c>
       <c r="E38" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F38" t="s">
-        <v>521</v>
+        <v>58</v>
       </c>
       <c r="G38">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I38">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="J38" t="s">
         <v>41</v>
       </c>
       <c r="K38" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L38" t="s">
         <v>43</v>
       </c>
       <c r="M38">
-        <v>105.9</v>
+        <v>90</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E39" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F39" t="s">
-        <v>521</v>
+        <v>58</v>
       </c>
       <c r="G39">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I39">
         <v>90.9</v>
@@ -3931,30 +3939,30 @@
         <v>105.9</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="21.75" customHeight="1">
       <c r="A40" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s">
         <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="E40" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F40" t="s">
-        <v>36</v>
+        <v>521</v>
       </c>
       <c r="G40">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H40" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I40">
         <v>90.9</v>
@@ -3972,30 +3980,30 @@
         <v>105.9</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="26.25" customHeight="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="21.75" customHeight="1">
       <c r="A41" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s">
         <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E41" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>521</v>
       </c>
       <c r="G41">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H41" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I41">
         <v>90.9</v>
@@ -4013,59 +4021,59 @@
         <v>105.9</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="26.25" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="21.75" customHeight="1">
       <c r="A42" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s">
         <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="E42" t="s">
         <v>522</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G42">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s">
         <v>40</v>
       </c>
       <c r="I42">
-        <v>90</v>
+        <v>90.9</v>
       </c>
       <c r="J42" t="s">
         <v>41</v>
       </c>
       <c r="K42" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L42" t="s">
         <v>43</v>
       </c>
       <c r="M42">
-        <v>100</v>
+        <v>105.9</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="26.25" customHeight="1">
       <c r="A43" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E43" t="s">
         <v>522</v>
@@ -4074,673 +4082,687 @@
         <v>58</v>
       </c>
       <c r="G43">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s">
         <v>40</v>
       </c>
       <c r="I43">
-        <v>120</v>
+        <v>90.9</v>
       </c>
       <c r="J43" t="s">
         <v>41</v>
       </c>
       <c r="K43" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L43" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M43">
-        <v>130</v>
+        <v>105.9</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="27.75" customHeight="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="26.25" customHeight="1">
       <c r="A44" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="E44" t="s">
         <v>522</v>
       </c>
       <c r="F44" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G44">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s">
         <v>40</v>
       </c>
       <c r="I44">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J44" t="s">
         <v>41</v>
       </c>
       <c r="K44" t="s">
+        <v>81</v>
+      </c>
+      <c r="L44" t="s">
+        <v>43</v>
+      </c>
+      <c r="M44">
+        <v>100</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="26.25" customHeight="1">
+      <c r="A45" t="s">
+        <v>346</v>
+      </c>
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45" t="s">
+        <v>522</v>
+      </c>
+      <c r="F45" t="s">
+        <v>58</v>
+      </c>
+      <c r="G45">
+        <v>100</v>
+      </c>
+      <c r="H45" t="s">
+        <v>40</v>
+      </c>
+      <c r="I45">
+        <v>120</v>
+      </c>
+      <c r="J45" t="s">
+        <v>41</v>
+      </c>
+      <c r="K45" t="s">
         <v>47</v>
       </c>
-      <c r="L44" t="s">
+      <c r="L45" t="s">
         <v>48</v>
       </c>
-      <c r="M44">
+      <c r="M45">
         <v>130</v>
       </c>
-      <c r="N44" s="1" t="s">
+      <c r="N45" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A46" t="s">
+        <v>347</v>
+      </c>
+      <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" t="s">
+        <v>522</v>
+      </c>
+      <c r="F46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46">
+        <v>100</v>
+      </c>
+      <c r="H46" t="s">
+        <v>40</v>
+      </c>
+      <c r="I46">
+        <v>120</v>
+      </c>
+      <c r="J46" t="s">
+        <v>41</v>
+      </c>
+      <c r="K46" t="s">
+        <v>47</v>
+      </c>
+      <c r="L46" t="s">
+        <v>48</v>
+      </c>
+      <c r="M46">
+        <v>130</v>
+      </c>
+      <c r="N46" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A45" t="str">
+    <row r="47" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A47" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1991E-W</v>
+      </c>
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>536</v>
+      </c>
+      <c r="E47" t="s">
+        <v>522</v>
+      </c>
+      <c r="F47" t="s">
+        <v>36</v>
+      </c>
+      <c r="G47">
+        <v>100</v>
+      </c>
+      <c r="H47" t="s">
+        <v>40</v>
+      </c>
+      <c r="I47">
+        <v>120</v>
+      </c>
+      <c r="J47" t="s">
+        <v>41</v>
+      </c>
+      <c r="K47" t="s">
+        <v>47</v>
+      </c>
+      <c r="L47" t="s">
+        <v>48</v>
+      </c>
+      <c r="M47">
+        <v>130</v>
+      </c>
+      <c r="N47" s="1"/>
+    </row>
+    <row r="48" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A48" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1991-W</v>
       </c>
-      <c r="B45" t="s">
-        <v>109</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
         <v>518</v>
-      </c>
-      <c r="E45" t="s">
-        <v>522</v>
-      </c>
-      <c r="F45" t="s">
-        <v>58</v>
-      </c>
-      <c r="G45">
-        <v>100</v>
-      </c>
-      <c r="H45" t="s">
-        <v>40</v>
-      </c>
-      <c r="I45">
-        <v>120</v>
-      </c>
-      <c r="J45" t="s">
-        <v>41</v>
-      </c>
-      <c r="K45" t="s">
-        <v>47</v>
-      </c>
-      <c r="L45" t="s">
-        <v>48</v>
-      </c>
-      <c r="N45" s="1"/>
-    </row>
-    <row r="46" spans="1:14" ht="30" customHeight="1">
-      <c r="A46" t="s">
-        <v>348</v>
-      </c>
-      <c r="B46" t="s">
-        <v>109</v>
-      </c>
-      <c r="C46" t="s">
-        <v>94</v>
-      </c>
-      <c r="E46" t="s">
-        <v>522</v>
-      </c>
-      <c r="F46" t="s">
-        <v>58</v>
-      </c>
-      <c r="G46">
-        <v>120</v>
-      </c>
-      <c r="H46" t="s">
-        <v>51</v>
-      </c>
-      <c r="I46">
-        <v>120</v>
-      </c>
-      <c r="J46" t="s">
-        <v>41</v>
-      </c>
-      <c r="K46" t="s">
-        <v>47</v>
-      </c>
-      <c r="L46" t="s">
-        <v>48</v>
-      </c>
-      <c r="M46">
-        <v>150</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="30" customHeight="1">
-      <c r="A47" t="s">
-        <v>349</v>
-      </c>
-      <c r="B47" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" t="s">
-        <v>96</v>
-      </c>
-      <c r="E47" t="s">
-        <v>522</v>
-      </c>
-      <c r="F47" t="s">
-        <v>58</v>
-      </c>
-      <c r="G47">
-        <v>110</v>
-      </c>
-      <c r="H47" t="s">
-        <v>51</v>
-      </c>
-      <c r="I47">
-        <v>120.5</v>
-      </c>
-      <c r="J47" t="s">
-        <v>41</v>
-      </c>
-      <c r="K47" t="s">
-        <v>97</v>
-      </c>
-      <c r="L47" t="s">
-        <v>48</v>
-      </c>
-      <c r="M47">
-        <v>125</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="30" customHeight="1">
-      <c r="A48" t="s">
-        <v>350</v>
-      </c>
-      <c r="B48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" t="s">
-        <v>99</v>
       </c>
       <c r="E48" t="s">
         <v>522</v>
       </c>
       <c r="F48" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G48">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H48" t="s">
-        <v>527</v>
+        <v>40</v>
       </c>
       <c r="I48">
-        <v>30.5</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
-        <v>500</v>
+        <v>41</v>
       </c>
       <c r="K48" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="L48" t="s">
-        <v>33</v>
-      </c>
-      <c r="M48">
-        <v>32.5</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="N48" s="1"/>
     </row>
     <row r="49" spans="1:14" ht="30" customHeight="1">
       <c r="A49" t="s">
-        <v>504</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s">
         <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>503</v>
+        <v>94</v>
       </c>
       <c r="E49" t="s">
         <v>522</v>
       </c>
       <c r="F49" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G49">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="H49" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="I49">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="J49" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="K49" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="L49" t="s">
-        <v>33</v>
-      </c>
-      <c r="N49" s="1"/>
-    </row>
-    <row r="50" spans="1:14" ht="34.5" customHeight="1">
+        <v>48</v>
+      </c>
+      <c r="M49">
+        <v>150</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="30" customHeight="1">
       <c r="A50" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E50" t="s">
         <v>522</v>
       </c>
       <c r="F50" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G50">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="H50" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I50">
-        <v>45.5</v>
+        <v>120.5</v>
       </c>
       <c r="J50" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="K50" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="L50" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="M50">
-        <v>55.5</v>
+        <v>125</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="34.5" customHeight="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="30" customHeight="1">
       <c r="A51" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B51" t="s">
         <v>109</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="E51" t="s">
         <v>522</v>
       </c>
       <c r="F51" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G51">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H51" t="s">
-        <v>51</v>
+        <v>527</v>
       </c>
       <c r="I51">
-        <v>120</v>
+        <v>30.5</v>
       </c>
       <c r="J51" t="s">
-        <v>41</v>
+        <v>500</v>
       </c>
       <c r="K51" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L51" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="M51">
-        <v>125</v>
+        <v>32.5</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="32.25" customHeight="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="30" customHeight="1">
       <c r="A52" t="s">
-        <v>531</v>
+        <v>504</v>
       </c>
       <c r="B52" t="s">
         <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>530</v>
+        <v>503</v>
       </c>
       <c r="E52" t="s">
         <v>522</v>
       </c>
       <c r="F52" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G52">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="I52">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="J52" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L52" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="1:14" ht="34.5" customHeight="1">
       <c r="A53" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s">
         <v>109</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E53" t="s">
         <v>522</v>
       </c>
       <c r="F53" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G53">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I53">
-        <v>130</v>
+        <v>45.5</v>
       </c>
       <c r="J53" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="L53" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="M53">
-        <v>145</v>
+        <v>55.5</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="33.75" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="34.5" customHeight="1">
       <c r="A54" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B54" t="s">
         <v>109</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E54" t="s">
         <v>522</v>
       </c>
       <c r="F54" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G54">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H54" t="s">
-        <v>527</v>
+        <v>51</v>
       </c>
       <c r="I54">
+        <v>120</v>
+      </c>
+      <c r="J54" t="s">
         <v>41</v>
       </c>
-      <c r="J54" t="s">
-        <v>15</v>
-      </c>
       <c r="K54" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="L54" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="M54">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="33.75" customHeight="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="32.25" customHeight="1">
       <c r="A55" t="s">
-        <v>356</v>
+        <v>531</v>
       </c>
       <c r="B55" t="s">
         <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>530</v>
       </c>
       <c r="E55" t="s">
         <v>522</v>
       </c>
       <c r="F55" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G55">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H55" t="s">
-        <v>527</v>
+        <v>51</v>
       </c>
       <c r="I55">
+        <v>120</v>
+      </c>
+      <c r="J55" t="s">
         <v>41</v>
       </c>
-      <c r="J55" t="s">
-        <v>15</v>
-      </c>
       <c r="K55" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="L55" t="s">
-        <v>17</v>
-      </c>
-      <c r="M55">
-        <v>41</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="37.5" customHeight="1">
+        <v>43</v>
+      </c>
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" spans="1:14" ht="34.5" customHeight="1">
       <c r="A56" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s">
         <v>109</v>
       </c>
       <c r="C56" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="E56" t="s">
         <v>522</v>
       </c>
       <c r="F56" t="s">
+        <v>58</v>
+      </c>
+      <c r="G56">
+        <v>110</v>
+      </c>
+      <c r="H56" t="s">
+        <v>51</v>
+      </c>
+      <c r="I56">
+        <v>130</v>
+      </c>
+      <c r="J56" t="s">
+        <v>46</v>
+      </c>
+      <c r="K56" t="s">
+        <v>47</v>
+      </c>
+      <c r="L56" t="s">
+        <v>48</v>
+      </c>
+      <c r="M56">
+        <v>145</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A57" t="s">
+        <v>355</v>
+      </c>
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" t="s">
+        <v>522</v>
+      </c>
+      <c r="F57" t="s">
         <v>23</v>
       </c>
-      <c r="G56">
+      <c r="G57">
+        <v>60</v>
+      </c>
+      <c r="H57" t="s">
+        <v>527</v>
+      </c>
+      <c r="I57">
+        <v>41</v>
+      </c>
+      <c r="J57" t="s">
+        <v>15</v>
+      </c>
+      <c r="K57" t="s">
+        <v>17</v>
+      </c>
+      <c r="L57" t="s">
+        <v>17</v>
+      </c>
+      <c r="M57">
+        <v>41</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A58" t="s">
+        <v>356</v>
+      </c>
+      <c r="B58" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" t="s">
+        <v>522</v>
+      </c>
+      <c r="F58" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58">
+        <v>60</v>
+      </c>
+      <c r="H58" t="s">
+        <v>527</v>
+      </c>
+      <c r="I58">
+        <v>41</v>
+      </c>
+      <c r="J58" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58" t="s">
+        <v>29</v>
+      </c>
+      <c r="L58" t="s">
+        <v>17</v>
+      </c>
+      <c r="M58">
+        <v>41</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="37.5" customHeight="1">
+      <c r="A59" t="s">
+        <v>357</v>
+      </c>
+      <c r="B59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" t="s">
+        <v>522</v>
+      </c>
+      <c r="F59" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59">
         <v>65</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H59" t="s">
         <v>20</v>
       </c>
-      <c r="I56">
+      <c r="I59">
         <v>30</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J59" t="s">
         <v>500</v>
       </c>
-      <c r="K56" t="s">
+      <c r="K59" t="s">
         <v>32</v>
       </c>
-      <c r="L56" t="s">
+      <c r="L59" t="s">
         <v>33</v>
       </c>
-      <c r="M56">
+      <c r="M59">
         <v>40</v>
       </c>
-      <c r="N56" s="1" t="s">
+      <c r="N59" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A57" t="str">
+    <row r="60" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A60" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS2811DS-B</v>
       </c>
-      <c r="B57" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="B60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" t="s">
         <v>524</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E60" t="s">
         <v>520</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F60" t="s">
         <v>521</v>
-      </c>
-      <c r="G57">
-        <v>75</v>
-      </c>
-      <c r="H57" t="s">
-        <v>14</v>
-      </c>
-      <c r="I57">
-        <v>130</v>
-      </c>
-      <c r="J57" t="s">
-        <v>46</v>
-      </c>
-      <c r="K57" t="s">
-        <v>47</v>
-      </c>
-      <c r="L57" t="s">
-        <v>48</v>
-      </c>
-      <c r="N57" s="1"/>
-    </row>
-    <row r="58" spans="1:14" ht="42" customHeight="1">
-      <c r="A58" t="s">
-        <v>526</v>
-      </c>
-      <c r="B58" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" t="s">
-        <v>525</v>
-      </c>
-      <c r="E58" t="s">
-        <v>520</v>
-      </c>
-      <c r="F58" t="s">
-        <v>36</v>
-      </c>
-      <c r="G58">
-        <v>75</v>
-      </c>
-      <c r="H58" t="s">
-        <v>14</v>
-      </c>
-      <c r="I58">
-        <v>130</v>
-      </c>
-      <c r="J58" t="s">
-        <v>46</v>
-      </c>
-      <c r="K58" t="s">
-        <v>47</v>
-      </c>
-      <c r="L58" t="s">
-        <v>48</v>
-      </c>
-      <c r="N58" s="1"/>
-    </row>
-    <row r="59" spans="1:14" ht="36.75" customHeight="1">
-      <c r="A59" t="s">
-        <v>529</v>
-      </c>
-      <c r="B59" t="s">
-        <v>109</v>
-      </c>
-      <c r="C59" t="s">
-        <v>528</v>
-      </c>
-      <c r="E59" t="s">
-        <v>522</v>
-      </c>
-      <c r="F59" t="s">
-        <v>23</v>
-      </c>
-      <c r="G59">
-        <v>75</v>
-      </c>
-      <c r="H59" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59">
-        <v>60</v>
-      </c>
-      <c r="J59" t="s">
-        <v>15</v>
-      </c>
-      <c r="K59" t="s">
-        <v>32</v>
-      </c>
-      <c r="L59" t="s">
-        <v>32</v>
-      </c>
-      <c r="N59" s="1"/>
-    </row>
-    <row r="60" spans="1:14" ht="29.25" customHeight="1">
-      <c r="A60" t="s">
-        <v>533</v>
-      </c>
-      <c r="B60" t="s">
-        <v>109</v>
-      </c>
-      <c r="C60" t="s">
-        <v>532</v>
-      </c>
-      <c r="E60" t="s">
-        <v>522</v>
-      </c>
-      <c r="F60" t="s">
-        <v>23</v>
       </c>
       <c r="G60">
         <v>75</v>
@@ -4749,18 +4771,126 @@
         <v>14</v>
       </c>
       <c r="I60">
+        <v>130</v>
+      </c>
+      <c r="J60" t="s">
+        <v>46</v>
+      </c>
+      <c r="K60" t="s">
+        <v>47</v>
+      </c>
+      <c r="L60" t="s">
+        <v>48</v>
+      </c>
+      <c r="N60" s="1"/>
+    </row>
+    <row r="61" spans="1:14" ht="42" customHeight="1">
+      <c r="A61" t="s">
+        <v>526</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" t="s">
+        <v>525</v>
+      </c>
+      <c r="E61" t="s">
+        <v>520</v>
+      </c>
+      <c r="F61" t="s">
+        <v>36</v>
+      </c>
+      <c r="G61">
+        <v>75</v>
+      </c>
+      <c r="H61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61">
+        <v>130</v>
+      </c>
+      <c r="J61" t="s">
+        <v>46</v>
+      </c>
+      <c r="K61" t="s">
+        <v>47</v>
+      </c>
+      <c r="L61" t="s">
+        <v>48</v>
+      </c>
+      <c r="N61" s="1"/>
+    </row>
+    <row r="62" spans="1:14" ht="36.75" customHeight="1">
+      <c r="A62" t="s">
+        <v>529</v>
+      </c>
+      <c r="B62" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" t="s">
+        <v>528</v>
+      </c>
+      <c r="E62" t="s">
+        <v>522</v>
+      </c>
+      <c r="F62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62">
+        <v>75</v>
+      </c>
+      <c r="H62" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62">
+        <v>60</v>
+      </c>
+      <c r="J62" t="s">
+        <v>15</v>
+      </c>
+      <c r="K62" t="s">
+        <v>32</v>
+      </c>
+      <c r="L62" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62" s="1"/>
+    </row>
+    <row r="63" spans="1:14" ht="29.25" customHeight="1">
+      <c r="A63" t="s">
+        <v>533</v>
+      </c>
+      <c r="B63" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" t="s">
+        <v>532</v>
+      </c>
+      <c r="E63" t="s">
+        <v>522</v>
+      </c>
+      <c r="F63" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63">
+        <v>75</v>
+      </c>
+      <c r="H63" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63">
         <v>65</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J63" t="s">
         <v>119</v>
       </c>
-      <c r="K60" t="s">
+      <c r="K63" t="s">
         <v>534</v>
       </c>
-      <c r="L60" t="s">
+      <c r="L63" t="s">
         <v>32</v>
       </c>
-      <c r="N60" s="1"/>
+      <c r="N63" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410CA4D4-6902-49E8-9301-E286FA63E81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6975711B-669F-45D3-B9C5-44EEDDCC0CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="541">
   <si>
     <t>image_url</t>
   </si>
@@ -1950,6 +1950,9 @@
   </si>
   <si>
     <t>images/1871-W</t>
+  </si>
+  <si>
+    <t>TS1137-W</t>
   </si>
 </sst>
 </file>
@@ -2052,8 +2055,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N63" totalsRowShown="0">
-  <autoFilter ref="A1:N63" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N62" totalsRowShown="0">
+  <autoFilter ref="A1:N62" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -2407,7 +2410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -2843,13 +2846,13 @@
     </row>
     <row r="12" spans="1:14" ht="21.75" customHeight="1">
       <c r="A12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B12" t="s">
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
         <v>522</v>
@@ -2857,14 +2860,14 @@
       <c r="F12" t="s">
         <v>58</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="4">
         <v>55</v>
       </c>
       <c r="H12" t="s">
         <v>527</v>
       </c>
       <c r="I12">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
@@ -2876,21 +2879,22 @@
         <v>17</v>
       </c>
       <c r="M12">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A13" t="s">
-        <v>325</v>
+      <c r="A13" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1137-W</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="E13" t="s">
         <v>522</v>
@@ -2919,9 +2923,7 @@
       <c r="M13">
         <v>45</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" ht="21.75" customHeight="1">
       <c r="A14" t="str">
@@ -4067,13 +4069,13 @@
     </row>
     <row r="43" spans="1:14" ht="26.25" customHeight="1">
       <c r="A43" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E43" t="s">
         <v>522</v>
@@ -4082,39 +4084,39 @@
         <v>58</v>
       </c>
       <c r="G43">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s">
         <v>40</v>
       </c>
       <c r="I43">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="J43" t="s">
         <v>41</v>
       </c>
       <c r="K43" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L43" t="s">
         <v>43</v>
       </c>
       <c r="M43">
-        <v>105.9</v>
+        <v>100</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="26.25" customHeight="1">
       <c r="A44" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E44" t="s">
         <v>522</v>
@@ -4123,45 +4125,45 @@
         <v>58</v>
       </c>
       <c r="G44">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H44" t="s">
         <v>40</v>
       </c>
       <c r="I44">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J44" t="s">
         <v>41</v>
       </c>
       <c r="K44" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L44" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M44">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="26.25" customHeight="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="27.75" customHeight="1">
       <c r="A45" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
         <v>522</v>
       </c>
       <c r="F45" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G45">
         <v>100</v>
@@ -4185,18 +4187,19 @@
         <v>130</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="27.75" customHeight="1">
-      <c r="A46" t="s">
-        <v>347</v>
+      <c r="A46" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1991E-W</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>536</v>
       </c>
       <c r="E46" t="s">
         <v>522</v>
@@ -4225,26 +4228,24 @@
       <c r="M46">
         <v>130</v>
       </c>
-      <c r="N46" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="27.75" customHeight="1">
+      <c r="N46" s="1"/>
+    </row>
+    <row r="47" spans="1:14" ht="32.25" customHeight="1">
       <c r="A47" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1991E-W</v>
+        <v>images/TS1991-W</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="E47" t="s">
         <v>522</v>
       </c>
       <c r="F47" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G47">
         <v>100</v>
@@ -4264,21 +4265,17 @@
       <c r="L47" t="s">
         <v>48</v>
       </c>
-      <c r="M47">
-        <v>130</v>
-      </c>
       <c r="N47" s="1"/>
     </row>
-    <row r="48" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A48" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1991-W</v>
+    <row r="48" spans="1:14" ht="30" customHeight="1">
+      <c r="A48" t="s">
+        <v>348</v>
       </c>
       <c r="B48" t="s">
         <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>518</v>
+        <v>94</v>
       </c>
       <c r="E48" t="s">
         <v>522</v>
@@ -4287,10 +4284,10 @@
         <v>58</v>
       </c>
       <c r="G48">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H48" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I48">
         <v>120</v>
@@ -4304,17 +4301,22 @@
       <c r="L48" t="s">
         <v>48</v>
       </c>
-      <c r="N48" s="1"/>
+      <c r="M48">
+        <v>150</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="49" spans="1:14" ht="30" customHeight="1">
       <c r="A49" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B49" t="s">
         <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E49" t="s">
         <v>522</v>
@@ -4323,80 +4325,80 @@
         <v>58</v>
       </c>
       <c r="G49">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H49" t="s">
         <v>51</v>
       </c>
       <c r="I49">
-        <v>120</v>
+        <v>120.5</v>
       </c>
       <c r="J49" t="s">
         <v>41</v>
       </c>
       <c r="K49" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="L49" t="s">
         <v>48</v>
       </c>
       <c r="M49">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="30" customHeight="1">
       <c r="A50" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E50" t="s">
         <v>522</v>
       </c>
       <c r="F50" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G50">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="H50" t="s">
-        <v>51</v>
+        <v>527</v>
       </c>
       <c r="I50">
-        <v>120.5</v>
+        <v>30.5</v>
       </c>
       <c r="J50" t="s">
-        <v>41</v>
+        <v>500</v>
       </c>
       <c r="K50" t="s">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="L50" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M50">
-        <v>125</v>
+        <v>32.5</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="30" customHeight="1">
       <c r="A51" t="s">
-        <v>350</v>
+        <v>504</v>
       </c>
       <c r="B51" t="s">
         <v>109</v>
       </c>
       <c r="C51" t="s">
-        <v>99</v>
+        <v>503</v>
       </c>
       <c r="E51" t="s">
         <v>522</v>
@@ -4405,16 +4407,16 @@
         <v>54</v>
       </c>
       <c r="G51">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s">
-        <v>527</v>
+        <v>14</v>
       </c>
       <c r="I51">
-        <v>30.5</v>
+        <v>40</v>
       </c>
       <c r="J51" t="s">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="K51" t="s">
         <v>32</v>
@@ -4422,22 +4424,17 @@
       <c r="L51" t="s">
         <v>33</v>
       </c>
-      <c r="M51">
-        <v>32.5</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="30" customHeight="1">
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" spans="1:14" ht="34.5" customHeight="1">
       <c r="A52" t="s">
-        <v>504</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s">
         <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>503</v>
+        <v>101</v>
       </c>
       <c r="E52" t="s">
         <v>522</v>
@@ -4446,75 +4443,80 @@
         <v>54</v>
       </c>
       <c r="G52">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I52">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="J52" t="s">
         <v>15</v>
       </c>
       <c r="K52" t="s">
+        <v>102</v>
+      </c>
+      <c r="L52" t="s">
         <v>32</v>
       </c>
-      <c r="L52" t="s">
-        <v>33</v>
-      </c>
-      <c r="N52" s="1"/>
+      <c r="M52">
+        <v>55.5</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="53" spans="1:14" ht="34.5" customHeight="1">
       <c r="A53" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B53" t="s">
         <v>109</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="E53" t="s">
         <v>522</v>
       </c>
       <c r="F53" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="G53">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H53" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I53">
-        <v>45.5</v>
+        <v>120</v>
       </c>
       <c r="J53" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="K53" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="L53" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M53">
-        <v>55.5</v>
+        <v>125</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="34.5" customHeight="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="32.25" customHeight="1">
       <c r="A54" t="s">
-        <v>353</v>
+        <v>531</v>
       </c>
       <c r="B54" t="s">
         <v>109</v>
       </c>
       <c r="C54" t="s">
-        <v>50</v>
+        <v>530</v>
       </c>
       <c r="E54" t="s">
         <v>522</v>
@@ -4540,99 +4542,99 @@
       <c r="L54" t="s">
         <v>43</v>
       </c>
-      <c r="M54">
-        <v>125</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="32.25" customHeight="1">
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="1:14" ht="34.5" customHeight="1">
       <c r="A55" t="s">
-        <v>531</v>
+        <v>354</v>
       </c>
       <c r="B55" t="s">
         <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>530</v>
+        <v>106</v>
       </c>
       <c r="E55" t="s">
         <v>522</v>
       </c>
       <c r="F55" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G55">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H55" t="s">
         <v>51</v>
       </c>
       <c r="I55">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="J55" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K55" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L55" t="s">
-        <v>43</v>
-      </c>
-      <c r="N55" s="1"/>
-    </row>
-    <row r="56" spans="1:14" ht="34.5" customHeight="1">
+        <v>48</v>
+      </c>
+      <c r="M55">
+        <v>145</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="33.75" customHeight="1">
       <c r="A56" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B56" t="s">
         <v>109</v>
       </c>
       <c r="C56" t="s">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="E56" t="s">
         <v>522</v>
       </c>
       <c r="F56" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G56">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="H56" t="s">
-        <v>51</v>
+        <v>527</v>
       </c>
       <c r="I56">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="J56" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="K56" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L56" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="M56">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="33.75" customHeight="1">
       <c r="A57" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B57" t="s">
         <v>109</v>
       </c>
       <c r="C57" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E57" t="s">
         <v>522</v>
@@ -4653,7 +4655,7 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L57" t="s">
         <v>17</v>
@@ -4662,18 +4664,18 @@
         <v>41</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="33.75" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="37.5" customHeight="1">
       <c r="A58" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B58" t="s">
         <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E58" t="s">
         <v>522</v>
@@ -4682,87 +4684,82 @@
         <v>23</v>
       </c>
       <c r="G58">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H58" t="s">
-        <v>527</v>
+        <v>20</v>
       </c>
       <c r="I58">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J58" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="K58" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L58" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="M58">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="37.5" customHeight="1">
-      <c r="A59" t="s">
-        <v>357</v>
-      </c>
-      <c r="B59" t="s">
-        <v>109</v>
-      </c>
-      <c r="C59" t="s">
-        <v>31</v>
-      </c>
-      <c r="E59" t="s">
-        <v>522</v>
-      </c>
-      <c r="F59" t="s">
-        <v>23</v>
-      </c>
-      <c r="G59">
-        <v>65</v>
-      </c>
-      <c r="H59" t="s">
-        <v>20</v>
-      </c>
-      <c r="I59">
-        <v>30</v>
-      </c>
-      <c r="J59" t="s">
-        <v>500</v>
-      </c>
-      <c r="K59" t="s">
-        <v>32</v>
-      </c>
-      <c r="L59" t="s">
-        <v>33</v>
-      </c>
-      <c r="M59">
-        <v>40</v>
-      </c>
-      <c r="N59" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A60" t="str">
+    <row r="59" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A59" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS2811DS-B</v>
       </c>
+      <c r="B59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" t="s">
+        <v>524</v>
+      </c>
+      <c r="E59" t="s">
+        <v>520</v>
+      </c>
+      <c r="F59" t="s">
+        <v>521</v>
+      </c>
+      <c r="G59">
+        <v>75</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59">
+        <v>130</v>
+      </c>
+      <c r="J59" t="s">
+        <v>46</v>
+      </c>
+      <c r="K59" t="s">
+        <v>47</v>
+      </c>
+      <c r="L59" t="s">
+        <v>48</v>
+      </c>
+      <c r="N59" s="1"/>
+    </row>
+    <row r="60" spans="1:14" ht="42" customHeight="1">
+      <c r="A60" t="s">
+        <v>526</v>
+      </c>
       <c r="B60" t="s">
         <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E60" t="s">
         <v>520</v>
       </c>
       <c r="F60" t="s">
-        <v>521</v>
+        <v>36</v>
       </c>
       <c r="G60">
         <v>75</v>
@@ -4784,21 +4781,21 @@
       </c>
       <c r="N60" s="1"/>
     </row>
-    <row r="61" spans="1:14" ht="42" customHeight="1">
+    <row r="61" spans="1:14" ht="36.75" customHeight="1">
       <c r="A61" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B61" t="s">
         <v>109</v>
       </c>
       <c r="C61" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E61" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F61" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G61">
         <v>75</v>
@@ -4807,28 +4804,28 @@
         <v>14</v>
       </c>
       <c r="I61">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="J61" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="L61" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="N61" s="1"/>
     </row>
-    <row r="62" spans="1:14" ht="36.75" customHeight="1">
+    <row r="62" spans="1:14" ht="29.25" customHeight="1">
       <c r="A62" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B62" t="s">
         <v>109</v>
       </c>
       <c r="C62" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E62" t="s">
         <v>522</v>
@@ -4843,54 +4840,18 @@
         <v>14</v>
       </c>
       <c r="I62">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J62" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K62" t="s">
-        <v>32</v>
+        <v>534</v>
       </c>
       <c r="L62" t="s">
         <v>32</v>
       </c>
       <c r="N62" s="1"/>
-    </row>
-    <row r="63" spans="1:14" ht="29.25" customHeight="1">
-      <c r="A63" t="s">
-        <v>533</v>
-      </c>
-      <c r="B63" t="s">
-        <v>109</v>
-      </c>
-      <c r="C63" t="s">
-        <v>532</v>
-      </c>
-      <c r="E63" t="s">
-        <v>522</v>
-      </c>
-      <c r="F63" t="s">
-        <v>23</v>
-      </c>
-      <c r="G63">
-        <v>75</v>
-      </c>
-      <c r="H63" t="s">
-        <v>14</v>
-      </c>
-      <c r="I63">
-        <v>65</v>
-      </c>
-      <c r="J63" t="s">
-        <v>119</v>
-      </c>
-      <c r="K63" t="s">
-        <v>534</v>
-      </c>
-      <c r="L63" t="s">
-        <v>32</v>
-      </c>
-      <c r="N63" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6975711B-669F-45D3-B9C5-44EEDDCC0CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B68AEE-FC97-4FDE-A34A-E188CB27FF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="543">
   <si>
     <t>image_url</t>
   </si>
@@ -1953,6 +1953,12 @@
   </si>
   <si>
     <t>TS1137-W</t>
+  </si>
+  <si>
+    <t>платформенное решение</t>
+  </si>
+  <si>
+    <t>images/new</t>
   </si>
 </sst>
 </file>
@@ -2057,6 +2063,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N62" totalsRowShown="0">
   <autoFilter ref="A1:N62" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N61">
+    <sortCondition ref="C1:C61"/>
+  </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -2510,51 +2519,49 @@
     </row>
     <row r="3" spans="1:14" ht="21.75" customHeight="1">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>533</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>532</v>
       </c>
       <c r="E3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F3" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
       </c>
       <c r="I3">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>534</v>
       </c>
       <c r="L3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" ht="21.75" customHeight="1">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
         <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>520</v>
@@ -2563,72 +2570,74 @@
         <v>521</v>
       </c>
       <c r="G4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H4" t="s">
-        <v>527</v>
+        <v>14</v>
       </c>
       <c r="I4">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="J4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>499</v>
+      <c r="A5" t="s">
+        <v>121</v>
       </c>
       <c r="B5" t="s">
         <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>496</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
         <v>520</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>521</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>527</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J5" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="K5" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="6" spans="1:14" ht="21.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B6" t="s">
         <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E6" t="s">
         <v>520</v>
@@ -2658,13 +2667,13 @@
     </row>
     <row r="7" spans="1:14" ht="21.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B7" t="s">
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E7" t="s">
         <v>520</v>
@@ -2693,52 +2702,50 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A8" t="s">
-        <v>276</v>
+      <c r="A8" s="3" t="s">
+        <v>497</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>494</v>
       </c>
       <c r="E8" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H8" t="s">
-        <v>527</v>
+        <v>40</v>
       </c>
       <c r="I8">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J8" t="s">
-        <v>500</v>
+        <v>119</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="L8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>111</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="21.75" customHeight="1">
       <c r="A9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B9" t="s">
         <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
         <v>522</v>
@@ -2747,36 +2754,36 @@
         <v>13</v>
       </c>
       <c r="G9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>527</v>
       </c>
       <c r="I9">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="K9" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="L9" t="s">
         <v>17</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="21.75" customHeight="1">
       <c r="A10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B10" t="s">
         <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
         <v>522</v>
@@ -2785,36 +2792,36 @@
         <v>13</v>
       </c>
       <c r="G10">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I10">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J10" t="s">
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L10" t="s">
         <v>17</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="21.75" customHeight="1">
       <c r="A11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B11" t="s">
         <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
         <v>522</v>
@@ -2823,51 +2830,51 @@
         <v>13</v>
       </c>
       <c r="G11">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s">
-        <v>527</v>
+        <v>14</v>
       </c>
       <c r="I11">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L11" t="s">
         <v>17</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="21.75" customHeight="1">
       <c r="A12" t="s">
-        <v>325</v>
+        <v>279</v>
       </c>
       <c r="B12" t="s">
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
         <v>522</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="4">
+        <v>13</v>
+      </c>
+      <c r="G12">
         <v>55</v>
       </c>
       <c r="H12" t="s">
         <v>527</v>
       </c>
       <c r="I12">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
@@ -2878,23 +2885,19 @@
       <c r="L12" t="s">
         <v>17</v>
       </c>
-      <c r="M12">
-        <v>45</v>
-      </c>
       <c r="N12" s="1" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A13" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1137-W</v>
+      <c r="A13" t="s">
+        <v>325</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>540</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>522</v>
@@ -2923,27 +2926,29 @@
       <c r="M13">
         <v>45</v>
       </c>
-      <c r="N13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="21.75" customHeight="1">
       <c r="A14" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1171-B</v>
+        <v>images/TS1137-W</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="E14" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F14" t="s">
         <v>58</v>
       </c>
-      <c r="G14">
-        <v>60</v>
+      <c r="G14" s="4">
+        <v>55</v>
       </c>
       <c r="H14" t="s">
         <v>527</v>
@@ -2966,29 +2971,30 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A15" t="s">
-        <v>327</v>
+      <c r="A15" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1171-B</v>
       </c>
       <c r="B15" t="s">
         <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>516</v>
       </c>
       <c r="E15" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G15">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>527</v>
       </c>
       <c r="I15">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J15" t="s">
         <v>15</v>
@@ -2999,19 +3005,20 @@
       <c r="L15" t="s">
         <v>17</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="M15">
+        <v>45</v>
+      </c>
+      <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="21.75" customHeight="1">
       <c r="A16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
         <v>522</v>
@@ -3043,92 +3050,89 @@
     </row>
     <row r="17" spans="1:14" ht="21.75" customHeight="1">
       <c r="A17" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B17" t="s">
         <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
         <v>522</v>
       </c>
       <c r="F17" t="s">
-        <v>488</v>
+        <v>23</v>
       </c>
       <c r="G17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I17">
-        <v>40.5</v>
+        <v>35</v>
       </c>
       <c r="J17" t="s">
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="L17" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="21.75" customHeight="1">
       <c r="A18" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B18" t="s">
         <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
         <v>522</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>488</v>
       </c>
       <c r="G18">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I18">
-        <v>45</v>
+        <v>40.5</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
-      </c>
-      <c r="M18">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="21.75" customHeight="1">
       <c r="A19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B19" t="s">
         <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
         <v>522</v>
@@ -3163,95 +3167,95 @@
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1">
       <c r="A20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s">
         <v>522</v>
       </c>
       <c r="F20" t="s">
-        <v>488</v>
+        <v>58</v>
       </c>
       <c r="G20">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="H20" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I20">
-        <v>65.5</v>
+        <v>45</v>
       </c>
       <c r="J20" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="L20" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M20">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1">
       <c r="A21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B21" t="s">
         <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
         <v>522</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>488</v>
       </c>
       <c r="G21">
+        <v>83</v>
+      </c>
+      <c r="H21" t="s">
+        <v>40</v>
+      </c>
+      <c r="I21">
+        <v>65.5</v>
+      </c>
+      <c r="J21" t="s">
+        <v>119</v>
+      </c>
+      <c r="K21" t="s">
+        <v>69</v>
+      </c>
+      <c r="L21" t="s">
+        <v>48</v>
+      </c>
+      <c r="M21">
         <v>70</v>
       </c>
-      <c r="H21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21">
-        <v>45.5</v>
-      </c>
-      <c r="J21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" t="s">
-        <v>32</v>
-      </c>
-      <c r="L21" t="s">
-        <v>33</v>
-      </c>
-      <c r="M21">
-        <v>55.5</v>
-      </c>
       <c r="N21" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1">
       <c r="A22" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B22" t="s">
         <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E22" t="s">
         <v>522</v>
@@ -3260,13 +3264,13 @@
         <v>58</v>
       </c>
       <c r="G22">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H22" t="s">
         <v>14</v>
       </c>
       <c r="I22">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
@@ -3278,27 +3282,27 @@
         <v>33</v>
       </c>
       <c r="M22">
-        <v>50</v>
+        <v>55.5</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1">
       <c r="A23" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
         <v>522</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G23">
         <v>75</v>
@@ -3307,76 +3311,81 @@
         <v>14</v>
       </c>
       <c r="I23">
+        <v>45</v>
+      </c>
+      <c r="J23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" t="s">
+        <v>33</v>
+      </c>
+      <c r="M23">
+        <v>50</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A24" t="s">
+        <v>337</v>
+      </c>
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" t="s">
+        <v>522</v>
+      </c>
+      <c r="F24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24">
         <v>65</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J24" t="s">
         <v>119</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K24" t="s">
         <v>37</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L24" t="s">
         <v>17</v>
       </c>
-      <c r="M23">
+      <c r="M24">
         <v>70</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A24" t="str">
+    <row r="25" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A25" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1552E-W</v>
       </c>
-      <c r="B24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" t="s">
         <v>517</v>
-      </c>
-      <c r="E24" t="s">
-        <v>522</v>
-      </c>
-      <c r="F24" t="s">
-        <v>36</v>
-      </c>
-      <c r="G24">
-        <v>75</v>
-      </c>
-      <c r="H24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24">
-        <v>67</v>
-      </c>
-      <c r="J24" t="s">
-        <v>119</v>
-      </c>
-      <c r="K24" t="s">
-        <v>32</v>
-      </c>
-      <c r="L24" t="s">
-        <v>33</v>
-      </c>
-      <c r="N24" s="1"/>
-    </row>
-    <row r="25" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A25" t="s">
-        <v>338</v>
-      </c>
-      <c r="B25" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" t="s">
-        <v>78</v>
       </c>
       <c r="E25" t="s">
         <v>522</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G25">
         <v>75</v>
@@ -3385,10 +3394,10 @@
         <v>14</v>
       </c>
       <c r="I25">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="J25" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K25" t="s">
         <v>32</v>
@@ -3396,19 +3405,17 @@
       <c r="L25" t="s">
         <v>33</v>
       </c>
-      <c r="M25">
-        <v>60</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" ht="21.75" customHeight="1">
       <c r="A26" t="s">
-        <v>538</v>
+        <v>338</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s">
         <v>522</v>
@@ -3437,7 +3444,9 @@
       <c r="M26">
         <v>60</v>
       </c>
-      <c r="N26" s="1"/>
+      <c r="N26" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1">
       <c r="A27" t="s">
@@ -3522,20 +3531,17 @@
       </c>
     </row>
     <row r="29" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B29" t="s">
-        <v>109</v>
+      <c r="A29" t="s">
+        <v>538</v>
       </c>
       <c r="C29" t="s">
-        <v>490</v>
+        <v>535</v>
       </c>
       <c r="E29" t="s">
         <v>522</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G29">
         <v>75</v>
@@ -3544,16 +3550,19 @@
         <v>14</v>
       </c>
       <c r="I29">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>491</v>
+        <v>32</v>
       </c>
       <c r="L29" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M29">
+        <v>60</v>
       </c>
       <c r="N29" s="1"/>
     </row>
@@ -3596,13 +3605,13 @@
     </row>
     <row r="31" spans="1:14" ht="21.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E31" t="s">
         <v>522</v>
@@ -3631,15 +3640,14 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A32" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-B</v>
+      <c r="A32" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="B32" t="s">
         <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="E32" t="s">
         <v>522</v>
@@ -3648,35 +3656,35 @@
         <v>23</v>
       </c>
       <c r="G32">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H32" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J32" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>81</v>
+        <v>491</v>
       </c>
       <c r="L32" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" ht="21.75" customHeight="1">
       <c r="A33" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-C</v>
+        <v>images/TS1590-B</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E33" t="s">
         <v>522</v>
@@ -3707,13 +3715,13 @@
     <row r="34" spans="1:14" ht="21.75" customHeight="1">
       <c r="A34" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-G</v>
+        <v>images/TS1590-C</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E34" t="s">
         <v>522</v>
@@ -3742,20 +3750,21 @@
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A35" t="s">
-        <v>339</v>
+      <c r="A35" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-G</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>515</v>
       </c>
       <c r="E35" t="s">
         <v>522</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G35">
         <v>90</v>
@@ -3764,7 +3773,7 @@
         <v>40</v>
       </c>
       <c r="I35">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J35" t="s">
         <v>41</v>
@@ -3775,22 +3784,17 @@
       <c r="L35" t="s">
         <v>43</v>
       </c>
-      <c r="M35">
-        <v>90</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="N35" s="1"/>
     </row>
     <row r="36" spans="1:14" ht="21.75" customHeight="1">
       <c r="A36" t="s">
-        <v>539</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s">
         <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>537</v>
+        <v>80</v>
       </c>
       <c r="E36" t="s">
         <v>522</v>
@@ -3819,7 +3823,9 @@
       <c r="M36">
         <v>90</v>
       </c>
-      <c r="N36" s="1"/>
+      <c r="N36" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="37" spans="1:14" ht="21.75" customHeight="1">
       <c r="A37" t="s">
@@ -3905,13 +3911,13 @@
     </row>
     <row r="39" spans="1:14" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>340</v>
+        <v>539</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>537</v>
       </c>
       <c r="E39" t="s">
         <v>522</v>
@@ -3920,51 +3926,49 @@
         <v>58</v>
       </c>
       <c r="G39">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s">
         <v>40</v>
       </c>
       <c r="I39">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="J39" t="s">
         <v>41</v>
       </c>
       <c r="K39" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L39" t="s">
         <v>43</v>
       </c>
       <c r="M39">
-        <v>105.9</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>84</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="N39" s="1"/>
     </row>
     <row r="40" spans="1:14" ht="21.75" customHeight="1">
       <c r="A40" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s">
         <v>109</v>
       </c>
       <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" t="s">
+        <v>522</v>
+      </c>
+      <c r="F40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40">
         <v>86</v>
       </c>
-      <c r="E40" t="s">
-        <v>520</v>
-      </c>
-      <c r="F40" t="s">
-        <v>521</v>
-      </c>
-      <c r="G40">
-        <v>65</v>
-      </c>
       <c r="H40" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I40">
         <v>90.9</v>
@@ -3982,18 +3986,18 @@
         <v>105.9</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="21.75" customHeight="1">
       <c r="A41" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s">
         <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
         <v>520</v>
@@ -4023,30 +4027,30 @@
         <v>105.9</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="21.75" customHeight="1">
       <c r="A42" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s">
         <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="E42" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F42" t="s">
-        <v>36</v>
+        <v>521</v>
       </c>
       <c r="G42">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H42" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I42">
         <v>90.9</v>
@@ -4064,59 +4068,59 @@
         <v>105.9</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="26.25" customHeight="1">
       <c r="A43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="E43" t="s">
         <v>522</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G43">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s">
         <v>40</v>
       </c>
       <c r="I43">
-        <v>90</v>
+        <v>90.9</v>
       </c>
       <c r="J43" t="s">
         <v>41</v>
       </c>
       <c r="K43" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L43" t="s">
         <v>43</v>
       </c>
       <c r="M43">
-        <v>100</v>
+        <v>105.9</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="26.25" customHeight="1">
       <c r="A44" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E44" t="s">
         <v>522</v>
@@ -4125,45 +4129,45 @@
         <v>58</v>
       </c>
       <c r="G44">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s">
         <v>40</v>
       </c>
       <c r="I44">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J44" t="s">
         <v>41</v>
       </c>
       <c r="K44" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L44" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M44">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="27.75" customHeight="1">
       <c r="A45" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="E45" t="s">
         <v>522</v>
       </c>
       <c r="F45" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G45">
         <v>100</v>
@@ -4187,19 +4191,18 @@
         <v>130</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="27.75" customHeight="1">
-      <c r="A46" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1991E-W</v>
+      <c r="A46" t="s">
+        <v>347</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>536</v>
+        <v>45</v>
       </c>
       <c r="E46" t="s">
         <v>522</v>
@@ -4228,24 +4231,26 @@
       <c r="M46">
         <v>130</v>
       </c>
-      <c r="N46" s="1"/>
+      <c r="N46" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="47" spans="1:14" ht="32.25" customHeight="1">
       <c r="A47" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1991-W</v>
+        <v>images/TS1991E-W</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="E47" t="s">
         <v>522</v>
       </c>
       <c r="F47" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G47">
         <v>100</v>
@@ -4265,17 +4270,21 @@
       <c r="L47" t="s">
         <v>48</v>
       </c>
+      <c r="M47">
+        <v>130</v>
+      </c>
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="1:14" ht="30" customHeight="1">
-      <c r="A48" t="s">
-        <v>348</v>
+      <c r="A48" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1991-W</v>
       </c>
       <c r="B48" t="s">
         <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
+        <v>518</v>
       </c>
       <c r="E48" t="s">
         <v>522</v>
@@ -4284,10 +4293,10 @@
         <v>58</v>
       </c>
       <c r="G48">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H48" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I48">
         <v>120</v>
@@ -4301,22 +4310,17 @@
       <c r="L48" t="s">
         <v>48</v>
       </c>
-      <c r="M48">
-        <v>150</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="N48" s="1"/>
     </row>
     <row r="49" spans="1:14" ht="30" customHeight="1">
       <c r="A49" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s">
         <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E49" t="s">
         <v>522</v>
@@ -4325,72 +4329,72 @@
         <v>58</v>
       </c>
       <c r="G49">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H49" t="s">
         <v>51</v>
       </c>
       <c r="I49">
-        <v>120.5</v>
+        <v>120</v>
       </c>
       <c r="J49" t="s">
         <v>41</v>
       </c>
       <c r="K49" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="L49" t="s">
         <v>48</v>
       </c>
       <c r="M49">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="30" customHeight="1">
       <c r="A50" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E50" t="s">
         <v>522</v>
       </c>
       <c r="F50" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G50">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="H50" t="s">
-        <v>527</v>
+        <v>51</v>
       </c>
       <c r="I50">
-        <v>30.5</v>
+        <v>120.5</v>
       </c>
       <c r="J50" t="s">
-        <v>500</v>
+        <v>41</v>
       </c>
       <c r="K50" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="L50" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="M50">
-        <v>32.5</v>
+        <v>125</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="30" customHeight="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="34.5" customHeight="1">
       <c r="A51" t="s">
         <v>504</v>
       </c>
@@ -4428,143 +4432,139 @@
     </row>
     <row r="52" spans="1:14" ht="34.5" customHeight="1">
       <c r="A52" t="s">
-        <v>351</v>
+        <v>529</v>
       </c>
       <c r="B52" t="s">
         <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>528</v>
       </c>
       <c r="E52" t="s">
         <v>522</v>
       </c>
       <c r="F52" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G52">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="I52">
-        <v>45.5</v>
+        <v>60</v>
       </c>
       <c r="J52" t="s">
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="L52" t="s">
         <v>32</v>
       </c>
-      <c r="M52">
-        <v>55.5</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="34.5" customHeight="1">
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" ht="32.25" customHeight="1">
       <c r="A53" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s">
         <v>109</v>
       </c>
       <c r="C53" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="E53" t="s">
         <v>522</v>
       </c>
       <c r="F53" t="s">
+        <v>54</v>
+      </c>
+      <c r="G53">
+        <v>80</v>
+      </c>
+      <c r="H53" t="s">
+        <v>40</v>
+      </c>
+      <c r="I53">
+        <v>45.5</v>
+      </c>
+      <c r="J53" t="s">
+        <v>15</v>
+      </c>
+      <c r="K53" t="s">
+        <v>102</v>
+      </c>
+      <c r="L53" t="s">
+        <v>32</v>
+      </c>
+      <c r="M53">
+        <v>55.5</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A54" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS2811DS-B</v>
+      </c>
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
+        <v>524</v>
+      </c>
+      <c r="E54" t="s">
+        <v>520</v>
+      </c>
+      <c r="F54" t="s">
+        <v>521</v>
+      </c>
+      <c r="G54">
+        <v>75</v>
+      </c>
+      <c r="H54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54">
+        <v>130</v>
+      </c>
+      <c r="J54" t="s">
+        <v>46</v>
+      </c>
+      <c r="K54" t="s">
+        <v>47</v>
+      </c>
+      <c r="L54" t="s">
+        <v>48</v>
+      </c>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A55" t="s">
+        <v>526</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" t="s">
+        <v>525</v>
+      </c>
+      <c r="E55" t="s">
+        <v>520</v>
+      </c>
+      <c r="F55" t="s">
         <v>36</v>
       </c>
-      <c r="G53">
-        <v>120</v>
-      </c>
-      <c r="H53" t="s">
-        <v>51</v>
-      </c>
-      <c r="I53">
-        <v>120</v>
-      </c>
-      <c r="J53" t="s">
-        <v>41</v>
-      </c>
-      <c r="K53" t="s">
-        <v>42</v>
-      </c>
-      <c r="L53" t="s">
-        <v>43</v>
-      </c>
-      <c r="M53">
-        <v>125</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A54" t="s">
-        <v>531</v>
-      </c>
-      <c r="B54" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" t="s">
-        <v>530</v>
-      </c>
-      <c r="E54" t="s">
-        <v>522</v>
-      </c>
-      <c r="F54" t="s">
-        <v>36</v>
-      </c>
-      <c r="G54">
-        <v>120</v>
-      </c>
-      <c r="H54" t="s">
-        <v>51</v>
-      </c>
-      <c r="I54">
-        <v>120</v>
-      </c>
-      <c r="J54" t="s">
-        <v>41</v>
-      </c>
-      <c r="K54" t="s">
-        <v>42</v>
-      </c>
-      <c r="L54" t="s">
-        <v>43</v>
-      </c>
-      <c r="N54" s="1"/>
-    </row>
-    <row r="55" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A55" t="s">
-        <v>354</v>
-      </c>
-      <c r="B55" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" t="s">
-        <v>106</v>
-      </c>
-      <c r="E55" t="s">
-        <v>522</v>
-      </c>
-      <c r="F55" t="s">
-        <v>58</v>
-      </c>
       <c r="G55">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="I55">
         <v>130</v>
@@ -4578,218 +4578,217 @@
       <c r="L55" t="s">
         <v>48</v>
       </c>
-      <c r="M55">
-        <v>145</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="N55" s="1"/>
     </row>
     <row r="56" spans="1:14" ht="33.75" customHeight="1">
       <c r="A56" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B56" t="s">
         <v>109</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E56" t="s">
         <v>522</v>
       </c>
       <c r="F56" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G56">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H56" t="s">
-        <v>527</v>
+        <v>51</v>
       </c>
       <c r="I56">
+        <v>120</v>
+      </c>
+      <c r="J56" t="s">
         <v>41</v>
       </c>
-      <c r="J56" t="s">
-        <v>15</v>
-      </c>
       <c r="K56" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="L56" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="M56">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="33.75" customHeight="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="37.5" customHeight="1">
       <c r="A57" t="s">
-        <v>356</v>
+        <v>531</v>
       </c>
       <c r="B57" t="s">
         <v>109</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>530</v>
       </c>
       <c r="E57" t="s">
         <v>522</v>
       </c>
       <c r="F57" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G57">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H57" t="s">
-        <v>527</v>
+        <v>51</v>
       </c>
       <c r="I57">
+        <v>120</v>
+      </c>
+      <c r="J57" t="s">
         <v>41</v>
       </c>
-      <c r="J57" t="s">
-        <v>15</v>
-      </c>
       <c r="K57" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="L57" t="s">
-        <v>17</v>
-      </c>
-      <c r="M57">
-        <v>41</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="37.5" customHeight="1">
+        <v>43</v>
+      </c>
+      <c r="N57" s="1"/>
+    </row>
+    <row r="58" spans="1:14" ht="32.25" customHeight="1">
       <c r="A58" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B58" t="s">
         <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="E58" t="s">
         <v>522</v>
       </c>
       <c r="F58" t="s">
+        <v>58</v>
+      </c>
+      <c r="G58">
+        <v>110</v>
+      </c>
+      <c r="H58" t="s">
+        <v>51</v>
+      </c>
+      <c r="I58">
+        <v>130</v>
+      </c>
+      <c r="J58" t="s">
+        <v>46</v>
+      </c>
+      <c r="K58" t="s">
+        <v>47</v>
+      </c>
+      <c r="L58" t="s">
+        <v>48</v>
+      </c>
+      <c r="M58">
+        <v>145</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="42" customHeight="1">
+      <c r="A59" t="s">
+        <v>355</v>
+      </c>
+      <c r="B59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" t="s">
+        <v>522</v>
+      </c>
+      <c r="F59" t="s">
         <v>23</v>
       </c>
-      <c r="G58">
-        <v>65</v>
-      </c>
-      <c r="H58" t="s">
-        <v>20</v>
-      </c>
-      <c r="I58">
+      <c r="G59">
+        <v>60</v>
+      </c>
+      <c r="H59" t="s">
+        <v>527</v>
+      </c>
+      <c r="I59">
+        <v>41</v>
+      </c>
+      <c r="J59" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59" t="s">
+        <v>17</v>
+      </c>
+      <c r="L59" t="s">
+        <v>17</v>
+      </c>
+      <c r="M59">
+        <v>41</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="36.75" customHeight="1">
+      <c r="A60" t="s">
+        <v>356</v>
+      </c>
+      <c r="B60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" t="s">
+        <v>522</v>
+      </c>
+      <c r="F60" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60">
+        <v>60</v>
+      </c>
+      <c r="H60" t="s">
+        <v>527</v>
+      </c>
+      <c r="I60">
+        <v>41</v>
+      </c>
+      <c r="J60" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60" t="s">
+        <v>29</v>
+      </c>
+      <c r="L60" t="s">
+        <v>17</v>
+      </c>
+      <c r="M60">
+        <v>41</v>
+      </c>
+      <c r="N60" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J58" t="s">
-        <v>500</v>
-      </c>
-      <c r="K58" t="s">
-        <v>32</v>
-      </c>
-      <c r="L58" t="s">
-        <v>33</v>
-      </c>
-      <c r="M58">
-        <v>40</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A59" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS2811DS-B</v>
-      </c>
-      <c r="B59" t="s">
-        <v>109</v>
-      </c>
-      <c r="C59" t="s">
-        <v>524</v>
-      </c>
-      <c r="E59" t="s">
-        <v>520</v>
-      </c>
-      <c r="F59" t="s">
-        <v>521</v>
-      </c>
-      <c r="G59">
-        <v>75</v>
-      </c>
-      <c r="H59" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59">
-        <v>130</v>
-      </c>
-      <c r="J59" t="s">
-        <v>46</v>
-      </c>
-      <c r="K59" t="s">
-        <v>47</v>
-      </c>
-      <c r="L59" t="s">
-        <v>48</v>
-      </c>
-      <c r="N59" s="1"/>
-    </row>
-    <row r="60" spans="1:14" ht="42" customHeight="1">
-      <c r="A60" t="s">
-        <v>526</v>
-      </c>
-      <c r="B60" t="s">
-        <v>109</v>
-      </c>
-      <c r="C60" t="s">
-        <v>525</v>
-      </c>
-      <c r="E60" t="s">
-        <v>520</v>
-      </c>
-      <c r="F60" t="s">
-        <v>36</v>
-      </c>
-      <c r="G60">
-        <v>75</v>
-      </c>
-      <c r="H60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I60">
-        <v>130</v>
-      </c>
-      <c r="J60" t="s">
-        <v>46</v>
-      </c>
-      <c r="K60" t="s">
-        <v>47</v>
-      </c>
-      <c r="L60" t="s">
-        <v>48</v>
-      </c>
-      <c r="N60" s="1"/>
-    </row>
-    <row r="61" spans="1:14" ht="36.75" customHeight="1">
+    </row>
+    <row r="61" spans="1:14" ht="29.25" customHeight="1">
       <c r="A61" t="s">
-        <v>529</v>
+        <v>357</v>
       </c>
       <c r="B61" t="s">
         <v>109</v>
       </c>
       <c r="C61" t="s">
-        <v>528</v>
+        <v>31</v>
       </c>
       <c r="E61" t="s">
         <v>522</v>
@@ -4798,58 +4797,48 @@
         <v>23</v>
       </c>
       <c r="G61">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H61" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I61">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J61" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="K61" t="s">
         <v>32</v>
       </c>
       <c r="L61" t="s">
-        <v>32</v>
-      </c>
-      <c r="N61" s="1"/>
-    </row>
-    <row r="62" spans="1:14" ht="29.25" customHeight="1">
+        <v>33</v>
+      </c>
+      <c r="M61">
+        <v>40</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="44.25" customHeight="1">
       <c r="A62" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="B62" t="s">
         <v>109</v>
       </c>
-      <c r="C62" t="s">
-        <v>532</v>
-      </c>
       <c r="E62" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F62" t="s">
-        <v>23</v>
-      </c>
-      <c r="G62">
-        <v>75</v>
-      </c>
-      <c r="H62" t="s">
-        <v>14</v>
+        <v>541</v>
       </c>
       <c r="I62">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="J62" t="s">
-        <v>119</v>
-      </c>
-      <c r="K62" t="s">
-        <v>534</v>
-      </c>
-      <c r="L62" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="N62" s="1"/>
     </row>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B68AEE-FC97-4FDE-A34A-E188CB27FF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA240F0-7A89-4BDD-94F5-3564E7358918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -1946,9 +1946,6 @@
     <t>TS1871-W</t>
   </si>
   <si>
-    <t>images/1571-W</t>
-  </si>
-  <si>
     <t>images/1871-W</t>
   </si>
   <si>
@@ -1959,6 +1956,9 @@
   </si>
   <si>
     <t>images/new</t>
+  </si>
+  <si>
+    <t>images/TS1571-W</t>
   </si>
 </sst>
 </file>
@@ -2939,7 +2939,7 @@
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E14" t="s">
         <v>522</v>
@@ -3532,7 +3532,7 @@
     </row>
     <row r="29" spans="1:14" ht="21.75" customHeight="1">
       <c r="A29" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C29" t="s">
         <v>535</v>
@@ -3911,7 +3911,7 @@
     </row>
     <row r="39" spans="1:14" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
@@ -4823,7 +4823,7 @@
     </row>
     <row r="62" spans="1:14" ht="44.25" customHeight="1">
       <c r="A62" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B62" t="s">
         <v>109</v>
@@ -4832,7 +4832,7 @@
         <v>520</v>
       </c>
       <c r="F62" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I62">
         <v>120</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA240F0-7A89-4BDD-94F5-3564E7358918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D356AD-905A-4E0C-B401-87C9A5BF42F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -1946,19 +1946,19 @@
     <t>TS1871-W</t>
   </si>
   <si>
-    <t>images/1871-W</t>
-  </si>
-  <si>
     <t>TS1137-W</t>
   </si>
   <si>
     <t>платформенное решение</t>
   </si>
   <si>
-    <t>images/new</t>
-  </si>
-  <si>
     <t>images/TS1571-W</t>
+  </si>
+  <si>
+    <t>images/TS1871-W</t>
+  </si>
+  <si>
+    <t>images/newTS</t>
   </si>
 </sst>
 </file>
@@ -2939,7 +2939,7 @@
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E14" t="s">
         <v>522</v>
@@ -3532,7 +3532,7 @@
     </row>
     <row r="29" spans="1:14" ht="21.75" customHeight="1">
       <c r="A29" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C29" t="s">
         <v>535</v>
@@ -3911,7 +3911,7 @@
     </row>
     <row r="39" spans="1:14" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
@@ -4823,7 +4823,7 @@
     </row>
     <row r="62" spans="1:14" ht="44.25" customHeight="1">
       <c r="A62" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B62" t="s">
         <v>109</v>
@@ -4832,7 +4832,7 @@
         <v>520</v>
       </c>
       <c r="F62" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I62">
         <v>120</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D356AD-905A-4E0C-B401-87C9A5BF42F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF755F5-EBA4-4227-9E86-705678AF7F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -1883,9 +1883,6 @@
     <t>TS1171-B</t>
   </si>
   <si>
-    <t>TS1552E-W</t>
-  </si>
-  <si>
     <t>TS1991-W</t>
   </si>
   <si>
@@ -1959,6 +1956,9 @@
   </si>
   <si>
     <t>images/newTS</t>
+  </si>
+  <si>
+    <t>TS1552E-WO</t>
   </si>
 </sst>
 </file>
@@ -2451,7 +2451,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -2492,7 +2492,7 @@
         <v>511</v>
       </c>
       <c r="E2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F2" t="s">
         <v>23</v>
@@ -2519,16 +2519,16 @@
     </row>
     <row r="3" spans="1:14" ht="21.75" customHeight="1">
       <c r="A3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F3" t="s">
         <v>23</v>
@@ -2546,7 +2546,7 @@
         <v>119</v>
       </c>
       <c r="K3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L3" t="s">
         <v>32</v>
@@ -2564,10 +2564,10 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
+        <v>519</v>
+      </c>
+      <c r="F4" t="s">
         <v>520</v>
-      </c>
-      <c r="F4" t="s">
-        <v>521</v>
       </c>
       <c r="G4">
         <v>70</v>
@@ -2602,16 +2602,16 @@
         <v>53</v>
       </c>
       <c r="E5" t="s">
+        <v>519</v>
+      </c>
+      <c r="F5" t="s">
         <v>520</v>
-      </c>
-      <c r="F5" t="s">
-        <v>521</v>
       </c>
       <c r="G5">
         <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I5">
         <v>200</v>
@@ -2640,7 +2640,7 @@
         <v>496</v>
       </c>
       <c r="E6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F6" t="s">
         <v>36</v>
@@ -2676,7 +2676,7 @@
         <v>495</v>
       </c>
       <c r="E7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F7" t="s">
         <v>36</v>
@@ -2712,7 +2712,7 @@
         <v>494</v>
       </c>
       <c r="E8" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F8" t="s">
         <v>36</v>
@@ -2748,7 +2748,7 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
@@ -2757,7 +2757,7 @@
         <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I9">
         <v>30</v>
@@ -2786,7 +2786,7 @@
         <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -2824,7 +2824,7 @@
         <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -2862,7 +2862,7 @@
         <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -2871,7 +2871,7 @@
         <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I12">
         <v>35</v>
@@ -2900,7 +2900,7 @@
         <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F13" t="s">
         <v>58</v>
@@ -2909,7 +2909,7 @@
         <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I13">
         <v>40</v>
@@ -2939,10 +2939,10 @@
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F14" t="s">
         <v>58</v>
@@ -2951,7 +2951,7 @@
         <v>55</v>
       </c>
       <c r="H14" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I14">
         <v>40</v>
@@ -2982,7 +2982,7 @@
         <v>516</v>
       </c>
       <c r="E15" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F15" t="s">
         <v>58</v>
@@ -2991,7 +2991,7 @@
         <v>60</v>
       </c>
       <c r="H15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I15">
         <v>40</v>
@@ -3021,7 +3021,7 @@
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F16" t="s">
         <v>23</v>
@@ -3059,7 +3059,7 @@
         <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F17" t="s">
         <v>23</v>
@@ -3097,7 +3097,7 @@
         <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F18" t="s">
         <v>488</v>
@@ -3135,7 +3135,7 @@
         <v>65</v>
       </c>
       <c r="E19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F19" t="s">
         <v>58</v>
@@ -3176,7 +3176,7 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F20" t="s">
         <v>58</v>
@@ -3217,7 +3217,7 @@
         <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F21" t="s">
         <v>488</v>
@@ -3258,7 +3258,7 @@
         <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F22" t="s">
         <v>58</v>
@@ -3299,7 +3299,7 @@
         <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F23" t="s">
         <v>58</v>
@@ -3340,7 +3340,7 @@
         <v>35</v>
       </c>
       <c r="E24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F24" t="s">
         <v>36</v>
@@ -3373,16 +3373,16 @@
     <row r="25" spans="1:14" ht="21.75" customHeight="1">
       <c r="A25" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1552E-W</v>
+        <v>images/TS1552E-WO</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>517</v>
+        <v>542</v>
       </c>
       <c r="E25" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F25" t="s">
         <v>36</v>
@@ -3418,7 +3418,7 @@
         <v>78</v>
       </c>
       <c r="E26" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F26" t="s">
         <v>58</v>
@@ -3459,7 +3459,7 @@
         <v>502</v>
       </c>
       <c r="E27" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F27" t="s">
         <v>58</v>
@@ -3500,7 +3500,7 @@
         <v>501</v>
       </c>
       <c r="E28" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F28" t="s">
         <v>58</v>
@@ -3532,13 +3532,13 @@
     </row>
     <row r="29" spans="1:14" ht="21.75" customHeight="1">
       <c r="A29" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C29" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E29" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F29" t="s">
         <v>58</v>
@@ -3575,10 +3575,10 @@
         <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E30" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F30" t="s">
         <v>23</v>
@@ -3614,7 +3614,7 @@
         <v>490</v>
       </c>
       <c r="E31" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F31" t="s">
         <v>23</v>
@@ -3650,7 +3650,7 @@
         <v>489</v>
       </c>
       <c r="E32" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F32" t="s">
         <v>23</v>
@@ -3687,7 +3687,7 @@
         <v>513</v>
       </c>
       <c r="E33" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F33" t="s">
         <v>23</v>
@@ -3724,7 +3724,7 @@
         <v>514</v>
       </c>
       <c r="E34" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F34" t="s">
         <v>23</v>
@@ -3761,7 +3761,7 @@
         <v>515</v>
       </c>
       <c r="E35" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F35" t="s">
         <v>23</v>
@@ -3797,7 +3797,7 @@
         <v>80</v>
       </c>
       <c r="E36" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F36" t="s">
         <v>58</v>
@@ -3838,7 +3838,7 @@
         <v>510</v>
       </c>
       <c r="E37" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F37" t="s">
         <v>58</v>
@@ -3879,7 +3879,7 @@
         <v>509</v>
       </c>
       <c r="E38" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F38" t="s">
         <v>58</v>
@@ -3911,16 +3911,16 @@
     </row>
     <row r="39" spans="1:14" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E39" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F39" t="s">
         <v>58</v>
@@ -3959,7 +3959,7 @@
         <v>83</v>
       </c>
       <c r="E40" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F40" t="s">
         <v>58</v>
@@ -4000,10 +4000,10 @@
         <v>86</v>
       </c>
       <c r="E41" t="s">
+        <v>519</v>
+      </c>
+      <c r="F41" t="s">
         <v>520</v>
-      </c>
-      <c r="F41" t="s">
-        <v>521</v>
       </c>
       <c r="G41">
         <v>65</v>
@@ -4041,10 +4041,10 @@
         <v>88</v>
       </c>
       <c r="E42" t="s">
+        <v>519</v>
+      </c>
+      <c r="F42" t="s">
         <v>520</v>
-      </c>
-      <c r="F42" t="s">
-        <v>521</v>
       </c>
       <c r="G42">
         <v>65</v>
@@ -4082,7 +4082,7 @@
         <v>39</v>
       </c>
       <c r="E43" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F43" t="s">
         <v>36</v>
@@ -4123,7 +4123,7 @@
         <v>90</v>
       </c>
       <c r="E44" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F44" t="s">
         <v>58</v>
@@ -4164,7 +4164,7 @@
         <v>92</v>
       </c>
       <c r="E45" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F45" t="s">
         <v>58</v>
@@ -4205,7 +4205,7 @@
         <v>45</v>
       </c>
       <c r="E46" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F46" t="s">
         <v>36</v>
@@ -4244,10 +4244,10 @@
         <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E47" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F47" t="s">
         <v>36</v>
@@ -4284,10 +4284,10 @@
         <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E48" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F48" t="s">
         <v>58</v>
@@ -4323,7 +4323,7 @@
         <v>94</v>
       </c>
       <c r="E49" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F49" t="s">
         <v>58</v>
@@ -4364,7 +4364,7 @@
         <v>96</v>
       </c>
       <c r="E50" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F50" t="s">
         <v>58</v>
@@ -4405,7 +4405,7 @@
         <v>503</v>
       </c>
       <c r="E51" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F51" t="s">
         <v>54</v>
@@ -4432,16 +4432,16 @@
     </row>
     <row r="52" spans="1:14" ht="34.5" customHeight="1">
       <c r="A52" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B52" t="s">
         <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E52" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F52" t="s">
         <v>23</v>
@@ -4477,7 +4477,7 @@
         <v>101</v>
       </c>
       <c r="E53" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F53" t="s">
         <v>54</v>
@@ -4516,13 +4516,13 @@
         <v>109</v>
       </c>
       <c r="C54" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E54" t="s">
+        <v>519</v>
+      </c>
+      <c r="F54" t="s">
         <v>520</v>
-      </c>
-      <c r="F54" t="s">
-        <v>521</v>
       </c>
       <c r="G54">
         <v>75</v>
@@ -4546,16 +4546,16 @@
     </row>
     <row r="55" spans="1:14" ht="33.75" customHeight="1">
       <c r="A55" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B55" t="s">
         <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E55" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F55" t="s">
         <v>36</v>
@@ -4591,7 +4591,7 @@
         <v>50</v>
       </c>
       <c r="E56" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F56" t="s">
         <v>36</v>
@@ -4623,16 +4623,16 @@
     </row>
     <row r="57" spans="1:14" ht="37.5" customHeight="1">
       <c r="A57" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B57" t="s">
         <v>109</v>
       </c>
       <c r="C57" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E57" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F57" t="s">
         <v>36</v>
@@ -4668,7 +4668,7 @@
         <v>106</v>
       </c>
       <c r="E58" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F58" t="s">
         <v>58</v>
@@ -4709,7 +4709,7 @@
         <v>26</v>
       </c>
       <c r="E59" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F59" t="s">
         <v>23</v>
@@ -4718,7 +4718,7 @@
         <v>60</v>
       </c>
       <c r="H59" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I59">
         <v>41</v>
@@ -4750,7 +4750,7 @@
         <v>28</v>
       </c>
       <c r="E60" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F60" t="s">
         <v>23</v>
@@ -4759,7 +4759,7 @@
         <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I60">
         <v>41</v>
@@ -4791,7 +4791,7 @@
         <v>31</v>
       </c>
       <c r="E61" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F61" t="s">
         <v>23</v>
@@ -4823,16 +4823,16 @@
     </row>
     <row r="62" spans="1:14" ht="44.25" customHeight="1">
       <c r="A62" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B62" t="s">
         <v>109</v>
       </c>
       <c r="E62" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F62" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I62">
         <v>120</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF755F5-EBA4-4227-9E86-705678AF7F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56557C4-EE25-4319-AD51-06AA4C4D9C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="4830" yWindow="1005" windowWidth="21600" windowHeight="14595" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="544">
   <si>
     <t>image_url</t>
   </si>
@@ -1959,6 +1959,9 @@
   </si>
   <si>
     <t>TS1552E-WO</t>
+  </si>
+  <si>
+    <t>images/TS1991-W</t>
   </si>
 </sst>
 </file>
@@ -4236,9 +4239,8 @@
       </c>
     </row>
     <row r="47" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A47" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1991E-W</v>
+      <c r="A47" t="s">
+        <v>543</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56557C4-EE25-4319-AD51-06AA4C4D9C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72817AE-FBC8-4E91-85F5-F7633B9E2A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4830" yWindow="1005" windowWidth="21600" windowHeight="14595" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="547">
   <si>
     <t>image_url</t>
   </si>
@@ -1962,6 +1962,15 @@
   </si>
   <si>
     <t>images/TS1991-W</t>
+  </si>
+  <si>
+    <t>images/TS1881-B_V2</t>
+  </si>
+  <si>
+    <t>90 kg</t>
+  </si>
+  <si>
+    <t>50"-90"</t>
   </si>
 </sst>
 </file>
@@ -2066,8 +2075,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N62" totalsRowShown="0">
   <autoFilter ref="A1:N62" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N61">
-    <sortCondition ref="C1:C61"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N62">
+    <sortCondition ref="L1:L62"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
@@ -2486,287 +2495,307 @@
     </row>
     <row r="2" spans="1:14" ht="21.75" customHeight="1">
       <c r="A2" t="s">
-        <v>512</v>
+        <v>276</v>
       </c>
       <c r="B2" t="s">
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>511</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>521</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>526</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="3" spans="1:14" ht="21.75" customHeight="1">
       <c r="A3" t="s">
-        <v>532</v>
+        <v>279</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>531</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
         <v>521</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>526</v>
       </c>
       <c r="I3">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="J3" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>533</v>
+        <v>17</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="4" spans="1:14" ht="21.75" customHeight="1">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>325</v>
       </c>
       <c r="B4" t="s">
         <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F4" t="s">
-        <v>520</v>
-      </c>
-      <c r="G4">
-        <v>70</v>
+        <v>58</v>
+      </c>
+      <c r="G4" s="4">
+        <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>526</v>
       </c>
       <c r="I4">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" t="s">
         <v>17</v>
       </c>
+      <c r="M4">
+        <v>45</v>
+      </c>
       <c r="N4" s="1" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A5" t="s">
-        <v>121</v>
+      <c r="A5" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1137-W</v>
       </c>
       <c r="B5" t="s">
         <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>537</v>
       </c>
       <c r="E5" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F5" t="s">
-        <v>520</v>
-      </c>
-      <c r="G5">
+        <v>58</v>
+      </c>
+      <c r="G5" s="4">
         <v>55</v>
       </c>
       <c r="H5" t="s">
         <v>526</v>
       </c>
       <c r="I5">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>56</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="M5">
+        <v>45</v>
+      </c>
+      <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>499</v>
+      <c r="A6" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1171-B</v>
       </c>
       <c r="B6" t="s">
         <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="E6" t="s">
         <v>519</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H6" t="s">
+        <v>526</v>
+      </c>
+      <c r="I6">
         <v>40</v>
       </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
       <c r="J6" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L6" t="s">
-        <v>48</v>
+        <v>17</v>
+      </c>
+      <c r="M6">
+        <v>45</v>
       </c>
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>498</v>
+      <c r="A7" t="s">
+        <v>355</v>
       </c>
       <c r="B7" t="s">
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>495</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>526</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="J7" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N7" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="M7">
+        <v>41</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>497</v>
+      <c r="A8" t="s">
+        <v>327</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>494</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="J8" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L8" t="s">
-        <v>48</v>
-      </c>
-      <c r="N8" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="9" spans="1:14" ht="21.75" customHeight="1">
       <c r="A9" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
         <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
         <v>521</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G9">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H9" t="s">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="I9">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J9" t="s">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
@@ -2775,56 +2804,56 @@
         <v>17</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="21.75" customHeight="1">
       <c r="A10" t="s">
-        <v>277</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
         <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>520</v>
       </c>
       <c r="G10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I10">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>545</v>
       </c>
       <c r="K10" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="L10" t="s">
         <v>17</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>114</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="21.75" customHeight="1">
       <c r="A11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B11" t="s">
         <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
         <v>521</v>
@@ -2833,128 +2862,130 @@
         <v>13</v>
       </c>
       <c r="G11">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I11">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="L11" t="s">
         <v>17</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="21.75" customHeight="1">
       <c r="A12" t="s">
-        <v>279</v>
+        <v>337</v>
       </c>
       <c r="B12" t="s">
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
         <v>521</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G12">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s">
-        <v>526</v>
+        <v>14</v>
       </c>
       <c r="I12">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K12" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="L12" t="s">
         <v>17</v>
       </c>
+      <c r="M12">
+        <v>70</v>
+      </c>
       <c r="N12" s="1" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="21.75" customHeight="1">
       <c r="A13" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
         <v>521</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="4">
-        <v>55</v>
+        <v>23</v>
+      </c>
+      <c r="G13">
+        <v>60</v>
       </c>
       <c r="H13" t="s">
         <v>526</v>
       </c>
       <c r="I13">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J13" t="s">
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L13" t="s">
         <v>17</v>
       </c>
       <c r="M13">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A14" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1137-W</v>
+      <c r="A14" t="s">
+        <v>278</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>537</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
         <v>521</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="4">
-        <v>55</v>
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>75</v>
       </c>
       <c r="H14" t="s">
-        <v>526</v>
+        <v>14</v>
       </c>
       <c r="I14">
         <v>40</v>
@@ -2963,65 +2994,61 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L14" t="s">
         <v>17</v>
       </c>
-      <c r="M14">
-        <v>45</v>
-      </c>
-      <c r="N14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A15" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1171-B</v>
+      <c r="A15" t="s">
+        <v>528</v>
       </c>
       <c r="B15" t="s">
         <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="E15" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G15">
+        <v>75</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15">
         <v>60</v>
-      </c>
-      <c r="H15" t="s">
-        <v>526</v>
-      </c>
-      <c r="I15">
-        <v>40</v>
       </c>
       <c r="J15" t="s">
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L15" t="s">
-        <v>17</v>
-      </c>
-      <c r="M15">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A16" t="s">
-        <v>327</v>
+      <c r="A16" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1580-B</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>522</v>
       </c>
       <c r="E16" t="s">
         <v>521</v>
@@ -3030,36 +3057,34 @@
         <v>23</v>
       </c>
       <c r="G16">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I16">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="J16" t="s">
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>17</v>
+        <v>491</v>
       </c>
       <c r="L16" t="s">
-        <v>17</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A17" t="s">
-        <v>328</v>
+      <c r="A17" s="2" t="s">
+        <v>492</v>
       </c>
       <c r="B17" t="s">
         <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>490</v>
       </c>
       <c r="E17" t="s">
         <v>521</v>
@@ -3068,215 +3093,203 @@
         <v>23</v>
       </c>
       <c r="G17">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I17">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="J17" t="s">
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>17</v>
+        <v>491</v>
       </c>
       <c r="L17" t="s">
-        <v>17</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A18" t="s">
-        <v>329</v>
+      <c r="A18" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="B18" t="s">
         <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>489</v>
       </c>
       <c r="E18" t="s">
         <v>521</v>
       </c>
       <c r="F18" t="s">
-        <v>488</v>
+        <v>23</v>
       </c>
       <c r="G18">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s">
         <v>14</v>
       </c>
       <c r="I18">
-        <v>40.5</v>
+        <v>60</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>63</v>
+        <v>491</v>
       </c>
       <c r="L18" t="s">
-        <v>43</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" ht="21.75" customHeight="1">
       <c r="A19" t="s">
-        <v>330</v>
+        <v>532</v>
       </c>
       <c r="B19" t="s">
         <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>531</v>
       </c>
       <c r="E19" t="s">
         <v>521</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G19">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19">
         <v>65</v>
       </c>
-      <c r="H19" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19">
-        <v>45</v>
-      </c>
       <c r="J19" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K19" t="s">
+        <v>533</v>
+      </c>
+      <c r="L19" t="s">
         <v>32</v>
       </c>
-      <c r="L19" t="s">
-        <v>33</v>
-      </c>
-      <c r="M19">
-        <v>50</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1">
       <c r="A20" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
         <v>521</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G20">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>546</v>
       </c>
       <c r="I20">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="J20" t="s">
         <v>15</v>
       </c>
       <c r="K20" t="s">
+        <v>102</v>
+      </c>
+      <c r="L20" t="s">
         <v>32</v>
       </c>
-      <c r="L20" t="s">
-        <v>33</v>
-      </c>
       <c r="M20">
-        <v>50</v>
+        <v>55.5</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1">
       <c r="A21" t="s">
-        <v>332</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s">
         <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F21" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="G21">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="H21" t="s">
-        <v>40</v>
+        <v>526</v>
       </c>
       <c r="I21">
-        <v>65.5</v>
+        <v>200</v>
       </c>
       <c r="J21" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="K21" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="L21" t="s">
-        <v>48</v>
-      </c>
-      <c r="M21">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1">
       <c r="A22" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="B22" t="s">
         <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
         <v>521</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I22">
-        <v>45.5</v>
+        <v>30</v>
       </c>
       <c r="J22" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="K22" t="s">
         <v>32</v>
@@ -3285,36 +3298,36 @@
         <v>33</v>
       </c>
       <c r="M22">
-        <v>55.5</v>
+        <v>40</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1">
       <c r="A23" t="s">
-        <v>334</v>
+        <v>512</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>511</v>
       </c>
       <c r="E23" t="s">
         <v>521</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G23">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I23">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
@@ -3325,82 +3338,76 @@
       <c r="L23" t="s">
         <v>33</v>
       </c>
-      <c r="M23">
-        <v>50</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1">
       <c r="A24" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B24" t="s">
         <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="E24" t="s">
         <v>521</v>
       </c>
       <c r="F24" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G24">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I24">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="J24" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L24" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="M24">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A25" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1552E-WO</v>
+      <c r="A25" t="s">
+        <v>331</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>542</v>
+        <v>67</v>
       </c>
       <c r="E25" t="s">
         <v>521</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G25">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I25">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="J25" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K25" t="s">
         <v>32</v>
@@ -3408,17 +3415,22 @@
       <c r="L25" t="s">
         <v>33</v>
       </c>
-      <c r="N25" s="1"/>
+      <c r="M25">
+        <v>50</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="26" spans="1:14" ht="21.75" customHeight="1">
       <c r="A26" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E26" t="s">
         <v>521</v>
@@ -3427,13 +3439,13 @@
         <v>58</v>
       </c>
       <c r="G26">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H26" t="s">
         <v>14</v>
       </c>
       <c r="I26">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
@@ -3445,27 +3457,27 @@
         <v>33</v>
       </c>
       <c r="M26">
-        <v>60</v>
+        <v>55.5</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1">
       <c r="A27" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B27" t="s">
         <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E27" t="s">
         <v>521</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G27">
         <v>75</v>
@@ -3474,7 +3486,7 @@
         <v>14</v>
       </c>
       <c r="I27">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J27" t="s">
         <v>15</v>
@@ -3485,22 +3497,17 @@
       <c r="L27" t="s">
         <v>33</v>
       </c>
-      <c r="M27">
-        <v>60</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" ht="21.75" customHeight="1">
       <c r="A28" t="s">
-        <v>505</v>
+        <v>334</v>
       </c>
       <c r="B28" t="s">
         <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>501</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s">
         <v>521</v>
@@ -3515,7 +3522,7 @@
         <v>14</v>
       </c>
       <c r="I28">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
@@ -3527,18 +3534,21 @@
         <v>33</v>
       </c>
       <c r="M28">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="21.75" customHeight="1">
       <c r="A29" t="s">
-        <v>539</v>
+        <v>338</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s">
         <v>521</v>
@@ -3567,24 +3577,25 @@
       <c r="M29">
         <v>60</v>
       </c>
-      <c r="N29" s="1"/>
+      <c r="N29" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="30" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A30" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1580-B</v>
+      <c r="A30" t="s">
+        <v>506</v>
       </c>
       <c r="B30" t="s">
         <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="E30" t="s">
         <v>521</v>
       </c>
       <c r="F30" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G30">
         <v>75</v>
@@ -3593,34 +3604,39 @@
         <v>14</v>
       </c>
       <c r="I30">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>491</v>
+        <v>32</v>
       </c>
       <c r="L30" t="s">
-        <v>32</v>
-      </c>
-      <c r="N30" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="M30">
+        <v>60</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="31" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>492</v>
+      <c r="A31" t="s">
+        <v>505</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E31" t="s">
         <v>521</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G31">
         <v>75</v>
@@ -3629,34 +3645,36 @@
         <v>14</v>
       </c>
       <c r="I31">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>491</v>
+        <v>32</v>
       </c>
       <c r="L31" t="s">
-        <v>32</v>
-      </c>
-      <c r="N31" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="M31">
+        <v>60</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="32" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A32" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B32" t="s">
-        <v>109</v>
+      <c r="A32" t="s">
+        <v>539</v>
       </c>
       <c r="C32" t="s">
-        <v>489</v>
+        <v>534</v>
       </c>
       <c r="E32" t="s">
         <v>521</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G32">
         <v>75</v>
@@ -3665,139 +3683,150 @@
         <v>14</v>
       </c>
       <c r="I32">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>491</v>
+        <v>32</v>
       </c>
       <c r="L32" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M32">
+        <v>60</v>
       </c>
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" ht="21.75" customHeight="1">
       <c r="A33" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-B</v>
+        <v>images/TS1552E-WO</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>513</v>
+        <v>542</v>
       </c>
       <c r="E33" t="s">
         <v>521</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G33">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H33" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="J33" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="K33" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="L33" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A34" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-C</v>
+      <c r="A34" t="s">
+        <v>342</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>514</v>
+        <v>86</v>
       </c>
       <c r="E34" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F34" t="s">
-        <v>23</v>
+        <v>520</v>
       </c>
       <c r="G34">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H34" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>90.9</v>
       </c>
       <c r="J34" t="s">
-        <v>41</v>
+        <v>545</v>
       </c>
       <c r="K34" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L34" t="s">
         <v>43</v>
       </c>
-      <c r="N34" s="1"/>
+      <c r="M34">
+        <v>105.9</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="35" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A35" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-G</v>
+      <c r="A35" t="s">
+        <v>343</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>515</v>
+        <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>520</v>
       </c>
       <c r="G35">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H35" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I35">
-        <v>100</v>
+        <v>90.9</v>
       </c>
       <c r="J35" t="s">
-        <v>41</v>
+        <v>545</v>
       </c>
       <c r="K35" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L35" t="s">
         <v>43</v>
       </c>
-      <c r="N35" s="1"/>
+      <c r="M35">
+        <v>105.9</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="36" spans="1:14" ht="21.75" customHeight="1">
       <c r="A36" t="s">
-        <v>339</v>
+        <v>544</v>
       </c>
       <c r="B36" t="s">
         <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E36" t="s">
         <v>521</v>
@@ -3806,160 +3835,157 @@
         <v>58</v>
       </c>
       <c r="G36">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s">
-        <v>40</v>
+        <v>546</v>
       </c>
       <c r="I36">
-        <v>75</v>
+        <v>90.9</v>
       </c>
       <c r="J36" t="s">
-        <v>41</v>
+        <v>545</v>
       </c>
       <c r="K36" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L36" t="s">
         <v>43</v>
       </c>
       <c r="M36">
-        <v>90</v>
+        <v>105.9</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="21.75" customHeight="1">
       <c r="A37" t="s">
-        <v>508</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s">
         <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>510</v>
+        <v>39</v>
       </c>
       <c r="E37" t="s">
         <v>521</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G37">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s">
-        <v>40</v>
+        <v>546</v>
       </c>
       <c r="I37">
-        <v>75</v>
+        <v>90.9</v>
       </c>
       <c r="J37" t="s">
-        <v>41</v>
+        <v>545</v>
       </c>
       <c r="K37" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L37" t="s">
         <v>43</v>
       </c>
       <c r="M37">
-        <v>90</v>
+        <v>105.9</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="21.75" customHeight="1">
       <c r="A38" t="s">
-        <v>507</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s">
         <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>509</v>
+        <v>50</v>
       </c>
       <c r="E38" t="s">
         <v>521</v>
       </c>
       <c r="F38" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G38">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H38" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I38">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="J38" t="s">
         <v>41</v>
       </c>
       <c r="K38" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L38" t="s">
         <v>43</v>
       </c>
       <c r="M38">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E39" t="s">
         <v>521</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G39">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H39" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I39">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="J39" t="s">
         <v>41</v>
       </c>
       <c r="K39" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L39" t="s">
         <v>43</v>
       </c>
-      <c r="M39">
-        <v>90</v>
-      </c>
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="1:14" ht="21.75" customHeight="1">
       <c r="A40" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B40" t="s">
         <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E40" t="s">
         <v>521</v>
@@ -3968,152 +3994,150 @@
         <v>58</v>
       </c>
       <c r="G40">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s">
-        <v>40</v>
+        <v>546</v>
       </c>
       <c r="I40">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="J40" t="s">
-        <v>41</v>
+        <v>545</v>
       </c>
       <c r="K40" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L40" t="s">
         <v>43</v>
       </c>
       <c r="M40">
-        <v>105.9</v>
+        <v>90</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="21.75" customHeight="1">
       <c r="A41" t="s">
-        <v>342</v>
+        <v>508</v>
       </c>
       <c r="B41" t="s">
         <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>510</v>
       </c>
       <c r="E41" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F41" t="s">
-        <v>520</v>
+        <v>58</v>
       </c>
       <c r="G41">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s">
-        <v>20</v>
+        <v>546</v>
       </c>
       <c r="I41">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="J41" t="s">
-        <v>41</v>
+        <v>545</v>
       </c>
       <c r="K41" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L41" t="s">
         <v>43</v>
       </c>
       <c r="M41">
-        <v>105.9</v>
+        <v>90</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="21.75" customHeight="1">
       <c r="A42" t="s">
-        <v>343</v>
+        <v>507</v>
       </c>
       <c r="B42" t="s">
         <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>509</v>
       </c>
       <c r="E42" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F42" t="s">
-        <v>520</v>
+        <v>58</v>
       </c>
       <c r="G42">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>546</v>
       </c>
       <c r="I42">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="J42" t="s">
-        <v>41</v>
+        <v>545</v>
       </c>
       <c r="K42" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L42" t="s">
         <v>43</v>
       </c>
       <c r="M42">
-        <v>105.9</v>
+        <v>90</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="26.25" customHeight="1">
       <c r="A43" t="s">
-        <v>344</v>
+        <v>540</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>536</v>
       </c>
       <c r="E43" t="s">
         <v>521</v>
       </c>
       <c r="F43" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G43">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s">
-        <v>40</v>
+        <v>546</v>
       </c>
       <c r="I43">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="J43" t="s">
-        <v>41</v>
+        <v>545</v>
       </c>
       <c r="K43" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L43" t="s">
         <v>43</v>
       </c>
       <c r="M43">
-        <v>105.9</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>44</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="N43" s="1"/>
     </row>
     <row r="44" spans="1:14" ht="26.25" customHeight="1">
       <c r="A44" t="s">
@@ -4135,13 +4159,13 @@
         <v>90</v>
       </c>
       <c r="H44" t="s">
-        <v>40</v>
+        <v>546</v>
       </c>
       <c r="I44">
         <v>90</v>
       </c>
       <c r="J44" t="s">
-        <v>41</v>
+        <v>545</v>
       </c>
       <c r="K44" t="s">
         <v>81</v>
@@ -4157,493 +4181,478 @@
       </c>
     </row>
     <row r="45" spans="1:14" ht="27.75" customHeight="1">
-      <c r="A45" t="s">
-        <v>346</v>
+      <c r="A45" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-B</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>513</v>
       </c>
       <c r="E45" t="s">
         <v>521</v>
       </c>
       <c r="F45" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G45">
+        <v>90</v>
+      </c>
+      <c r="H45" t="s">
+        <v>546</v>
+      </c>
+      <c r="I45">
         <v>100</v>
       </c>
-      <c r="H45" t="s">
-        <v>40</v>
-      </c>
-      <c r="I45">
-        <v>120</v>
-      </c>
       <c r="J45" t="s">
-        <v>41</v>
+        <v>545</v>
       </c>
       <c r="K45" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L45" t="s">
-        <v>48</v>
-      </c>
-      <c r="M45">
-        <v>130</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>93</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="N45" s="1"/>
     </row>
     <row r="46" spans="1:14" ht="27.75" customHeight="1">
-      <c r="A46" t="s">
-        <v>347</v>
+      <c r="A46" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-C</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>514</v>
       </c>
       <c r="E46" t="s">
         <v>521</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G46">
+        <v>90</v>
+      </c>
+      <c r="H46" t="s">
+        <v>546</v>
+      </c>
+      <c r="I46">
         <v>100</v>
       </c>
-      <c r="H46" t="s">
-        <v>40</v>
-      </c>
-      <c r="I46">
-        <v>120</v>
-      </c>
       <c r="J46" t="s">
-        <v>41</v>
+        <v>545</v>
       </c>
       <c r="K46" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L46" t="s">
-        <v>48</v>
-      </c>
-      <c r="M46">
-        <v>130</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>49</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="N46" s="1"/>
     </row>
     <row r="47" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A47" t="s">
-        <v>543</v>
+      <c r="A47" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-G</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="E47" t="s">
         <v>521</v>
       </c>
       <c r="F47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47">
+        <v>90</v>
+      </c>
+      <c r="H47" t="s">
+        <v>546</v>
+      </c>
+      <c r="I47">
+        <v>100</v>
+      </c>
+      <c r="J47" t="s">
+        <v>545</v>
+      </c>
+      <c r="K47" t="s">
+        <v>81</v>
+      </c>
+      <c r="L47" t="s">
+        <v>43</v>
+      </c>
+      <c r="N47" s="1"/>
+    </row>
+    <row r="48" spans="1:14" ht="30" customHeight="1">
+      <c r="A48" t="s">
+        <v>329</v>
+      </c>
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" t="s">
+        <v>521</v>
+      </c>
+      <c r="F48" t="s">
+        <v>488</v>
+      </c>
+      <c r="G48">
+        <v>70</v>
+      </c>
+      <c r="H48" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48">
+        <v>40.5</v>
+      </c>
+      <c r="J48" t="s">
+        <v>15</v>
+      </c>
+      <c r="K48" t="s">
+        <v>63</v>
+      </c>
+      <c r="L48" t="s">
+        <v>43</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="30" customHeight="1">
+      <c r="A49" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS2811DS-B</v>
+      </c>
+      <c r="B49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" t="s">
+        <v>523</v>
+      </c>
+      <c r="E49" t="s">
+        <v>519</v>
+      </c>
+      <c r="F49" t="s">
+        <v>520</v>
+      </c>
+      <c r="G49">
+        <v>75</v>
+      </c>
+      <c r="H49" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49">
+        <v>130</v>
+      </c>
+      <c r="J49" t="s">
+        <v>46</v>
+      </c>
+      <c r="K49" t="s">
+        <v>47</v>
+      </c>
+      <c r="L49" t="s">
+        <v>48</v>
+      </c>
+      <c r="N49" s="1"/>
+    </row>
+    <row r="50" spans="1:14" ht="30" customHeight="1">
+      <c r="A50" t="s">
+        <v>525</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
+        <v>524</v>
+      </c>
+      <c r="E50" t="s">
+        <v>519</v>
+      </c>
+      <c r="F50" t="s">
         <v>36</v>
       </c>
-      <c r="G47">
+      <c r="G50">
+        <v>75</v>
+      </c>
+      <c r="H50" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50">
+        <v>130</v>
+      </c>
+      <c r="J50" t="s">
+        <v>46</v>
+      </c>
+      <c r="K50" t="s">
+        <v>47</v>
+      </c>
+      <c r="L50" t="s">
+        <v>48</v>
+      </c>
+      <c r="N50" s="1"/>
+    </row>
+    <row r="51" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" t="s">
+        <v>496</v>
+      </c>
+      <c r="E51" t="s">
+        <v>519</v>
+      </c>
+      <c r="F51" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51">
         <v>100</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H51" t="s">
         <v>40</v>
       </c>
-      <c r="I47">
+      <c r="I51">
+        <v>100</v>
+      </c>
+      <c r="J51" t="s">
+        <v>545</v>
+      </c>
+      <c r="K51" t="s">
+        <v>47</v>
+      </c>
+      <c r="L51" t="s">
+        <v>48</v>
+      </c>
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A52" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" t="s">
+        <v>495</v>
+      </c>
+      <c r="E52" t="s">
+        <v>519</v>
+      </c>
+      <c r="F52" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52">
+        <v>100</v>
+      </c>
+      <c r="H52" t="s">
+        <v>40</v>
+      </c>
+      <c r="I52">
+        <v>100</v>
+      </c>
+      <c r="J52" t="s">
+        <v>545</v>
+      </c>
+      <c r="K52" t="s">
+        <v>47</v>
+      </c>
+      <c r="L52" t="s">
+        <v>48</v>
+      </c>
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A53" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>494</v>
+      </c>
+      <c r="E53" t="s">
+        <v>519</v>
+      </c>
+      <c r="F53" t="s">
+        <v>36</v>
+      </c>
+      <c r="G53">
+        <v>100</v>
+      </c>
+      <c r="H53" t="s">
+        <v>40</v>
+      </c>
+      <c r="I53">
+        <v>100</v>
+      </c>
+      <c r="J53" t="s">
+        <v>545</v>
+      </c>
+      <c r="K53" t="s">
+        <v>47</v>
+      </c>
+      <c r="L53" t="s">
+        <v>48</v>
+      </c>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A54" t="s">
+        <v>346</v>
+      </c>
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
+        <v>92</v>
+      </c>
+      <c r="E54" t="s">
+        <v>521</v>
+      </c>
+      <c r="F54" t="s">
+        <v>58</v>
+      </c>
+      <c r="G54">
+        <v>100</v>
+      </c>
+      <c r="H54" t="s">
+        <v>40</v>
+      </c>
+      <c r="I54">
         <v>120</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J54" t="s">
         <v>41</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K54" t="s">
         <v>47</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L54" t="s">
         <v>48</v>
       </c>
-      <c r="M47">
+      <c r="M54">
         <v>130</v>
       </c>
-      <c r="N47" s="1"/>
-    </row>
-    <row r="48" spans="1:14" ht="30" customHeight="1">
-      <c r="A48" t="str">
+      <c r="N54" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A55" t="s">
+        <v>347</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" t="s">
+        <v>521</v>
+      </c>
+      <c r="F55" t="s">
+        <v>36</v>
+      </c>
+      <c r="G55">
+        <v>100</v>
+      </c>
+      <c r="H55" t="s">
+        <v>40</v>
+      </c>
+      <c r="I55">
+        <v>120</v>
+      </c>
+      <c r="J55" t="s">
+        <v>41</v>
+      </c>
+      <c r="K55" t="s">
+        <v>47</v>
+      </c>
+      <c r="L55" t="s">
+        <v>48</v>
+      </c>
+      <c r="M55">
+        <v>130</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A56" t="s">
+        <v>543</v>
+      </c>
+      <c r="B56" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" t="s">
+        <v>535</v>
+      </c>
+      <c r="E56" t="s">
+        <v>521</v>
+      </c>
+      <c r="F56" t="s">
+        <v>36</v>
+      </c>
+      <c r="G56">
+        <v>100</v>
+      </c>
+      <c r="H56" t="s">
+        <v>40</v>
+      </c>
+      <c r="I56">
+        <v>120</v>
+      </c>
+      <c r="J56" t="s">
+        <v>41</v>
+      </c>
+      <c r="K56" t="s">
+        <v>47</v>
+      </c>
+      <c r="L56" t="s">
+        <v>48</v>
+      </c>
+      <c r="M56">
+        <v>130</v>
+      </c>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="1:14" ht="37.5" customHeight="1">
+      <c r="A57" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1991-W</v>
       </c>
-      <c r="B48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s">
         <v>517</v>
-      </c>
-      <c r="E48" t="s">
-        <v>521</v>
-      </c>
-      <c r="F48" t="s">
-        <v>58</v>
-      </c>
-      <c r="G48">
-        <v>100</v>
-      </c>
-      <c r="H48" t="s">
-        <v>40</v>
-      </c>
-      <c r="I48">
-        <v>120</v>
-      </c>
-      <c r="J48" t="s">
-        <v>41</v>
-      </c>
-      <c r="K48" t="s">
-        <v>47</v>
-      </c>
-      <c r="L48" t="s">
-        <v>48</v>
-      </c>
-      <c r="N48" s="1"/>
-    </row>
-    <row r="49" spans="1:14" ht="30" customHeight="1">
-      <c r="A49" t="s">
-        <v>348</v>
-      </c>
-      <c r="B49" t="s">
-        <v>109</v>
-      </c>
-      <c r="C49" t="s">
-        <v>94</v>
-      </c>
-      <c r="E49" t="s">
-        <v>521</v>
-      </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
-      <c r="G49">
-        <v>120</v>
-      </c>
-      <c r="H49" t="s">
-        <v>51</v>
-      </c>
-      <c r="I49">
-        <v>120</v>
-      </c>
-      <c r="J49" t="s">
-        <v>41</v>
-      </c>
-      <c r="K49" t="s">
-        <v>47</v>
-      </c>
-      <c r="L49" t="s">
-        <v>48</v>
-      </c>
-      <c r="M49">
-        <v>150</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="30" customHeight="1">
-      <c r="A50" t="s">
-        <v>349</v>
-      </c>
-      <c r="B50" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50" t="s">
-        <v>96</v>
-      </c>
-      <c r="E50" t="s">
-        <v>521</v>
-      </c>
-      <c r="F50" t="s">
-        <v>58</v>
-      </c>
-      <c r="G50">
-        <v>110</v>
-      </c>
-      <c r="H50" t="s">
-        <v>51</v>
-      </c>
-      <c r="I50">
-        <v>120.5</v>
-      </c>
-      <c r="J50" t="s">
-        <v>41</v>
-      </c>
-      <c r="K50" t="s">
-        <v>97</v>
-      </c>
-      <c r="L50" t="s">
-        <v>48</v>
-      </c>
-      <c r="M50">
-        <v>125</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A51" t="s">
-        <v>504</v>
-      </c>
-      <c r="B51" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" t="s">
-        <v>503</v>
-      </c>
-      <c r="E51" t="s">
-        <v>521</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-      <c r="G51">
-        <v>75</v>
-      </c>
-      <c r="H51" t="s">
-        <v>14</v>
-      </c>
-      <c r="I51">
-        <v>40</v>
-      </c>
-      <c r="J51" t="s">
-        <v>15</v>
-      </c>
-      <c r="K51" t="s">
-        <v>32</v>
-      </c>
-      <c r="L51" t="s">
-        <v>33</v>
-      </c>
-      <c r="N51" s="1"/>
-    </row>
-    <row r="52" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A52" t="s">
-        <v>528</v>
-      </c>
-      <c r="B52" t="s">
-        <v>109</v>
-      </c>
-      <c r="C52" t="s">
-        <v>527</v>
-      </c>
-      <c r="E52" t="s">
-        <v>521</v>
-      </c>
-      <c r="F52" t="s">
-        <v>23</v>
-      </c>
-      <c r="G52">
-        <v>75</v>
-      </c>
-      <c r="H52" t="s">
-        <v>14</v>
-      </c>
-      <c r="I52">
-        <v>60</v>
-      </c>
-      <c r="J52" t="s">
-        <v>15</v>
-      </c>
-      <c r="K52" t="s">
-        <v>32</v>
-      </c>
-      <c r="L52" t="s">
-        <v>32</v>
-      </c>
-      <c r="N52" s="1"/>
-    </row>
-    <row r="53" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A53" t="s">
-        <v>351</v>
-      </c>
-      <c r="B53" t="s">
-        <v>109</v>
-      </c>
-      <c r="C53" t="s">
-        <v>101</v>
-      </c>
-      <c r="E53" t="s">
-        <v>521</v>
-      </c>
-      <c r="F53" t="s">
-        <v>54</v>
-      </c>
-      <c r="G53">
-        <v>80</v>
-      </c>
-      <c r="H53" t="s">
-        <v>40</v>
-      </c>
-      <c r="I53">
-        <v>45.5</v>
-      </c>
-      <c r="J53" t="s">
-        <v>15</v>
-      </c>
-      <c r="K53" t="s">
-        <v>102</v>
-      </c>
-      <c r="L53" t="s">
-        <v>32</v>
-      </c>
-      <c r="M53">
-        <v>55.5</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A54" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS2811DS-B</v>
-      </c>
-      <c r="B54" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" t="s">
-        <v>523</v>
-      </c>
-      <c r="E54" t="s">
-        <v>519</v>
-      </c>
-      <c r="F54" t="s">
-        <v>520</v>
-      </c>
-      <c r="G54">
-        <v>75</v>
-      </c>
-      <c r="H54" t="s">
-        <v>14</v>
-      </c>
-      <c r="I54">
-        <v>130</v>
-      </c>
-      <c r="J54" t="s">
-        <v>46</v>
-      </c>
-      <c r="K54" t="s">
-        <v>47</v>
-      </c>
-      <c r="L54" t="s">
-        <v>48</v>
-      </c>
-      <c r="N54" s="1"/>
-    </row>
-    <row r="55" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A55" t="s">
-        <v>525</v>
-      </c>
-      <c r="B55" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" t="s">
-        <v>524</v>
-      </c>
-      <c r="E55" t="s">
-        <v>519</v>
-      </c>
-      <c r="F55" t="s">
-        <v>36</v>
-      </c>
-      <c r="G55">
-        <v>75</v>
-      </c>
-      <c r="H55" t="s">
-        <v>14</v>
-      </c>
-      <c r="I55">
-        <v>130</v>
-      </c>
-      <c r="J55" t="s">
-        <v>46</v>
-      </c>
-      <c r="K55" t="s">
-        <v>47</v>
-      </c>
-      <c r="L55" t="s">
-        <v>48</v>
-      </c>
-      <c r="N55" s="1"/>
-    </row>
-    <row r="56" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A56" t="s">
-        <v>353</v>
-      </c>
-      <c r="B56" t="s">
-        <v>109</v>
-      </c>
-      <c r="C56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E56" t="s">
-        <v>521</v>
-      </c>
-      <c r="F56" t="s">
-        <v>36</v>
-      </c>
-      <c r="G56">
-        <v>120</v>
-      </c>
-      <c r="H56" t="s">
-        <v>51</v>
-      </c>
-      <c r="I56">
-        <v>120</v>
-      </c>
-      <c r="J56" t="s">
-        <v>41</v>
-      </c>
-      <c r="K56" t="s">
-        <v>42</v>
-      </c>
-      <c r="L56" t="s">
-        <v>43</v>
-      </c>
-      <c r="M56">
-        <v>125</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="37.5" customHeight="1">
-      <c r="A57" t="s">
-        <v>530</v>
-      </c>
-      <c r="B57" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57" t="s">
-        <v>529</v>
       </c>
       <c r="E57" t="s">
         <v>521</v>
       </c>
       <c r="F57" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G57">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H57" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I57">
         <v>120</v>
@@ -4652,10 +4661,10 @@
         <v>41</v>
       </c>
       <c r="K57" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L57" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N57" s="1"/>
     </row>
@@ -4702,125 +4711,125 @@
     </row>
     <row r="59" spans="1:14" ht="42" customHeight="1">
       <c r="A59" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B59" t="s">
         <v>109</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="E59" t="s">
         <v>521</v>
       </c>
       <c r="F59" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G59">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H59" t="s">
-        <v>526</v>
+        <v>51</v>
       </c>
       <c r="I59">
+        <v>120</v>
+      </c>
+      <c r="J59" t="s">
         <v>41</v>
       </c>
-      <c r="J59" t="s">
-        <v>15</v>
-      </c>
       <c r="K59" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="L59" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="M59">
-        <v>41</v>
+        <v>150</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="36.75" customHeight="1">
       <c r="A60" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="B60" t="s">
         <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E60" t="s">
         <v>521</v>
       </c>
       <c r="F60" t="s">
-        <v>23</v>
+        <v>488</v>
       </c>
       <c r="G60">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="I60">
-        <v>41</v>
+        <v>65.5</v>
       </c>
       <c r="J60" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K60" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="L60" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="M60">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="29.25" customHeight="1">
       <c r="A61" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s">
         <v>109</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="E61" t="s">
         <v>521</v>
       </c>
       <c r="F61" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G61">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="H61" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="I61">
-        <v>30</v>
+        <v>120.5</v>
       </c>
       <c r="J61" t="s">
-        <v>500</v>
+        <v>41</v>
       </c>
       <c r="K61" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="L61" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="M61">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="44.25" customHeight="1">

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72817AE-FBC8-4E91-85F5-F7633B9E2A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAF6DAB-FE6D-47D8-918B-AC64440267C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -1967,10 +1967,10 @@
     <t>images/TS1881-B_V2</t>
   </si>
   <si>
-    <t>90 kg</t>
-  </si>
-  <si>
     <t>50"-90"</t>
+  </si>
+  <si>
+    <t>100 kg</t>
   </si>
 </sst>
 </file>
@@ -2076,7 +2076,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N62" totalsRowShown="0">
   <autoFilter ref="A1:N62" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N62">
-    <sortCondition ref="L1:L62"/>
+    <sortCondition ref="I1:I62"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
@@ -2533,66 +2533,69 @@
     </row>
     <row r="3" spans="1:14" ht="21.75" customHeight="1">
       <c r="A3" t="s">
-        <v>279</v>
+        <v>357</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>521</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H3" t="s">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="I3">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L3" t="s">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="M3">
+        <v>40</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="21.75" customHeight="1">
       <c r="A4" t="s">
-        <v>325</v>
+        <v>279</v>
       </c>
       <c r="B4" t="s">
         <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
         <v>521</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="4">
+        <v>13</v>
+      </c>
+      <c r="G4">
         <v>55</v>
       </c>
       <c r="H4" t="s">
         <v>526</v>
       </c>
       <c r="I4">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
@@ -2603,257 +2606,254 @@
       <c r="L4" t="s">
         <v>17</v>
       </c>
-      <c r="M4">
+      <c r="N4" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>521</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5">
+        <v>65</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>35</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>521</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>65</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>35</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" t="s">
+        <v>521</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>65</v>
+      </c>
+      <c r="H7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>35</v>
+      </c>
+      <c r="J7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" t="s">
+        <v>521</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="4">
+        <v>55</v>
+      </c>
+      <c r="H8" t="s">
+        <v>526</v>
+      </c>
+      <c r="I8">
+        <v>40</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8">
         <v>45</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A5" t="str">
+    <row r="9" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A9" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1137-W</v>
       </c>
-      <c r="B5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" t="s">
         <v>537</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E9" t="s">
         <v>521</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F9" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G9" s="4">
         <v>55</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H9" t="s">
         <v>526</v>
       </c>
-      <c r="I5">
+      <c r="I9">
         <v>40</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J9" t="s">
         <v>15</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K9" t="s">
         <v>17</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L9" t="s">
         <v>17</v>
       </c>
-      <c r="M5">
+      <c r="M9">
         <v>45</v>
       </c>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A6" t="str">
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A10" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1171-B</v>
       </c>
-      <c r="B6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" t="s">
         <v>516</v>
-      </c>
-      <c r="E6" t="s">
-        <v>519</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6">
-        <v>60</v>
-      </c>
-      <c r="H6" t="s">
-        <v>526</v>
-      </c>
-      <c r="I6">
-        <v>40</v>
-      </c>
-      <c r="J6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6">
-        <v>45</v>
-      </c>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A7" t="s">
-        <v>355</v>
-      </c>
-      <c r="B7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>521</v>
-      </c>
-      <c r="F7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7">
-        <v>60</v>
-      </c>
-      <c r="H7" t="s">
-        <v>526</v>
-      </c>
-      <c r="I7">
-        <v>41</v>
-      </c>
-      <c r="J7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7">
-        <v>41</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A8" t="s">
-        <v>327</v>
-      </c>
-      <c r="B8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>521</v>
-      </c>
-      <c r="F8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8">
-        <v>65</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8">
-        <v>35</v>
-      </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A9" t="s">
-        <v>328</v>
-      </c>
-      <c r="B9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>521</v>
-      </c>
-      <c r="F9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9">
-        <v>65</v>
-      </c>
-      <c r="H9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9">
-        <v>35</v>
-      </c>
-      <c r="J9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
       </c>
       <c r="E10" t="s">
         <v>519</v>
       </c>
       <c r="F10" t="s">
-        <v>520</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>526</v>
       </c>
       <c r="I10">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="J10" t="s">
-        <v>545</v>
+        <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" t="s">
         <v>17</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="M10">
+        <v>45</v>
+      </c>
+      <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="21.75" customHeight="1">
       <c r="A11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B11" t="s">
         <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
         <v>521</v>
@@ -2862,156 +2862,146 @@
         <v>13</v>
       </c>
       <c r="G11">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I11">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="L11" t="s">
         <v>17</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="21.75" customHeight="1">
       <c r="A12" t="s">
-        <v>337</v>
+        <v>512</v>
       </c>
       <c r="B12" t="s">
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>511</v>
       </c>
       <c r="E12" t="s">
         <v>521</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G12">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I12">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J12" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L12" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12">
-        <v>70</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" ht="21.75" customHeight="1">
       <c r="A13" t="s">
-        <v>356</v>
+        <v>504</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>503</v>
       </c>
       <c r="E13" t="s">
         <v>521</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="G13">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s">
-        <v>526</v>
+        <v>14</v>
       </c>
       <c r="I13">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J13" t="s">
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L13" t="s">
-        <v>17</v>
-      </c>
-      <c r="M13">
-        <v>41</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" ht="21.75" customHeight="1">
       <c r="A14" t="s">
-        <v>278</v>
+        <v>329</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
         <v>521</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>488</v>
       </c>
       <c r="G14">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
       </c>
       <c r="I14">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="J14" t="s">
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="L14" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="21.75" customHeight="1">
       <c r="A15" t="s">
-        <v>528</v>
+        <v>355</v>
       </c>
       <c r="B15" t="s">
         <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>527</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
         <v>521</v>
@@ -3020,35 +3010,39 @@
         <v>23</v>
       </c>
       <c r="G15">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>526</v>
       </c>
       <c r="I15">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="J15" t="s">
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L15" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="M15">
+        <v>41</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A16" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1580-B</v>
+      <c r="A16" t="s">
+        <v>356</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>522</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
         <v>521</v>
@@ -3057,112 +3051,127 @@
         <v>23</v>
       </c>
       <c r="G16">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
+        <v>526</v>
       </c>
       <c r="I16">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="J16" t="s">
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>491</v>
+        <v>29</v>
       </c>
       <c r="L16" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="M16">
+        <v>41</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="17" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>492</v>
+      <c r="A17" t="s">
+        <v>330</v>
       </c>
       <c r="B17" t="s">
         <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>490</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
         <v>521</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G17">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I17">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J17" t="s">
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>491</v>
+        <v>32</v>
       </c>
       <c r="L17" t="s">
-        <v>32</v>
-      </c>
-      <c r="N17" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="M17">
+        <v>50</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="18" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>493</v>
+      <c r="A18" t="s">
+        <v>331</v>
       </c>
       <c r="B18" t="s">
         <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>489</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
         <v>521</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G18">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I18">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>491</v>
+        <v>32</v>
       </c>
       <c r="L18" t="s">
-        <v>32</v>
-      </c>
-      <c r="N18" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="M18">
+        <v>50</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="19" spans="1:14" ht="21.75" customHeight="1">
       <c r="A19" t="s">
-        <v>532</v>
+        <v>334</v>
       </c>
       <c r="B19" t="s">
         <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>531</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
         <v>521</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G19">
         <v>75</v>
@@ -3171,18 +3180,23 @@
         <v>14</v>
       </c>
       <c r="I19">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="J19" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>533</v>
+        <v>32</v>
       </c>
       <c r="L19" t="s">
-        <v>32</v>
-      </c>
-      <c r="N19" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="M19">
+        <v>50</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1">
       <c r="A20" t="s">
@@ -3204,7 +3218,7 @@
         <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I20">
         <v>45.5</v>
@@ -3227,31 +3241,31 @@
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>333</v>
       </c>
       <c r="B21" t="s">
         <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F21" t="s">
-        <v>520</v>
+        <v>58</v>
       </c>
       <c r="G21">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H21" t="s">
-        <v>526</v>
+        <v>14</v>
       </c>
       <c r="I21">
-        <v>200</v>
+        <v>45.5</v>
       </c>
       <c r="J21" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="K21" t="s">
         <v>32</v>
@@ -3259,37 +3273,40 @@
       <c r="L21" t="s">
         <v>33</v>
       </c>
+      <c r="M21">
+        <v>55.5</v>
+      </c>
       <c r="N21" s="1" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1">
       <c r="A22" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="B22" t="s">
         <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
         <v>521</v>
       </c>
       <c r="F22" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G22">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I22">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J22" t="s">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="K22" t="s">
         <v>32</v>
@@ -3298,36 +3315,36 @@
         <v>33</v>
       </c>
       <c r="M22">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1">
       <c r="A23" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="E23" t="s">
         <v>521</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G23">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I23">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
@@ -3338,17 +3355,22 @@
       <c r="L23" t="s">
         <v>33</v>
       </c>
-      <c r="N23" s="1"/>
+      <c r="M23">
+        <v>60</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1">
       <c r="A24" t="s">
-        <v>330</v>
+        <v>505</v>
       </c>
       <c r="B24" t="s">
         <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>501</v>
       </c>
       <c r="E24" t="s">
         <v>521</v>
@@ -3357,13 +3379,13 @@
         <v>58</v>
       </c>
       <c r="G24">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I24">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
@@ -3375,21 +3397,18 @@
         <v>33</v>
       </c>
       <c r="M24">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="21.75" customHeight="1">
       <c r="A25" t="s">
-        <v>331</v>
-      </c>
-      <c r="B25" t="s">
-        <v>109</v>
+        <v>539</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>534</v>
       </c>
       <c r="E25" t="s">
         <v>521</v>
@@ -3398,13 +3417,13 @@
         <v>58</v>
       </c>
       <c r="G25">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I25">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J25" t="s">
         <v>15</v>
@@ -3416,36 +3435,34 @@
         <v>33</v>
       </c>
       <c r="M25">
-        <v>50</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>66</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" ht="21.75" customHeight="1">
       <c r="A26" t="s">
-        <v>333</v>
+        <v>528</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>527</v>
       </c>
       <c r="E26" t="s">
         <v>521</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G26">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s">
         <v>14</v>
       </c>
       <c r="I26">
-        <v>45.5</v>
+        <v>60</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
@@ -3454,30 +3471,26 @@
         <v>32</v>
       </c>
       <c r="L26" t="s">
-        <v>33</v>
-      </c>
-      <c r="M26">
-        <v>55.5</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A27" t="s">
-        <v>504</v>
+      <c r="A27" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1580-B</v>
       </c>
       <c r="B27" t="s">
         <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="E27" t="s">
         <v>521</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G27">
         <v>75</v>
@@ -3486,34 +3499,34 @@
         <v>14</v>
       </c>
       <c r="I27">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J27" t="s">
         <v>15</v>
       </c>
       <c r="K27" t="s">
+        <v>491</v>
+      </c>
+      <c r="L27" t="s">
         <v>32</v>
       </c>
-      <c r="L27" t="s">
-        <v>33</v>
-      </c>
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A28" t="s">
-        <v>334</v>
+      <c r="A28" s="2" t="s">
+        <v>492</v>
       </c>
       <c r="B28" t="s">
         <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>490</v>
       </c>
       <c r="E28" t="s">
         <v>521</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G28">
         <v>75</v>
@@ -3522,39 +3535,34 @@
         <v>14</v>
       </c>
       <c r="I28">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
       </c>
       <c r="K28" t="s">
+        <v>491</v>
+      </c>
+      <c r="L28" t="s">
         <v>32</v>
       </c>
-      <c r="L28" t="s">
-        <v>33</v>
-      </c>
-      <c r="M28">
-        <v>50</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A29" t="s">
-        <v>338</v>
+      <c r="A29" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="B29" t="s">
         <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>489</v>
       </c>
       <c r="E29" t="s">
         <v>521</v>
       </c>
       <c r="F29" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G29">
         <v>75</v>
@@ -3563,39 +3571,34 @@
         <v>14</v>
       </c>
       <c r="I29">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
       </c>
       <c r="K29" t="s">
+        <v>491</v>
+      </c>
+      <c r="L29" t="s">
         <v>32</v>
       </c>
-      <c r="L29" t="s">
-        <v>33</v>
-      </c>
-      <c r="M29">
-        <v>60</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" ht="21.75" customHeight="1">
       <c r="A30" t="s">
-        <v>506</v>
+        <v>337</v>
       </c>
       <c r="B30" t="s">
         <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>502</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s">
         <v>521</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G30">
         <v>75</v>
@@ -3604,39 +3607,39 @@
         <v>14</v>
       </c>
       <c r="I30">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K30" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L30" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="M30">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="21.75" customHeight="1">
       <c r="A31" t="s">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>501</v>
+        <v>531</v>
       </c>
       <c r="E31" t="s">
         <v>521</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G31">
         <v>75</v>
@@ -3645,59 +3648,59 @@
         <v>14</v>
       </c>
       <c r="I31">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J31" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K31" t="s">
+        <v>533</v>
+      </c>
+      <c r="L31" t="s">
         <v>32</v>
       </c>
-      <c r="L31" t="s">
-        <v>33</v>
-      </c>
-      <c r="M31">
-        <v>60</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" ht="21.75" customHeight="1">
       <c r="A32" t="s">
-        <v>539</v>
+        <v>332</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>534</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
         <v>521</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>488</v>
       </c>
       <c r="G32">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s">
-        <v>14</v>
+        <v>545</v>
       </c>
       <c r="I32">
-        <v>50</v>
+        <v>65.5</v>
       </c>
       <c r="J32" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K32" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="L32" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="M32">
-        <v>60</v>
-      </c>
-      <c r="N32" s="1"/>
+        <v>70</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="33" spans="1:14" ht="21.75" customHeight="1">
       <c r="A33" t="str">
@@ -3738,95 +3741,95 @@
     </row>
     <row r="34" spans="1:14" ht="21.75" customHeight="1">
       <c r="A34" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E34" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F34" t="s">
-        <v>520</v>
+        <v>58</v>
       </c>
       <c r="G34">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
       <c r="I34">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="J34" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K34" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L34" t="s">
         <v>43</v>
       </c>
       <c r="M34">
-        <v>105.9</v>
+        <v>90</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="21.75" customHeight="1">
       <c r="A35" t="s">
-        <v>343</v>
+        <v>508</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>510</v>
       </c>
       <c r="E35" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F35" t="s">
-        <v>520</v>
+        <v>58</v>
       </c>
       <c r="G35">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
       <c r="I35">
-        <v>90.9</v>
+        <v>75</v>
       </c>
       <c r="J35" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K35" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L35" t="s">
         <v>43</v>
       </c>
       <c r="M35">
-        <v>105.9</v>
+        <v>90</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="21.75" customHeight="1">
       <c r="A36" t="s">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="B36" t="s">
         <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>509</v>
       </c>
       <c r="E36" t="s">
         <v>521</v>
@@ -3835,239 +3838,239 @@
         <v>58</v>
       </c>
       <c r="G36">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s">
+        <v>545</v>
+      </c>
+      <c r="I36">
+        <v>75</v>
+      </c>
+      <c r="J36" t="s">
         <v>546</v>
       </c>
-      <c r="I36">
-        <v>90.9</v>
-      </c>
-      <c r="J36" t="s">
-        <v>545</v>
-      </c>
       <c r="K36" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L36" t="s">
         <v>43</v>
       </c>
       <c r="M36">
-        <v>105.9</v>
+        <v>90</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="21.75" customHeight="1">
       <c r="A37" t="s">
-        <v>344</v>
+        <v>540</v>
       </c>
       <c r="B37" t="s">
         <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>536</v>
       </c>
       <c r="E37" t="s">
         <v>521</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G37">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s">
+        <v>545</v>
+      </c>
+      <c r="I37">
+        <v>75</v>
+      </c>
+      <c r="J37" t="s">
         <v>546</v>
       </c>
-      <c r="I37">
-        <v>90.9</v>
-      </c>
-      <c r="J37" t="s">
-        <v>545</v>
-      </c>
       <c r="K37" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L37" t="s">
         <v>43</v>
       </c>
       <c r="M37">
-        <v>105.9</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>44</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="N37" s="1"/>
     </row>
     <row r="38" spans="1:14" ht="21.75" customHeight="1">
       <c r="A38" t="s">
-        <v>353</v>
+        <v>159</v>
       </c>
       <c r="B38" t="s">
         <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F38" t="s">
-        <v>36</v>
+        <v>520</v>
       </c>
       <c r="G38">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H38" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="I38">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J38" t="s">
-        <v>41</v>
+        <v>546</v>
       </c>
       <c r="K38" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="L38" t="s">
-        <v>43</v>
-      </c>
-      <c r="M38">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>530</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>529</v>
+        <v>90</v>
       </c>
       <c r="E39" t="s">
         <v>521</v>
       </c>
       <c r="F39" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G39">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s">
-        <v>51</v>
+        <v>545</v>
       </c>
       <c r="I39">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J39" t="s">
-        <v>41</v>
+        <v>546</v>
       </c>
       <c r="K39" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L39" t="s">
         <v>43</v>
       </c>
-      <c r="N39" s="1"/>
+      <c r="M39">
+        <v>100</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="40" spans="1:14" ht="21.75" customHeight="1">
       <c r="A40" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s">
         <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E40" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>520</v>
       </c>
       <c r="G40">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H40" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40">
+        <v>90.9</v>
+      </c>
+      <c r="J40" t="s">
         <v>546</v>
       </c>
-      <c r="I40">
-        <v>75</v>
-      </c>
-      <c r="J40" t="s">
-        <v>545</v>
-      </c>
       <c r="K40" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L40" t="s">
         <v>43</v>
       </c>
       <c r="M40">
-        <v>90</v>
+        <v>105.9</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="21.75" customHeight="1">
       <c r="A41" t="s">
-        <v>508</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s">
         <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>510</v>
+        <v>88</v>
       </c>
       <c r="E41" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>520</v>
       </c>
       <c r="G41">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H41" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41">
+        <v>90.9</v>
+      </c>
+      <c r="J41" t="s">
         <v>546</v>
       </c>
-      <c r="I41">
-        <v>75</v>
-      </c>
-      <c r="J41" t="s">
-        <v>545</v>
-      </c>
       <c r="K41" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L41" t="s">
         <v>43</v>
       </c>
       <c r="M41">
-        <v>90</v>
+        <v>105.9</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="21.75" customHeight="1">
       <c r="A42" t="s">
-        <v>507</v>
+        <v>544</v>
       </c>
       <c r="B42" t="s">
         <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>509</v>
+        <v>83</v>
       </c>
       <c r="E42" t="s">
         <v>521</v>
@@ -4076,96 +4079,99 @@
         <v>58</v>
       </c>
       <c r="G42">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s">
+        <v>545</v>
+      </c>
+      <c r="I42">
+        <v>90.9</v>
+      </c>
+      <c r="J42" t="s">
         <v>546</v>
       </c>
-      <c r="I42">
-        <v>75</v>
-      </c>
-      <c r="J42" t="s">
-        <v>545</v>
-      </c>
       <c r="K42" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L42" t="s">
         <v>43</v>
       </c>
       <c r="M42">
-        <v>90</v>
+        <v>105.9</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="26.25" customHeight="1">
       <c r="A43" t="s">
-        <v>540</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>536</v>
+        <v>39</v>
       </c>
       <c r="E43" t="s">
         <v>521</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G43">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s">
+        <v>545</v>
+      </c>
+      <c r="I43">
+        <v>90.9</v>
+      </c>
+      <c r="J43" t="s">
         <v>546</v>
       </c>
-      <c r="I43">
-        <v>75</v>
-      </c>
-      <c r="J43" t="s">
-        <v>545</v>
-      </c>
       <c r="K43" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L43" t="s">
         <v>43</v>
       </c>
       <c r="M43">
-        <v>90</v>
-      </c>
-      <c r="N43" s="1"/>
+        <v>105.9</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="44" spans="1:14" ht="26.25" customHeight="1">
-      <c r="A44" t="s">
-        <v>345</v>
+      <c r="A44" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-B</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>513</v>
       </c>
       <c r="E44" t="s">
         <v>521</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G44">
         <v>90</v>
       </c>
       <c r="H44" t="s">
+        <v>545</v>
+      </c>
+      <c r="I44">
+        <v>100</v>
+      </c>
+      <c r="J44" t="s">
         <v>546</v>
-      </c>
-      <c r="I44">
-        <v>90</v>
-      </c>
-      <c r="J44" t="s">
-        <v>545</v>
       </c>
       <c r="K44" t="s">
         <v>81</v>
@@ -4173,23 +4179,18 @@
       <c r="L44" t="s">
         <v>43</v>
       </c>
-      <c r="M44">
-        <v>100</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="N44" s="1"/>
     </row>
     <row r="45" spans="1:14" ht="27.75" customHeight="1">
       <c r="A45" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-B</v>
+        <v>images/TS1590-C</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E45" t="s">
         <v>521</v>
@@ -4201,13 +4202,13 @@
         <v>90</v>
       </c>
       <c r="H45" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I45">
         <v>100</v>
       </c>
       <c r="J45" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K45" t="s">
         <v>81</v>
@@ -4220,13 +4221,13 @@
     <row r="46" spans="1:14" ht="27.75" customHeight="1">
       <c r="A46" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-C</v>
+        <v>images/TS1590-G</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E46" t="s">
         <v>521</v>
@@ -4238,13 +4239,13 @@
         <v>90</v>
       </c>
       <c r="H46" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I46">
         <v>100</v>
       </c>
       <c r="J46" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K46" t="s">
         <v>81</v>
@@ -4255,487 +4256,479 @@
       <c r="N46" s="1"/>
     </row>
     <row r="47" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A47" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-G</v>
+      <c r="A47" s="3" t="s">
+        <v>499</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="E47" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F47" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G47">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H47" t="s">
-        <v>546</v>
+        <v>40</v>
       </c>
       <c r="I47">
         <v>100</v>
       </c>
       <c r="J47" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K47" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L47" t="s">
+        <v>48</v>
+      </c>
+      <c r="N47" s="1"/>
+    </row>
+    <row r="48" spans="1:14" ht="30" customHeight="1">
+      <c r="A48" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
+        <v>495</v>
+      </c>
+      <c r="E48" t="s">
+        <v>519</v>
+      </c>
+      <c r="F48" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48">
+        <v>100</v>
+      </c>
+      <c r="H48" t="s">
+        <v>40</v>
+      </c>
+      <c r="I48">
+        <v>100</v>
+      </c>
+      <c r="J48" t="s">
+        <v>546</v>
+      </c>
+      <c r="K48" t="s">
+        <v>47</v>
+      </c>
+      <c r="L48" t="s">
+        <v>48</v>
+      </c>
+      <c r="N48" s="1"/>
+    </row>
+    <row r="49" spans="1:14" ht="30" customHeight="1">
+      <c r="A49" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" t="s">
+        <v>494</v>
+      </c>
+      <c r="E49" t="s">
+        <v>519</v>
+      </c>
+      <c r="F49" t="s">
+        <v>36</v>
+      </c>
+      <c r="G49">
+        <v>100</v>
+      </c>
+      <c r="H49" t="s">
+        <v>40</v>
+      </c>
+      <c r="I49">
+        <v>100</v>
+      </c>
+      <c r="J49" t="s">
+        <v>546</v>
+      </c>
+      <c r="K49" t="s">
+        <v>47</v>
+      </c>
+      <c r="L49" t="s">
+        <v>48</v>
+      </c>
+      <c r="N49" s="1"/>
+    </row>
+    <row r="50" spans="1:14" ht="30" customHeight="1">
+      <c r="A50" t="s">
+        <v>353</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
+        <v>50</v>
+      </c>
+      <c r="E50" t="s">
+        <v>521</v>
+      </c>
+      <c r="F50" t="s">
+        <v>36</v>
+      </c>
+      <c r="G50">
+        <v>120</v>
+      </c>
+      <c r="H50" t="s">
+        <v>51</v>
+      </c>
+      <c r="I50">
+        <v>120</v>
+      </c>
+      <c r="J50" t="s">
+        <v>41</v>
+      </c>
+      <c r="K50" t="s">
+        <v>42</v>
+      </c>
+      <c r="L50" t="s">
         <v>43</v>
       </c>
-      <c r="N47" s="1"/>
-    </row>
-    <row r="48" spans="1:14" ht="30" customHeight="1">
-      <c r="A48" t="s">
-        <v>329</v>
-      </c>
-      <c r="B48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" t="s">
-        <v>62</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="M50">
+        <v>125</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A51" t="s">
+        <v>530</v>
+      </c>
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" t="s">
+        <v>529</v>
+      </c>
+      <c r="E51" t="s">
         <v>521</v>
       </c>
-      <c r="F48" t="s">
-        <v>488</v>
-      </c>
-      <c r="G48">
-        <v>70</v>
-      </c>
-      <c r="H48" t="s">
-        <v>14</v>
-      </c>
-      <c r="I48">
-        <v>40.5</v>
-      </c>
-      <c r="J48" t="s">
-        <v>15</v>
-      </c>
-      <c r="K48" t="s">
-        <v>63</v>
-      </c>
-      <c r="L48" t="s">
+      <c r="F51" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51">
+        <v>120</v>
+      </c>
+      <c r="H51" t="s">
+        <v>51</v>
+      </c>
+      <c r="I51">
+        <v>120</v>
+      </c>
+      <c r="J51" t="s">
+        <v>41</v>
+      </c>
+      <c r="K51" t="s">
+        <v>42</v>
+      </c>
+      <c r="L51" t="s">
         <v>43</v>
       </c>
-      <c r="N48" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="30" customHeight="1">
-      <c r="A49" t="str">
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A52" t="s">
+        <v>346</v>
+      </c>
+      <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" t="s">
+        <v>521</v>
+      </c>
+      <c r="F52" t="s">
+        <v>58</v>
+      </c>
+      <c r="G52">
+        <v>100</v>
+      </c>
+      <c r="H52" t="s">
+        <v>40</v>
+      </c>
+      <c r="I52">
+        <v>120</v>
+      </c>
+      <c r="J52" t="s">
+        <v>41</v>
+      </c>
+      <c r="K52" t="s">
+        <v>47</v>
+      </c>
+      <c r="L52" t="s">
+        <v>48</v>
+      </c>
+      <c r="M52">
+        <v>130</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A53" t="s">
+        <v>347</v>
+      </c>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53" t="s">
+        <v>521</v>
+      </c>
+      <c r="F53" t="s">
+        <v>36</v>
+      </c>
+      <c r="G53">
+        <v>100</v>
+      </c>
+      <c r="H53" t="s">
+        <v>40</v>
+      </c>
+      <c r="I53">
+        <v>120</v>
+      </c>
+      <c r="J53" t="s">
+        <v>41</v>
+      </c>
+      <c r="K53" t="s">
+        <v>47</v>
+      </c>
+      <c r="L53" t="s">
+        <v>48</v>
+      </c>
+      <c r="M53">
+        <v>130</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A54" t="s">
+        <v>543</v>
+      </c>
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
+        <v>535</v>
+      </c>
+      <c r="E54" t="s">
+        <v>521</v>
+      </c>
+      <c r="F54" t="s">
+        <v>36</v>
+      </c>
+      <c r="G54">
+        <v>100</v>
+      </c>
+      <c r="H54" t="s">
+        <v>40</v>
+      </c>
+      <c r="I54">
+        <v>120</v>
+      </c>
+      <c r="J54" t="s">
+        <v>41</v>
+      </c>
+      <c r="K54" t="s">
+        <v>47</v>
+      </c>
+      <c r="L54" t="s">
+        <v>48</v>
+      </c>
+      <c r="M54">
+        <v>130</v>
+      </c>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A55" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1991-W</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" t="s">
+        <v>517</v>
+      </c>
+      <c r="E55" t="s">
+        <v>521</v>
+      </c>
+      <c r="F55" t="s">
+        <v>58</v>
+      </c>
+      <c r="G55">
+        <v>100</v>
+      </c>
+      <c r="H55" t="s">
+        <v>40</v>
+      </c>
+      <c r="I55">
+        <v>120</v>
+      </c>
+      <c r="J55" t="s">
+        <v>41</v>
+      </c>
+      <c r="K55" t="s">
+        <v>47</v>
+      </c>
+      <c r="L55" t="s">
+        <v>48</v>
+      </c>
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A56" t="s">
+        <v>348</v>
+      </c>
+      <c r="B56" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" t="s">
+        <v>94</v>
+      </c>
+      <c r="E56" t="s">
+        <v>521</v>
+      </c>
+      <c r="F56" t="s">
+        <v>58</v>
+      </c>
+      <c r="G56">
+        <v>120</v>
+      </c>
+      <c r="H56" t="s">
+        <v>51</v>
+      </c>
+      <c r="I56">
+        <v>120</v>
+      </c>
+      <c r="J56" t="s">
+        <v>41</v>
+      </c>
+      <c r="K56" t="s">
+        <v>47</v>
+      </c>
+      <c r="L56" t="s">
+        <v>48</v>
+      </c>
+      <c r="M56">
+        <v>150</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="37.5" customHeight="1">
+      <c r="A57" t="s">
+        <v>541</v>
+      </c>
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="E57" t="s">
+        <v>519</v>
+      </c>
+      <c r="F57" t="s">
+        <v>538</v>
+      </c>
+      <c r="I57">
+        <v>120</v>
+      </c>
+      <c r="J57" t="s">
+        <v>41</v>
+      </c>
+      <c r="N57" s="1"/>
+    </row>
+    <row r="58" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A58" t="s">
+        <v>349</v>
+      </c>
+      <c r="B58" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" t="s">
+        <v>96</v>
+      </c>
+      <c r="E58" t="s">
+        <v>521</v>
+      </c>
+      <c r="F58" t="s">
+        <v>58</v>
+      </c>
+      <c r="G58">
+        <v>110</v>
+      </c>
+      <c r="H58" t="s">
+        <v>51</v>
+      </c>
+      <c r="I58">
+        <v>120.5</v>
+      </c>
+      <c r="J58" t="s">
+        <v>41</v>
+      </c>
+      <c r="K58" t="s">
+        <v>97</v>
+      </c>
+      <c r="L58" t="s">
+        <v>48</v>
+      </c>
+      <c r="M58">
+        <v>125</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="42" customHeight="1">
+      <c r="A59" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS2811DS-B</v>
       </c>
-      <c r="B49" t="s">
-        <v>109</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B59" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" t="s">
         <v>523</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E59" t="s">
         <v>519</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F59" t="s">
         <v>520</v>
       </c>
-      <c r="G49">
+      <c r="G59">
         <v>75</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H59" t="s">
         <v>14</v>
       </c>
-      <c r="I49">
+      <c r="I59">
         <v>130</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J59" t="s">
         <v>46</v>
-      </c>
-      <c r="K49" t="s">
-        <v>47</v>
-      </c>
-      <c r="L49" t="s">
-        <v>48</v>
-      </c>
-      <c r="N49" s="1"/>
-    </row>
-    <row r="50" spans="1:14" ht="30" customHeight="1">
-      <c r="A50" t="s">
-        <v>525</v>
-      </c>
-      <c r="B50" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50" t="s">
-        <v>524</v>
-      </c>
-      <c r="E50" t="s">
-        <v>519</v>
-      </c>
-      <c r="F50" t="s">
-        <v>36</v>
-      </c>
-      <c r="G50">
-        <v>75</v>
-      </c>
-      <c r="H50" t="s">
-        <v>14</v>
-      </c>
-      <c r="I50">
-        <v>130</v>
-      </c>
-      <c r="J50" t="s">
-        <v>46</v>
-      </c>
-      <c r="K50" t="s">
-        <v>47</v>
-      </c>
-      <c r="L50" t="s">
-        <v>48</v>
-      </c>
-      <c r="N50" s="1"/>
-    </row>
-    <row r="51" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A51" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="B51" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" t="s">
-        <v>496</v>
-      </c>
-      <c r="E51" t="s">
-        <v>519</v>
-      </c>
-      <c r="F51" t="s">
-        <v>36</v>
-      </c>
-      <c r="G51">
-        <v>100</v>
-      </c>
-      <c r="H51" t="s">
-        <v>40</v>
-      </c>
-      <c r="I51">
-        <v>100</v>
-      </c>
-      <c r="J51" t="s">
-        <v>545</v>
-      </c>
-      <c r="K51" t="s">
-        <v>47</v>
-      </c>
-      <c r="L51" t="s">
-        <v>48</v>
-      </c>
-      <c r="N51" s="1"/>
-    </row>
-    <row r="52" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A52" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="B52" t="s">
-        <v>109</v>
-      </c>
-      <c r="C52" t="s">
-        <v>495</v>
-      </c>
-      <c r="E52" t="s">
-        <v>519</v>
-      </c>
-      <c r="F52" t="s">
-        <v>36</v>
-      </c>
-      <c r="G52">
-        <v>100</v>
-      </c>
-      <c r="H52" t="s">
-        <v>40</v>
-      </c>
-      <c r="I52">
-        <v>100</v>
-      </c>
-      <c r="J52" t="s">
-        <v>545</v>
-      </c>
-      <c r="K52" t="s">
-        <v>47</v>
-      </c>
-      <c r="L52" t="s">
-        <v>48</v>
-      </c>
-      <c r="N52" s="1"/>
-    </row>
-    <row r="53" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A53" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="B53" t="s">
-        <v>109</v>
-      </c>
-      <c r="C53" t="s">
-        <v>494</v>
-      </c>
-      <c r="E53" t="s">
-        <v>519</v>
-      </c>
-      <c r="F53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G53">
-        <v>100</v>
-      </c>
-      <c r="H53" t="s">
-        <v>40</v>
-      </c>
-      <c r="I53">
-        <v>100</v>
-      </c>
-      <c r="J53" t="s">
-        <v>545</v>
-      </c>
-      <c r="K53" t="s">
-        <v>47</v>
-      </c>
-      <c r="L53" t="s">
-        <v>48</v>
-      </c>
-      <c r="N53" s="1"/>
-    </row>
-    <row r="54" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A54" t="s">
-        <v>346</v>
-      </c>
-      <c r="B54" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" t="s">
-        <v>92</v>
-      </c>
-      <c r="E54" t="s">
-        <v>521</v>
-      </c>
-      <c r="F54" t="s">
-        <v>58</v>
-      </c>
-      <c r="G54">
-        <v>100</v>
-      </c>
-      <c r="H54" t="s">
-        <v>40</v>
-      </c>
-      <c r="I54">
-        <v>120</v>
-      </c>
-      <c r="J54" t="s">
-        <v>41</v>
-      </c>
-      <c r="K54" t="s">
-        <v>47</v>
-      </c>
-      <c r="L54" t="s">
-        <v>48</v>
-      </c>
-      <c r="M54">
-        <v>130</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A55" t="s">
-        <v>347</v>
-      </c>
-      <c r="B55" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" t="s">
-        <v>45</v>
-      </c>
-      <c r="E55" t="s">
-        <v>521</v>
-      </c>
-      <c r="F55" t="s">
-        <v>36</v>
-      </c>
-      <c r="G55">
-        <v>100</v>
-      </c>
-      <c r="H55" t="s">
-        <v>40</v>
-      </c>
-      <c r="I55">
-        <v>120</v>
-      </c>
-      <c r="J55" t="s">
-        <v>41</v>
-      </c>
-      <c r="K55" t="s">
-        <v>47</v>
-      </c>
-      <c r="L55" t="s">
-        <v>48</v>
-      </c>
-      <c r="M55">
-        <v>130</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A56" t="s">
-        <v>543</v>
-      </c>
-      <c r="B56" t="s">
-        <v>109</v>
-      </c>
-      <c r="C56" t="s">
-        <v>535</v>
-      </c>
-      <c r="E56" t="s">
-        <v>521</v>
-      </c>
-      <c r="F56" t="s">
-        <v>36</v>
-      </c>
-      <c r="G56">
-        <v>100</v>
-      </c>
-      <c r="H56" t="s">
-        <v>40</v>
-      </c>
-      <c r="I56">
-        <v>120</v>
-      </c>
-      <c r="J56" t="s">
-        <v>41</v>
-      </c>
-      <c r="K56" t="s">
-        <v>47</v>
-      </c>
-      <c r="L56" t="s">
-        <v>48</v>
-      </c>
-      <c r="M56">
-        <v>130</v>
-      </c>
-      <c r="N56" s="1"/>
-    </row>
-    <row r="57" spans="1:14" ht="37.5" customHeight="1">
-      <c r="A57" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1991-W</v>
-      </c>
-      <c r="B57" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57" t="s">
-        <v>517</v>
-      </c>
-      <c r="E57" t="s">
-        <v>521</v>
-      </c>
-      <c r="F57" t="s">
-        <v>58</v>
-      </c>
-      <c r="G57">
-        <v>100</v>
-      </c>
-      <c r="H57" t="s">
-        <v>40</v>
-      </c>
-      <c r="I57">
-        <v>120</v>
-      </c>
-      <c r="J57" t="s">
-        <v>41</v>
-      </c>
-      <c r="K57" t="s">
-        <v>47</v>
-      </c>
-      <c r="L57" t="s">
-        <v>48</v>
-      </c>
-      <c r="N57" s="1"/>
-    </row>
-    <row r="58" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A58" t="s">
-        <v>354</v>
-      </c>
-      <c r="B58" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" t="s">
-        <v>106</v>
-      </c>
-      <c r="E58" t="s">
-        <v>521</v>
-      </c>
-      <c r="F58" t="s">
-        <v>58</v>
-      </c>
-      <c r="G58">
-        <v>110</v>
-      </c>
-      <c r="H58" t="s">
-        <v>51</v>
-      </c>
-      <c r="I58">
-        <v>130</v>
-      </c>
-      <c r="J58" t="s">
-        <v>46</v>
-      </c>
-      <c r="K58" t="s">
-        <v>47</v>
-      </c>
-      <c r="L58" t="s">
-        <v>48</v>
-      </c>
-      <c r="M58">
-        <v>145</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="42" customHeight="1">
-      <c r="A59" t="s">
-        <v>348</v>
-      </c>
-      <c r="B59" t="s">
-        <v>109</v>
-      </c>
-      <c r="C59" t="s">
-        <v>94</v>
-      </c>
-      <c r="E59" t="s">
-        <v>521</v>
-      </c>
-      <c r="F59" t="s">
-        <v>58</v>
-      </c>
-      <c r="G59">
-        <v>120</v>
-      </c>
-      <c r="H59" t="s">
-        <v>51</v>
-      </c>
-      <c r="I59">
-        <v>120</v>
-      </c>
-      <c r="J59" t="s">
-        <v>41</v>
       </c>
       <c r="K59" t="s">
         <v>47</v>
@@ -4743,63 +4736,53 @@
       <c r="L59" t="s">
         <v>48</v>
       </c>
-      <c r="M59">
-        <v>150</v>
-      </c>
-      <c r="N59" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="N59" s="1"/>
     </row>
     <row r="60" spans="1:14" ht="36.75" customHeight="1">
       <c r="A60" t="s">
-        <v>332</v>
+        <v>525</v>
       </c>
       <c r="B60" t="s">
         <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>68</v>
+        <v>524</v>
       </c>
       <c r="E60" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F60" t="s">
-        <v>488</v>
+        <v>36</v>
       </c>
       <c r="G60">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H60" t="s">
-        <v>546</v>
+        <v>14</v>
       </c>
       <c r="I60">
-        <v>65.5</v>
+        <v>130</v>
       </c>
       <c r="J60" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="K60" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="L60" t="s">
         <v>48</v>
       </c>
-      <c r="M60">
-        <v>70</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="N60" s="1"/>
     </row>
     <row r="61" spans="1:14" ht="29.25" customHeight="1">
       <c r="A61" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B61" t="s">
         <v>109</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E61" t="s">
         <v>521</v>
@@ -4814,44 +4797,61 @@
         <v>51</v>
       </c>
       <c r="I61">
-        <v>120.5</v>
+        <v>130</v>
       </c>
       <c r="J61" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K61" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="L61" t="s">
         <v>48</v>
       </c>
       <c r="M61">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="44.25" customHeight="1">
       <c r="A62" t="s">
-        <v>541</v>
+        <v>121</v>
       </c>
       <c r="B62" t="s">
         <v>109</v>
+      </c>
+      <c r="C62" t="s">
+        <v>53</v>
       </c>
       <c r="E62" t="s">
         <v>519</v>
       </c>
       <c r="F62" t="s">
-        <v>538</v>
+        <v>520</v>
+      </c>
+      <c r="G62">
+        <v>55</v>
+      </c>
+      <c r="H62" t="s">
+        <v>526</v>
       </c>
       <c r="I62">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="J62" t="s">
-        <v>41</v>
-      </c>
-      <c r="N62" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="K62" t="s">
+        <v>32</v>
+      </c>
+      <c r="L62" t="s">
+        <v>33</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAF6DAB-FE6D-47D8-918B-AC64440267C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2901A671-D692-4456-9D86-FF4638AD5532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -2598,7 +2598,7 @@
         <v>35</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="K4" t="s">
         <v>17</v>
@@ -2636,7 +2636,7 @@
         <v>35</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
@@ -2674,7 +2674,7 @@
         <v>35</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
@@ -2712,7 +2712,7 @@
         <v>35</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="K7" t="s">
         <v>113</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2901A671-D692-4456-9D86-FF4638AD5532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A6F285-71A0-41F6-976B-B9DBA61D8B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="548">
   <si>
     <t>image_url</t>
   </si>
@@ -1971,6 +1971,9 @@
   </si>
   <si>
     <t>100 kg</t>
+  </si>
+  <si>
+    <t>40 kg</t>
   </si>
 </sst>
 </file>
@@ -2519,7 +2522,7 @@
         <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="K2" t="s">
         <v>17</v>
@@ -2557,7 +2560,7 @@
         <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="K3" t="s">
         <v>32</v>
@@ -2598,7 +2601,7 @@
         <v>35</v>
       </c>
       <c r="J4" t="s">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="K4" t="s">
         <v>17</v>
@@ -2636,7 +2639,7 @@
         <v>35</v>
       </c>
       <c r="J5" t="s">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="K5" t="s">
         <v>17</v>
@@ -2674,7 +2677,7 @@
         <v>35</v>
       </c>
       <c r="J6" t="s">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
@@ -2712,7 +2715,7 @@
         <v>35</v>
       </c>
       <c r="J7" t="s">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="K7" t="s">
         <v>113</v>
@@ -2750,7 +2753,7 @@
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
+        <v>547</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -2792,7 +2795,7 @@
         <v>40</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>547</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A6F285-71A0-41F6-976B-B9DBA61D8B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5A9A52-D86B-4AB1-B633-F8CF37E12E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="549">
   <si>
     <t>image_url</t>
   </si>
@@ -1974,6 +1974,9 @@
   </si>
   <si>
     <t>40 kg</t>
+  </si>
+  <si>
+    <t>49 kg</t>
   </si>
 </sst>
 </file>
@@ -2835,7 +2838,7 @@
         <v>40</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K10" t="s">
         <v>17</v>
@@ -2874,7 +2877,7 @@
         <v>40</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K11" t="s">
         <v>29</v>
@@ -2912,7 +2915,7 @@
         <v>40</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K12" t="s">
         <v>32</v>
@@ -2948,7 +2951,7 @@
         <v>40</v>
       </c>
       <c r="J13" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K13" t="s">
         <v>32</v>
@@ -2984,7 +2987,7 @@
         <v>40.5</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K14" t="s">
         <v>63</v>
@@ -3022,7 +3025,7 @@
         <v>41</v>
       </c>
       <c r="J15" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K15" t="s">
         <v>17</v>
@@ -3063,7 +3066,7 @@
         <v>41</v>
       </c>
       <c r="J16" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K16" t="s">
         <v>29</v>
@@ -3104,7 +3107,7 @@
         <v>45</v>
       </c>
       <c r="J17" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K17" t="s">
         <v>32</v>
@@ -3145,7 +3148,7 @@
         <v>45</v>
       </c>
       <c r="J18" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K18" t="s">
         <v>32</v>
@@ -3186,7 +3189,7 @@
         <v>45</v>
       </c>
       <c r="J19" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K19" t="s">
         <v>32</v>
@@ -3227,7 +3230,7 @@
         <v>45.5</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K20" t="s">
         <v>102</v>
@@ -3268,7 +3271,7 @@
         <v>45.5</v>
       </c>
       <c r="J21" t="s">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="K21" t="s">
         <v>32</v>
@@ -3309,7 +3312,7 @@
         <v>50</v>
       </c>
       <c r="J22" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K22" t="s">
         <v>32</v>
@@ -3350,7 +3353,7 @@
         <v>50</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K23" t="s">
         <v>32</v>
@@ -3391,7 +3394,7 @@
         <v>50</v>
       </c>
       <c r="J24" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K24" t="s">
         <v>32</v>
@@ -3429,7 +3432,7 @@
         <v>50</v>
       </c>
       <c r="J25" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K25" t="s">
         <v>32</v>
@@ -3468,7 +3471,7 @@
         <v>60</v>
       </c>
       <c r="J26" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K26" t="s">
         <v>32</v>
@@ -3505,7 +3508,7 @@
         <v>60</v>
       </c>
       <c r="J27" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K27" t="s">
         <v>491</v>
@@ -3541,7 +3544,7 @@
         <v>60</v>
       </c>
       <c r="J28" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K28" t="s">
         <v>491</v>
@@ -3577,7 +3580,7 @@
         <v>60</v>
       </c>
       <c r="J29" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K29" t="s">
         <v>491</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5A9A52-D86B-4AB1-B633-F8CF37E12E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CDE435-DEEC-4C6B-B3D1-7D290A8EA974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="549">
   <si>
     <t>image_url</t>
   </si>
@@ -2079,10 +2079,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N62" totalsRowShown="0">
-  <autoFilter ref="A1:N62" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N62">
-    <sortCondition ref="I1:I62"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N61" totalsRowShown="0">
+  <autoFilter ref="A1:N61" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N61">
+    <sortCondition ref="C1:C61"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
@@ -2437,7 +2437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -2501,301 +2501,284 @@
     </row>
     <row r="2" spans="1:14" ht="21.75" customHeight="1">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>512</v>
       </c>
       <c r="B2" t="s">
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>511</v>
       </c>
       <c r="E2" t="s">
         <v>521</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>111</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="21.75" customHeight="1">
       <c r="A3" t="s">
-        <v>357</v>
+        <v>532</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>531</v>
       </c>
       <c r="E3" t="s">
         <v>521</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G3">
+        <v>75</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3">
         <v>65</v>
       </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3">
-        <v>30</v>
-      </c>
       <c r="J3" t="s">
-        <v>547</v>
+        <v>119</v>
       </c>
       <c r="K3" t="s">
+        <v>533</v>
+      </c>
+      <c r="L3" t="s">
         <v>32</v>
       </c>
-      <c r="L3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3">
-        <v>40</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" ht="21.75" customHeight="1">
       <c r="A4" t="s">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
         <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>520</v>
       </c>
       <c r="G4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H4" t="s">
-        <v>526</v>
+        <v>14</v>
       </c>
       <c r="I4">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L4" t="s">
         <v>17</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>118</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="21.75" customHeight="1">
       <c r="A5" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
         <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>520</v>
       </c>
       <c r="G5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>526</v>
       </c>
       <c r="I5">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="J5" t="s">
-        <v>547</v>
+        <v>46</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A6" t="s">
-        <v>328</v>
+      <c r="A6" s="3" t="s">
+        <v>499</v>
       </c>
       <c r="B6" t="s">
         <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>496</v>
       </c>
       <c r="E6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I6">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="J6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="L6" t="s">
-        <v>17</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A7" t="s">
-        <v>277</v>
+      <c r="A7" s="3" t="s">
+        <v>498</v>
       </c>
       <c r="B7" t="s">
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>495</v>
       </c>
       <c r="E7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I7">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="J7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K7" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="L7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A8" t="s">
-        <v>325</v>
+      <c r="A8" s="3" t="s">
+        <v>497</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>494</v>
       </c>
       <c r="E8" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="4">
-        <v>55</v>
+        <v>36</v>
+      </c>
+      <c r="G8">
+        <v>100</v>
       </c>
       <c r="H8" t="s">
-        <v>526</v>
+        <v>40</v>
       </c>
       <c r="I8">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J8" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="L8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>45</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>61</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A9" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1137-W</v>
+      <c r="A9" t="s">
+        <v>276</v>
       </c>
       <c r="B9" t="s">
         <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>537</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
         <v>521</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="4">
+        <v>13</v>
+      </c>
+      <c r="G9">
         <v>55</v>
       </c>
       <c r="H9" t="s">
         <v>526</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J9" t="s">
         <v>547</v>
@@ -2806,50 +2789,47 @@
       <c r="L9" t="s">
         <v>17</v>
       </c>
-      <c r="M9">
-        <v>45</v>
-      </c>
-      <c r="N9" s="1"/>
+      <c r="N9" s="1" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A10" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1171-B</v>
+      <c r="A10" t="s">
+        <v>277</v>
       </c>
       <c r="B10" t="s">
         <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>516</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H10" t="s">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="I10">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K10" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="L10" t="s">
         <v>17</v>
       </c>
-      <c r="M10">
-        <v>45</v>
-      </c>
-      <c r="N10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="21.75" customHeight="1">
       <c r="A11" t="s">
@@ -2891,129 +2871,139 @@
     </row>
     <row r="12" spans="1:14" ht="21.75" customHeight="1">
       <c r="A12" t="s">
-        <v>512</v>
+        <v>279</v>
       </c>
       <c r="B12" t="s">
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>511</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
         <v>521</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>526</v>
       </c>
       <c r="I12">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J12" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K12" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="21.75" customHeight="1">
       <c r="A13" t="s">
-        <v>504</v>
+        <v>325</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>503</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>521</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
-        <v>75</v>
+        <v>58</v>
+      </c>
+      <c r="G13" s="4">
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>526</v>
       </c>
       <c r="I13">
         <v>40</v>
       </c>
       <c r="J13" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L13" t="s">
-        <v>33</v>
-      </c>
-      <c r="N13" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="M13">
+        <v>45</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A14" t="s">
-        <v>329</v>
+      <c r="A14" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1137-W</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>537</v>
       </c>
       <c r="E14" t="s">
         <v>521</v>
       </c>
       <c r="F14" t="s">
-        <v>488</v>
-      </c>
-      <c r="G14">
-        <v>70</v>
+        <v>58</v>
+      </c>
+      <c r="G14" s="4">
+        <v>55</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>526</v>
       </c>
       <c r="I14">
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="J14" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K14" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="L14" t="s">
-        <v>43</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="M14">
+        <v>45</v>
+      </c>
+      <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A15" t="s">
-        <v>355</v>
+      <c r="A15" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1171-B</v>
       </c>
       <c r="B15" t="s">
         <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>516</v>
       </c>
       <c r="E15" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G15">
         <v>60</v>
@@ -3022,7 +3012,7 @@
         <v>526</v>
       </c>
       <c r="I15">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J15" t="s">
         <v>548</v>
@@ -3034,21 +3024,19 @@
         <v>17</v>
       </c>
       <c r="M15">
-        <v>41</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="21.75" customHeight="1">
       <c r="A16" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
         <v>521</v>
@@ -3057,45 +3045,42 @@
         <v>23</v>
       </c>
       <c r="G16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="I16">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J16" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K16" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="L16" t="s">
         <v>17</v>
       </c>
-      <c r="M16">
-        <v>41</v>
-      </c>
       <c r="N16" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="21.75" customHeight="1">
       <c r="A17" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B17" t="s">
         <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
         <v>521</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G17">
         <v>65</v>
@@ -3104,74 +3089,68 @@
         <v>20</v>
       </c>
       <c r="I17">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J17" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K17" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
-      </c>
-      <c r="M17">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="21.75" customHeight="1">
       <c r="A18" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B18" t="s">
         <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
         <v>521</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>488</v>
       </c>
       <c r="G18">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I18">
-        <v>45</v>
+        <v>40.5</v>
       </c>
       <c r="J18" t="s">
         <v>548</v>
       </c>
       <c r="K18" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
-      </c>
-      <c r="M18">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="21.75" customHeight="1">
       <c r="A19" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B19" t="s">
         <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
         <v>521</v>
@@ -3180,10 +3159,10 @@
         <v>58</v>
       </c>
       <c r="G19">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I19">
         <v>45</v>
@@ -3201,48 +3180,48 @@
         <v>50</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1">
       <c r="A20" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s">
         <v>521</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G20">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H20" t="s">
-        <v>545</v>
+        <v>20</v>
       </c>
       <c r="I20">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="J20" t="s">
         <v>548</v>
       </c>
       <c r="K20" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="L20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M20">
-        <v>55.5</v>
+        <v>50</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1">
@@ -3288,13 +3267,13 @@
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1">
       <c r="A22" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B22" t="s">
         <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s">
         <v>521</v>
@@ -3309,10 +3288,10 @@
         <v>14</v>
       </c>
       <c r="I22">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J22" t="s">
-        <v>119</v>
+        <v>548</v>
       </c>
       <c r="K22" t="s">
         <v>32</v>
@@ -3321,27 +3300,27 @@
         <v>33</v>
       </c>
       <c r="M22">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1">
       <c r="A23" t="s">
-        <v>506</v>
+        <v>337</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>502</v>
+        <v>35</v>
       </c>
       <c r="E23" t="s">
         <v>521</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G23">
         <v>75</v>
@@ -3350,39 +3329,40 @@
         <v>14</v>
       </c>
       <c r="I23">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J23" t="s">
         <v>119</v>
       </c>
       <c r="K23" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="M23">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A24" t="s">
-        <v>505</v>
+      <c r="A24" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1552E-WO</v>
       </c>
       <c r="B24" t="s">
         <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>501</v>
+        <v>542</v>
       </c>
       <c r="E24" t="s">
         <v>521</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G24">
         <v>75</v>
@@ -3391,7 +3371,7 @@
         <v>14</v>
       </c>
       <c r="I24">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="J24" t="s">
         <v>119</v>
@@ -3402,19 +3382,17 @@
       <c r="L24" t="s">
         <v>33</v>
       </c>
-      <c r="M24">
-        <v>60</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="N24" s="1"/>
     </row>
     <row r="25" spans="1:14" ht="21.75" customHeight="1">
       <c r="A25" t="s">
-        <v>539</v>
+        <v>338</v>
+      </c>
+      <c r="B25" t="s">
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
         <v>521</v>
@@ -3443,23 +3421,25 @@
       <c r="M25">
         <v>60</v>
       </c>
-      <c r="N25" s="1"/>
+      <c r="N25" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="26" spans="1:14" ht="21.75" customHeight="1">
       <c r="A26" t="s">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>527</v>
+        <v>502</v>
       </c>
       <c r="E26" t="s">
         <v>521</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G26">
         <v>75</v>
@@ -3468,7 +3448,7 @@
         <v>14</v>
       </c>
       <c r="I26">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J26" t="s">
         <v>119</v>
@@ -3477,92 +3457,102 @@
         <v>32</v>
       </c>
       <c r="L26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M26">
+        <v>60</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A27" t="s">
+        <v>505</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>501</v>
+      </c>
+      <c r="E27" t="s">
+        <v>521</v>
+      </c>
+      <c r="F27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G27">
+        <v>75</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27">
+        <v>50</v>
+      </c>
+      <c r="J27" t="s">
+        <v>119</v>
+      </c>
+      <c r="K27" t="s">
         <v>32</v>
       </c>
-      <c r="N26" s="1"/>
-    </row>
-    <row r="27" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A27" t="str">
+      <c r="L27" t="s">
+        <v>33</v>
+      </c>
+      <c r="M27">
+        <v>60</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A28" t="s">
+        <v>539</v>
+      </c>
+      <c r="C28" t="s">
+        <v>534</v>
+      </c>
+      <c r="E28" t="s">
+        <v>521</v>
+      </c>
+      <c r="F28" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28">
+        <v>75</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28">
+        <v>50</v>
+      </c>
+      <c r="J28" t="s">
+        <v>119</v>
+      </c>
+      <c r="K28" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" t="s">
+        <v>33</v>
+      </c>
+      <c r="M28">
+        <v>60</v>
+      </c>
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A29" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1580-B</v>
       </c>
-      <c r="B27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
         <v>522</v>
-      </c>
-      <c r="E27" t="s">
-        <v>521</v>
-      </c>
-      <c r="F27" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27">
-        <v>75</v>
-      </c>
-      <c r="H27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27">
-        <v>60</v>
-      </c>
-      <c r="J27" t="s">
-        <v>119</v>
-      </c>
-      <c r="K27" t="s">
-        <v>491</v>
-      </c>
-      <c r="L27" t="s">
-        <v>32</v>
-      </c>
-      <c r="N27" s="1"/>
-    </row>
-    <row r="28" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" t="s">
-        <v>490</v>
-      </c>
-      <c r="E28" t="s">
-        <v>521</v>
-      </c>
-      <c r="F28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28">
-        <v>75</v>
-      </c>
-      <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28">
-        <v>60</v>
-      </c>
-      <c r="J28" t="s">
-        <v>119</v>
-      </c>
-      <c r="K28" t="s">
-        <v>491</v>
-      </c>
-      <c r="L28" t="s">
-        <v>32</v>
-      </c>
-      <c r="N28" s="1"/>
-    </row>
-    <row r="29" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B29" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" t="s">
-        <v>489</v>
       </c>
       <c r="E29" t="s">
         <v>521</v>
@@ -3591,20 +3581,20 @@
       <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A30" t="s">
-        <v>337</v>
+      <c r="A30" s="2" t="s">
+        <v>492</v>
       </c>
       <c r="B30" t="s">
         <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>490</v>
       </c>
       <c r="E30" t="s">
         <v>521</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G30">
         <v>75</v>
@@ -3613,33 +3603,28 @@
         <v>14</v>
       </c>
       <c r="I30">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J30" t="s">
         <v>119</v>
       </c>
       <c r="K30" t="s">
-        <v>37</v>
+        <v>491</v>
       </c>
       <c r="L30" t="s">
-        <v>17</v>
-      </c>
-      <c r="M30">
-        <v>70</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A31" t="s">
-        <v>532</v>
+      <c r="A31" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>531</v>
+        <v>489</v>
       </c>
       <c r="E31" t="s">
         <v>521</v>
@@ -3654,13 +3639,13 @@
         <v>14</v>
       </c>
       <c r="I31">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J31" t="s">
         <v>119</v>
       </c>
       <c r="K31" t="s">
-        <v>533</v>
+        <v>491</v>
       </c>
       <c r="L31" t="s">
         <v>32</v>
@@ -3668,98 +3653,95 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A32" t="s">
-        <v>332</v>
+      <c r="A32" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-B</v>
       </c>
       <c r="B32" t="s">
         <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>513</v>
       </c>
       <c r="E32" t="s">
         <v>521</v>
       </c>
       <c r="F32" t="s">
-        <v>488</v>
+        <v>23</v>
       </c>
       <c r="G32">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s">
         <v>545</v>
       </c>
       <c r="I32">
-        <v>65.5</v>
+        <v>100</v>
       </c>
       <c r="J32" t="s">
-        <v>119</v>
+        <v>546</v>
       </c>
       <c r="K32" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="L32" t="s">
-        <v>48</v>
-      </c>
-      <c r="M32">
-        <v>70</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" ht="21.75" customHeight="1">
       <c r="A33" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1552E-WO</v>
+        <v>images/TS1590-C</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>542</v>
+        <v>514</v>
       </c>
       <c r="E33" t="s">
         <v>521</v>
       </c>
       <c r="F33" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G33">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s">
-        <v>14</v>
+        <v>545</v>
       </c>
       <c r="I33">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J33" t="s">
-        <v>119</v>
+        <v>546</v>
       </c>
       <c r="K33" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="L33" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A34" t="s">
-        <v>339</v>
+      <c r="A34" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-G</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>515</v>
       </c>
       <c r="E34" t="s">
         <v>521</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G34">
         <v>90</v>
@@ -3768,7 +3750,7 @@
         <v>545</v>
       </c>
       <c r="I34">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J34" t="s">
         <v>546</v>
@@ -3779,22 +3761,17 @@
       <c r="L34" t="s">
         <v>43</v>
       </c>
-      <c r="M34">
-        <v>90</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="N34" s="1"/>
     </row>
     <row r="35" spans="1:14" ht="21.75" customHeight="1">
       <c r="A35" t="s">
-        <v>508</v>
+        <v>339</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>510</v>
+        <v>80</v>
       </c>
       <c r="E35" t="s">
         <v>521</v>
@@ -3829,13 +3806,13 @@
     </row>
     <row r="36" spans="1:14" ht="21.75" customHeight="1">
       <c r="A36" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B36" t="s">
         <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E36" t="s">
         <v>521</v>
@@ -3870,13 +3847,13 @@
     </row>
     <row r="37" spans="1:14" ht="21.75" customHeight="1">
       <c r="A37" t="s">
-        <v>540</v>
+        <v>507</v>
       </c>
       <c r="B37" t="s">
         <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>536</v>
+        <v>509</v>
       </c>
       <c r="E37" t="s">
         <v>521</v>
@@ -3905,55 +3882,58 @@
       <c r="M37">
         <v>90</v>
       </c>
-      <c r="N37" s="1"/>
+      <c r="N37" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="38" spans="1:14" ht="21.75" customHeight="1">
       <c r="A38" t="s">
-        <v>159</v>
+        <v>540</v>
       </c>
       <c r="B38" t="s">
         <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>536</v>
       </c>
       <c r="E38" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F38" t="s">
-        <v>520</v>
+        <v>58</v>
       </c>
       <c r="G38">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s">
-        <v>14</v>
+        <v>545</v>
       </c>
       <c r="I38">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="J38" t="s">
         <v>546</v>
       </c>
       <c r="K38" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="L38" t="s">
-        <v>17</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="M38">
+        <v>90</v>
+      </c>
+      <c r="N38" s="1"/>
     </row>
     <row r="39" spans="1:14" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>345</v>
+        <v>544</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E39" t="s">
         <v>521</v>
@@ -3962,28 +3942,28 @@
         <v>58</v>
       </c>
       <c r="G39">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s">
         <v>545</v>
       </c>
       <c r="I39">
-        <v>90</v>
+        <v>90.9</v>
       </c>
       <c r="J39" t="s">
         <v>546</v>
       </c>
       <c r="K39" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L39" t="s">
         <v>43</v>
       </c>
       <c r="M39">
-        <v>100</v>
+        <v>105.9</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="21.75" customHeight="1">
@@ -4068,21 +4048,21 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="21.75" customHeight="1">
+    <row r="42" spans="1:14" ht="26.25" customHeight="1">
       <c r="A42" t="s">
-        <v>544</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s">
         <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="E42" t="s">
         <v>521</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G42">
         <v>86</v>
@@ -4106,176 +4086,187 @@
         <v>105.9</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="26.25" customHeight="1">
       <c r="A43" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="E43" t="s">
         <v>521</v>
       </c>
       <c r="F43" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G43">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s">
         <v>545</v>
       </c>
       <c r="I43">
-        <v>90.9</v>
+        <v>90</v>
       </c>
       <c r="J43" t="s">
         <v>546</v>
       </c>
       <c r="K43" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="L43" t="s">
         <v>43</v>
       </c>
       <c r="M43">
-        <v>105.9</v>
+        <v>100</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="26.25" customHeight="1">
-      <c r="A44" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-B</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A44" t="s">
+        <v>346</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>513</v>
+        <v>92</v>
       </c>
       <c r="E44" t="s">
         <v>521</v>
       </c>
       <c r="F44" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G44">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H44" t="s">
-        <v>545</v>
+        <v>40</v>
       </c>
       <c r="I44">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J44" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K44" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L44" t="s">
-        <v>43</v>
-      </c>
-      <c r="N44" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="M44">
+        <v>130</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="45" spans="1:14" ht="27.75" customHeight="1">
-      <c r="A45" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-C</v>
+      <c r="A45" t="s">
+        <v>347</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>514</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
         <v>521</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G45">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H45" t="s">
-        <v>545</v>
+        <v>40</v>
       </c>
       <c r="I45">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J45" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K45" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L45" t="s">
-        <v>43</v>
-      </c>
-      <c r="N45" s="1"/>
-    </row>
-    <row r="46" spans="1:14" ht="27.75" customHeight="1">
-      <c r="A46" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-G</v>
+        <v>48</v>
+      </c>
+      <c r="M45">
+        <v>130</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A46" t="s">
+        <v>543</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="E46" t="s">
         <v>521</v>
       </c>
       <c r="F46" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G46">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H46" t="s">
-        <v>545</v>
+        <v>40</v>
       </c>
       <c r="I46">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J46" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K46" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L46" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="M46">
+        <v>130</v>
       </c>
       <c r="N46" s="1"/>
     </row>
-    <row r="47" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A47" s="3" t="s">
-        <v>499</v>
+    <row r="47" spans="1:14" ht="30" customHeight="1">
+      <c r="A47" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1991-W</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="E47" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F47" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G47">
         <v>100</v>
@@ -4284,10 +4275,10 @@
         <v>40</v>
       </c>
       <c r="I47">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J47" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K47" t="s">
         <v>47</v>
@@ -4298,32 +4289,32 @@
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="1:14" ht="30" customHeight="1">
-      <c r="A48" s="3" t="s">
-        <v>498</v>
+      <c r="A48" t="s">
+        <v>348</v>
       </c>
       <c r="B48" t="s">
         <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>495</v>
+        <v>94</v>
       </c>
       <c r="E48" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F48" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G48">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H48" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I48">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K48" t="s">
         <v>47</v>
@@ -4331,189 +4322,195 @@
       <c r="L48" t="s">
         <v>48</v>
       </c>
-      <c r="N48" s="1"/>
+      <c r="M48">
+        <v>150</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="49" spans="1:14" ht="30" customHeight="1">
-      <c r="A49" s="3" t="s">
-        <v>497</v>
+      <c r="A49" t="s">
+        <v>349</v>
       </c>
       <c r="B49" t="s">
         <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>494</v>
+        <v>96</v>
       </c>
       <c r="E49" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F49" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G49">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H49" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I49">
-        <v>100</v>
+        <v>120.5</v>
       </c>
       <c r="J49" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K49" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="L49" t="s">
         <v>48</v>
       </c>
-      <c r="N49" s="1"/>
-    </row>
-    <row r="50" spans="1:14" ht="30" customHeight="1">
+      <c r="M49">
+        <v>125</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="34.5" customHeight="1">
       <c r="A50" t="s">
-        <v>353</v>
+        <v>504</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>503</v>
       </c>
       <c r="E50" t="s">
         <v>521</v>
       </c>
       <c r="F50" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G50">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="I50">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="J50" t="s">
-        <v>41</v>
+        <v>548</v>
       </c>
       <c r="K50" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L50" t="s">
-        <v>43</v>
-      </c>
-      <c r="M50">
-        <v>125</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N50" s="1"/>
     </row>
     <row r="51" spans="1:14" ht="34.5" customHeight="1">
       <c r="A51" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B51" t="s">
         <v>109</v>
       </c>
       <c r="C51" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E51" t="s">
         <v>521</v>
       </c>
       <c r="F51" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G51">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="I51">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="J51" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="K51" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L51" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="N51" s="1"/>
     </row>
-    <row r="52" spans="1:14" ht="34.5" customHeight="1">
+    <row r="52" spans="1:14" ht="32.25" customHeight="1">
       <c r="A52" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s">
         <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E52" t="s">
         <v>521</v>
       </c>
       <c r="F52" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G52">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s">
-        <v>40</v>
+        <v>545</v>
       </c>
       <c r="I52">
-        <v>120</v>
+        <v>45.5</v>
       </c>
       <c r="J52" t="s">
-        <v>41</v>
+        <v>548</v>
       </c>
       <c r="K52" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="L52" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="M52">
+        <v>55.5</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A53" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS2811DS-B</v>
+      </c>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>523</v>
+      </c>
+      <c r="E53" t="s">
+        <v>519</v>
+      </c>
+      <c r="F53" t="s">
+        <v>520</v>
+      </c>
+      <c r="G53">
+        <v>75</v>
+      </c>
+      <c r="H53" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53">
         <v>130</v>
       </c>
-      <c r="N52" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A53" t="s">
-        <v>347</v>
-      </c>
-      <c r="B53" t="s">
-        <v>109</v>
-      </c>
-      <c r="C53" t="s">
-        <v>45</v>
-      </c>
-      <c r="E53" t="s">
-        <v>521</v>
-      </c>
-      <c r="F53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G53">
-        <v>100</v>
-      </c>
-      <c r="H53" t="s">
-        <v>40</v>
-      </c>
-      <c r="I53">
-        <v>120</v>
-      </c>
       <c r="J53" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K53" t="s">
         <v>47</v>
@@ -4521,40 +4518,35 @@
       <c r="L53" t="s">
         <v>48</v>
       </c>
-      <c r="M53">
-        <v>130</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="34.5" customHeight="1">
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" ht="33.75" customHeight="1">
       <c r="A54" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B54" t="s">
         <v>109</v>
       </c>
       <c r="C54" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="E54" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F54" t="s">
         <v>36</v>
       </c>
       <c r="G54">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="I54">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="J54" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K54" t="s">
         <v>47</v>
@@ -4562,33 +4554,29 @@
       <c r="L54" t="s">
         <v>48</v>
       </c>
-      <c r="M54">
-        <v>130</v>
-      </c>
       <c r="N54" s="1"/>
     </row>
     <row r="55" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A55" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1991-W</v>
+      <c r="A55" t="s">
+        <v>353</v>
       </c>
       <c r="B55" t="s">
         <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>517</v>
+        <v>50</v>
       </c>
       <c r="E55" t="s">
         <v>521</v>
       </c>
       <c r="F55" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G55">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H55" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I55">
         <v>120</v>
@@ -4597,28 +4585,33 @@
         <v>41</v>
       </c>
       <c r="K55" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L55" t="s">
-        <v>48</v>
-      </c>
-      <c r="N55" s="1"/>
-    </row>
-    <row r="56" spans="1:14" ht="33.75" customHeight="1">
+        <v>43</v>
+      </c>
+      <c r="M55">
+        <v>125</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="37.5" customHeight="1">
       <c r="A56" t="s">
-        <v>348</v>
+        <v>530</v>
       </c>
       <c r="B56" t="s">
         <v>109</v>
       </c>
       <c r="C56" t="s">
-        <v>94</v>
+        <v>529</v>
       </c>
       <c r="E56" t="s">
         <v>521</v>
       </c>
       <c r="F56" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G56">
         <v>120</v>
@@ -4633,231 +4626,197 @@
         <v>41</v>
       </c>
       <c r="K56" t="s">
+        <v>42</v>
+      </c>
+      <c r="L56" t="s">
+        <v>43</v>
+      </c>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A57" t="s">
+        <v>354</v>
+      </c>
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E57" t="s">
+        <v>521</v>
+      </c>
+      <c r="F57" t="s">
+        <v>58</v>
+      </c>
+      <c r="G57">
+        <v>110</v>
+      </c>
+      <c r="H57" t="s">
+        <v>51</v>
+      </c>
+      <c r="I57">
+        <v>130</v>
+      </c>
+      <c r="J57" t="s">
+        <v>46</v>
+      </c>
+      <c r="K57" t="s">
         <v>47</v>
       </c>
-      <c r="L56" t="s">
+      <c r="L57" t="s">
         <v>48</v>
       </c>
-      <c r="M56">
-        <v>150</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="37.5" customHeight="1">
-      <c r="A57" t="s">
-        <v>541</v>
-      </c>
-      <c r="B57" t="s">
-        <v>109</v>
-      </c>
-      <c r="E57" t="s">
-        <v>519</v>
-      </c>
-      <c r="F57" t="s">
-        <v>538</v>
-      </c>
-      <c r="I57">
-        <v>120</v>
-      </c>
-      <c r="J57" t="s">
-        <v>41</v>
-      </c>
-      <c r="N57" s="1"/>
-    </row>
-    <row r="58" spans="1:14" ht="32.25" customHeight="1">
+      <c r="M57">
+        <v>145</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="42" customHeight="1">
       <c r="A58" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B58" t="s">
         <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="E58" t="s">
         <v>521</v>
       </c>
       <c r="F58" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G58">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="H58" t="s">
-        <v>51</v>
+        <v>526</v>
       </c>
       <c r="I58">
-        <v>120.5</v>
+        <v>41</v>
       </c>
       <c r="J58" t="s">
+        <v>548</v>
+      </c>
+      <c r="K58" t="s">
+        <v>17</v>
+      </c>
+      <c r="L58" t="s">
+        <v>17</v>
+      </c>
+      <c r="M58">
         <v>41</v>
       </c>
-      <c r="K58" t="s">
-        <v>97</v>
-      </c>
-      <c r="L58" t="s">
-        <v>48</v>
-      </c>
-      <c r="M58">
-        <v>125</v>
-      </c>
       <c r="N58" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="42" customHeight="1">
-      <c r="A59" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS2811DS-B</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="36.75" customHeight="1">
+      <c r="A59" t="s">
+        <v>356</v>
       </c>
       <c r="B59" t="s">
         <v>109</v>
       </c>
       <c r="C59" t="s">
-        <v>523</v>
+        <v>28</v>
       </c>
       <c r="E59" t="s">
+        <v>521</v>
+      </c>
+      <c r="F59" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59">
+        <v>60</v>
+      </c>
+      <c r="H59" t="s">
+        <v>526</v>
+      </c>
+      <c r="I59">
+        <v>41</v>
+      </c>
+      <c r="J59" t="s">
+        <v>548</v>
+      </c>
+      <c r="K59" t="s">
+        <v>29</v>
+      </c>
+      <c r="L59" t="s">
+        <v>17</v>
+      </c>
+      <c r="M59">
+        <v>41</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="29.25" customHeight="1">
+      <c r="A60" t="s">
+        <v>357</v>
+      </c>
+      <c r="B60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" t="s">
+        <v>521</v>
+      </c>
+      <c r="F60" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60">
+        <v>65</v>
+      </c>
+      <c r="H60" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60">
+        <v>30</v>
+      </c>
+      <c r="J60" t="s">
+        <v>547</v>
+      </c>
+      <c r="K60" t="s">
+        <v>32</v>
+      </c>
+      <c r="L60" t="s">
+        <v>33</v>
+      </c>
+      <c r="M60">
+        <v>40</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="44.25" customHeight="1">
+      <c r="A61" t="s">
+        <v>541</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="E61" t="s">
         <v>519</v>
       </c>
-      <c r="F59" t="s">
-        <v>520</v>
-      </c>
-      <c r="G59">
-        <v>75</v>
-      </c>
-      <c r="H59" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59">
-        <v>130</v>
-      </c>
-      <c r="J59" t="s">
-        <v>46</v>
-      </c>
-      <c r="K59" t="s">
-        <v>47</v>
-      </c>
-      <c r="L59" t="s">
-        <v>48</v>
-      </c>
-      <c r="N59" s="1"/>
-    </row>
-    <row r="60" spans="1:14" ht="36.75" customHeight="1">
-      <c r="A60" t="s">
-        <v>525</v>
-      </c>
-      <c r="B60" t="s">
-        <v>109</v>
-      </c>
-      <c r="C60" t="s">
-        <v>524</v>
-      </c>
-      <c r="E60" t="s">
-        <v>519</v>
-      </c>
-      <c r="F60" t="s">
-        <v>36</v>
-      </c>
-      <c r="G60">
-        <v>75</v>
-      </c>
-      <c r="H60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I60">
-        <v>130</v>
-      </c>
-      <c r="J60" t="s">
-        <v>46</v>
-      </c>
-      <c r="K60" t="s">
-        <v>47</v>
-      </c>
-      <c r="L60" t="s">
-        <v>48</v>
-      </c>
-      <c r="N60" s="1"/>
-    </row>
-    <row r="61" spans="1:14" ht="29.25" customHeight="1">
-      <c r="A61" t="s">
-        <v>354</v>
-      </c>
-      <c r="B61" t="s">
-        <v>109</v>
-      </c>
-      <c r="C61" t="s">
-        <v>106</v>
-      </c>
-      <c r="E61" t="s">
-        <v>521</v>
-      </c>
       <c r="F61" t="s">
-        <v>58</v>
-      </c>
-      <c r="G61">
-        <v>110</v>
-      </c>
-      <c r="H61" t="s">
-        <v>51</v>
+        <v>538</v>
       </c>
       <c r="I61">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J61" t="s">
-        <v>46</v>
-      </c>
-      <c r="K61" t="s">
-        <v>47</v>
-      </c>
-      <c r="L61" t="s">
-        <v>48</v>
-      </c>
-      <c r="M61">
-        <v>145</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" ht="44.25" customHeight="1">
-      <c r="A62" t="s">
-        <v>121</v>
-      </c>
-      <c r="B62" t="s">
-        <v>109</v>
-      </c>
-      <c r="C62" t="s">
-        <v>53</v>
-      </c>
-      <c r="E62" t="s">
-        <v>519</v>
-      </c>
-      <c r="F62" t="s">
-        <v>520</v>
-      </c>
-      <c r="G62">
-        <v>55</v>
-      </c>
-      <c r="H62" t="s">
-        <v>526</v>
-      </c>
-      <c r="I62">
-        <v>200</v>
-      </c>
-      <c r="J62" t="s">
-        <v>46</v>
-      </c>
-      <c r="K62" t="s">
-        <v>32</v>
-      </c>
-      <c r="L62" t="s">
-        <v>33</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>56</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="N61" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CDE435-DEEC-4C6B-B3D1-7D290A8EA974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81B3E74-B059-422A-B387-46A701911CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="-90" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="552">
   <si>
     <t>image_url</t>
   </si>
@@ -1977,6 +1977,15 @@
   </si>
   <si>
     <t>49 kg</t>
+  </si>
+  <si>
+    <t>ONKRON BASIC</t>
+  </si>
+  <si>
+    <t>TS2771-ST</t>
+  </si>
+  <si>
+    <t>images/TS2771-ST</t>
   </si>
 </sst>
 </file>
@@ -2079,11 +2088,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N61" totalsRowShown="0">
-  <autoFilter ref="A1:N61" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N61">
-    <sortCondition ref="C1:C61"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N62" totalsRowShown="0">
+  <autoFilter ref="A1:N62" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -2437,13 +2443,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
     <col min="6" max="6" width="28.5703125" customWidth="1"/>
     <col min="7" max="7" width="26.140625" customWidth="1"/>
     <col min="8" max="8" width="18.85546875" customWidth="1"/>
@@ -2766,7 +2772,7 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
@@ -2804,7 +2810,7 @@
         <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -2842,7 +2848,7 @@
         <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -2880,7 +2886,7 @@
         <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -2918,7 +2924,7 @@
         <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="F13" t="s">
         <v>58</v>
@@ -2960,7 +2966,7 @@
         <v>537</v>
       </c>
       <c r="E14" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="F14" t="s">
         <v>58</v>
@@ -4387,13 +4393,13 @@
         <v>54</v>
       </c>
       <c r="G50">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H50" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I50">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J50" t="s">
         <v>548</v>
@@ -4423,16 +4429,16 @@
         <v>23</v>
       </c>
       <c r="G51">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H51" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I51">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J51" t="s">
-        <v>119</v>
+        <v>548</v>
       </c>
       <c r="K51" t="s">
         <v>32</v>
@@ -4483,58 +4489,58 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A53" t="str">
+    <row r="53" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A53" t="s">
+        <v>551</v>
+      </c>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>550</v>
+      </c>
+      <c r="E53" t="s">
+        <v>521</v>
+      </c>
+      <c r="F53" t="s">
+        <v>54</v>
+      </c>
+      <c r="G53">
+        <v>80</v>
+      </c>
+      <c r="H53" t="s">
+        <v>545</v>
+      </c>
+      <c r="I53">
+        <v>60</v>
+      </c>
+      <c r="J53" t="s">
+        <v>119</v>
+      </c>
+      <c r="K53" t="s">
+        <v>102</v>
+      </c>
+      <c r="L53" t="s">
+        <v>32</v>
+      </c>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A54" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS2811DS-B</v>
       </c>
-      <c r="B53" t="s">
-        <v>109</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
         <v>523</v>
-      </c>
-      <c r="E53" t="s">
-        <v>519</v>
-      </c>
-      <c r="F53" t="s">
-        <v>520</v>
-      </c>
-      <c r="G53">
-        <v>75</v>
-      </c>
-      <c r="H53" t="s">
-        <v>14</v>
-      </c>
-      <c r="I53">
-        <v>130</v>
-      </c>
-      <c r="J53" t="s">
-        <v>46</v>
-      </c>
-      <c r="K53" t="s">
-        <v>47</v>
-      </c>
-      <c r="L53" t="s">
-        <v>48</v>
-      </c>
-      <c r="N53" s="1"/>
-    </row>
-    <row r="54" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A54" t="s">
-        <v>525</v>
-      </c>
-      <c r="B54" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" t="s">
-        <v>524</v>
       </c>
       <c r="E54" t="s">
         <v>519</v>
       </c>
       <c r="F54" t="s">
-        <v>36</v>
+        <v>520</v>
       </c>
       <c r="G54">
         <v>75</v>
@@ -4558,54 +4564,49 @@
     </row>
     <row r="55" spans="1:14" ht="33.75" customHeight="1">
       <c r="A55" t="s">
-        <v>353</v>
+        <v>525</v>
       </c>
       <c r="B55" t="s">
         <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>50</v>
+        <v>524</v>
       </c>
       <c r="E55" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F55" t="s">
         <v>36</v>
       </c>
       <c r="G55">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="I55">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="J55" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K55" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L55" t="s">
-        <v>43</v>
-      </c>
-      <c r="M55">
-        <v>125</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="37.5" customHeight="1">
+        <v>48</v>
+      </c>
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" spans="1:14" ht="33.75" customHeight="1">
       <c r="A56" t="s">
-        <v>530</v>
+        <v>353</v>
       </c>
       <c r="B56" t="s">
         <v>109</v>
       </c>
       <c r="C56" t="s">
-        <v>529</v>
+        <v>50</v>
       </c>
       <c r="E56" t="s">
         <v>521</v>
@@ -4631,99 +4632,99 @@
       <c r="L56" t="s">
         <v>43</v>
       </c>
-      <c r="N56" s="1"/>
-    </row>
-    <row r="57" spans="1:14" ht="32.25" customHeight="1">
+      <c r="M56">
+        <v>125</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="37.5" customHeight="1">
       <c r="A57" t="s">
-        <v>354</v>
+        <v>530</v>
       </c>
       <c r="B57" t="s">
         <v>109</v>
       </c>
       <c r="C57" t="s">
-        <v>106</v>
+        <v>529</v>
       </c>
       <c r="E57" t="s">
         <v>521</v>
       </c>
       <c r="F57" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G57">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H57" t="s">
         <v>51</v>
       </c>
       <c r="I57">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J57" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K57" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L57" t="s">
-        <v>48</v>
-      </c>
-      <c r="M57">
-        <v>145</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="42" customHeight="1">
+        <v>43</v>
+      </c>
+      <c r="N57" s="1"/>
+    </row>
+    <row r="58" spans="1:14" ht="32.25" customHeight="1">
       <c r="A58" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B58" t="s">
         <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="E58" t="s">
         <v>521</v>
       </c>
       <c r="F58" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G58">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="H58" t="s">
-        <v>526</v>
+        <v>51</v>
       </c>
       <c r="I58">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="J58" t="s">
-        <v>548</v>
+        <v>46</v>
       </c>
       <c r="K58" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="L58" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="M58">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="36.75" customHeight="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="42" customHeight="1">
       <c r="A59" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B59" t="s">
         <v>109</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E59" t="s">
         <v>521</v>
@@ -4744,7 +4745,7 @@
         <v>548</v>
       </c>
       <c r="K59" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="L59" t="s">
         <v>17</v>
@@ -4753,18 +4754,18 @@
         <v>41</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" ht="29.25" customHeight="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="36.75" customHeight="1">
       <c r="A60" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B60" t="s">
         <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E60" t="s">
         <v>521</v>
@@ -4773,50 +4774,91 @@
         <v>23</v>
       </c>
       <c r="G60">
+        <v>60</v>
+      </c>
+      <c r="H60" t="s">
+        <v>526</v>
+      </c>
+      <c r="I60">
+        <v>41</v>
+      </c>
+      <c r="J60" t="s">
+        <v>548</v>
+      </c>
+      <c r="K60" t="s">
+        <v>29</v>
+      </c>
+      <c r="L60" t="s">
+        <v>17</v>
+      </c>
+      <c r="M60">
+        <v>41</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="29.25" customHeight="1">
+      <c r="A61" t="s">
+        <v>357</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" t="s">
+        <v>521</v>
+      </c>
+      <c r="F61" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61">
         <v>65</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H61" t="s">
         <v>20</v>
       </c>
-      <c r="I60">
+      <c r="I61">
         <v>30</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J61" t="s">
         <v>547</v>
       </c>
-      <c r="K60" t="s">
+      <c r="K61" t="s">
         <v>32</v>
       </c>
-      <c r="L60" t="s">
+      <c r="L61" t="s">
         <v>33</v>
       </c>
-      <c r="M60">
+      <c r="M61">
         <v>40</v>
       </c>
-      <c r="N60" s="1" t="s">
+      <c r="N61" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="44.25" customHeight="1">
-      <c r="A61" t="s">
+    <row r="62" spans="1:14" ht="44.25" customHeight="1">
+      <c r="A62" t="s">
         <v>541</v>
       </c>
-      <c r="B61" t="s">
-        <v>109</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="B62" t="s">
+        <v>109</v>
+      </c>
+      <c r="E62" t="s">
         <v>519</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F62" t="s">
         <v>538</v>
       </c>
-      <c r="I61">
+      <c r="I62">
         <v>120</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J62" t="s">
         <v>41</v>
       </c>
-      <c r="N61" s="1"/>
+      <c r="N62" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81B3E74-B059-422A-B387-46A701911CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E99795-D0E1-4617-ADA7-499FC089F628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="556">
   <si>
     <t>image_url</t>
   </si>
@@ -1986,6 +1986,18 @@
   </si>
   <si>
     <t>images/TS2771-ST</t>
+  </si>
+  <si>
+    <t>50 kg</t>
+  </si>
+  <si>
+    <t>motorised interior</t>
+  </si>
+  <si>
+    <t>PR6530E-B</t>
+  </si>
+  <si>
+    <t>images/PR6530E-B</t>
   </si>
 </sst>
 </file>
@@ -2088,8 +2100,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N62" totalsRowShown="0">
-  <autoFilter ref="A1:N62" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N63" totalsRowShown="0">
+  <autoFilter ref="A1:N63" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N62">
+    <sortCondition ref="C1:C62"/>
+  </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -2443,7 +2458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252C29AA-C21A-42CF-8776-7C160F6BD0D1}">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -2555,7 +2570,7 @@
         <v>521</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>553</v>
       </c>
       <c r="G3">
         <v>75</v>
@@ -3247,16 +3262,16 @@
         <v>58</v>
       </c>
       <c r="G21">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s">
         <v>14</v>
       </c>
       <c r="I21">
-        <v>45.5</v>
+        <v>70</v>
       </c>
       <c r="J21" t="s">
-        <v>548</v>
+        <v>119</v>
       </c>
       <c r="K21" t="s">
         <v>32</v>
@@ -3294,10 +3309,10 @@
         <v>14</v>
       </c>
       <c r="I22">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="J22" t="s">
-        <v>548</v>
+        <v>119</v>
       </c>
       <c r="K22" t="s">
         <v>32</v>
@@ -3368,7 +3383,7 @@
         <v>521</v>
       </c>
       <c r="F24" t="s">
-        <v>36</v>
+        <v>553</v>
       </c>
       <c r="G24">
         <v>75</v>
@@ -4398,11 +4413,11 @@
       <c r="H50" t="s">
         <v>20</v>
       </c>
-      <c r="I50">
-        <v>45</v>
-      </c>
-      <c r="J50" t="s">
-        <v>548</v>
+      <c r="I50" s="4">
+        <v>50</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>552</v>
       </c>
       <c r="K50" t="s">
         <v>32</v>
@@ -4470,11 +4485,11 @@
       <c r="H52" t="s">
         <v>545</v>
       </c>
-      <c r="I52">
-        <v>45.5</v>
-      </c>
-      <c r="J52" t="s">
-        <v>548</v>
+      <c r="I52" s="4">
+        <v>75</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>546</v>
       </c>
       <c r="K52" t="s">
         <v>102</v>
@@ -4511,11 +4526,11 @@
       <c r="H53" t="s">
         <v>545</v>
       </c>
-      <c r="I53">
-        <v>60</v>
-      </c>
-      <c r="J53" t="s">
-        <v>119</v>
+      <c r="I53" s="4">
+        <v>75</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>546</v>
       </c>
       <c r="K53" t="s">
         <v>102</v>
@@ -4653,7 +4668,7 @@
         <v>521</v>
       </c>
       <c r="F57" t="s">
-        <v>36</v>
+        <v>553</v>
       </c>
       <c r="G57">
         <v>120</v>
@@ -4859,6 +4874,42 @@
         <v>41</v>
       </c>
       <c r="N62" s="1"/>
+    </row>
+    <row r="63" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A63" t="s">
+        <v>555</v>
+      </c>
+      <c r="B63" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" t="s">
+        <v>554</v>
+      </c>
+      <c r="E63" t="s">
+        <v>519</v>
+      </c>
+      <c r="F63" t="s">
+        <v>36</v>
+      </c>
+      <c r="G63">
+        <v>76</v>
+      </c>
+      <c r="H63" t="s">
+        <v>545</v>
+      </c>
+      <c r="I63">
+        <v>100</v>
+      </c>
+      <c r="J63" t="s">
+        <v>546</v>
+      </c>
+      <c r="K63" t="s">
+        <v>81</v>
+      </c>
+      <c r="L63" t="s">
+        <v>43</v>
+      </c>
+      <c r="N63" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E99795-D0E1-4617-ADA7-499FC089F628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A022AD-A28D-4B64-92FB-641009CCA0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="555">
   <si>
     <t>image_url</t>
   </si>
@@ -1977,9 +1977,6 @@
   </si>
   <si>
     <t>49 kg</t>
-  </si>
-  <si>
-    <t>ONKRON BASIC</t>
   </si>
   <si>
     <t>TS2771-ST</t>
@@ -2102,9 +2099,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N63" totalsRowShown="0">
   <autoFilter ref="A1:N63" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N62">
-    <sortCondition ref="C1:C62"/>
-  </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -2570,7 +2564,7 @@
         <v>521</v>
       </c>
       <c r="F3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G3">
         <v>75</v>
@@ -2787,7 +2781,7 @@
         <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
@@ -2825,7 +2819,7 @@
         <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -2863,7 +2857,7 @@
         <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -2901,7 +2895,7 @@
         <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -2939,7 +2933,7 @@
         <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="F13" t="s">
         <v>58</v>
@@ -2981,7 +2975,7 @@
         <v>537</v>
       </c>
       <c r="E14" t="s">
-        <v>549</v>
+        <v>521</v>
       </c>
       <c r="F14" t="s">
         <v>58</v>
@@ -3383,7 +3377,7 @@
         <v>521</v>
       </c>
       <c r="F24" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G24">
         <v>75</v>
@@ -4417,7 +4411,7 @@
         <v>50</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K50" t="s">
         <v>32</v>
@@ -4506,13 +4500,13 @@
     </row>
     <row r="53" spans="1:14" ht="32.25" customHeight="1">
       <c r="A53" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B53" t="s">
         <v>109</v>
       </c>
       <c r="C53" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E53" t="s">
         <v>521</v>
@@ -4668,7 +4662,7 @@
         <v>521</v>
       </c>
       <c r="F57" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G57">
         <v>120</v>
@@ -4877,13 +4871,13 @@
     </row>
     <row r="63" spans="1:14" ht="34.5" customHeight="1">
       <c r="A63" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B63" t="s">
         <v>109</v>
       </c>
       <c r="C63" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E63" t="s">
         <v>519</v>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A022AD-A28D-4B64-92FB-641009CCA0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6328D4DB-12E2-4ADB-A688-374A1CE1619A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="2625" yWindow="-16035" windowWidth="21600" windowHeight="14595" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="551">
   <si>
     <t>image_url</t>
   </si>
@@ -1910,9 +1910,6 @@
     <t>images/TS2811DS-B</t>
   </si>
   <si>
-    <t>17"-60"</t>
-  </si>
-  <si>
     <t>TS2551-ST</t>
   </si>
   <si>
@@ -1967,27 +1964,12 @@
     <t>images/TS1881-B_V2</t>
   </si>
   <si>
-    <t>50"-90"</t>
-  </si>
-  <si>
-    <t>100 kg</t>
-  </si>
-  <si>
-    <t>40 kg</t>
-  </si>
-  <si>
-    <t>49 kg</t>
-  </si>
-  <si>
     <t>TS2771-ST</t>
   </si>
   <si>
     <t>images/TS2771-ST</t>
   </si>
   <si>
-    <t>50 kg</t>
-  </si>
-  <si>
     <t>motorised interior</t>
   </si>
   <si>
@@ -1995,6 +1977,12 @@
   </si>
   <si>
     <t>images/PR6530E-B</t>
+  </si>
+  <si>
+    <t>30 kg</t>
+  </si>
+  <si>
+    <t>43"-75"</t>
   </si>
 </sst>
 </file>
@@ -2099,6 +2087,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N63" totalsRowShown="0">
   <autoFilter ref="A1:N63" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N63">
+    <sortCondition ref="G1:G63"/>
+  </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
     <tableColumn id="13" xr3:uid="{8D23DBDF-9583-4A0F-869D-D326F7A5AAA2}" name="Domain"/>
@@ -2516,481 +2507,499 @@
     </row>
     <row r="2" spans="1:14" ht="21.75" customHeight="1">
       <c r="A2" t="s">
-        <v>512</v>
+        <v>276</v>
       </c>
       <c r="B2" t="s">
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>511</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>521</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
         <v>20</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="3" spans="1:14" ht="21.75" customHeight="1">
       <c r="A3" t="s">
-        <v>532</v>
+        <v>279</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>531</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
         <v>521</v>
       </c>
       <c r="F3" t="s">
-        <v>552</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I3">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="J3" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>533</v>
+        <v>17</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="4" spans="1:14" ht="21.75" customHeight="1">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>325</v>
       </c>
       <c r="B4" t="s">
         <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F4" t="s">
-        <v>520</v>
-      </c>
-      <c r="G4">
-        <v>70</v>
+        <v>58</v>
+      </c>
+      <c r="G4" s="4">
+        <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I4">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="J4" t="s">
-        <v>546</v>
+        <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" t="s">
         <v>17</v>
       </c>
+      <c r="M4">
+        <v>45</v>
+      </c>
       <c r="N4" s="1" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A5" t="s">
+      <c r="A5" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1137-W</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>536</v>
+      </c>
+      <c r="E5" t="s">
+        <v>521</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="4">
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5">
+        <v>45</v>
+      </c>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A6" t="s">
         <v>121</v>
       </c>
-      <c r="B5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
         <v>53</v>
-      </c>
-      <c r="E5" t="s">
-        <v>519</v>
-      </c>
-      <c r="F5" t="s">
-        <v>520</v>
-      </c>
-      <c r="G5">
-        <v>55</v>
-      </c>
-      <c r="H5" t="s">
-        <v>526</v>
-      </c>
-      <c r="I5">
-        <v>200</v>
-      </c>
-      <c r="J5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="B6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" t="s">
-        <v>496</v>
       </c>
       <c r="E6" t="s">
         <v>519</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>520</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J6" t="s">
-        <v>546</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N6" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>498</v>
+      <c r="A7" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1171-B</v>
       </c>
       <c r="B7" t="s">
         <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="E7" t="s">
         <v>519</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7">
         <v>40</v>
       </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
       <c r="J7" t="s">
-        <v>546</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>48</v>
+        <v>17</v>
+      </c>
+      <c r="M7">
+        <v>45</v>
       </c>
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>497</v>
+      <c r="A8" t="s">
+        <v>355</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>494</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="J8" t="s">
-        <v>546</v>
+        <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="L8" t="s">
-        <v>48</v>
-      </c>
-      <c r="N8" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="M8">
+        <v>41</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" spans="1:14" ht="21.75" customHeight="1">
       <c r="A9" t="s">
-        <v>276</v>
+        <v>356</v>
       </c>
       <c r="B9" t="s">
         <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
         <v>521</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="I9">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="J9" t="s">
-        <v>547</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L9" t="s">
         <v>17</v>
       </c>
+      <c r="M9">
+        <v>41</v>
+      </c>
       <c r="N9" s="1" t="s">
-        <v>111</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="21.75" customHeight="1">
       <c r="A10" t="s">
-        <v>277</v>
+        <v>527</v>
       </c>
       <c r="B10" t="s">
         <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>526</v>
       </c>
       <c r="E10" t="s">
         <v>521</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
         <v>20</v>
       </c>
       <c r="I10">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J10" t="s">
-        <v>547</v>
+        <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="L10" t="s">
-        <v>17</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="21.75" customHeight="1">
       <c r="A11" t="s">
-        <v>278</v>
+        <v>504</v>
       </c>
       <c r="B11" t="s">
         <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>503</v>
       </c>
       <c r="E11" t="s">
         <v>521</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="G11">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="I11" s="4">
+        <v>50</v>
       </c>
       <c r="J11" t="s">
-        <v>548</v>
+        <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L11" t="s">
-        <v>17</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" ht="21.75" customHeight="1">
       <c r="A12" t="s">
-        <v>279</v>
+        <v>357</v>
       </c>
       <c r="B12" t="s">
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
         <v>521</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G12">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H12" t="s">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="I12">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J12" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K12" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L12" t="s">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="M12">
+        <v>40</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="21.75" customHeight="1">
       <c r="A13" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
         <v>521</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="4">
-        <v>55</v>
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>65</v>
       </c>
       <c r="H13" t="s">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="I13">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J13" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K13" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="L13" t="s">
         <v>17</v>
       </c>
-      <c r="M13">
-        <v>45</v>
-      </c>
       <c r="N13" s="1" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A14" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1137-W</v>
+      <c r="A14" t="s">
+        <v>327</v>
       </c>
       <c r="B14" t="s">
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>537</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
         <v>521</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="4">
-        <v>55</v>
+        <v>23</v>
+      </c>
+      <c r="G14">
+        <v>65</v>
       </c>
       <c r="H14" t="s">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="I14">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J14" t="s">
-        <v>547</v>
+        <v>15</v>
       </c>
       <c r="K14" t="s">
         <v>17</v>
@@ -2998,39 +3007,37 @@
       <c r="L14" t="s">
         <v>17</v>
       </c>
-      <c r="M14">
-        <v>45</v>
-      </c>
-      <c r="N14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A15" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1171-B</v>
+      <c r="A15" t="s">
+        <v>328</v>
       </c>
       <c r="B15" t="s">
         <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>516</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H15" t="s">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="I15">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J15" t="s">
-        <v>548</v>
+        <v>15</v>
       </c>
       <c r="K15" t="s">
         <v>17</v>
@@ -3038,20 +3045,19 @@
       <c r="L15" t="s">
         <v>17</v>
       </c>
-      <c r="M15">
-        <v>45</v>
-      </c>
-      <c r="N15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="21.75" customHeight="1">
       <c r="A16" t="s">
-        <v>327</v>
+        <v>512</v>
       </c>
       <c r="B16" t="s">
         <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>511</v>
       </c>
       <c r="E16" t="s">
         <v>521</v>
@@ -3066,36 +3072,34 @@
         <v>20</v>
       </c>
       <c r="I16">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J16" t="s">
-        <v>547</v>
+        <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L16" t="s">
-        <v>17</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" ht="21.75" customHeight="1">
       <c r="A17" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B17" t="s">
         <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
         <v>521</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G17">
         <v>65</v>
@@ -3104,74 +3108,80 @@
         <v>20</v>
       </c>
       <c r="I17">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J17" t="s">
-        <v>547</v>
+        <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L17" t="s">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="M17">
+        <v>50</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="21.75" customHeight="1">
       <c r="A18" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B18" t="s">
         <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
         <v>521</v>
       </c>
       <c r="F18" t="s">
-        <v>488</v>
+        <v>58</v>
       </c>
       <c r="G18">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I18">
-        <v>40.5</v>
+        <v>45</v>
       </c>
       <c r="J18" t="s">
-        <v>548</v>
+        <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="L18" t="s">
-        <v>43</v>
+        <v>33</v>
+      </c>
+      <c r="M18">
+        <v>50</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="21.75" customHeight="1">
       <c r="A19" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B19" t="s">
         <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>520</v>
       </c>
       <c r="G19">
         <v>65</v>
@@ -3180,39 +3190,39 @@
         <v>20</v>
       </c>
       <c r="I19">
-        <v>45</v>
+        <v>90.9</v>
       </c>
       <c r="J19" t="s">
-        <v>548</v>
+        <v>41</v>
       </c>
       <c r="K19" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L19" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M19">
-        <v>50</v>
+        <v>105.9</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1">
       <c r="A20" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>520</v>
       </c>
       <c r="G20">
         <v>65</v>
@@ -3221,175 +3231,165 @@
         <v>20</v>
       </c>
       <c r="I20">
-        <v>45</v>
+        <v>90.9</v>
       </c>
       <c r="J20" t="s">
-        <v>548</v>
+        <v>41</v>
       </c>
       <c r="K20" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M20">
-        <v>50</v>
+        <v>105.9</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1">
       <c r="A21" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B21" t="s">
         <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s">
         <v>521</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>488</v>
       </c>
       <c r="G21">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H21" t="s">
-        <v>14</v>
+        <v>550</v>
       </c>
       <c r="I21">
-        <v>70</v>
+        <v>40.5</v>
       </c>
       <c r="J21" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="L21" t="s">
-        <v>33</v>
-      </c>
-      <c r="M21">
-        <v>55.5</v>
+        <v>43</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1">
       <c r="A22" t="s">
-        <v>334</v>
+        <v>159</v>
       </c>
       <c r="B22" t="s">
         <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>520</v>
       </c>
       <c r="G22">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
+        <v>550</v>
       </c>
       <c r="I22">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="J22" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="K22" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="L22" t="s">
-        <v>33</v>
-      </c>
-      <c r="M22">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1">
       <c r="A23" t="s">
-        <v>337</v>
+        <v>278</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="E23" t="s">
         <v>521</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G23">
         <v>75</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
+        <v>550</v>
       </c>
       <c r="I23">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J23" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L23" t="s">
         <v>17</v>
       </c>
-      <c r="M23">
-        <v>70</v>
-      </c>
       <c r="N23" s="1" t="s">
-        <v>38</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A24" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1552E-WO</v>
+      <c r="A24" t="s">
+        <v>338</v>
       </c>
       <c r="B24" t="s">
         <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>542</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s">
         <v>521</v>
       </c>
       <c r="F24" t="s">
-        <v>552</v>
+        <v>58</v>
       </c>
       <c r="G24">
         <v>75</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
+        <v>550</v>
       </c>
       <c r="I24">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="J24" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K24" t="s">
         <v>32</v>
@@ -3397,17 +3397,22 @@
       <c r="L24" t="s">
         <v>33</v>
       </c>
-      <c r="N24" s="1"/>
+      <c r="M24">
+        <v>60</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="25" spans="1:14" ht="21.75" customHeight="1">
       <c r="A25" t="s">
-        <v>338</v>
+        <v>506</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>502</v>
       </c>
       <c r="E25" t="s">
         <v>521</v>
@@ -3419,13 +3424,13 @@
         <v>75</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
+        <v>550</v>
       </c>
       <c r="I25">
         <v>50</v>
       </c>
       <c r="J25" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K25" t="s">
         <v>32</v>
@@ -3442,13 +3447,13 @@
     </row>
     <row r="26" spans="1:14" ht="21.75" customHeight="1">
       <c r="A26" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E26" t="s">
         <v>521</v>
@@ -3460,13 +3465,13 @@
         <v>75</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
+        <v>550</v>
       </c>
       <c r="I26">
         <v>50</v>
       </c>
       <c r="J26" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K26" t="s">
         <v>32</v>
@@ -3483,13 +3488,10 @@
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1">
       <c r="A27" t="s">
-        <v>505</v>
-      </c>
-      <c r="B27" t="s">
-        <v>109</v>
+        <v>538</v>
       </c>
       <c r="C27" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="E27" t="s">
         <v>521</v>
@@ -3501,13 +3503,13 @@
         <v>75</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
+        <v>550</v>
       </c>
       <c r="I27">
         <v>50</v>
       </c>
       <c r="J27" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K27" t="s">
         <v>32</v>
@@ -3518,56 +3520,54 @@
       <c r="M27">
         <v>60</v>
       </c>
-      <c r="N27" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A28" t="s">
-        <v>539</v>
+      <c r="A28" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1580-B</v>
+      </c>
+      <c r="B28" t="s">
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="E28" t="s">
         <v>521</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G28">
         <v>75</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
+        <v>550</v>
       </c>
       <c r="I28">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J28" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K28" t="s">
+        <v>491</v>
+      </c>
+      <c r="L28" t="s">
         <v>32</v>
       </c>
-      <c r="L28" t="s">
-        <v>33</v>
-      </c>
-      <c r="M28">
-        <v>60</v>
-      </c>
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A29" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1580-B</v>
+      <c r="A29" s="2" t="s">
+        <v>492</v>
       </c>
       <c r="B29" t="s">
         <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>522</v>
+        <v>490</v>
       </c>
       <c r="E29" t="s">
         <v>521</v>
@@ -3579,13 +3579,13 @@
         <v>75</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
+        <v>550</v>
       </c>
       <c r="I29">
         <v>60</v>
       </c>
       <c r="J29" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K29" t="s">
         <v>491</v>
@@ -3597,13 +3597,13 @@
     </row>
     <row r="30" spans="1:14" ht="21.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B30" t="s">
         <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E30" t="s">
         <v>521</v>
@@ -3615,13 +3615,13 @@
         <v>75</v>
       </c>
       <c r="H30" t="s">
-        <v>14</v>
+        <v>550</v>
       </c>
       <c r="I30">
         <v>60</v>
       </c>
       <c r="J30" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K30" t="s">
         <v>491</v>
@@ -3632,35 +3632,35 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>493</v>
+      <c r="A31" t="s">
+        <v>531</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="E31" t="s">
         <v>521</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>546</v>
       </c>
       <c r="G31">
         <v>75</v>
       </c>
       <c r="H31" t="s">
-        <v>14</v>
+        <v>550</v>
       </c>
       <c r="I31">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J31" t="s">
         <v>119</v>
       </c>
       <c r="K31" t="s">
-        <v>491</v>
+        <v>532</v>
       </c>
       <c r="L31" t="s">
         <v>32</v>
@@ -3668,125 +3668,133 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A32" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-B</v>
+      <c r="A32" t="s">
+        <v>337</v>
       </c>
       <c r="B32" t="s">
         <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>513</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
         <v>521</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G32">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H32" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="J32" t="s">
-        <v>546</v>
+        <v>119</v>
       </c>
       <c r="K32" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="L32" t="s">
-        <v>43</v>
-      </c>
-      <c r="N32" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="M32">
+        <v>70</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="33" spans="1:14" ht="21.75" customHeight="1">
       <c r="A33" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-C</v>
+        <v>images/TS1552E-WO</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>514</v>
+        <v>541</v>
       </c>
       <c r="E33" t="s">
         <v>521</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>546</v>
       </c>
       <c r="G33">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H33" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="J33" t="s">
-        <v>546</v>
+        <v>119</v>
       </c>
       <c r="K33" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="L33" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A34" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-G</v>
+      <c r="A34" t="s">
+        <v>333</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>515</v>
+        <v>71</v>
       </c>
       <c r="E34" t="s">
         <v>521</v>
       </c>
       <c r="F34" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G34">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J34" t="s">
-        <v>546</v>
+        <v>119</v>
       </c>
       <c r="K34" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="L34" t="s">
-        <v>43</v>
-      </c>
-      <c r="N34" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="M34">
+        <v>55.5</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="35" spans="1:14" ht="21.75" customHeight="1">
       <c r="A35" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E35" t="s">
         <v>521</v>
@@ -3795,139 +3803,130 @@
         <v>58</v>
       </c>
       <c r="G35">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H35" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="I35">
+        <v>70</v>
+      </c>
+      <c r="J35" t="s">
+        <v>119</v>
+      </c>
+      <c r="K35" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" t="s">
+        <v>33</v>
+      </c>
+      <c r="M35">
+        <v>50</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A36" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS2811DS-B</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>523</v>
+      </c>
+      <c r="E36" t="s">
+        <v>519</v>
+      </c>
+      <c r="F36" t="s">
+        <v>520</v>
+      </c>
+      <c r="G36">
         <v>75</v>
       </c>
-      <c r="J35" t="s">
-        <v>546</v>
-      </c>
-      <c r="K35" t="s">
-        <v>81</v>
-      </c>
-      <c r="L35" t="s">
-        <v>43</v>
-      </c>
-      <c r="M35">
-        <v>90</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A36" t="s">
-        <v>508</v>
-      </c>
-      <c r="B36" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36" t="s">
-        <v>510</v>
-      </c>
-      <c r="E36" t="s">
-        <v>521</v>
-      </c>
-      <c r="F36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G36">
-        <v>90</v>
-      </c>
       <c r="H36" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="I36">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="J36" t="s">
-        <v>546</v>
+        <v>46</v>
       </c>
       <c r="K36" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L36" t="s">
-        <v>43</v>
-      </c>
-      <c r="M36">
-        <v>90</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>82</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="N36" s="1"/>
     </row>
     <row r="37" spans="1:14" ht="21.75" customHeight="1">
       <c r="A37" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="B37" t="s">
         <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="E37" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G37">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H37" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="I37">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="J37" t="s">
-        <v>546</v>
+        <v>46</v>
       </c>
       <c r="K37" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L37" t="s">
-        <v>43</v>
-      </c>
-      <c r="M37">
-        <v>90</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>82</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="N37" s="1"/>
     </row>
     <row r="38" spans="1:14" ht="21.75" customHeight="1">
       <c r="A38" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B38" t="s">
         <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="E38" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F38" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G38">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s">
-        <v>545</v>
+        <v>40</v>
       </c>
       <c r="I38">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J38" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K38" t="s">
         <v>81</v>
@@ -3935,120 +3934,112 @@
       <c r="L38" t="s">
         <v>43</v>
       </c>
-      <c r="M38">
-        <v>90</v>
-      </c>
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="1:14" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>544</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="E39" t="s">
         <v>521</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G39">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s">
-        <v>545</v>
-      </c>
-      <c r="I39">
-        <v>90.9</v>
+        <v>40</v>
+      </c>
+      <c r="I39" s="4">
+        <v>75</v>
       </c>
       <c r="J39" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K39" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="L39" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="M39">
-        <v>105.9</v>
+        <v>55.5</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="21.75" customHeight="1">
       <c r="A40" t="s">
-        <v>342</v>
+        <v>545</v>
       </c>
       <c r="B40" t="s">
         <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>544</v>
       </c>
       <c r="E40" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F40" t="s">
-        <v>520</v>
+        <v>54</v>
       </c>
       <c r="G40">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>20</v>
-      </c>
-      <c r="I40">
-        <v>90.9</v>
+        <v>40</v>
+      </c>
+      <c r="I40" s="4">
+        <v>75</v>
       </c>
       <c r="J40" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K40" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="L40" t="s">
-        <v>43</v>
-      </c>
-      <c r="M40">
-        <v>105.9</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>87</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N40" s="1"/>
     </row>
     <row r="41" spans="1:14" ht="21.75" customHeight="1">
       <c r="A41" t="s">
-        <v>343</v>
+        <v>543</v>
       </c>
       <c r="B41" t="s">
         <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F41" t="s">
-        <v>520</v>
+        <v>58</v>
       </c>
       <c r="G41">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I41">
         <v>90.9</v>
       </c>
       <c r="J41" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K41" t="s">
         <v>42</v>
@@ -4060,7 +4051,7 @@
         <v>105.9</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="26.25" customHeight="1">
@@ -4083,13 +4074,13 @@
         <v>86</v>
       </c>
       <c r="H42" t="s">
-        <v>545</v>
+        <v>40</v>
       </c>
       <c r="I42">
         <v>90.9</v>
       </c>
       <c r="J42" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K42" t="s">
         <v>42</v>
@@ -4106,13 +4097,13 @@
     </row>
     <row r="43" spans="1:14" ht="26.25" customHeight="1">
       <c r="A43" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E43" t="s">
         <v>521</v>
@@ -4124,13 +4115,13 @@
         <v>90</v>
       </c>
       <c r="H43" t="s">
-        <v>545</v>
+        <v>40</v>
       </c>
       <c r="I43">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="J43" t="s">
-        <v>546</v>
+        <v>41</v>
       </c>
       <c r="K43" t="s">
         <v>81</v>
@@ -4139,21 +4130,21 @@
         <v>43</v>
       </c>
       <c r="M43">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="27.75" customHeight="1">
       <c r="A44" t="s">
-        <v>346</v>
+        <v>508</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>510</v>
       </c>
       <c r="E44" t="s">
         <v>521</v>
@@ -4162,74 +4153,74 @@
         <v>58</v>
       </c>
       <c r="G44">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s">
         <v>40</v>
       </c>
       <c r="I44">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="J44" t="s">
         <v>41</v>
       </c>
       <c r="K44" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L44" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M44">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="27.75" customHeight="1">
       <c r="A45" t="s">
-        <v>347</v>
+        <v>507</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>509</v>
       </c>
       <c r="E45" t="s">
         <v>521</v>
       </c>
       <c r="F45" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G45">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s">
         <v>40</v>
       </c>
       <c r="I45">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="J45" t="s">
         <v>41</v>
       </c>
       <c r="K45" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L45" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M45">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="32.25" customHeight="1">
       <c r="A46" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
@@ -4241,434 +4232,434 @@
         <v>521</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G46">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s">
         <v>40</v>
       </c>
       <c r="I46">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="J46" t="s">
         <v>41</v>
       </c>
       <c r="K46" t="s">
+        <v>81</v>
+      </c>
+      <c r="L46" t="s">
+        <v>43</v>
+      </c>
+      <c r="M46">
+        <v>90</v>
+      </c>
+      <c r="N46" s="1"/>
+    </row>
+    <row r="47" spans="1:14" ht="30" customHeight="1">
+      <c r="A47" t="s">
+        <v>345</v>
+      </c>
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" t="s">
+        <v>521</v>
+      </c>
+      <c r="F47" t="s">
+        <v>58</v>
+      </c>
+      <c r="G47">
+        <v>90</v>
+      </c>
+      <c r="H47" t="s">
+        <v>40</v>
+      </c>
+      <c r="I47">
+        <v>90</v>
+      </c>
+      <c r="J47" t="s">
+        <v>41</v>
+      </c>
+      <c r="K47" t="s">
+        <v>81</v>
+      </c>
+      <c r="L47" t="s">
+        <v>43</v>
+      </c>
+      <c r="M47">
+        <v>100</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="30" customHeight="1">
+      <c r="A48" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-B</v>
+      </c>
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
+        <v>513</v>
+      </c>
+      <c r="E48" t="s">
+        <v>521</v>
+      </c>
+      <c r="F48" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48">
+        <v>90</v>
+      </c>
+      <c r="H48" t="s">
+        <v>40</v>
+      </c>
+      <c r="I48">
+        <v>100</v>
+      </c>
+      <c r="J48" t="s">
+        <v>41</v>
+      </c>
+      <c r="K48" t="s">
+        <v>81</v>
+      </c>
+      <c r="L48" t="s">
+        <v>43</v>
+      </c>
+      <c r="N48" s="1"/>
+    </row>
+    <row r="49" spans="1:14" ht="30" customHeight="1">
+      <c r="A49" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-C</v>
+      </c>
+      <c r="B49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" t="s">
+        <v>514</v>
+      </c>
+      <c r="E49" t="s">
+        <v>521</v>
+      </c>
+      <c r="F49" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49">
+        <v>90</v>
+      </c>
+      <c r="H49" t="s">
+        <v>40</v>
+      </c>
+      <c r="I49">
+        <v>100</v>
+      </c>
+      <c r="J49" t="s">
+        <v>41</v>
+      </c>
+      <c r="K49" t="s">
+        <v>81</v>
+      </c>
+      <c r="L49" t="s">
+        <v>43</v>
+      </c>
+      <c r="N49" s="1"/>
+    </row>
+    <row r="50" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A50" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-G</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
+        <v>515</v>
+      </c>
+      <c r="E50" t="s">
+        <v>521</v>
+      </c>
+      <c r="F50" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50">
+        <v>90</v>
+      </c>
+      <c r="H50" t="s">
+        <v>40</v>
+      </c>
+      <c r="I50">
+        <v>100</v>
+      </c>
+      <c r="J50" t="s">
+        <v>41</v>
+      </c>
+      <c r="K50" t="s">
+        <v>81</v>
+      </c>
+      <c r="L50" t="s">
+        <v>43</v>
+      </c>
+      <c r="N50" s="1"/>
+    </row>
+    <row r="51" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" t="s">
+        <v>496</v>
+      </c>
+      <c r="E51" t="s">
+        <v>519</v>
+      </c>
+      <c r="F51" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51">
+        <v>100</v>
+      </c>
+      <c r="H51" t="s">
+        <v>40</v>
+      </c>
+      <c r="I51">
+        <v>100</v>
+      </c>
+      <c r="J51" t="s">
+        <v>41</v>
+      </c>
+      <c r="K51" t="s">
         <v>47</v>
       </c>
-      <c r="L46" t="s">
+      <c r="L51" t="s">
         <v>48</v>
       </c>
-      <c r="M46">
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A52" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" t="s">
+        <v>495</v>
+      </c>
+      <c r="E52" t="s">
+        <v>519</v>
+      </c>
+      <c r="F52" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52">
+        <v>100</v>
+      </c>
+      <c r="H52" t="s">
+        <v>40</v>
+      </c>
+      <c r="I52">
+        <v>100</v>
+      </c>
+      <c r="J52" t="s">
+        <v>41</v>
+      </c>
+      <c r="K52" t="s">
+        <v>47</v>
+      </c>
+      <c r="L52" t="s">
+        <v>48</v>
+      </c>
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A53" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>494</v>
+      </c>
+      <c r="E53" t="s">
+        <v>519</v>
+      </c>
+      <c r="F53" t="s">
+        <v>36</v>
+      </c>
+      <c r="G53">
+        <v>100</v>
+      </c>
+      <c r="H53" t="s">
+        <v>40</v>
+      </c>
+      <c r="I53">
+        <v>100</v>
+      </c>
+      <c r="J53" t="s">
+        <v>41</v>
+      </c>
+      <c r="K53" t="s">
+        <v>47</v>
+      </c>
+      <c r="L53" t="s">
+        <v>48</v>
+      </c>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" ht="34.5" customHeight="1">
+      <c r="A54" t="s">
+        <v>346</v>
+      </c>
+      <c r="B54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
+        <v>92</v>
+      </c>
+      <c r="E54" t="s">
+        <v>521</v>
+      </c>
+      <c r="F54" t="s">
+        <v>58</v>
+      </c>
+      <c r="G54">
+        <v>100</v>
+      </c>
+      <c r="H54" t="s">
+        <v>40</v>
+      </c>
+      <c r="I54">
+        <v>120</v>
+      </c>
+      <c r="J54" t="s">
+        <v>41</v>
+      </c>
+      <c r="K54" t="s">
+        <v>47</v>
+      </c>
+      <c r="L54" t="s">
+        <v>48</v>
+      </c>
+      <c r="M54">
         <v>130</v>
       </c>
-      <c r="N46" s="1"/>
-    </row>
-    <row r="47" spans="1:14" ht="30" customHeight="1">
-      <c r="A47" t="str">
+      <c r="N54" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A55" t="s">
+        <v>347</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" t="s">
+        <v>521</v>
+      </c>
+      <c r="F55" t="s">
+        <v>36</v>
+      </c>
+      <c r="G55">
+        <v>100</v>
+      </c>
+      <c r="H55" t="s">
+        <v>40</v>
+      </c>
+      <c r="I55">
+        <v>120</v>
+      </c>
+      <c r="J55" t="s">
+        <v>41</v>
+      </c>
+      <c r="K55" t="s">
+        <v>47</v>
+      </c>
+      <c r="L55" t="s">
+        <v>48</v>
+      </c>
+      <c r="M55">
+        <v>130</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A56" t="s">
+        <v>542</v>
+      </c>
+      <c r="B56" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" t="s">
+        <v>534</v>
+      </c>
+      <c r="E56" t="s">
+        <v>521</v>
+      </c>
+      <c r="F56" t="s">
+        <v>36</v>
+      </c>
+      <c r="G56">
+        <v>100</v>
+      </c>
+      <c r="H56" t="s">
+        <v>40</v>
+      </c>
+      <c r="I56">
+        <v>120</v>
+      </c>
+      <c r="J56" t="s">
+        <v>41</v>
+      </c>
+      <c r="K56" t="s">
+        <v>47</v>
+      </c>
+      <c r="L56" t="s">
+        <v>48</v>
+      </c>
+      <c r="M56">
+        <v>130</v>
+      </c>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="1:14" ht="37.5" customHeight="1">
+      <c r="A57" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1991-W</v>
       </c>
-      <c r="B47" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" t="s">
         <v>517</v>
-      </c>
-      <c r="E47" t="s">
-        <v>521</v>
-      </c>
-      <c r="F47" t="s">
-        <v>58</v>
-      </c>
-      <c r="G47">
-        <v>100</v>
-      </c>
-      <c r="H47" t="s">
-        <v>40</v>
-      </c>
-      <c r="I47">
-        <v>120</v>
-      </c>
-      <c r="J47" t="s">
-        <v>41</v>
-      </c>
-      <c r="K47" t="s">
-        <v>47</v>
-      </c>
-      <c r="L47" t="s">
-        <v>48</v>
-      </c>
-      <c r="N47" s="1"/>
-    </row>
-    <row r="48" spans="1:14" ht="30" customHeight="1">
-      <c r="A48" t="s">
-        <v>348</v>
-      </c>
-      <c r="B48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" t="s">
-        <v>94</v>
-      </c>
-      <c r="E48" t="s">
-        <v>521</v>
-      </c>
-      <c r="F48" t="s">
-        <v>58</v>
-      </c>
-      <c r="G48">
-        <v>120</v>
-      </c>
-      <c r="H48" t="s">
-        <v>51</v>
-      </c>
-      <c r="I48">
-        <v>120</v>
-      </c>
-      <c r="J48" t="s">
-        <v>41</v>
-      </c>
-      <c r="K48" t="s">
-        <v>47</v>
-      </c>
-      <c r="L48" t="s">
-        <v>48</v>
-      </c>
-      <c r="M48">
-        <v>150</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="30" customHeight="1">
-      <c r="A49" t="s">
-        <v>349</v>
-      </c>
-      <c r="B49" t="s">
-        <v>109</v>
-      </c>
-      <c r="C49" t="s">
-        <v>96</v>
-      </c>
-      <c r="E49" t="s">
-        <v>521</v>
-      </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
-      <c r="G49">
-        <v>110</v>
-      </c>
-      <c r="H49" t="s">
-        <v>51</v>
-      </c>
-      <c r="I49">
-        <v>120.5</v>
-      </c>
-      <c r="J49" t="s">
-        <v>41</v>
-      </c>
-      <c r="K49" t="s">
-        <v>97</v>
-      </c>
-      <c r="L49" t="s">
-        <v>48</v>
-      </c>
-      <c r="M49">
-        <v>125</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A50" t="s">
-        <v>504</v>
-      </c>
-      <c r="B50" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50" t="s">
-        <v>503</v>
-      </c>
-      <c r="E50" t="s">
-        <v>521</v>
-      </c>
-      <c r="F50" t="s">
-        <v>54</v>
-      </c>
-      <c r="G50">
-        <v>60</v>
-      </c>
-      <c r="H50" t="s">
-        <v>20</v>
-      </c>
-      <c r="I50" s="4">
-        <v>50</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="K50" t="s">
-        <v>32</v>
-      </c>
-      <c r="L50" t="s">
-        <v>33</v>
-      </c>
-      <c r="N50" s="1"/>
-    </row>
-    <row r="51" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A51" t="s">
-        <v>528</v>
-      </c>
-      <c r="B51" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" t="s">
-        <v>527</v>
-      </c>
-      <c r="E51" t="s">
-        <v>521</v>
-      </c>
-      <c r="F51" t="s">
-        <v>23</v>
-      </c>
-      <c r="G51">
-        <v>60</v>
-      </c>
-      <c r="H51" t="s">
-        <v>20</v>
-      </c>
-      <c r="I51">
-        <v>45</v>
-      </c>
-      <c r="J51" t="s">
-        <v>548</v>
-      </c>
-      <c r="K51" t="s">
-        <v>32</v>
-      </c>
-      <c r="L51" t="s">
-        <v>32</v>
-      </c>
-      <c r="N51" s="1"/>
-    </row>
-    <row r="52" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A52" t="s">
-        <v>351</v>
-      </c>
-      <c r="B52" t="s">
-        <v>109</v>
-      </c>
-      <c r="C52" t="s">
-        <v>101</v>
-      </c>
-      <c r="E52" t="s">
-        <v>521</v>
-      </c>
-      <c r="F52" t="s">
-        <v>54</v>
-      </c>
-      <c r="G52">
-        <v>80</v>
-      </c>
-      <c r="H52" t="s">
-        <v>545</v>
-      </c>
-      <c r="I52" s="4">
-        <v>75</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="K52" t="s">
-        <v>102</v>
-      </c>
-      <c r="L52" t="s">
-        <v>32</v>
-      </c>
-      <c r="M52">
-        <v>55.5</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A53" t="s">
-        <v>550</v>
-      </c>
-      <c r="B53" t="s">
-        <v>109</v>
-      </c>
-      <c r="C53" t="s">
-        <v>549</v>
-      </c>
-      <c r="E53" t="s">
-        <v>521</v>
-      </c>
-      <c r="F53" t="s">
-        <v>54</v>
-      </c>
-      <c r="G53">
-        <v>80</v>
-      </c>
-      <c r="H53" t="s">
-        <v>545</v>
-      </c>
-      <c r="I53" s="4">
-        <v>75</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="K53" t="s">
-        <v>102</v>
-      </c>
-      <c r="L53" t="s">
-        <v>32</v>
-      </c>
-      <c r="N53" s="1"/>
-    </row>
-    <row r="54" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A54" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS2811DS-B</v>
-      </c>
-      <c r="B54" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" t="s">
-        <v>523</v>
-      </c>
-      <c r="E54" t="s">
-        <v>519</v>
-      </c>
-      <c r="F54" t="s">
-        <v>520</v>
-      </c>
-      <c r="G54">
-        <v>75</v>
-      </c>
-      <c r="H54" t="s">
-        <v>14</v>
-      </c>
-      <c r="I54">
-        <v>130</v>
-      </c>
-      <c r="J54" t="s">
-        <v>46</v>
-      </c>
-      <c r="K54" t="s">
-        <v>47</v>
-      </c>
-      <c r="L54" t="s">
-        <v>48</v>
-      </c>
-      <c r="N54" s="1"/>
-    </row>
-    <row r="55" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A55" t="s">
-        <v>525</v>
-      </c>
-      <c r="B55" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" t="s">
-        <v>524</v>
-      </c>
-      <c r="E55" t="s">
-        <v>519</v>
-      </c>
-      <c r="F55" t="s">
-        <v>36</v>
-      </c>
-      <c r="G55">
-        <v>75</v>
-      </c>
-      <c r="H55" t="s">
-        <v>14</v>
-      </c>
-      <c r="I55">
-        <v>130</v>
-      </c>
-      <c r="J55" t="s">
-        <v>46</v>
-      </c>
-      <c r="K55" t="s">
-        <v>47</v>
-      </c>
-      <c r="L55" t="s">
-        <v>48</v>
-      </c>
-      <c r="N55" s="1"/>
-    </row>
-    <row r="56" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A56" t="s">
-        <v>353</v>
-      </c>
-      <c r="B56" t="s">
-        <v>109</v>
-      </c>
-      <c r="C56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E56" t="s">
-        <v>521</v>
-      </c>
-      <c r="F56" t="s">
-        <v>36</v>
-      </c>
-      <c r="G56">
-        <v>120</v>
-      </c>
-      <c r="H56" t="s">
-        <v>51</v>
-      </c>
-      <c r="I56">
-        <v>120</v>
-      </c>
-      <c r="J56" t="s">
-        <v>41</v>
-      </c>
-      <c r="K56" t="s">
-        <v>42</v>
-      </c>
-      <c r="L56" t="s">
-        <v>43</v>
-      </c>
-      <c r="M56">
-        <v>125</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="37.5" customHeight="1">
-      <c r="A57" t="s">
-        <v>530</v>
-      </c>
-      <c r="B57" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57" t="s">
-        <v>529</v>
       </c>
       <c r="E57" t="s">
         <v>521</v>
       </c>
       <c r="F57" t="s">
-        <v>552</v>
+        <v>58</v>
       </c>
       <c r="G57">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H57" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I57">
         <v>120</v>
@@ -4677,22 +4668,22 @@
         <v>41</v>
       </c>
       <c r="K57" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L57" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="1:14" ht="32.25" customHeight="1">
       <c r="A58" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B58" t="s">
         <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E58" t="s">
         <v>521</v>
@@ -4707,159 +4698,168 @@
         <v>51</v>
       </c>
       <c r="I58">
-        <v>130</v>
+        <v>120.5</v>
       </c>
       <c r="J58" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K58" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="L58" t="s">
         <v>48</v>
       </c>
       <c r="M58">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="42" customHeight="1">
       <c r="A59" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B59" t="s">
         <v>109</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="E59" t="s">
         <v>521</v>
       </c>
       <c r="F59" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G59">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="H59" t="s">
-        <v>526</v>
+        <v>51</v>
       </c>
       <c r="I59">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="J59" t="s">
-        <v>548</v>
+        <v>46</v>
       </c>
       <c r="K59" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="L59" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="M59">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="36.75" customHeight="1">
       <c r="A60" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B60" t="s">
         <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="E60" t="s">
         <v>521</v>
       </c>
       <c r="F60" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G60">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H60" t="s">
-        <v>526</v>
+        <v>51</v>
       </c>
       <c r="I60">
+        <v>120</v>
+      </c>
+      <c r="J60" t="s">
         <v>41</v>
       </c>
-      <c r="J60" t="s">
-        <v>548</v>
-      </c>
       <c r="K60" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="L60" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="M60">
-        <v>41</v>
+        <v>150</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="29.25" customHeight="1">
       <c r="A61" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B61" t="s">
         <v>109</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E61" t="s">
         <v>521</v>
       </c>
       <c r="F61" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G61">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="H61" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="I61">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J61" t="s">
-        <v>547</v>
+        <v>41</v>
       </c>
       <c r="K61" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L61" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M61">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="44.25" customHeight="1">
       <c r="A62" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="B62" t="s">
         <v>109</v>
       </c>
+      <c r="C62" t="s">
+        <v>528</v>
+      </c>
       <c r="E62" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F62" t="s">
-        <v>538</v>
+        <v>546</v>
+      </c>
+      <c r="G62">
+        <v>120</v>
+      </c>
+      <c r="H62" t="s">
+        <v>51</v>
       </c>
       <c r="I62">
         <v>120</v>
@@ -4867,41 +4867,32 @@
       <c r="J62" t="s">
         <v>41</v>
       </c>
+      <c r="K62" t="s">
+        <v>42</v>
+      </c>
+      <c r="L62" t="s">
+        <v>43</v>
+      </c>
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="1:14" ht="34.5" customHeight="1">
       <c r="A63" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="B63" t="s">
         <v>109</v>
-      </c>
-      <c r="C63" t="s">
-        <v>553</v>
       </c>
       <c r="E63" t="s">
         <v>519</v>
       </c>
       <c r="F63" t="s">
-        <v>36</v>
-      </c>
-      <c r="G63">
-        <v>76</v>
-      </c>
-      <c r="H63" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I63">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J63" t="s">
-        <v>546</v>
-      </c>
-      <c r="K63" t="s">
-        <v>81</v>
-      </c>
-      <c r="L63" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N63" s="1"/>
     </row>

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6328D4DB-12E2-4ADB-A688-374A1CE1619A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4B3FF7-6129-494F-9A2E-8B99A831F500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="-16035" windowWidth="21600" windowHeight="14595" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
+    <workbookView xWindow="2190" yWindow="0" windowWidth="21600" windowHeight="14595" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -2088,7 +2088,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}" name="Таблица1" displayName="Таблица1" ref="A1:N63" totalsRowShown="0">
   <autoFilter ref="A1:N63" xr:uid="{9A71E811-2E0D-4344-A156-CF0A204ACD9A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N63">
-    <sortCondition ref="G1:G63"/>
+    <sortCondition ref="C1:C63"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{5C26076C-B06F-4FD5-B816-E33E9522C8DC}" name="image_url"/>
@@ -2507,566 +2507,548 @@
     </row>
     <row r="2" spans="1:14" ht="21.75" customHeight="1">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>512</v>
       </c>
       <c r="B2" t="s">
         <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>511</v>
       </c>
       <c r="E2" t="s">
         <v>521</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
         <v>20</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>549</v>
+        <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>111</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="21.75" customHeight="1">
       <c r="A3" t="s">
-        <v>279</v>
+        <v>531</v>
       </c>
       <c r="B3" t="s">
         <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>530</v>
       </c>
       <c r="E3" t="s">
         <v>521</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>546</v>
       </c>
       <c r="G3">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>550</v>
       </c>
       <c r="I3">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>532</v>
       </c>
       <c r="L3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" ht="21.75" customHeight="1">
       <c r="A4" t="s">
-        <v>325</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
         <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="4">
-        <v>55</v>
+        <v>520</v>
+      </c>
+      <c r="G4">
+        <v>70</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>550</v>
       </c>
       <c r="I4">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L4" t="s">
         <v>17</v>
       </c>
-      <c r="M4">
+      <c r="N4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>519</v>
+      </c>
+      <c r="F5" t="s">
+        <v>520</v>
+      </c>
+      <c r="G5">
+        <v>55</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>200</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A6" t="s">
+        <v>548</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E6" t="s">
+        <v>519</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6">
+        <v>76</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>496</v>
+      </c>
+      <c r="E7" t="s">
+        <v>519</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" t="s">
+        <v>495</v>
+      </c>
+      <c r="E8" t="s">
+        <v>519</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8">
+        <v>100</v>
+      </c>
+      <c r="H8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" t="s">
+        <v>494</v>
+      </c>
+      <c r="E9" t="s">
+        <v>519</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A10" t="s">
+        <v>276</v>
+      </c>
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" t="s">
+        <v>521</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>55</v>
+      </c>
+      <c r="H10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10">
+        <v>30</v>
+      </c>
+      <c r="J10" t="s">
+        <v>549</v>
+      </c>
+      <c r="K10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A11" t="s">
+        <v>277</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" t="s">
+        <v>521</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
+        <v>65</v>
+      </c>
+      <c r="H11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11">
+        <v>35</v>
+      </c>
+      <c r="J11" t="s">
+        <v>549</v>
+      </c>
+      <c r="K11" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" t="s">
+        <v>521</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>75</v>
+      </c>
+      <c r="H12" t="s">
+        <v>550</v>
+      </c>
+      <c r="I12">
+        <v>40</v>
+      </c>
+      <c r="J12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" t="s">
+        <v>29</v>
+      </c>
+      <c r="L12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" t="s">
+        <v>521</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>55</v>
+      </c>
+      <c r="H13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13">
+        <v>35</v>
+      </c>
+      <c r="J13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A14" t="s">
+        <v>325</v>
+      </c>
+      <c r="B14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>521</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="4">
+        <v>55</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14">
+        <v>40</v>
+      </c>
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14">
         <v>45</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A5" t="str">
+    <row r="15" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A15" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1137-W</v>
       </c>
-      <c r="B5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" t="s">
         <v>536</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E15" t="s">
         <v>521</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F15" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G15" s="4">
         <v>55</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H15" t="s">
         <v>20</v>
       </c>
-      <c r="I5">
+      <c r="I15">
         <v>40</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J15" t="s">
         <v>15</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K15" t="s">
         <v>17</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L15" t="s">
         <v>17</v>
       </c>
-      <c r="M5">
+      <c r="M15">
         <v>45</v>
       </c>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s">
-        <v>519</v>
-      </c>
-      <c r="F6" t="s">
-        <v>520</v>
-      </c>
-      <c r="G6">
-        <v>55</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6">
-        <v>200</v>
-      </c>
-      <c r="J6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A7" t="str">
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A16" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1171-B</v>
       </c>
-      <c r="B7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" t="s">
         <v>516</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E16" t="s">
         <v>519</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F16" t="s">
         <v>58</v>
       </c>
-      <c r="G7">
+      <c r="G16">
         <v>60</v>
-      </c>
-      <c r="H7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7">
-        <v>40</v>
-      </c>
-      <c r="J7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7">
-        <v>45</v>
-      </c>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A8" t="s">
-        <v>355</v>
-      </c>
-      <c r="B8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>521</v>
-      </c>
-      <c r="F8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8">
-        <v>60</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8">
-        <v>41</v>
-      </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8">
-        <v>41</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A9" t="s">
-        <v>356</v>
-      </c>
-      <c r="B9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" t="s">
-        <v>521</v>
-      </c>
-      <c r="F9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9">
-        <v>60</v>
-      </c>
-      <c r="H9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9">
-        <v>41</v>
-      </c>
-      <c r="J9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9">
-        <v>41</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A10" t="s">
-        <v>527</v>
-      </c>
-      <c r="B10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" t="s">
-        <v>526</v>
-      </c>
-      <c r="E10" t="s">
-        <v>521</v>
-      </c>
-      <c r="F10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10">
-        <v>60</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10">
-        <v>45</v>
-      </c>
-      <c r="J10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" t="s">
-        <v>32</v>
-      </c>
-      <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A11" t="s">
-        <v>504</v>
-      </c>
-      <c r="B11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" t="s">
-        <v>503</v>
-      </c>
-      <c r="E11" t="s">
-        <v>521</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>60</v>
-      </c>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="4">
-        <v>50</v>
-      </c>
-      <c r="J11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A12" t="s">
-        <v>357</v>
-      </c>
-      <c r="B12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" t="s">
-        <v>521</v>
-      </c>
-      <c r="F12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12">
-        <v>65</v>
-      </c>
-      <c r="H12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12">
-        <v>30</v>
-      </c>
-      <c r="J12" t="s">
-        <v>549</v>
-      </c>
-      <c r="K12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" t="s">
-        <v>33</v>
-      </c>
-      <c r="M12">
-        <v>40</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A13" t="s">
-        <v>277</v>
-      </c>
-      <c r="B13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13" t="s">
-        <v>521</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
-        <v>65</v>
-      </c>
-      <c r="H13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13">
-        <v>35</v>
-      </c>
-      <c r="J13" t="s">
-        <v>549</v>
-      </c>
-      <c r="K13" t="s">
-        <v>113</v>
-      </c>
-      <c r="L13" t="s">
-        <v>17</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A14" t="s">
-        <v>327</v>
-      </c>
-      <c r="B14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" t="s">
-        <v>521</v>
-      </c>
-      <c r="F14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14">
-        <v>65</v>
-      </c>
-      <c r="H14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14">
-        <v>35</v>
-      </c>
-      <c r="J14" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" t="s">
-        <v>17</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A15" t="s">
-        <v>328</v>
-      </c>
-      <c r="B15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>521</v>
-      </c>
-      <c r="F15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15">
-        <v>65</v>
-      </c>
-      <c r="H15" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15">
-        <v>35</v>
-      </c>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" t="s">
-        <v>17</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A16" t="s">
-        <v>512</v>
-      </c>
-      <c r="B16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" t="s">
-        <v>511</v>
-      </c>
-      <c r="E16" t="s">
-        <v>521</v>
-      </c>
-      <c r="F16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16">
-        <v>65</v>
       </c>
       <c r="H16" t="s">
         <v>20</v>
@@ -3078,28 +3060,31 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>17</v>
+      </c>
+      <c r="M16">
+        <v>45</v>
       </c>
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" ht="21.75" customHeight="1">
       <c r="A17" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B17" t="s">
         <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
         <v>521</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G17">
         <v>65</v>
@@ -3108,39 +3093,36 @@
         <v>20</v>
       </c>
       <c r="I17">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J17" t="s">
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
-      </c>
-      <c r="M17">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="21.75" customHeight="1">
       <c r="A18" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B18" t="s">
         <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
         <v>521</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G18">
         <v>65</v>
@@ -3149,80 +3131,74 @@
         <v>20</v>
       </c>
       <c r="I18">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
-      </c>
-      <c r="M18">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="21.75" customHeight="1">
       <c r="A19" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B19" t="s">
         <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F19" t="s">
-        <v>520</v>
+        <v>488</v>
       </c>
       <c r="G19">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>550</v>
       </c>
       <c r="I19">
-        <v>90.9</v>
+        <v>40.5</v>
       </c>
       <c r="J19" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="L19" t="s">
         <v>43</v>
       </c>
-      <c r="M19">
-        <v>105.9</v>
-      </c>
       <c r="N19" s="1" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1">
       <c r="A20" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="B20" t="s">
         <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F20" t="s">
-        <v>520</v>
+        <v>58</v>
       </c>
       <c r="G20">
         <v>65</v>
@@ -3231,115 +3207,121 @@
         <v>20</v>
       </c>
       <c r="I20">
-        <v>90.9</v>
+        <v>45</v>
       </c>
       <c r="J20" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L20" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="M20">
-        <v>105.9</v>
+        <v>50</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1">
       <c r="A21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B21" t="s">
         <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
         <v>521</v>
       </c>
       <c r="F21" t="s">
-        <v>488</v>
+        <v>58</v>
       </c>
       <c r="G21">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H21" t="s">
-        <v>550</v>
+        <v>20</v>
       </c>
       <c r="I21">
-        <v>40.5</v>
+        <v>45</v>
       </c>
       <c r="J21" t="s">
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="L21" t="s">
-        <v>43</v>
+        <v>33</v>
+      </c>
+      <c r="M21">
+        <v>50</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1">
       <c r="A22" t="s">
-        <v>159</v>
+        <v>333</v>
       </c>
       <c r="B22" t="s">
         <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F22" t="s">
-        <v>520</v>
+        <v>58</v>
       </c>
       <c r="G22">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s">
         <v>550</v>
       </c>
       <c r="I22">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J22" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="K22" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="L22" t="s">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="M22">
+        <v>55.5</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1">
       <c r="A23" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="B23" t="s">
         <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
         <v>521</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="G23">
         <v>75</v>
@@ -3348,36 +3330,39 @@
         <v>550</v>
       </c>
       <c r="I23">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K23" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L23" t="s">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="M23">
+        <v>50</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1">
       <c r="A24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B24" t="s">
         <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s">
         <v>521</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G24">
         <v>75</v>
@@ -3386,39 +3371,40 @@
         <v>550</v>
       </c>
       <c r="I24">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J24" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K24" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L24" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="M24">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A25" t="s">
-        <v>506</v>
+      <c r="A25" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1552E-WO</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="E25" t="s">
         <v>521</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>546</v>
       </c>
       <c r="G25">
         <v>75</v>
@@ -3427,10 +3413,10 @@
         <v>550</v>
       </c>
       <c r="I25">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="J25" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="K25" t="s">
         <v>32</v>
@@ -3438,22 +3424,17 @@
       <c r="L25" t="s">
         <v>33</v>
       </c>
-      <c r="M25">
-        <v>60</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" ht="21.75" customHeight="1">
       <c r="A26" t="s">
-        <v>505</v>
+        <v>338</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>501</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s">
         <v>521</v>
@@ -3488,10 +3469,13 @@
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1">
       <c r="A27" t="s">
-        <v>538</v>
+        <v>506</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>533</v>
+        <v>502</v>
       </c>
       <c r="E27" t="s">
         <v>521</v>
@@ -3520,90 +3504,97 @@
       <c r="M27">
         <v>60</v>
       </c>
-      <c r="N27" s="1"/>
+      <c r="N27" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="28" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A28" t="str">
+      <c r="A28" t="s">
+        <v>505</v>
+      </c>
+      <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s">
+        <v>501</v>
+      </c>
+      <c r="E28" t="s">
+        <v>521</v>
+      </c>
+      <c r="F28" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28">
+        <v>75</v>
+      </c>
+      <c r="H28" t="s">
+        <v>550</v>
+      </c>
+      <c r="I28">
+        <v>50</v>
+      </c>
+      <c r="J28" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" t="s">
+        <v>33</v>
+      </c>
+      <c r="M28">
+        <v>60</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A29" t="s">
+        <v>538</v>
+      </c>
+      <c r="C29" t="s">
+        <v>533</v>
+      </c>
+      <c r="E29" t="s">
+        <v>521</v>
+      </c>
+      <c r="F29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s">
+        <v>550</v>
+      </c>
+      <c r="I29">
+        <v>50</v>
+      </c>
+      <c r="J29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" t="s">
+        <v>33</v>
+      </c>
+      <c r="M29">
+        <v>60</v>
+      </c>
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A30" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
         <v>images/TS1580-B</v>
       </c>
-      <c r="B28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" t="s">
         <v>522</v>
-      </c>
-      <c r="E28" t="s">
-        <v>521</v>
-      </c>
-      <c r="F28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28">
-        <v>75</v>
-      </c>
-      <c r="H28" t="s">
-        <v>550</v>
-      </c>
-      <c r="I28">
-        <v>60</v>
-      </c>
-      <c r="J28" t="s">
-        <v>15</v>
-      </c>
-      <c r="K28" t="s">
-        <v>491</v>
-      </c>
-      <c r="L28" t="s">
-        <v>32</v>
-      </c>
-      <c r="N28" s="1"/>
-    </row>
-    <row r="29" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B29" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" t="s">
-        <v>490</v>
-      </c>
-      <c r="E29" t="s">
-        <v>521</v>
-      </c>
-      <c r="F29" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29">
-        <v>75</v>
-      </c>
-      <c r="H29" t="s">
-        <v>550</v>
-      </c>
-      <c r="I29">
-        <v>60</v>
-      </c>
-      <c r="J29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29" t="s">
-        <v>491</v>
-      </c>
-      <c r="L29" t="s">
-        <v>32</v>
-      </c>
-      <c r="N29" s="1"/>
-    </row>
-    <row r="30" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" t="s">
-        <v>489</v>
       </c>
       <c r="E30" t="s">
         <v>521</v>
@@ -3632,20 +3623,20 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A31" t="s">
-        <v>531</v>
+      <c r="A31" s="2" t="s">
+        <v>492</v>
       </c>
       <c r="B31" t="s">
         <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>530</v>
+        <v>490</v>
       </c>
       <c r="E31" t="s">
         <v>521</v>
       </c>
       <c r="F31" t="s">
-        <v>546</v>
+        <v>23</v>
       </c>
       <c r="G31">
         <v>75</v>
@@ -3654,13 +3645,13 @@
         <v>550</v>
       </c>
       <c r="I31">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J31" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="L31" t="s">
         <v>32</v>
@@ -3668,20 +3659,20 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A32" t="s">
-        <v>337</v>
+      <c r="A32" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="B32" t="s">
         <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>489</v>
       </c>
       <c r="E32" t="s">
         <v>521</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G32">
         <v>75</v>
@@ -3690,240 +3681,236 @@
         <v>550</v>
       </c>
       <c r="I32">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J32" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>37</v>
+        <v>491</v>
       </c>
       <c r="L32" t="s">
-        <v>17</v>
-      </c>
-      <c r="M32">
-        <v>70</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" ht="21.75" customHeight="1">
       <c r="A33" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1552E-WO</v>
+        <v>images/TS1590-B</v>
       </c>
       <c r="B33" t="s">
         <v>109</v>
       </c>
       <c r="C33" t="s">
-        <v>541</v>
+        <v>513</v>
       </c>
       <c r="E33" t="s">
         <v>521</v>
       </c>
       <c r="F33" t="s">
-        <v>546</v>
+        <v>23</v>
       </c>
       <c r="G33">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s">
-        <v>550</v>
+        <v>40</v>
       </c>
       <c r="I33">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="J33" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="K33" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="L33" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A34" t="s">
-        <v>333</v>
+      <c r="A34" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-C</v>
       </c>
       <c r="B34" t="s">
         <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>514</v>
       </c>
       <c r="E34" t="s">
         <v>521</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G34">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s">
-        <v>550</v>
+        <v>40</v>
       </c>
       <c r="I34">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J34" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="K34" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="L34" t="s">
-        <v>33</v>
-      </c>
-      <c r="M34">
-        <v>55.5</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="N34" s="1"/>
     </row>
     <row r="35" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A35" t="s">
-        <v>334</v>
+      <c r="A35" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS1590-G</v>
       </c>
       <c r="B35" t="s">
         <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>515</v>
       </c>
       <c r="E35" t="s">
         <v>521</v>
       </c>
       <c r="F35" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35">
+        <v>90</v>
+      </c>
+      <c r="H35" t="s">
+        <v>40</v>
+      </c>
+      <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35" t="s">
+        <v>41</v>
+      </c>
+      <c r="K35" t="s">
+        <v>81</v>
+      </c>
+      <c r="L35" t="s">
+        <v>43</v>
+      </c>
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" spans="1:14" ht="21.75" customHeight="1">
+      <c r="A36" t="s">
+        <v>339</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" t="s">
+        <v>521</v>
+      </c>
+      <c r="F36" t="s">
         <v>58</v>
       </c>
-      <c r="G35">
+      <c r="G36">
+        <v>90</v>
+      </c>
+      <c r="H36" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36">
         <v>75</v>
       </c>
-      <c r="H35" t="s">
-        <v>550</v>
-      </c>
-      <c r="I35">
-        <v>70</v>
-      </c>
-      <c r="J35" t="s">
-        <v>119</v>
-      </c>
-      <c r="K35" t="s">
-        <v>32</v>
-      </c>
-      <c r="L35" t="s">
-        <v>33</v>
-      </c>
-      <c r="M35">
-        <v>50</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A36" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS2811DS-B</v>
-      </c>
-      <c r="B36" t="s">
-        <v>109</v>
-      </c>
-      <c r="C36" t="s">
-        <v>523</v>
-      </c>
-      <c r="E36" t="s">
-        <v>519</v>
-      </c>
-      <c r="F36" t="s">
-        <v>520</v>
-      </c>
-      <c r="G36">
-        <v>75</v>
-      </c>
-      <c r="H36" t="s">
-        <v>550</v>
-      </c>
-      <c r="I36">
-        <v>130</v>
-      </c>
       <c r="J36" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K36" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L36" t="s">
-        <v>48</v>
-      </c>
-      <c r="N36" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="M36">
+        <v>90</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="37" spans="1:14" ht="21.75" customHeight="1">
       <c r="A37" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="B37" t="s">
         <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="E37" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G37">
+        <v>90</v>
+      </c>
+      <c r="H37" t="s">
+        <v>40</v>
+      </c>
+      <c r="I37">
         <v>75</v>
       </c>
-      <c r="H37" t="s">
-        <v>550</v>
-      </c>
-      <c r="I37">
-        <v>130</v>
-      </c>
       <c r="J37" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K37" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L37" t="s">
-        <v>48</v>
-      </c>
-      <c r="N37" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="M37">
+        <v>90</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="38" spans="1:14" ht="21.75" customHeight="1">
       <c r="A38" t="s">
-        <v>548</v>
+        <v>507</v>
       </c>
       <c r="B38" t="s">
         <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>547</v>
+        <v>509</v>
       </c>
       <c r="E38" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F38" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G38">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s">
         <v>40</v>
       </c>
       <c r="I38">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J38" t="s">
         <v>41</v>
@@ -3934,106 +3921,114 @@
       <c r="L38" t="s">
         <v>43</v>
       </c>
-      <c r="N38" s="1"/>
+      <c r="M38">
+        <v>90</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="39" spans="1:14" ht="21.75" customHeight="1">
       <c r="A39" t="s">
-        <v>351</v>
+        <v>539</v>
       </c>
       <c r="B39" t="s">
         <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>535</v>
       </c>
       <c r="E39" t="s">
         <v>521</v>
       </c>
       <c r="F39" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G39">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s">
         <v>40</v>
       </c>
-      <c r="I39" s="4">
+      <c r="I39">
         <v>75</v>
       </c>
       <c r="J39" t="s">
         <v>41</v>
       </c>
       <c r="K39" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="L39" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M39">
-        <v>55.5</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>103</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="N39" s="1"/>
     </row>
     <row r="40" spans="1:14" ht="21.75" customHeight="1">
       <c r="A40" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B40" t="s">
         <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="E40" t="s">
         <v>521</v>
       </c>
       <c r="F40" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G40">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s">
         <v>40</v>
       </c>
-      <c r="I40" s="4">
-        <v>75</v>
+      <c r="I40">
+        <v>90.9</v>
       </c>
       <c r="J40" t="s">
         <v>41</v>
       </c>
       <c r="K40" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="L40" t="s">
-        <v>32</v>
-      </c>
-      <c r="N40" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="M40">
+        <v>105.9</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="41" spans="1:14" ht="21.75" customHeight="1">
       <c r="A41" t="s">
-        <v>543</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s">
         <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>520</v>
       </c>
       <c r="G41">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H41" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I41">
         <v>90.9</v>
@@ -4051,30 +4046,30 @@
         <v>105.9</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="26.25" customHeight="1">
       <c r="A42" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s">
         <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="E42" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F42" t="s">
-        <v>36</v>
+        <v>520</v>
       </c>
       <c r="G42">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H42" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I42">
         <v>90.9</v>
@@ -4092,59 +4087,59 @@
         <v>105.9</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="26.25" customHeight="1">
       <c r="A43" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="E43" t="s">
         <v>521</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G43">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s">
         <v>40</v>
       </c>
       <c r="I43">
-        <v>75</v>
+        <v>90.9</v>
       </c>
       <c r="J43" t="s">
         <v>41</v>
       </c>
       <c r="K43" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="L43" t="s">
         <v>43</v>
       </c>
       <c r="M43">
-        <v>90</v>
+        <v>105.9</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="27.75" customHeight="1">
       <c r="A44" t="s">
-        <v>508</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>510</v>
+        <v>90</v>
       </c>
       <c r="E44" t="s">
         <v>521</v>
@@ -4159,7 +4154,7 @@
         <v>40</v>
       </c>
       <c r="I44">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="J44" t="s">
         <v>41</v>
@@ -4171,21 +4166,21 @@
         <v>43</v>
       </c>
       <c r="M44">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="27.75" customHeight="1">
       <c r="A45" t="s">
-        <v>507</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s">
         <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>509</v>
+        <v>92</v>
       </c>
       <c r="E45" t="s">
         <v>521</v>
@@ -4194,397 +4189,406 @@
         <v>58</v>
       </c>
       <c r="G45">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H45" t="s">
         <v>40</v>
       </c>
       <c r="I45">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="J45" t="s">
         <v>41</v>
       </c>
       <c r="K45" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L45" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M45">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="32.25" customHeight="1">
       <c r="A46" t="s">
-        <v>539</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s">
         <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>535</v>
+        <v>45</v>
       </c>
       <c r="E46" t="s">
         <v>521</v>
       </c>
       <c r="F46" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G46">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H46" t="s">
         <v>40</v>
       </c>
       <c r="I46">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="J46" t="s">
         <v>41</v>
       </c>
       <c r="K46" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L46" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M46">
-        <v>90</v>
-      </c>
-      <c r="N46" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="47" spans="1:14" ht="30" customHeight="1">
       <c r="A47" t="s">
-        <v>345</v>
+        <v>542</v>
       </c>
       <c r="B47" t="s">
         <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>534</v>
       </c>
       <c r="E47" t="s">
         <v>521</v>
       </c>
       <c r="F47" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G47">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H47" t="s">
         <v>40</v>
       </c>
       <c r="I47">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J47" t="s">
         <v>41</v>
       </c>
       <c r="K47" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L47" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M47">
-        <v>100</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>91</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="N47" s="1"/>
     </row>
     <row r="48" spans="1:14" ht="30" customHeight="1">
       <c r="A48" t="str">
         <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-B</v>
+        <v>images/TS1991-W</v>
       </c>
       <c r="B48" t="s">
         <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="E48" t="s">
         <v>521</v>
       </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G48">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H48" t="s">
         <v>40</v>
       </c>
       <c r="I48">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
         <v>41</v>
       </c>
       <c r="K48" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L48" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="1:14" ht="30" customHeight="1">
-      <c r="A49" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-C</v>
+      <c r="A49" t="s">
+        <v>348</v>
       </c>
       <c r="B49" t="s">
         <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>514</v>
+        <v>94</v>
       </c>
       <c r="E49" t="s">
         <v>521</v>
       </c>
       <c r="F49" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G49">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H49" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I49">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J49" t="s">
         <v>41</v>
       </c>
       <c r="K49" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L49" t="s">
-        <v>43</v>
-      </c>
-      <c r="N49" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="M49">
+        <v>150</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="50" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A50" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1590-G</v>
+      <c r="A50" t="s">
+        <v>349</v>
       </c>
       <c r="B50" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>515</v>
+        <v>96</v>
       </c>
       <c r="E50" t="s">
         <v>521</v>
       </c>
       <c r="F50" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G50">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="H50" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I50">
-        <v>100</v>
+        <v>120.5</v>
       </c>
       <c r="J50" t="s">
         <v>41</v>
       </c>
       <c r="K50" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="L50" t="s">
-        <v>43</v>
-      </c>
-      <c r="N50" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="M50">
+        <v>125</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="51" spans="1:14" ht="34.5" customHeight="1">
-      <c r="A51" s="3" t="s">
-        <v>499</v>
+      <c r="A51" t="s">
+        <v>504</v>
       </c>
       <c r="B51" t="s">
         <v>109</v>
       </c>
       <c r="C51" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="E51" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F51" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G51">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H51" t="s">
-        <v>40</v>
-      </c>
-      <c r="I51">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I51" s="4">
+        <v>50</v>
       </c>
       <c r="J51" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="L51" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N51" s="1"/>
     </row>
     <row r="52" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A52" s="3" t="s">
-        <v>498</v>
+      <c r="A52" t="s">
+        <v>527</v>
       </c>
       <c r="B52" t="s">
         <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>495</v>
+        <v>526</v>
       </c>
       <c r="E52" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F52" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G52">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H52" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I52">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="J52" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="L52" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A53" s="3" t="s">
-        <v>497</v>
+      <c r="A53" t="s">
+        <v>351</v>
       </c>
       <c r="B53" t="s">
         <v>109</v>
       </c>
       <c r="C53" t="s">
-        <v>494</v>
+        <v>101</v>
       </c>
       <c r="E53" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F53" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G53">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s">
         <v>40</v>
       </c>
-      <c r="I53">
-        <v>100</v>
+      <c r="I53" s="4">
+        <v>75</v>
       </c>
       <c r="J53" t="s">
         <v>41</v>
       </c>
       <c r="K53" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="L53" t="s">
-        <v>48</v>
-      </c>
-      <c r="N53" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="M53">
+        <v>55.5</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="54" spans="1:14" ht="34.5" customHeight="1">
       <c r="A54" t="s">
-        <v>346</v>
+        <v>545</v>
       </c>
       <c r="B54" t="s">
         <v>109</v>
       </c>
       <c r="C54" t="s">
-        <v>92</v>
+        <v>544</v>
       </c>
       <c r="E54" t="s">
         <v>521</v>
       </c>
       <c r="F54" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G54">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s">
         <v>40</v>
       </c>
-      <c r="I54">
-        <v>120</v>
+      <c r="I54" s="4">
+        <v>75</v>
       </c>
       <c r="J54" t="s">
         <v>41</v>
       </c>
       <c r="K54" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="L54" t="s">
-        <v>48</v>
-      </c>
-      <c r="M54">
+        <v>32</v>
+      </c>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="1:14" ht="33.75" customHeight="1">
+      <c r="A55" t="str">
+        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
+        <v>images/TS2811DS-B</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" t="s">
+        <v>523</v>
+      </c>
+      <c r="E55" t="s">
+        <v>519</v>
+      </c>
+      <c r="F55" t="s">
+        <v>520</v>
+      </c>
+      <c r="G55">
+        <v>75</v>
+      </c>
+      <c r="H55" t="s">
+        <v>550</v>
+      </c>
+      <c r="I55">
         <v>130</v>
       </c>
-      <c r="N54" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A55" t="s">
-        <v>347</v>
-      </c>
-      <c r="B55" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" t="s">
-        <v>45</v>
-      </c>
-      <c r="E55" t="s">
-        <v>521</v>
-      </c>
-      <c r="F55" t="s">
-        <v>36</v>
-      </c>
-      <c r="G55">
-        <v>100</v>
-      </c>
-      <c r="H55" t="s">
-        <v>40</v>
-      </c>
-      <c r="I55">
-        <v>120</v>
-      </c>
       <c r="J55" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K55" t="s">
         <v>47</v>
@@ -4592,40 +4596,35 @@
       <c r="L55" t="s">
         <v>48</v>
       </c>
-      <c r="M55">
-        <v>130</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="N55" s="1"/>
     </row>
     <row r="56" spans="1:14" ht="33.75" customHeight="1">
       <c r="A56" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="B56" t="s">
         <v>109</v>
       </c>
       <c r="C56" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="E56" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F56" t="s">
         <v>36</v>
       </c>
       <c r="G56">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s">
-        <v>40</v>
+        <v>550</v>
       </c>
       <c r="I56">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="J56" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K56" t="s">
         <v>47</v>
@@ -4633,33 +4632,29 @@
       <c r="L56" t="s">
         <v>48</v>
       </c>
-      <c r="M56">
-        <v>130</v>
-      </c>
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" ht="37.5" customHeight="1">
-      <c r="A57" t="str">
-        <f>"images/"&amp;Таблица1[[#This Row],[sku]]</f>
-        <v>images/TS1991-W</v>
+      <c r="A57" t="s">
+        <v>353</v>
       </c>
       <c r="B57" t="s">
         <v>109</v>
       </c>
       <c r="C57" t="s">
-        <v>517</v>
+        <v>50</v>
       </c>
       <c r="E57" t="s">
         <v>521</v>
       </c>
       <c r="F57" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G57">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H57" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I57">
         <v>120</v>
@@ -4668,53 +4663,53 @@
         <v>41</v>
       </c>
       <c r="K57" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L57" t="s">
-        <v>48</v>
-      </c>
-      <c r="N57" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="M57">
+        <v>125</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="58" spans="1:14" ht="32.25" customHeight="1">
       <c r="A58" t="s">
-        <v>349</v>
+        <v>529</v>
       </c>
       <c r="B58" t="s">
         <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>528</v>
       </c>
       <c r="E58" t="s">
         <v>521</v>
       </c>
       <c r="F58" t="s">
-        <v>58</v>
+        <v>546</v>
       </c>
       <c r="G58">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H58" t="s">
         <v>51</v>
       </c>
       <c r="I58">
-        <v>120.5</v>
+        <v>120</v>
       </c>
       <c r="J58" t="s">
         <v>41</v>
       </c>
       <c r="K58" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="L58" t="s">
-        <v>48</v>
-      </c>
-      <c r="M58">
-        <v>125</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>98</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="N58" s="1"/>
     </row>
     <row r="59" spans="1:14" ht="42" customHeight="1">
       <c r="A59" t="s">
@@ -4759,121 +4754,126 @@
     </row>
     <row r="60" spans="1:14" ht="36.75" customHeight="1">
       <c r="A60" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B60" t="s">
         <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="E60" t="s">
         <v>521</v>
       </c>
       <c r="F60" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G60">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="I60">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="J60" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60" t="s">
+        <v>17</v>
+      </c>
+      <c r="L60" t="s">
+        <v>17</v>
+      </c>
+      <c r="M60">
         <v>41</v>
       </c>
-      <c r="K60" t="s">
-        <v>47</v>
-      </c>
-      <c r="L60" t="s">
-        <v>48</v>
-      </c>
-      <c r="M60">
-        <v>150</v>
-      </c>
       <c r="N60" s="1" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="29.25" customHeight="1">
       <c r="A61" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B61" t="s">
         <v>109</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E61" t="s">
         <v>521</v>
       </c>
       <c r="F61" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G61">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H61" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="I61">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="J61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" t="s">
+        <v>29</v>
+      </c>
+      <c r="L61" t="s">
+        <v>17</v>
+      </c>
+      <c r="M61">
         <v>41</v>
       </c>
-      <c r="K61" t="s">
-        <v>42</v>
-      </c>
-      <c r="L61" t="s">
-        <v>43</v>
-      </c>
-      <c r="M61">
-        <v>125</v>
-      </c>
       <c r="N61" s="1" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="44.25" customHeight="1">
       <c r="A62" t="s">
-        <v>529</v>
+        <v>357</v>
       </c>
       <c r="B62" t="s">
         <v>109</v>
       </c>
       <c r="C62" t="s">
-        <v>528</v>
+        <v>31</v>
       </c>
       <c r="E62" t="s">
         <v>521</v>
       </c>
       <c r="F62" t="s">
-        <v>546</v>
+        <v>23</v>
       </c>
       <c r="G62">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="H62" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="I62">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="J62" t="s">
-        <v>41</v>
+        <v>549</v>
       </c>
       <c r="K62" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L62" t="s">
-        <v>43</v>
-      </c>
-      <c r="N62" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="M62">
+        <v>40</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="63" spans="1:14" ht="34.5" customHeight="1">
       <c r="A63" t="s">

--- a/sample_test_onkron.xlsx
+++ b/sample_test_onkron.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.turchaninova\PycharmProjects\segmentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4B3FF7-6129-494F-9A2E-8B99A831F500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9AB3E7-005E-4E46-BCCF-2CBAE2381214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2190" yWindow="0" windowWidth="21600" windowHeight="14595" xr2:uid="{0190D395-6836-4E29-A1D2-00559080D764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="551">
   <si>
     <t>image_url</t>
   </si>
@@ -4888,6 +4888,12 @@
       <c r="F63" t="s">
         <v>537</v>
       </c>
+      <c r="G63">
+        <v>100</v>
+      </c>
+      <c r="H63" t="s">
+        <v>40</v>
+      </c>
       <c r="I63">
         <v>120</v>
       </c>
